--- a/reports/screener_2026-08-29.xlsx
+++ b/reports/screener_2026-08-29.xlsx
@@ -1206,10 +1206,10 @@
         <v>10.35999965667725</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.851813302662554</v>
+        <v>5.85181314153473</v>
       </c>
       <c r="CB2" t="n">
-        <v>10.85511367643904</v>
+        <v>10.85511337754692</v>
       </c>
       <c r="CC2" t="n">
         <v>41.59696831847682</v>
@@ -1218,7 +1218,7 @@
         <v>27.90166392450355</v>
       </c>
       <c r="CE2" t="n">
-        <v>71.91678214770741</v>
+        <v>71.91678146413481</v>
       </c>
       <c r="CF2" t="n">
         <v>19.57807411896471</v>
@@ -1280,7 +1280,7 @@
         <v>-4.516135553592537</v>
       </c>
       <c r="DC2" t="n">
-        <v>-26.80358213834876</v>
+        <v>-26.80357709863755</v>
       </c>
       <c r="DD2" t="b">
         <v>1</v>
@@ -1529,10 +1529,10 @@
         <v>13.46000003814697</v>
       </c>
       <c r="CA3" t="n">
-        <v>14.84732047183941</v>
+        <v>14.84732059754322</v>
       </c>
       <c r="CB3" t="n">
-        <v>27.54177947526211</v>
+        <v>27.54177970844266</v>
       </c>
       <c r="CC3" t="n">
         <v>38.93995644223742</v>
@@ -1541,13 +1541,13 @@
         <v>23.51205793312256</v>
       </c>
       <c r="CE3" t="n">
-        <v>75.54482877750478</v>
+        <v>75.54482854474766</v>
       </c>
       <c r="CF3" t="n">
-        <v>48.52515945161966</v>
+        <v>48.52515935922475</v>
       </c>
       <c r="CG3" t="n">
-        <v>26.80868525178779</v>
+        <v>26.80868486395637</v>
       </c>
       <c r="CH3" t="n">
         <v>8.920136085713818</v>
@@ -1852,10 +1852,10 @@
         <v>24.61000061035156</v>
       </c>
       <c r="CA4" t="n">
-        <v>16.31411908729732</v>
+        <v>16.31411912109865</v>
       </c>
       <c r="CB4" t="n">
-        <v>30.26269090693654</v>
+        <v>30.26269096963799</v>
       </c>
       <c r="CC4" t="n">
         <v>72.30210822331667</v>
@@ -1864,19 +1864,19 @@
         <v>52.41049602817493</v>
       </c>
       <c r="CE4" t="n">
-        <v>127.9950261375635</v>
+        <v>127.9950261271193</v>
       </c>
       <c r="CF4" t="n">
-        <v>25.7314236582745</v>
+        <v>25.73142365350962</v>
       </c>
       <c r="CG4" t="n">
-        <v>63.19894121982481</v>
+        <v>63.19894114730609</v>
       </c>
       <c r="CH4" t="n">
         <v>42.85100954601229</v>
       </c>
       <c r="CI4" t="n">
-        <v>47.79277826375662</v>
+        <v>47.79277826132627</v>
       </c>
       <c r="CJ4" t="n">
         <v>47.63075278709361</v>
@@ -1897,7 +1897,7 @@
         <v>74.18803919229917</v>
       </c>
       <c r="CP4" t="n">
-        <v>94.20063827082484</v>
+        <v>94.20063826094938</v>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
@@ -2183,10 +2183,10 @@
         <v>4.119999885559082</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.742268119905749</v>
+        <v>3.742268130875503</v>
       </c>
       <c r="CB5" t="n">
-        <v>6.941907362425163</v>
+        <v>6.941907382774058</v>
       </c>
       <c r="CC5" t="n">
         <v>12.63657372306894</v>
@@ -2195,19 +2195,19 @@
         <v>8.512687176725057</v>
       </c>
       <c r="CE5" t="n">
-        <v>24.29926425581659</v>
+        <v>24.29926424787384</v>
       </c>
       <c r="CF5" t="n">
-        <v>11.19291967147257</v>
+        <v>11.19291966694585</v>
       </c>
       <c r="CG5" t="n">
-        <v>10.19843573572495</v>
+        <v>10.19843570838657</v>
       </c>
       <c r="CH5" t="n">
         <v>5.258139118319559</v>
       </c>
       <c r="CI5" t="n">
-        <v>8.354704415377428</v>
+        <v>8.354704415299363</v>
       </c>
       <c r="CJ5" t="n">
         <v>8.512687176725057</v>
@@ -2228,7 +2228,7 @@
         <v>85.95676388017426</v>
       </c>
       <c r="CP5" t="n">
-        <v>102.7840933845972</v>
+        <v>102.7840933827025</v>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>-2.254690866785281</v>
       </c>
       <c r="DC5" t="n">
-        <v>-36.92337647573303</v>
+        <v>-36.92338129060463</v>
       </c>
       <c r="DD5" t="b">
         <v>1</v>
@@ -2516,10 +2516,10 @@
         <v>4.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.282599895150733</v>
+        <v>3.282599894210626</v>
       </c>
       <c r="CB6" t="n">
-        <v>6.08922280550461</v>
+        <v>6.089222803760711</v>
       </c>
       <c r="CC6" t="n">
         <v>12.96195652173913</v>
@@ -2528,7 +2528,7 @@
         <v>8.728772626887835</v>
       </c>
       <c r="CE6" t="n">
-        <v>24.66443446350224</v>
+        <v>24.66443446064104</v>
       </c>
       <c r="CF6" t="n">
         <v>11.57513776217851</v>
@@ -2540,7 +2540,7 @@
         <v>5.383571029035719</v>
       </c>
       <c r="CI6" t="n">
-        <v>11.60572167579817</v>
+        <v>11.6057216751403</v>
       </c>
       <c r="CJ6" t="n">
         <v>11.57513776217851</v>
@@ -2561,7 +2561,7 @@
         <v>131.5027552435702</v>
       </c>
       <c r="CP6" t="n">
-        <v>157.9049261288482</v>
+        <v>157.9049261142289</v>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
@@ -2839,10 +2839,10 @@
         <v>48.34000015258789</v>
       </c>
       <c r="CA7" t="n">
-        <v>18.42191759848097</v>
+        <v>18.421917577112</v>
       </c>
       <c r="CB7" t="n">
-        <v>34.17265714518221</v>
+        <v>34.17265710554276</v>
       </c>
       <c r="CC7" t="n">
         <v>74.65093263657221</v>
@@ -2851,23 +2851,23 @@
         <v>55.91472932652801</v>
       </c>
       <c r="CE7" t="n">
-        <v>99.8344550591067</v>
+        <v>99.83445509256833</v>
       </c>
       <c r="CF7" t="n">
-        <v>48.37202137970021</v>
+        <v>48.37202138492027</v>
       </c>
       <c r="CG7" t="n">
-        <v>58.90972737559709</v>
+        <v>58.90972741854703</v>
       </c>
       <c r="CH7" t="inlineStr"/>
       <c r="CI7" t="n">
-        <v>43.9043821899839</v>
+        <v>43.90438217603681</v>
       </c>
       <c r="CJ7" t="n">
-        <v>41.27233926244121</v>
+        <v>41.27233924523151</v>
       </c>
       <c r="CK7" t="n">
-        <v>37.14510533619709</v>
+        <v>37.14510532070836</v>
       </c>
       <c r="CL7" t="n">
         <v>4</v>
@@ -2879,10 +2879,10 @@
         <v>4.1</v>
       </c>
       <c r="CO7" t="n">
-        <v>-23.15865697363155</v>
+        <v>-23.15865700567279</v>
       </c>
       <c r="CP7" t="n">
-        <v>-9.17587494539247</v>
+        <v>-9.175874974244525</v>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         <v>15.69999980926514</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.403272786852184</v>
+        <v>6.403272805631215</v>
       </c>
       <c r="CB8" t="n">
-        <v>11.8780710196108</v>
+        <v>11.8780710544459</v>
       </c>
       <c r="CC8" t="n">
         <v>25.39987759130195</v>
@@ -3182,19 +3182,19 @@
         <v>18.63509665364473</v>
       </c>
       <c r="CE8" t="n">
-        <v>35.2441967285137</v>
+        <v>35.24419669801659</v>
       </c>
       <c r="CF8" t="n">
-        <v>12.29886962062783</v>
+        <v>12.29886961706348</v>
       </c>
       <c r="CG8" t="n">
-        <v>20.39435314969272</v>
+        <v>20.39435311034539</v>
       </c>
       <c r="CH8" t="n">
         <v>18.40902666520164</v>
       </c>
       <c r="CI8" t="n">
-        <v>20.32278448979906</v>
+        <v>20.32278448428853</v>
       </c>
       <c r="CJ8" t="n">
         <v>18.63509665364473</v>
@@ -3215,7 +3215,7 @@
         <v>6.825396127602112</v>
       </c>
       <c r="CP8" t="n">
-        <v>29.44448876875685</v>
+        <v>29.44448873365793</v>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
@@ -3505,10 +3505,10 @@
         <v>42.70000076293945</v>
       </c>
       <c r="CA9" t="n">
-        <v>125.1024114745125</v>
+        <v>125.1024118332479</v>
       </c>
       <c r="CB9" t="n">
-        <v>232.0649732852206</v>
+        <v>232.0649739506748</v>
       </c>
       <c r="CC9" t="n">
         <v>134.3883634463059</v>
@@ -3529,13 +3529,13 @@
         <v>54.40212095818906</v>
       </c>
       <c r="CI9" t="n">
-        <v>140.0389271837773</v>
+        <v>140.038927311801</v>
       </c>
       <c r="CJ9" t="n">
-        <v>123.9134396127393</v>
+        <v>123.913439792107</v>
       </c>
       <c r="CK9" t="n">
-        <v>111.5220956514654</v>
+        <v>111.5220958128963</v>
       </c>
       <c r="CL9" t="n">
         <v>8</v>
@@ -3547,10 +3547,10 @@
         <v>5.6</v>
       </c>
       <c r="CO9" t="n">
-        <v>161.175863369676</v>
+        <v>161.1758637477344</v>
       </c>
       <c r="CP9" t="n">
-        <v>227.9600109640304</v>
+        <v>227.9600112638517</v>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>32.47999954223633</v>
       </c>
       <c r="CA10" t="n">
-        <v>45.35763240419051</v>
+        <v>45.35763219127636</v>
       </c>
       <c r="CB10" t="n">
-        <v>84.13840810977339</v>
+        <v>84.13840771481763</v>
       </c>
       <c r="CC10" t="n">
         <v>68.20285165366582</v>
@@ -3862,7 +3862,7 @@
         <v>25.67266223983068</v>
       </c>
       <c r="CI10" t="n">
-        <v>77.37745295143534</v>
+        <v>77.37745286459679</v>
       </c>
       <c r="CJ10" t="n">
         <v>68.20285165366582</v>
@@ -3883,7 +3883,7 @@
         <v>88.98573692551506</v>
       </c>
       <c r="CP10" t="n">
-        <v>138.2310777154269</v>
+        <v>138.2310774480669</v>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
@@ -4179,37 +4179,37 @@
         <v>32.84999847412109</v>
       </c>
       <c r="CA11" t="n">
-        <v>24.40136931092796</v>
+        <v>24.40136932160346</v>
       </c>
       <c r="CB11" t="n">
-        <v>32.24270572677878</v>
+        <v>32.24270565046241</v>
       </c>
       <c r="CC11" t="n">
-        <v>33.81078576994144</v>
+        <v>33.81078567512144</v>
       </c>
       <c r="CD11" t="n">
         <v>20.85130777065122</v>
       </c>
       <c r="CE11" t="n">
-        <v>48.28249341817388</v>
+        <v>48.28249333526282</v>
       </c>
       <c r="CF11" t="n">
-        <v>50.84680029791828</v>
+        <v>50.84680028425728</v>
       </c>
       <c r="CG11" t="n">
-        <v>16.50214466972086</v>
+        <v>16.50214460736058</v>
       </c>
       <c r="CH11" t="n">
         <v>24.29339039885633</v>
       </c>
       <c r="CI11" t="n">
-        <v>31.40387467037109</v>
+        <v>31.40387463044694</v>
       </c>
       <c r="CJ11" t="n">
-        <v>28.32203751885337</v>
+        <v>28.32203748603293</v>
       </c>
       <c r="CK11" t="n">
-        <v>25.48983376696803</v>
+        <v>25.48983373742964</v>
       </c>
       <c r="CL11" t="n">
         <v>8</v>
@@ -4221,10 +4221,10 @@
         <v>3.1</v>
       </c>
       <c r="CO11" t="n">
-        <v>-22.40537305641377</v>
+        <v>-22.40537314633277</v>
       </c>
       <c r="CP11" t="n">
-        <v>-4.402203564451435</v>
+        <v>-4.402203685986139</v>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
@@ -4514,10 +4514,10 @@
         <v>47.31000137329102</v>
       </c>
       <c r="CA12" t="n">
-        <v>131.3198828881482</v>
+        <v>131.3198817888239</v>
       </c>
       <c r="CB12" t="n">
-        <v>243.5983827575148</v>
+        <v>243.5983807182684</v>
       </c>
       <c r="CC12" t="n">
         <v>134.5187807287781</v>
@@ -4538,13 +4538,13 @@
         <v>53.17581509382557</v>
       </c>
       <c r="CI12" t="n">
-        <v>142.2129205558937</v>
+        <v>142.2129201635724</v>
       </c>
       <c r="CJ12" t="n">
-        <v>127.0817243428747</v>
+        <v>127.0817237932125</v>
       </c>
       <c r="CK12" t="n">
-        <v>114.3735519085872</v>
+        <v>114.3735514138913</v>
       </c>
       <c r="CL12" t="n">
         <v>8</v>
@@ -4556,10 +4556,10 @@
         <v>5.7</v>
       </c>
       <c r="CO12" t="n">
-        <v>141.7534318085162</v>
+        <v>141.7534307628686</v>
       </c>
       <c r="CP12" t="n">
-        <v>200.5980055544457</v>
+        <v>200.5980047251891</v>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>-1.560432066163409</v>
       </c>
       <c r="DC12" t="n">
-        <v>-10.93847029890879</v>
+        <v>-10.93846372884365</v>
       </c>
       <c r="DD12" t="b">
         <v>1</v>
@@ -4847,10 +4847,10 @@
         <v>7.239999771118164</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.268913165541576</v>
+        <v>3.268913169515907</v>
       </c>
       <c r="CB13" t="n">
-        <v>6.063833922079623</v>
+        <v>6.063833929452008</v>
       </c>
       <c r="CC13" t="n">
         <v>20.4541571358882</v>
@@ -4859,7 +4859,7 @@
         <v>14.0164620450613</v>
       </c>
       <c r="CE13" t="n">
-        <v>32.91359933568327</v>
+        <v>32.91359934754694</v>
       </c>
       <c r="CF13" t="n">
         <v>10.95072400487419</v>
@@ -5152,10 +5152,10 @@
         <v>19.30999946594238</v>
       </c>
       <c r="CA14" t="n">
-        <v>13.27333703885629</v>
+        <v>13.27333702384396</v>
       </c>
       <c r="CB14" t="n">
-        <v>24.62204020707841</v>
+        <v>24.62204017923054</v>
       </c>
       <c r="CC14" t="n">
         <v>19.98886663466692</v>
@@ -5164,7 +5164,7 @@
         <v>12.49234273346821</v>
       </c>
       <c r="CE14" t="n">
-        <v>33.82771185219145</v>
+        <v>33.82771183577172</v>
       </c>
       <c r="CF14" t="n">
         <v>22.8984489302328</v>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="CH14" t="inlineStr"/>
       <c r="CI14" t="n">
-        <v>20.1956732027086</v>
+        <v>20.19567319199356</v>
       </c>
       <c r="CJ14" t="n">
         <v>21.44365778244985</v>
@@ -5195,7 +5195,7 @@
         <v>-0.05545034714474761</v>
       </c>
       <c r="CP14" t="n">
-        <v>4.586606738795118</v>
+        <v>4.586606683305527</v>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
@@ -5491,10 +5491,10 @@
         <v>17.21999931335449</v>
       </c>
       <c r="CA15" t="n">
-        <v>10.55474904779928</v>
+        <v>10.55474908527501</v>
       </c>
       <c r="CB15" t="n">
-        <v>19.57905948366767</v>
+        <v>19.57905955318514</v>
       </c>
       <c r="CC15" t="n">
         <v>37.03977125031607</v>
@@ -5503,25 +5503,25 @@
         <v>36.56718452753732</v>
       </c>
       <c r="CE15" t="n">
-        <v>41.35653251466345</v>
+        <v>41.35653253068535</v>
       </c>
       <c r="CF15" t="n">
-        <v>34.51133421135384</v>
+        <v>34.51133420331627</v>
       </c>
       <c r="CG15" t="n">
-        <v>18.3851786431524</v>
+        <v>18.38517859968655</v>
       </c>
       <c r="CH15" t="n">
         <v>31.59171947190627</v>
       </c>
       <c r="CI15" t="n">
-        <v>31.29011144322814</v>
+        <v>31.29011144809042</v>
       </c>
       <c r="CJ15" t="n">
-        <v>34.51133421135384</v>
+        <v>34.51133420331627</v>
       </c>
       <c r="CK15" t="n">
-        <v>31.06020079021846</v>
+        <v>31.06020078298464</v>
       </c>
       <c r="CL15" t="n">
         <v>7</v>
@@ -5533,10 +5533,10 @@
         <v>3.9</v>
       </c>
       <c r="CO15" t="n">
-        <v>80.37283408095482</v>
+        <v>80.37283403894659</v>
       </c>
       <c r="CP15" t="n">
-        <v>81.70797149197308</v>
+        <v>81.70797152020933</v>
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>-1.768404798336243</v>
       </c>
       <c r="DC15" t="n">
-        <v>-24.57900422609433</v>
+        <v>-24.57901058396539</v>
       </c>
       <c r="DD15" t="b">
         <v>1</v>
@@ -5824,37 +5824,37 @@
         <v>10.10999965667725</v>
       </c>
       <c r="CA16" t="n">
-        <v>10.12952178280262</v>
+        <v>10.12952182665193</v>
       </c>
       <c r="CB16" t="n">
-        <v>18.71325025888591</v>
+        <v>18.71325013446309</v>
       </c>
       <c r="CC16" t="n">
-        <v>24.61410798311763</v>
+        <v>24.61410771290942</v>
       </c>
       <c r="CD16" t="n">
         <v>17.7286584153084</v>
       </c>
       <c r="CE16" t="n">
-        <v>37.29961186413532</v>
+        <v>37.29961182454053</v>
       </c>
       <c r="CF16" t="n">
-        <v>24.22565667861713</v>
+        <v>24.22565665988301</v>
       </c>
       <c r="CG16" t="n">
-        <v>11.9820663019273</v>
+        <v>11.9820662058447</v>
       </c>
       <c r="CH16" t="n">
         <v>10.10999965667725</v>
       </c>
       <c r="CI16" t="n">
-        <v>19.35035911768394</v>
+        <v>19.35035905453479</v>
       </c>
       <c r="CJ16" t="n">
-        <v>18.22095433709715</v>
+        <v>18.22095427488574</v>
       </c>
       <c r="CK16" t="n">
-        <v>16.39885890338743</v>
+        <v>16.39885884739717</v>
       </c>
       <c r="CL16" t="n">
         <v>8</v>
@@ -5866,10 +5866,10 @@
         <v>3.7</v>
       </c>
       <c r="CO16" t="n">
-        <v>62.20434678805009</v>
+        <v>62.20434623423934</v>
       </c>
       <c r="CP16" t="n">
-        <v>91.39821735704821</v>
+        <v>91.3982167324275</v>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
@@ -6159,10 +6159,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="CA17" t="n">
-        <v>5.044566675915342</v>
+        <v>5.044566653942212</v>
       </c>
       <c r="CB17" t="n">
-        <v>9.357671183822958</v>
+        <v>9.357671143062804</v>
       </c>
       <c r="CC17" t="n">
         <v>8.579313567043014</v>
@@ -6482,10 +6482,10 @@
         <v>10.97000026702881</v>
       </c>
       <c r="CA18" t="n">
-        <v>9.497073397998388</v>
+        <v>9.497073338236024</v>
       </c>
       <c r="CB18" t="n">
-        <v>17.61707115328701</v>
+        <v>17.61707104242782</v>
       </c>
       <c r="CC18" t="n">
         <v>21.98978873496697</v>
@@ -6494,25 +6494,25 @@
         <v>12.98356721691296</v>
       </c>
       <c r="CE18" t="n">
-        <v>32.25283416633335</v>
+        <v>32.25283434748484</v>
       </c>
       <c r="CF18" t="n">
-        <v>25.3672351516493</v>
+        <v>25.36723519548015</v>
       </c>
       <c r="CG18" t="n">
-        <v>12.0631232455236</v>
+        <v>12.06312343895286</v>
       </c>
       <c r="CH18" t="n">
         <v>9.632374997322403</v>
       </c>
       <c r="CI18" t="n">
-        <v>17.67538350799925</v>
+        <v>17.675383538973</v>
       </c>
       <c r="CJ18" t="n">
-        <v>15.30031918509999</v>
+        <v>15.30031912967039</v>
       </c>
       <c r="CK18" t="n">
-        <v>13.77028726658999</v>
+        <v>13.77028721670335</v>
       </c>
       <c r="CL18" t="n">
         <v>8</v>
@@ -6524,10 +6524,10 @@
         <v>3.4</v>
       </c>
       <c r="CO18" t="n">
-        <v>25.52677239195391</v>
+        <v>25.52677193719881</v>
       </c>
       <c r="CP18" t="n">
-        <v>61.12473179352595</v>
+        <v>61.12473207587556</v>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
@@ -6815,10 +6815,10 @@
         <v>10.63000011444092</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.315025661609432</v>
+        <v>3.315025657679916</v>
       </c>
       <c r="CB19" t="n">
-        <v>6.149372602285496</v>
+        <v>6.149372594996244</v>
       </c>
       <c r="CC19" t="n">
         <v>19.53502101474926</v>
@@ -6827,13 +6827,13 @@
         <v>18.41366451165369</v>
       </c>
       <c r="CE19" t="n">
-        <v>20.99446707931569</v>
+        <v>20.99446707961297</v>
       </c>
       <c r="CF19" t="n">
-        <v>15.93445353560463</v>
+        <v>15.93445353638441</v>
       </c>
       <c r="CG19" t="n">
-        <v>13.08904091557589</v>
+        <v>13.08904092055883</v>
       </c>
       <c r="CH19" t="n">
         <v>29.73646810990179</v>
@@ -7138,10 +7138,10 @@
         <v>27.42000007629395</v>
       </c>
       <c r="CA20" t="n">
-        <v>7.265285075463376</v>
+        <v>7.265285076459099</v>
       </c>
       <c r="CB20" t="n">
-        <v>13.47710381498456</v>
+        <v>13.47710381683163</v>
       </c>
       <c r="CC20" t="n">
         <v>35.82988175649849</v>
@@ -7150,19 +7150,19 @@
         <v>28.32096620307184</v>
       </c>
       <c r="CE20" t="n">
-        <v>44.64824885986749</v>
+        <v>44.64824885838173</v>
       </c>
       <c r="CF20" t="n">
-        <v>26.46426766347906</v>
+        <v>26.46426766323088</v>
       </c>
       <c r="CG20" t="n">
-        <v>28.98335745153566</v>
+        <v>28.98335744973761</v>
       </c>
       <c r="CH20" t="n">
         <v>24.27856406616775</v>
       </c>
       <c r="CI20" t="n">
-        <v>28.85748425937212</v>
+        <v>28.85748425913142</v>
       </c>
       <c r="CJ20" t="n">
         <v>28.32096620307184</v>
@@ -7183,7 +7183,7 @@
         <v>-7.042780773727464</v>
       </c>
       <c r="CP20" t="n">
-        <v>5.24246600685081</v>
+        <v>5.242466005972979</v>
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>-2.176241867315365</v>
       </c>
       <c r="DC20" t="n">
-        <v>-22.27487236182183</v>
+        <v>-22.27486391968831</v>
       </c>
       <c r="DD20" t="b">
         <v>1</v>
@@ -7479,10 +7479,10 @@
         <v>22.60000038146973</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.184692829840589</v>
+        <v>3.184692834576809</v>
       </c>
       <c r="CB21" t="n">
-        <v>5.907605199354292</v>
+        <v>5.90760520813998</v>
       </c>
       <c r="CC21" t="n">
         <v>33.79796896777358</v>
@@ -7491,7 +7491,7 @@
         <v>28.20908778885038</v>
       </c>
       <c r="CE21" t="n">
-        <v>43.29409766815058</v>
+        <v>43.29409767563445</v>
       </c>
       <c r="CF21" t="n">
         <v>10.85340539909456</v>
@@ -7782,10 +7782,10 @@
         <v>39.45000076293945</v>
       </c>
       <c r="CA22" t="n">
-        <v>36.12452920685543</v>
+        <v>36.12452926568335</v>
       </c>
       <c r="CB22" t="n">
-        <v>52.5973145251815</v>
+        <v>52.59731461083496</v>
       </c>
       <c r="CC22" t="n">
         <v>48.55384709284856</v>
@@ -7802,13 +7802,13 @@
       </c>
       <c r="CH22" t="inlineStr"/>
       <c r="CI22" t="n">
-        <v>49.1949639521758</v>
+        <v>49.19496398829614</v>
       </c>
       <c r="CJ22" t="n">
-        <v>50.57558080901504</v>
+        <v>50.57558085184176</v>
       </c>
       <c r="CK22" t="n">
-        <v>45.51802272811354</v>
+        <v>45.51802276665759</v>
       </c>
       <c r="CL22" t="n">
         <v>4</v>
@@ -7820,10 +7820,10 @@
         <v>1.6</v>
       </c>
       <c r="CO22" t="n">
-        <v>15.38155094504985</v>
+        <v>15.38155104275338</v>
       </c>
       <c r="CP22" t="n">
-        <v>24.70206083846534</v>
+        <v>24.70206093002516</v>
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
@@ -8119,10 +8119,10 @@
         <v>34.68999862670898</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.441715129974142</v>
+        <v>3.441715135618347</v>
       </c>
       <c r="CB23" t="n">
-        <v>6.384381566102033</v>
+        <v>6.384381576572033</v>
       </c>
       <c r="CC23" t="n">
         <v>32.87857523633004</v>
@@ -8131,7 +8131,7 @@
         <v>23.03538757661248</v>
       </c>
       <c r="CE23" t="n">
-        <v>40.66766746926129</v>
+        <v>40.66766747491356</v>
       </c>
       <c r="CF23" t="n">
         <v>10.59424454785779</v>
@@ -8422,35 +8422,35 @@
         <v>12.84000015258789</v>
       </c>
       <c r="CA24" t="n">
-        <v>8.620453608860551</v>
+        <v>8.620453699055004</v>
       </c>
       <c r="CB24" t="n">
-        <v>13.75172347439505</v>
+        <v>13.75172337055989</v>
       </c>
       <c r="CC24" t="n">
-        <v>18.28832866588292</v>
+        <v>18.2883283364453</v>
       </c>
       <c r="CD24" t="n">
         <v>17.29599079072038</v>
       </c>
       <c r="CE24" t="n">
-        <v>22.79371672331302</v>
+        <v>22.79371663669027</v>
       </c>
       <c r="CF24" t="n">
-        <v>17.32775209408891</v>
+        <v>17.32775206890582</v>
       </c>
       <c r="CG24" t="n">
-        <v>9.132623021575037</v>
+        <v>9.13262286791255</v>
       </c>
       <c r="CH24" t="inlineStr"/>
       <c r="CI24" t="n">
-        <v>14.49706446080686</v>
+        <v>14.4970643687415</v>
       </c>
       <c r="CJ24" t="n">
-        <v>15.53973778424198</v>
+        <v>15.53973771973286</v>
       </c>
       <c r="CK24" t="n">
-        <v>13.98576400581778</v>
+        <v>13.98576394775957</v>
       </c>
       <c r="CL24" t="n">
         <v>4</v>
@@ -8462,10 +8462,10 @@
         <v>2.1</v>
       </c>
       <c r="CO24" t="n">
-        <v>8.923394389516147</v>
+        <v>8.923393937349399</v>
       </c>
       <c r="CP24" t="n">
-        <v>12.90548511313676</v>
+        <v>12.90548439611687</v>
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
@@ -8739,10 +8739,10 @@
         <v>39.09999847412109</v>
       </c>
       <c r="CA25" t="n">
-        <v>19.98811954040033</v>
+        <v>19.9881195590459</v>
       </c>
       <c r="CB25" t="n">
-        <v>37.07796174744261</v>
+        <v>37.07796178203014</v>
       </c>
       <c r="CC25" t="n">
         <v>55.88726858490879</v>
@@ -8751,23 +8751,23 @@
         <v>42.23733079208057</v>
       </c>
       <c r="CE25" t="n">
-        <v>62.05637365125566</v>
+        <v>62.05637362081207</v>
       </c>
       <c r="CF25" t="n">
-        <v>45.20951665016102</v>
+        <v>45.20951664432093</v>
       </c>
       <c r="CG25" t="n">
-        <v>31.30000271636338</v>
+        <v>31.3000026795272</v>
       </c>
       <c r="CH25" t="inlineStr"/>
       <c r="CI25" t="n">
-        <v>39.54071663072818</v>
+        <v>39.54071664257643</v>
       </c>
       <c r="CJ25" t="n">
-        <v>41.14373919880181</v>
+        <v>41.14373921317554</v>
       </c>
       <c r="CK25" t="n">
-        <v>37.02936527892163</v>
+        <v>37.02936529185799</v>
       </c>
       <c r="CL25" t="n">
         <v>4</v>
@@ -8779,10 +8779,10 @@
         <v>2.8</v>
       </c>
       <c r="CO25" t="n">
-        <v>-5.295737278787726</v>
+        <v>-5.295737245702414</v>
       </c>
       <c r="CP25" t="n">
-        <v>1.127156454747147</v>
+        <v>1.127156485049574</v>
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>-7.739505689776549</v>
       </c>
       <c r="DC25" t="n">
-        <v>-19.71089251072075</v>
+        <v>-19.71089883815426</v>
       </c>
       <c r="DD25" t="b">
         <v>1</v>
@@ -9078,10 +9078,10 @@
         <v>6.010000228881836</v>
       </c>
       <c r="CA26" t="n">
-        <v>7.129314286253146</v>
+        <v>7.129314335517792</v>
       </c>
       <c r="CB26" t="n">
-        <v>13.22487800099958</v>
+        <v>13.2248780923855</v>
       </c>
       <c r="CC26" t="n">
         <v>5.700250753950201</v>
@@ -9102,7 +9102,7 @@
         <v>5.504458217875779</v>
       </c>
       <c r="CI26" t="n">
-        <v>7.42796296784184</v>
+        <v>7.427962985423161</v>
       </c>
       <c r="CJ26" t="n">
         <v>5.916792043641768</v>
@@ -9123,7 +9123,7 @@
         <v>-11.39579639802557</v>
       </c>
       <c r="CP26" t="n">
-        <v>23.59338910081565</v>
+        <v>23.59338939335012</v>
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
@@ -9395,10 +9395,10 @@
         <v>14.96000003814697</v>
       </c>
       <c r="CA27" t="n">
-        <v>9.298791796674807</v>
+        <v>9.298791826816277</v>
       </c>
       <c r="CB27" t="n">
-        <v>17.24925878283177</v>
+        <v>17.24925883874419</v>
       </c>
       <c r="CC27" t="n">
         <v>30.82737177378653</v>
@@ -9407,23 +9407,23 @@
         <v>29.3357145487105</v>
       </c>
       <c r="CE27" t="n">
-        <v>34.72610762496628</v>
+        <v>34.72610763096726</v>
       </c>
       <c r="CF27" t="n">
-        <v>25.49561712208956</v>
+        <v>25.49561711593838</v>
       </c>
       <c r="CG27" t="n">
-        <v>15.31698429157356</v>
+        <v>15.31698425409445</v>
       </c>
       <c r="CH27" t="inlineStr"/>
       <c r="CI27" t="n">
-        <v>20.71775986884566</v>
+        <v>20.71775988882134</v>
       </c>
       <c r="CJ27" t="n">
-        <v>21.37243795246066</v>
+        <v>21.37243797734128</v>
       </c>
       <c r="CK27" t="n">
-        <v>19.2351941572146</v>
+        <v>19.23519417960716</v>
       </c>
       <c r="CL27" t="n">
         <v>4</v>
@@ -9435,10 +9435,10 @@
         <v>3.3</v>
       </c>
       <c r="CO27" t="n">
-        <v>28.57750072303591</v>
+        <v>28.5775008727188</v>
       </c>
       <c r="CP27" t="n">
-        <v>38.48769930492513</v>
+        <v>38.48769943845238</v>
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>-5.015872773670016</v>
       </c>
       <c r="DC27" t="n">
-        <v>-17.75793314155376</v>
+        <v>-17.75794205146741</v>
       </c>
       <c r="DD27" t="b">
         <v>1</v>
@@ -9726,37 +9726,37 @@
         <v>26.64999961853027</v>
       </c>
       <c r="CA28" t="n">
-        <v>17.04026343140696</v>
+        <v>17.04026358136929</v>
       </c>
       <c r="CB28" t="n">
-        <v>28.24459566395387</v>
+        <v>28.24459568212314</v>
       </c>
       <c r="CC28" t="n">
-        <v>47.30449332245774</v>
+        <v>47.30449293658613</v>
       </c>
       <c r="CD28" t="n">
         <v>53.09041087001181</v>
       </c>
       <c r="CE28" t="n">
-        <v>56.22805797747338</v>
+        <v>56.22805802539393</v>
       </c>
       <c r="CF28" t="n">
-        <v>42.93955285992938</v>
+        <v>42.93955283264891</v>
       </c>
       <c r="CG28" t="n">
-        <v>23.53514266469771</v>
+        <v>23.53514249696784</v>
       </c>
       <c r="CH28" t="n">
         <v>30.99183173163939</v>
       </c>
       <c r="CI28" t="n">
-        <v>37.42179356519628</v>
+        <v>37.42179351959255</v>
       </c>
       <c r="CJ28" t="n">
-        <v>36.96569229578439</v>
+        <v>36.96569228214415</v>
       </c>
       <c r="CK28" t="n">
-        <v>33.26912306620595</v>
+        <v>33.26912305392973</v>
       </c>
       <c r="CL28" t="n">
         <v>8</v>
@@ -9768,10 +9768,10 @@
         <v>3.3</v>
       </c>
       <c r="CO28" t="n">
-        <v>24.8372365569314</v>
+        <v>24.83723651086678</v>
       </c>
       <c r="CP28" t="n">
-        <v>40.41949005949015</v>
+        <v>40.41948988836923</v>
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
@@ -10059,37 +10059,37 @@
         <v>15.11999988555908</v>
       </c>
       <c r="CA29" t="n">
-        <v>5.865830787236021</v>
+        <v>5.865830805980611</v>
       </c>
       <c r="CB29" t="n">
-        <v>8.474845215612692</v>
+        <v>8.474845200009646</v>
       </c>
       <c r="CC29" t="n">
-        <v>10.77599632720064</v>
+        <v>10.77599627292565</v>
       </c>
       <c r="CD29" t="n">
         <v>11.55627711976371</v>
       </c>
       <c r="CE29" t="n">
-        <v>9.774262772991017</v>
+        <v>9.774262742828176</v>
       </c>
       <c r="CF29" t="n">
-        <v>14.9164232401739</v>
+        <v>14.916423233537</v>
       </c>
       <c r="CG29" t="n">
-        <v>5.368455516564914</v>
+        <v>5.368455486213674</v>
       </c>
       <c r="CH29" t="n">
         <v>10.8369287109083</v>
       </c>
       <c r="CI29" t="n">
-        <v>9.6961274613064</v>
+        <v>9.696127446520844</v>
       </c>
       <c r="CJ29" t="n">
-        <v>10.27512955009583</v>
+        <v>10.27512950787691</v>
       </c>
       <c r="CK29" t="n">
-        <v>9.247616595086248</v>
+        <v>9.247616557089222</v>
       </c>
       <c r="CL29" t="n">
         <v>8</v>
@@ -10101,10 +10101,10 @@
         <v>2.8</v>
       </c>
       <c r="CO29" t="n">
-        <v>-38.83851411984119</v>
+        <v>-38.83851437114426</v>
       </c>
       <c r="CP29" t="n">
-        <v>-35.87217238958416</v>
+        <v>-35.87217248737223</v>
       </c>
       <c r="CQ29" t="inlineStr">
         <is>
@@ -10392,37 +10392,37 @@
         <v>38.70000076293945</v>
       </c>
       <c r="CA30" t="n">
-        <v>30.84756125820635</v>
+        <v>30.84756156679863</v>
       </c>
       <c r="CB30" t="n">
-        <v>35.74245458360979</v>
+        <v>35.74245434017883</v>
       </c>
       <c r="CC30" t="n">
-        <v>39.0600346478168</v>
+        <v>39.06003399104274</v>
       </c>
       <c r="CD30" t="n">
         <v>49.9060657389037</v>
       </c>
       <c r="CE30" t="n">
-        <v>60.73976176178693</v>
+        <v>60.739761418545</v>
       </c>
       <c r="CF30" t="n">
-        <v>16.6127311962797</v>
+        <v>16.61273116616696</v>
       </c>
       <c r="CG30" t="n">
-        <v>17.68241890464684</v>
+        <v>17.68241835772257</v>
       </c>
       <c r="CH30" t="n">
         <v>28.82212409504474</v>
       </c>
       <c r="CI30" t="n">
-        <v>34.92664402328685</v>
+        <v>34.9266438343004</v>
       </c>
       <c r="CJ30" t="n">
-        <v>33.29500792090807</v>
+        <v>33.29500795348874</v>
       </c>
       <c r="CK30" t="n">
-        <v>29.96550712881726</v>
+        <v>29.96550715813986</v>
       </c>
       <c r="CL30" t="n">
         <v>8</v>
@@ -10434,10 +10434,10 @@
         <v>3.7</v>
       </c>
       <c r="CO30" t="n">
-        <v>-22.56975054761927</v>
+        <v>-22.56975047185029</v>
       </c>
       <c r="CP30" t="n">
-        <v>-9.750275620836945</v>
+        <v>-9.750276109174028</v>
       </c>
       <c r="CQ30" t="inlineStr">
         <is>
@@ -10707,35 +10707,35 @@
         <v>16.93000030517578</v>
       </c>
       <c r="CA31" t="n">
-        <v>10.07551305271984</v>
+        <v>10.07551297601118</v>
       </c>
       <c r="CB31" t="n">
-        <v>17.56141117258434</v>
+        <v>17.56141118553893</v>
       </c>
       <c r="CC31" t="n">
-        <v>28.83392700366752</v>
+        <v>28.83392724446106</v>
       </c>
       <c r="CD31" t="n">
         <v>29.26650917734455</v>
       </c>
       <c r="CE31" t="n">
-        <v>32.09024621456947</v>
+        <v>32.0902462194033</v>
       </c>
       <c r="CF31" t="n">
-        <v>27.8843817471833</v>
+        <v>27.88438176449679</v>
       </c>
       <c r="CG31" t="n">
-        <v>14.22884660747816</v>
+        <v>14.22884670286078</v>
       </c>
       <c r="CH31" t="inlineStr"/>
       <c r="CI31" t="n">
-        <v>21.08880824403875</v>
+        <v>21.08880829262699</v>
       </c>
       <c r="CJ31" t="n">
-        <v>22.72289645988382</v>
+        <v>22.72289647501785</v>
       </c>
       <c r="CK31" t="n">
-        <v>20.45060681389544</v>
+        <v>20.45060682751607</v>
       </c>
       <c r="CL31" t="n">
         <v>4</v>
@@ -10747,10 +10747,10 @@
         <v>2.9</v>
       </c>
       <c r="CO31" t="n">
-        <v>20.7950764634266</v>
+        <v>20.7950765438792</v>
       </c>
       <c r="CP31" t="n">
-        <v>24.5647245357199</v>
+        <v>24.56472482271479</v>
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>-6.204980494321388</v>
       </c>
       <c r="DC31" t="n">
-        <v>-20.28805503364547</v>
+        <v>-20.28806233739286</v>
       </c>
       <c r="DD31" t="b">
         <v>1</v>
@@ -11042,37 +11042,37 @@
         <v>44.06000137329102</v>
       </c>
       <c r="CA32" t="n">
-        <v>31.96096257437985</v>
+        <v>31.96096264123675</v>
       </c>
       <c r="CB32" t="n">
-        <v>43.40679471696702</v>
+        <v>43.40679459074402</v>
       </c>
       <c r="CC32" t="n">
-        <v>49.69994250523287</v>
+        <v>49.69994225674613</v>
       </c>
       <c r="CD32" t="n">
         <v>47.301358204649</v>
       </c>
       <c r="CE32" t="n">
-        <v>69.17517562383775</v>
+        <v>69.17517548529065</v>
       </c>
       <c r="CF32" t="n">
-        <v>59.81377114128137</v>
+        <v>59.81377111333469</v>
       </c>
       <c r="CG32" t="n">
-        <v>24.46371057649108</v>
+        <v>24.46371042099262</v>
       </c>
       <c r="CH32" t="n">
         <v>76.33330481362214</v>
       </c>
       <c r="CI32" t="n">
-        <v>50.26937751955764</v>
+        <v>50.269377440827</v>
       </c>
       <c r="CJ32" t="n">
-        <v>48.50065035494093</v>
+        <v>48.50065023069757</v>
       </c>
       <c r="CK32" t="n">
-        <v>43.65058531944684</v>
+        <v>43.65058520762781</v>
       </c>
       <c r="CL32" t="n">
         <v>8</v>
@@ -11084,10 +11084,10 @@
         <v>3.1</v>
       </c>
       <c r="CO32" t="n">
-        <v>-0.9292238789905261</v>
+        <v>-0.9292241327785944</v>
       </c>
       <c r="CP32" t="n">
-        <v>14.09300034663803</v>
+        <v>14.09300016794843</v>
       </c>
       <c r="CQ32" t="inlineStr">
         <is>
@@ -11365,10 +11365,10 @@
         <v>53.7400016784668</v>
       </c>
       <c r="CA33" t="n">
-        <v>10.50731955363538</v>
+        <v>10.50731958635367</v>
       </c>
       <c r="CB33" t="n">
-        <v>19.49107777199363</v>
+        <v>19.49107783268605</v>
       </c>
       <c r="CC33" t="n">
         <v>62.18821154931746</v>
@@ -11377,7 +11377,7 @@
         <v>46.54098234247379</v>
       </c>
       <c r="CE33" t="n">
-        <v>83.24912654392116</v>
+        <v>83.24912658392606</v>
       </c>
       <c r="CF33" t="n">
         <v>11.76833333333333</v>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="CH33" t="inlineStr"/>
       <c r="CI33" t="n">
-        <v>13.92224355298745</v>
+        <v>13.92224358412435</v>
       </c>
       <c r="CJ33" t="n">
         <v>11.76833333333333</v>
@@ -11408,7 +11408,7 @@
         <v>-80.29121758616556</v>
       </c>
       <c r="CP33" t="n">
-        <v>-74.09333249320314</v>
+        <v>-74.09333243526324</v>
       </c>
       <c r="CQ33" t="inlineStr">
         <is>
@@ -11527,12 +11527,12 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Bandeira de alta</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Fundo duplo (pré-confirmação) — pescoço R$27.67, preço 6.5% acima do pescoço; falta fechar acima e segurar</t>
+          <t>Bandeira de alta (pré-confirmação) — pescoço R$29.65, preço 0.6% abaixo do pescoço; falta fechar acima e segurar</t>
         </is>
       </c>
       <c r="U34" t="b">
@@ -11686,10 +11686,10 @@
         <v>29.46999931335449</v>
       </c>
       <c r="CA34" t="n">
-        <v>15.40499609631564</v>
+        <v>15.4049961404869</v>
       </c>
       <c r="CB34" t="n">
-        <v>28.57626775866552</v>
+        <v>28.57626784060319</v>
       </c>
       <c r="CC34" t="n">
         <v>53.78477836114972</v>
@@ -11698,23 +11698,23 @@
         <v>48.59041952862963</v>
       </c>
       <c r="CE34" t="n">
-        <v>59.55728565402742</v>
+        <v>59.55728564217956</v>
       </c>
       <c r="CF34" t="n">
-        <v>36.60763963896498</v>
+        <v>36.60763963081416</v>
       </c>
       <c r="CG34" t="n">
-        <v>29.60722472567762</v>
+        <v>29.60722466468949</v>
       </c>
       <c r="CH34" t="inlineStr"/>
       <c r="CI34" t="n">
-        <v>33.59342046377397</v>
+        <v>33.59342049326349</v>
       </c>
       <c r="CJ34" t="n">
-        <v>32.59195369881525</v>
+        <v>32.59195373570867</v>
       </c>
       <c r="CK34" t="n">
-        <v>29.33275832893373</v>
+        <v>29.33275836213781</v>
       </c>
       <c r="CL34" t="n">
         <v>4</v>
@@ -11726,10 +11726,10 @@
         <v>3.5</v>
       </c>
       <c r="CO34" t="n">
-        <v>-0.4656972772936974</v>
+        <v>-0.4656971646229247</v>
       </c>
       <c r="CP34" t="n">
-        <v>13.99192822020503</v>
+        <v>13.9919283202713</v>
       </c>
       <c r="CQ34" t="inlineStr">
         <is>
@@ -12019,10 +12019,10 @@
         <v>10.39999961853027</v>
       </c>
       <c r="CA35" t="n">
-        <v>12.95046613209858</v>
+        <v>12.95046604910022</v>
       </c>
       <c r="CB35" t="n">
-        <v>18.85587868833553</v>
+        <v>18.85587856748992</v>
       </c>
       <c r="CC35" t="n">
         <v>16.51297649354425</v>
@@ -12041,7 +12041,7 @@
         <v>14.71449508364002</v>
       </c>
       <c r="CI35" t="n">
-        <v>16.0256887432667</v>
+        <v>16.0256887092927</v>
       </c>
       <c r="CJ35" t="n">
         <v>15.61373578859213</v>
@@ -12062,7 +12062,7 @@
         <v>35.11887235740878</v>
       </c>
       <c r="CP35" t="n">
-        <v>54.09316664505266</v>
+        <v>54.09316631837959</v>
       </c>
       <c r="CQ35" t="inlineStr">
         <is>
@@ -12358,37 +12358,37 @@
         <v>18.73999977111816</v>
       </c>
       <c r="CA36" t="n">
-        <v>8.791279506096567</v>
+        <v>8.791279524812904</v>
       </c>
       <c r="CB36" t="n">
-        <v>9.149669700004923</v>
+        <v>9.149669699019631</v>
       </c>
       <c r="CC36" t="n">
-        <v>9.503003816599623</v>
+        <v>9.503003795344707</v>
       </c>
       <c r="CD36" t="n">
         <v>16.79875791329259</v>
       </c>
       <c r="CE36" t="n">
-        <v>9.013371306400025</v>
+        <v>9.01337129021001</v>
       </c>
       <c r="CF36" t="n">
-        <v>17.5186208391091</v>
+        <v>17.51862083446328</v>
       </c>
       <c r="CG36" t="n">
-        <v>3.803290595326335</v>
+        <v>3.803290573914844</v>
       </c>
       <c r="CH36" t="n">
         <v>16.19033501601518</v>
       </c>
       <c r="CI36" t="n">
-        <v>11.34604108660554</v>
+        <v>11.34604108088414</v>
       </c>
       <c r="CJ36" t="n">
-        <v>9.326336758302272</v>
+        <v>9.326336747182168</v>
       </c>
       <c r="CK36" t="n">
-        <v>8.393703082472046</v>
+        <v>8.393703072463952</v>
       </c>
       <c r="CL36" t="n">
         <v>8</v>
@@ -12400,10 +12400,10 @@
         <v>4.6</v>
       </c>
       <c r="CO36" t="n">
-        <v>-55.20969485064611</v>
+        <v>-55.2096949040511</v>
       </c>
       <c r="CP36" t="n">
-        <v>-39.45548972688939</v>
+        <v>-39.45548975741979</v>
       </c>
       <c r="CQ36" t="inlineStr">
         <is>
@@ -13262,10 +13262,10 @@
         <v>10.35999965667725</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.851813302662554</v>
+        <v>5.85181314153473</v>
       </c>
       <c r="CB2" t="n">
-        <v>10.85511367643904</v>
+        <v>10.85511337754692</v>
       </c>
       <c r="CC2" t="n">
         <v>41.59696831847682</v>
@@ -13274,7 +13274,7 @@
         <v>27.90166392450355</v>
       </c>
       <c r="CE2" t="n">
-        <v>71.91678214770741</v>
+        <v>71.91678146413481</v>
       </c>
       <c r="CF2" t="n">
         <v>19.57807411896471</v>
@@ -13336,7 +13336,7 @@
         <v>-4.516135553592537</v>
       </c>
       <c r="DC2" t="n">
-        <v>-26.80358213834876</v>
+        <v>-26.80357709863755</v>
       </c>
       <c r="DD2" t="b">
         <v>1</v>
@@ -13585,10 +13585,10 @@
         <v>13.46000003814697</v>
       </c>
       <c r="CA3" t="n">
-        <v>14.84732047183941</v>
+        <v>14.84732059754322</v>
       </c>
       <c r="CB3" t="n">
-        <v>27.54177947526211</v>
+        <v>27.54177970844266</v>
       </c>
       <c r="CC3" t="n">
         <v>38.93995644223742</v>
@@ -13597,13 +13597,13 @@
         <v>23.51205793312256</v>
       </c>
       <c r="CE3" t="n">
-        <v>75.54482877750478</v>
+        <v>75.54482854474766</v>
       </c>
       <c r="CF3" t="n">
-        <v>48.52515945161966</v>
+        <v>48.52515935922475</v>
       </c>
       <c r="CG3" t="n">
-        <v>26.80868525178779</v>
+        <v>26.80868486395637</v>
       </c>
       <c r="CH3" t="n">
         <v>8.920136085713818</v>
@@ -13908,10 +13908,10 @@
         <v>24.61000061035156</v>
       </c>
       <c r="CA4" t="n">
-        <v>16.31411908729732</v>
+        <v>16.31411912109865</v>
       </c>
       <c r="CB4" t="n">
-        <v>30.26269090693654</v>
+        <v>30.26269096963799</v>
       </c>
       <c r="CC4" t="n">
         <v>72.30210822331667</v>
@@ -13920,19 +13920,19 @@
         <v>52.41049602817493</v>
       </c>
       <c r="CE4" t="n">
-        <v>127.9950261375635</v>
+        <v>127.9950261271193</v>
       </c>
       <c r="CF4" t="n">
-        <v>25.7314236582745</v>
+        <v>25.73142365350962</v>
       </c>
       <c r="CG4" t="n">
-        <v>63.19894121982481</v>
+        <v>63.19894114730609</v>
       </c>
       <c r="CH4" t="n">
         <v>42.85100954601229</v>
       </c>
       <c r="CI4" t="n">
-        <v>47.79277826375662</v>
+        <v>47.79277826132627</v>
       </c>
       <c r="CJ4" t="n">
         <v>47.63075278709361</v>
@@ -13953,7 +13953,7 @@
         <v>74.18803919229917</v>
       </c>
       <c r="CP4" t="n">
-        <v>94.20063827082484</v>
+        <v>94.20063826094938</v>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
@@ -14239,10 +14239,10 @@
         <v>4.119999885559082</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.742268119905749</v>
+        <v>3.742268130875503</v>
       </c>
       <c r="CB5" t="n">
-        <v>6.941907362425163</v>
+        <v>6.941907382774058</v>
       </c>
       <c r="CC5" t="n">
         <v>12.63657372306894</v>
@@ -14251,19 +14251,19 @@
         <v>8.512687176725057</v>
       </c>
       <c r="CE5" t="n">
-        <v>24.29926425581659</v>
+        <v>24.29926424787384</v>
       </c>
       <c r="CF5" t="n">
-        <v>11.19291967147257</v>
+        <v>11.19291966694585</v>
       </c>
       <c r="CG5" t="n">
-        <v>10.19843573572495</v>
+        <v>10.19843570838657</v>
       </c>
       <c r="CH5" t="n">
         <v>5.258139118319559</v>
       </c>
       <c r="CI5" t="n">
-        <v>8.354704415377428</v>
+        <v>8.354704415299363</v>
       </c>
       <c r="CJ5" t="n">
         <v>8.512687176725057</v>
@@ -14284,7 +14284,7 @@
         <v>85.95676388017426</v>
       </c>
       <c r="CP5" t="n">
-        <v>102.7840933845972</v>
+        <v>102.7840933827025</v>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>-2.254690866785281</v>
       </c>
       <c r="DC5" t="n">
-        <v>-36.92337647573303</v>
+        <v>-36.92338129060463</v>
       </c>
       <c r="DD5" t="b">
         <v>1</v>
@@ -14572,10 +14572,10 @@
         <v>4.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.282599895150733</v>
+        <v>3.282599894210626</v>
       </c>
       <c r="CB6" t="n">
-        <v>6.08922280550461</v>
+        <v>6.089222803760711</v>
       </c>
       <c r="CC6" t="n">
         <v>12.96195652173913</v>
@@ -14584,7 +14584,7 @@
         <v>8.728772626887835</v>
       </c>
       <c r="CE6" t="n">
-        <v>24.66443446350224</v>
+        <v>24.66443446064104</v>
       </c>
       <c r="CF6" t="n">
         <v>11.57513776217851</v>
@@ -14596,7 +14596,7 @@
         <v>5.383571029035719</v>
       </c>
       <c r="CI6" t="n">
-        <v>11.60572167579817</v>
+        <v>11.6057216751403</v>
       </c>
       <c r="CJ6" t="n">
         <v>11.57513776217851</v>
@@ -14617,7 +14617,7 @@
         <v>131.5027552435702</v>
       </c>
       <c r="CP6" t="n">
-        <v>157.9049261288482</v>
+        <v>157.9049261142289</v>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
@@ -14895,10 +14895,10 @@
         <v>48.34000015258789</v>
       </c>
       <c r="CA7" t="n">
-        <v>18.42191759848097</v>
+        <v>18.421917577112</v>
       </c>
       <c r="CB7" t="n">
-        <v>34.17265714518221</v>
+        <v>34.17265710554276</v>
       </c>
       <c r="CC7" t="n">
         <v>74.65093263657221</v>
@@ -14907,23 +14907,23 @@
         <v>55.91472932652801</v>
       </c>
       <c r="CE7" t="n">
-        <v>99.8344550591067</v>
+        <v>99.83445509256833</v>
       </c>
       <c r="CF7" t="n">
-        <v>48.37202137970021</v>
+        <v>48.37202138492027</v>
       </c>
       <c r="CG7" t="n">
-        <v>58.90972737559709</v>
+        <v>58.90972741854703</v>
       </c>
       <c r="CH7" t="inlineStr"/>
       <c r="CI7" t="n">
-        <v>43.9043821899839</v>
+        <v>43.90438217603681</v>
       </c>
       <c r="CJ7" t="n">
-        <v>41.27233926244121</v>
+        <v>41.27233924523151</v>
       </c>
       <c r="CK7" t="n">
-        <v>37.14510533619709</v>
+        <v>37.14510532070836</v>
       </c>
       <c r="CL7" t="n">
         <v>4</v>
@@ -14935,10 +14935,10 @@
         <v>4.1</v>
       </c>
       <c r="CO7" t="n">
-        <v>-23.15865697363155</v>
+        <v>-23.15865700567279</v>
       </c>
       <c r="CP7" t="n">
-        <v>-9.17587494539247</v>
+        <v>-9.175874974244525</v>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
@@ -15441,10 +15441,10 @@
         <v>15.69999980926514</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.403272786852184</v>
+        <v>6.403272805631215</v>
       </c>
       <c r="CB9" t="n">
-        <v>11.8780710196108</v>
+        <v>11.8780710544459</v>
       </c>
       <c r="CC9" t="n">
         <v>25.39987759130195</v>
@@ -15453,19 +15453,19 @@
         <v>18.63509665364473</v>
       </c>
       <c r="CE9" t="n">
-        <v>35.2441967285137</v>
+        <v>35.24419669801659</v>
       </c>
       <c r="CF9" t="n">
-        <v>12.29886962062783</v>
+        <v>12.29886961706348</v>
       </c>
       <c r="CG9" t="n">
-        <v>20.39435314969272</v>
+        <v>20.39435311034539</v>
       </c>
       <c r="CH9" t="n">
         <v>18.40902666520164</v>
       </c>
       <c r="CI9" t="n">
-        <v>20.32278448979906</v>
+        <v>20.32278448428853</v>
       </c>
       <c r="CJ9" t="n">
         <v>18.63509665364473</v>
@@ -15486,7 +15486,7 @@
         <v>6.825396127602112</v>
       </c>
       <c r="CP9" t="n">
-        <v>29.44448876875685</v>
+        <v>29.44448873365793</v>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
@@ -15776,10 +15776,10 @@
         <v>42.70000076293945</v>
       </c>
       <c r="CA10" t="n">
-        <v>125.1024114745125</v>
+        <v>125.1024118332479</v>
       </c>
       <c r="CB10" t="n">
-        <v>232.0649732852206</v>
+        <v>232.0649739506748</v>
       </c>
       <c r="CC10" t="n">
         <v>134.3883634463059</v>
@@ -15800,13 +15800,13 @@
         <v>54.40212095818906</v>
       </c>
       <c r="CI10" t="n">
-        <v>140.0389271837773</v>
+        <v>140.038927311801</v>
       </c>
       <c r="CJ10" t="n">
-        <v>123.9134396127393</v>
+        <v>123.913439792107</v>
       </c>
       <c r="CK10" t="n">
-        <v>111.5220956514654</v>
+        <v>111.5220958128963</v>
       </c>
       <c r="CL10" t="n">
         <v>8</v>
@@ -15818,10 +15818,10 @@
         <v>5.6</v>
       </c>
       <c r="CO10" t="n">
-        <v>161.175863369676</v>
+        <v>161.1758637477344</v>
       </c>
       <c r="CP10" t="n">
-        <v>227.9600109640304</v>
+        <v>227.9600112638517</v>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
@@ -16109,10 +16109,10 @@
         <v>32.47999954223633</v>
       </c>
       <c r="CA11" t="n">
-        <v>45.35763240419051</v>
+        <v>45.35763219127636</v>
       </c>
       <c r="CB11" t="n">
-        <v>84.13840810977339</v>
+        <v>84.13840771481763</v>
       </c>
       <c r="CC11" t="n">
         <v>68.20285165366582</v>
@@ -16133,7 +16133,7 @@
         <v>25.67266223983068</v>
       </c>
       <c r="CI11" t="n">
-        <v>77.37745295143534</v>
+        <v>77.37745286459679</v>
       </c>
       <c r="CJ11" t="n">
         <v>68.20285165366582</v>
@@ -16154,7 +16154,7 @@
         <v>88.98573692551506</v>
       </c>
       <c r="CP11" t="n">
-        <v>138.2310777154269</v>
+        <v>138.2310774480669</v>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
@@ -16442,10 +16442,10 @@
         <v>6.920000076293945</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.500811647126639</v>
+        <v>6.500811651552686</v>
       </c>
       <c r="CB12" t="n">
-        <v>12.05900560541991</v>
+        <v>12.05900561363023</v>
       </c>
       <c r="CC12" t="n">
         <v>40.39207092990959</v>
@@ -16454,7 +16454,7 @@
         <v>27.23293457569906</v>
       </c>
       <c r="CE12" t="n">
-        <v>85.81998423091724</v>
+        <v>85.81998425821445</v>
       </c>
       <c r="CF12" t="n">
         <v>51.88018214566937</v>
@@ -16769,37 +16769,37 @@
         <v>32.84999847412109</v>
       </c>
       <c r="CA13" t="n">
-        <v>24.40136931092796</v>
+        <v>24.40136932160346</v>
       </c>
       <c r="CB13" t="n">
-        <v>32.24270572677878</v>
+        <v>32.24270565046241</v>
       </c>
       <c r="CC13" t="n">
-        <v>33.81078576994144</v>
+        <v>33.81078567512144</v>
       </c>
       <c r="CD13" t="n">
         <v>20.85130777065122</v>
       </c>
       <c r="CE13" t="n">
-        <v>48.28249341817388</v>
+        <v>48.28249333526282</v>
       </c>
       <c r="CF13" t="n">
-        <v>50.84680029791828</v>
+        <v>50.84680028425728</v>
       </c>
       <c r="CG13" t="n">
-        <v>16.50214466972086</v>
+        <v>16.50214460736058</v>
       </c>
       <c r="CH13" t="n">
         <v>24.29339039885633</v>
       </c>
       <c r="CI13" t="n">
-        <v>31.40387467037109</v>
+        <v>31.40387463044694</v>
       </c>
       <c r="CJ13" t="n">
-        <v>28.32203751885337</v>
+        <v>28.32203748603293</v>
       </c>
       <c r="CK13" t="n">
-        <v>25.48983376696803</v>
+        <v>25.48983373742964</v>
       </c>
       <c r="CL13" t="n">
         <v>8</v>
@@ -16811,10 +16811,10 @@
         <v>3.1</v>
       </c>
       <c r="CO13" t="n">
-        <v>-22.40537305641377</v>
+        <v>-22.40537314633277</v>
       </c>
       <c r="CP13" t="n">
-        <v>-4.402203564451435</v>
+        <v>-4.402203685986139</v>
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
@@ -17104,10 +17104,10 @@
         <v>47.31000137329102</v>
       </c>
       <c r="CA14" t="n">
-        <v>131.3198828881482</v>
+        <v>131.3198817888239</v>
       </c>
       <c r="CB14" t="n">
-        <v>243.5983827575148</v>
+        <v>243.5983807182684</v>
       </c>
       <c r="CC14" t="n">
         <v>134.5187807287781</v>
@@ -17128,13 +17128,13 @@
         <v>53.17581509382557</v>
       </c>
       <c r="CI14" t="n">
-        <v>142.2129205558937</v>
+        <v>142.2129201635724</v>
       </c>
       <c r="CJ14" t="n">
-        <v>127.0817243428747</v>
+        <v>127.0817237932125</v>
       </c>
       <c r="CK14" t="n">
-        <v>114.3735519085872</v>
+        <v>114.3735514138913</v>
       </c>
       <c r="CL14" t="n">
         <v>8</v>
@@ -17146,10 +17146,10 @@
         <v>5.7</v>
       </c>
       <c r="CO14" t="n">
-        <v>141.7534318085162</v>
+        <v>141.7534307628686</v>
       </c>
       <c r="CP14" t="n">
-        <v>200.5980055544457</v>
+        <v>200.5980047251891</v>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>-1.560432066163409</v>
       </c>
       <c r="DC14" t="n">
-        <v>-10.93847029890879</v>
+        <v>-10.93846372884365</v>
       </c>
       <c r="DD14" t="b">
         <v>1</v>
@@ -17435,10 +17435,10 @@
         <v>13.64999961853027</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.2010593269665734</v>
+        <v>0.2010593269434413</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.2927423800633308</v>
+        <v>0.2927423800296505</v>
       </c>
       <c r="CC15" t="n">
         <v>75.91443638113093</v>
@@ -17746,10 +17746,10 @@
         <v>13.80000019073486</v>
       </c>
       <c r="CA16" t="n">
-        <v>10.017773647919</v>
+        <v>10.01777364502784</v>
       </c>
       <c r="CB16" t="n">
-        <v>18.58297011688975</v>
+        <v>18.58297011152664</v>
       </c>
       <c r="CC16" t="n">
         <v>49.41891960195592</v>
@@ -17758,23 +17758,23 @@
         <v>48.6151297750832</v>
       </c>
       <c r="CE16" t="n">
-        <v>68.76431137838433</v>
+        <v>68.76431137281195</v>
       </c>
       <c r="CF16" t="n">
-        <v>33.93512327114811</v>
+        <v>33.93512327159912</v>
       </c>
       <c r="CG16" t="n">
-        <v>29.36093189556094</v>
+        <v>29.36093189893458</v>
       </c>
       <c r="CH16" t="inlineStr"/>
       <c r="CI16" t="n">
-        <v>33.97900432999793</v>
+        <v>33.97900432836056</v>
       </c>
       <c r="CJ16" t="n">
-        <v>33.93512327114811</v>
+        <v>33.93512327159912</v>
       </c>
       <c r="CK16" t="n">
-        <v>30.54161094403331</v>
+        <v>30.54161094443921</v>
       </c>
       <c r="CL16" t="n">
         <v>3</v>
@@ -17786,10 +17786,10 @@
         <v>4.9</v>
       </c>
       <c r="CO16" t="n">
-        <v>121.3160182746848</v>
+        <v>121.3160182776261</v>
       </c>
       <c r="CP16" t="n">
-        <v>146.2246656547946</v>
+        <v>146.2246656429296</v>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
@@ -18073,10 +18073,10 @@
         <v>7.239999771118164</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.268913165541576</v>
+        <v>3.268913169515907</v>
       </c>
       <c r="CB17" t="n">
-        <v>6.063833922079623</v>
+        <v>6.063833929452008</v>
       </c>
       <c r="CC17" t="n">
         <v>20.4541571358882</v>
@@ -18085,7 +18085,7 @@
         <v>14.0164620450613</v>
       </c>
       <c r="CE17" t="n">
-        <v>32.91359933568327</v>
+        <v>32.91359934754694</v>
       </c>
       <c r="CF17" t="n">
         <v>10.95072400487419</v>
@@ -18378,10 +18378,10 @@
         <v>19.30999946594238</v>
       </c>
       <c r="CA18" t="n">
-        <v>13.27333703885629</v>
+        <v>13.27333702384396</v>
       </c>
       <c r="CB18" t="n">
-        <v>24.62204020707841</v>
+        <v>24.62204017923054</v>
       </c>
       <c r="CC18" t="n">
         <v>19.98886663466692</v>
@@ -18390,7 +18390,7 @@
         <v>12.49234273346821</v>
       </c>
       <c r="CE18" t="n">
-        <v>33.82771185219145</v>
+        <v>33.82771183577172</v>
       </c>
       <c r="CF18" t="n">
         <v>22.8984489302328</v>
@@ -18400,7 +18400,7 @@
       </c>
       <c r="CH18" t="inlineStr"/>
       <c r="CI18" t="n">
-        <v>20.1956732027086</v>
+        <v>20.19567319199356</v>
       </c>
       <c r="CJ18" t="n">
         <v>21.44365778244985</v>
@@ -18421,7 +18421,7 @@
         <v>-0.05545034714474761</v>
       </c>
       <c r="CP18" t="n">
-        <v>4.586606738795118</v>
+        <v>4.586606683305527</v>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
@@ -18717,10 +18717,10 @@
         <v>17.21999931335449</v>
       </c>
       <c r="CA19" t="n">
-        <v>10.55474904779928</v>
+        <v>10.55474908527501</v>
       </c>
       <c r="CB19" t="n">
-        <v>19.57905948366767</v>
+        <v>19.57905955318514</v>
       </c>
       <c r="CC19" t="n">
         <v>37.03977125031607</v>
@@ -18729,25 +18729,25 @@
         <v>36.56718452753732</v>
       </c>
       <c r="CE19" t="n">
-        <v>41.35653251466345</v>
+        <v>41.35653253068535</v>
       </c>
       <c r="CF19" t="n">
-        <v>34.51133421135384</v>
+        <v>34.51133420331627</v>
       </c>
       <c r="CG19" t="n">
-        <v>18.3851786431524</v>
+        <v>18.38517859968655</v>
       </c>
       <c r="CH19" t="n">
         <v>31.59171947190627</v>
       </c>
       <c r="CI19" t="n">
-        <v>31.29011144322814</v>
+        <v>31.29011144809042</v>
       </c>
       <c r="CJ19" t="n">
-        <v>34.51133421135384</v>
+        <v>34.51133420331627</v>
       </c>
       <c r="CK19" t="n">
-        <v>31.06020079021846</v>
+        <v>31.06020078298464</v>
       </c>
       <c r="CL19" t="n">
         <v>7</v>
@@ -18759,10 +18759,10 @@
         <v>3.9</v>
       </c>
       <c r="CO19" t="n">
-        <v>80.37283408095482</v>
+        <v>80.37283403894659</v>
       </c>
       <c r="CP19" t="n">
-        <v>81.70797149197308</v>
+        <v>81.70797152020933</v>
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>-1.768404798336243</v>
       </c>
       <c r="DC19" t="n">
-        <v>-24.57900422609433</v>
+        <v>-24.57901058396539</v>
       </c>
       <c r="DD19" t="b">
         <v>1</v>
@@ -19050,37 +19050,37 @@
         <v>10.10999965667725</v>
       </c>
       <c r="CA20" t="n">
-        <v>10.12952178280262</v>
+        <v>10.12952182665193</v>
       </c>
       <c r="CB20" t="n">
-        <v>18.71325025888591</v>
+        <v>18.71325013446309</v>
       </c>
       <c r="CC20" t="n">
-        <v>24.61410798311763</v>
+        <v>24.61410771290942</v>
       </c>
       <c r="CD20" t="n">
         <v>17.7286584153084</v>
       </c>
       <c r="CE20" t="n">
-        <v>37.29961186413532</v>
+        <v>37.29961182454053</v>
       </c>
       <c r="CF20" t="n">
-        <v>24.22565667861713</v>
+        <v>24.22565665988301</v>
       </c>
       <c r="CG20" t="n">
-        <v>11.9820663019273</v>
+        <v>11.9820662058447</v>
       </c>
       <c r="CH20" t="n">
         <v>10.10999965667725</v>
       </c>
       <c r="CI20" t="n">
-        <v>19.35035911768394</v>
+        <v>19.35035905453479</v>
       </c>
       <c r="CJ20" t="n">
-        <v>18.22095433709715</v>
+        <v>18.22095427488574</v>
       </c>
       <c r="CK20" t="n">
-        <v>16.39885890338743</v>
+        <v>16.39885884739717</v>
       </c>
       <c r="CL20" t="n">
         <v>8</v>
@@ -19092,10 +19092,10 @@
         <v>3.7</v>
       </c>
       <c r="CO20" t="n">
-        <v>62.20434678805009</v>
+        <v>62.20434623423934</v>
       </c>
       <c r="CP20" t="n">
-        <v>91.39821735704821</v>
+        <v>91.3982167324275</v>
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
@@ -19385,10 +19385,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="CA21" t="n">
-        <v>5.044566675915342</v>
+        <v>5.044566653942212</v>
       </c>
       <c r="CB21" t="n">
-        <v>9.357671183822958</v>
+        <v>9.357671143062804</v>
       </c>
       <c r="CC21" t="n">
         <v>8.579313567043014</v>
@@ -19708,37 +19708,37 @@
         <v>35.20000076293945</v>
       </c>
       <c r="CA22" t="n">
-        <v>25.30988628740988</v>
+        <v>25.30988629074186</v>
       </c>
       <c r="CB22" t="n">
-        <v>31.05606612847724</v>
+        <v>31.05606612350457</v>
       </c>
       <c r="CC22" t="n">
-        <v>34.16513457586648</v>
+        <v>34.16513456589826</v>
       </c>
       <c r="CD22" t="n">
         <v>36.55813791194976</v>
       </c>
       <c r="CE22" t="n">
-        <v>48.30357191237576</v>
+        <v>48.30357190562313</v>
       </c>
       <c r="CF22" t="n">
-        <v>48.4515069927446</v>
+        <v>48.45150699129687</v>
       </c>
       <c r="CG22" t="n">
-        <v>16.11056064206664</v>
+        <v>16.11056063457502</v>
       </c>
       <c r="CH22" t="n">
         <v>30.9183777534985</v>
       </c>
       <c r="CI22" t="n">
-        <v>33.8591552755486</v>
+        <v>33.85915527213599</v>
       </c>
       <c r="CJ22" t="n">
-        <v>32.61060035217186</v>
+        <v>32.61060034470142</v>
       </c>
       <c r="CK22" t="n">
-        <v>29.34954031695467</v>
+        <v>29.34954031023128</v>
       </c>
       <c r="CL22" t="n">
         <v>8</v>
@@ -19750,10 +19750,10 @@
         <v>3</v>
       </c>
       <c r="CO22" t="n">
-        <v>-16.62062590675984</v>
+        <v>-16.62062592586041</v>
       </c>
       <c r="CP22" t="n">
-        <v>-3.809220052070483</v>
+        <v>-3.809220061765395</v>
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
@@ -20037,10 +20037,10 @@
         <v>10.97000026702881</v>
       </c>
       <c r="CA23" t="n">
-        <v>9.497073397998388</v>
+        <v>9.497073338236024</v>
       </c>
       <c r="CB23" t="n">
-        <v>17.61707115328701</v>
+        <v>17.61707104242782</v>
       </c>
       <c r="CC23" t="n">
         <v>21.98978873496697</v>
@@ -20049,25 +20049,25 @@
         <v>12.98356721691296</v>
       </c>
       <c r="CE23" t="n">
-        <v>32.25283416633335</v>
+        <v>32.25283434748484</v>
       </c>
       <c r="CF23" t="n">
-        <v>25.3672351516493</v>
+        <v>25.36723519548015</v>
       </c>
       <c r="CG23" t="n">
-        <v>12.0631232455236</v>
+        <v>12.06312343895286</v>
       </c>
       <c r="CH23" t="n">
         <v>9.632374997322403</v>
       </c>
       <c r="CI23" t="n">
-        <v>17.67538350799925</v>
+        <v>17.675383538973</v>
       </c>
       <c r="CJ23" t="n">
-        <v>15.30031918509999</v>
+        <v>15.30031912967039</v>
       </c>
       <c r="CK23" t="n">
-        <v>13.77028726658999</v>
+        <v>13.77028721670335</v>
       </c>
       <c r="CL23" t="n">
         <v>8</v>
@@ -20079,10 +20079,10 @@
         <v>3.4</v>
       </c>
       <c r="CO23" t="n">
-        <v>25.52677239195391</v>
+        <v>25.52677193719881</v>
       </c>
       <c r="CP23" t="n">
-        <v>61.12473179352595</v>
+        <v>61.12473207587556</v>
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
@@ -20370,10 +20370,10 @@
         <v>10.63000011444092</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.315025661609432</v>
+        <v>3.315025657679916</v>
       </c>
       <c r="CB24" t="n">
-        <v>6.149372602285496</v>
+        <v>6.149372594996244</v>
       </c>
       <c r="CC24" t="n">
         <v>19.53502101474926</v>
@@ -20382,13 +20382,13 @@
         <v>18.41366451165369</v>
       </c>
       <c r="CE24" t="n">
-        <v>20.99446707931569</v>
+        <v>20.99446707961297</v>
       </c>
       <c r="CF24" t="n">
-        <v>15.93445353560463</v>
+        <v>15.93445353638441</v>
       </c>
       <c r="CG24" t="n">
-        <v>13.08904091557589</v>
+        <v>13.08904092055883</v>
       </c>
       <c r="CH24" t="n">
         <v>29.73646810990179</v>
@@ -20701,10 +20701,10 @@
         <v>14.72999954223633</v>
       </c>
       <c r="CA25" t="n">
-        <v>4.523502071725631</v>
+        <v>4.523502098020554</v>
       </c>
       <c r="CB25" t="n">
-        <v>8.391096343051045</v>
+        <v>8.391096391828126</v>
       </c>
       <c r="CC25" t="n">
         <v>24.2149496196813</v>
@@ -20713,25 +20713,25 @@
         <v>20.36807772582785</v>
       </c>
       <c r="CE25" t="n">
-        <v>29.43735273839877</v>
+        <v>29.43735271755145</v>
       </c>
       <c r="CF25" t="n">
-        <v>16.70161176519869</v>
+        <v>16.7016117597615</v>
       </c>
       <c r="CG25" t="n">
-        <v>18.44681923672625</v>
+        <v>18.44681919491311</v>
       </c>
       <c r="CH25" t="n">
         <v>14.61024983224005</v>
       </c>
       <c r="CI25" t="n">
-        <v>18.88145103730342</v>
+        <v>18.88145103454334</v>
       </c>
       <c r="CJ25" t="n">
-        <v>18.44681923672625</v>
+        <v>18.44681919491311</v>
       </c>
       <c r="CK25" t="n">
-        <v>16.60213731305362</v>
+        <v>16.6021372754218</v>
       </c>
       <c r="CL25" t="n">
         <v>7</v>
@@ -20743,10 +20743,10 @@
         <v>6.5</v>
       </c>
       <c r="CO25" t="n">
-        <v>12.70969334010625</v>
+        <v>12.70969308462886</v>
       </c>
       <c r="CP25" t="n">
-        <v>28.18364985798782</v>
+        <v>28.18364983924999</v>
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
@@ -21028,10 +21028,10 @@
         <v>8.140000343322754</v>
       </c>
       <c r="CA26" t="n">
-        <v>3.771663344142528</v>
+        <v>3.771663348271938</v>
       </c>
       <c r="CB26" t="n">
-        <v>6.996435503384389</v>
+        <v>6.996435511044444</v>
       </c>
       <c r="CC26" t="n">
         <v>23.80905177682704</v>
@@ -21040,13 +21040,13 @@
         <v>22.16303232632007</v>
       </c>
       <c r="CE26" t="n">
-        <v>30.42304109722089</v>
+        <v>30.42304110143251</v>
       </c>
       <c r="CF26" t="n">
-        <v>9.586527745031702</v>
+        <v>9.586527744618676</v>
       </c>
       <c r="CG26" t="n">
-        <v>16.59651843490264</v>
+        <v>16.59651842952813</v>
       </c>
       <c r="CH26" t="inlineStr"/>
       <c r="CI26" t="inlineStr"/>
@@ -21174,12 +21174,12 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Bandeira de alta</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Fundo duplo (pré-confirmação) — pescoço R$12.73, preço 12.5% acima do pescoço; falta fechar acima e segurar</t>
+          <t>Bandeira de alta (pré-confirmação) — pescoço R$13.33, preço 7.4% acima do pescoço; falta fechar acima e segurar</t>
         </is>
       </c>
       <c r="U27" t="b">
@@ -21353,10 +21353,10 @@
         <v>14.31999969482422</v>
       </c>
       <c r="CA27" t="n">
-        <v>8.981535421628671</v>
+        <v>8.981535409827668</v>
       </c>
       <c r="CB27" t="n">
-        <v>16.66074820712118</v>
+        <v>16.66074818523033</v>
       </c>
       <c r="CC27" t="n">
         <v>13.52387711735003</v>
@@ -21377,7 +21377,7 @@
         <v>6.210695553020633</v>
       </c>
       <c r="CI27" t="n">
-        <v>11.29322925604008</v>
+        <v>11.29322925122696</v>
       </c>
       <c r="CJ27" t="n">
         <v>10.99565184259889</v>
@@ -21398,7 +21398,7 @@
         <v>-30.89324811985986</v>
       </c>
       <c r="CP27" t="n">
-        <v>-21.13666552575506</v>
+        <v>-21.13666555936625</v>
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
@@ -21682,10 +21682,10 @@
         <v>27.42000007629395</v>
       </c>
       <c r="CA28" t="n">
-        <v>7.265285075463376</v>
+        <v>7.265285076459099</v>
       </c>
       <c r="CB28" t="n">
-        <v>13.47710381498456</v>
+        <v>13.47710381683163</v>
       </c>
       <c r="CC28" t="n">
         <v>35.82988175649849</v>
@@ -21694,19 +21694,19 @@
         <v>28.32096620307184</v>
       </c>
       <c r="CE28" t="n">
-        <v>44.64824885986749</v>
+        <v>44.64824885838173</v>
       </c>
       <c r="CF28" t="n">
-        <v>26.46426766347906</v>
+        <v>26.46426766323088</v>
       </c>
       <c r="CG28" t="n">
-        <v>28.98335745153566</v>
+        <v>28.98335744973761</v>
       </c>
       <c r="CH28" t="n">
         <v>24.27856406616775</v>
       </c>
       <c r="CI28" t="n">
-        <v>28.85748425937212</v>
+        <v>28.85748425913142</v>
       </c>
       <c r="CJ28" t="n">
         <v>28.32096620307184</v>
@@ -21727,7 +21727,7 @@
         <v>-7.042780773727464</v>
       </c>
       <c r="CP28" t="n">
-        <v>5.24246600685081</v>
+        <v>5.242466005972979</v>
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>-2.176241867315365</v>
       </c>
       <c r="DC28" t="n">
-        <v>-22.27487236182183</v>
+        <v>-22.27486391968831</v>
       </c>
       <c r="DD28" t="b">
         <v>1</v>
@@ -22015,10 +22015,10 @@
         <v>23.79999923706055</v>
       </c>
       <c r="CA29" t="n">
-        <v>12.34802658997896</v>
+        <v>12.3480265890507</v>
       </c>
       <c r="CB29" t="n">
-        <v>22.90558932441097</v>
+        <v>22.90558932268904</v>
       </c>
       <c r="CC29" t="n">
         <v>61.59179490059613</v>
@@ -22027,13 +22027,13 @@
         <v>51.73586889978424</v>
       </c>
       <c r="CE29" t="n">
-        <v>87.07810606139948</v>
+        <v>87.07810606123427</v>
       </c>
       <c r="CF29" t="n">
-        <v>33.74455760916484</v>
+        <v>33.74455760931939</v>
       </c>
       <c r="CG29" t="n">
-        <v>45.92960717470801</v>
+        <v>45.92960717619964</v>
       </c>
       <c r="CH29" t="n">
         <v>5.609791711095563</v>
@@ -22354,10 +22354,10 @@
         <v>22.60000038146973</v>
       </c>
       <c r="CA30" t="n">
-        <v>3.184692829840589</v>
+        <v>3.184692834576809</v>
       </c>
       <c r="CB30" t="n">
-        <v>5.907605199354292</v>
+        <v>5.90760520813998</v>
       </c>
       <c r="CC30" t="n">
         <v>33.79796896777358</v>
@@ -22366,7 +22366,7 @@
         <v>28.20908778885038</v>
       </c>
       <c r="CE30" t="n">
-        <v>43.29409766815058</v>
+        <v>43.29409767563445</v>
       </c>
       <c r="CF30" t="n">
         <v>10.85340539909456</v>
@@ -22657,10 +22657,10 @@
         <v>39.45000076293945</v>
       </c>
       <c r="CA31" t="n">
-        <v>36.12452920685543</v>
+        <v>36.12452926568335</v>
       </c>
       <c r="CB31" t="n">
-        <v>52.5973145251815</v>
+        <v>52.59731461083496</v>
       </c>
       <c r="CC31" t="n">
         <v>48.55384709284856</v>
@@ -22677,13 +22677,13 @@
       </c>
       <c r="CH31" t="inlineStr"/>
       <c r="CI31" t="n">
-        <v>49.1949639521758</v>
+        <v>49.19496398829614</v>
       </c>
       <c r="CJ31" t="n">
-        <v>50.57558080901504</v>
+        <v>50.57558085184176</v>
       </c>
       <c r="CK31" t="n">
-        <v>45.51802272811354</v>
+        <v>45.51802276665759</v>
       </c>
       <c r="CL31" t="n">
         <v>4</v>
@@ -22695,10 +22695,10 @@
         <v>1.6</v>
       </c>
       <c r="CO31" t="n">
-        <v>15.38155094504985</v>
+        <v>15.38155104275338</v>
       </c>
       <c r="CP31" t="n">
-        <v>24.70206083846534</v>
+        <v>24.70206093002516</v>
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
@@ -23287,35 +23287,35 @@
         <v>23.04999923706055</v>
       </c>
       <c r="CA33" t="n">
-        <v>16.54461546601307</v>
+        <v>16.5446154256833</v>
       </c>
       <c r="CB33" t="n">
-        <v>29.57431142601902</v>
+        <v>29.57431143213461</v>
       </c>
       <c r="CC33" t="n">
-        <v>49.88257132478946</v>
+        <v>49.88257145670015</v>
       </c>
       <c r="CD33" t="n">
         <v>49.40798271639872</v>
       </c>
       <c r="CE33" t="n">
-        <v>61.60540337918003</v>
+        <v>61.60540336281092</v>
       </c>
       <c r="CF33" t="n">
-        <v>45.75579822352145</v>
+        <v>45.75579823230964</v>
       </c>
       <c r="CG33" t="n">
-        <v>24.48336427966442</v>
+        <v>24.48336432952815</v>
       </c>
       <c r="CH33" t="inlineStr"/>
       <c r="CI33" t="n">
-        <v>35.43932411008575</v>
+        <v>35.43932413670693</v>
       </c>
       <c r="CJ33" t="n">
-        <v>37.66505482477023</v>
+        <v>37.66505483222213</v>
       </c>
       <c r="CK33" t="n">
-        <v>33.89854934229321</v>
+        <v>33.89854934899991</v>
       </c>
       <c r="CL33" t="n">
         <v>4</v>
@@ -23327,10 +23327,10 @@
         <v>3</v>
       </c>
       <c r="CO33" t="n">
-        <v>47.06529485601894</v>
+        <v>47.06529488511529</v>
       </c>
       <c r="CP33" t="n">
-        <v>53.7497843084751</v>
+        <v>53.74978442396829</v>
       </c>
       <c r="CQ33" t="inlineStr">
         <is>
@@ -23614,10 +23614,10 @@
         <v>33.38999938964844</v>
       </c>
       <c r="CA34" t="n">
-        <v>7.919773871237688</v>
+        <v>7.919773897684482</v>
       </c>
       <c r="CB34" t="n">
-        <v>14.69118053114591</v>
+        <v>14.69118058020471</v>
       </c>
       <c r="CC34" t="n">
         <v>63.74891814306077</v>
@@ -23626,7 +23626,7 @@
         <v>37.2141137927402</v>
       </c>
       <c r="CE34" t="n">
-        <v>88.14507565447467</v>
+        <v>88.14507570782554</v>
       </c>
       <c r="CF34" t="n">
         <v>22.51480113099953</v>
@@ -23937,10 +23937,10 @@
         <v>33.36000061035156</v>
       </c>
       <c r="CA35" t="n">
-        <v>15.11688476212761</v>
+        <v>15.11688474818725</v>
       </c>
       <c r="CB35" t="n">
-        <v>28.04182123374672</v>
+        <v>28.04182120788734</v>
       </c>
       <c r="CC35" t="n">
         <v>20.05535426892732</v>
@@ -23949,7 +23949,7 @@
         <v>36.99750756788258</v>
       </c>
       <c r="CE35" t="n">
-        <v>27.00891078442965</v>
+        <v>27.00891077557461</v>
       </c>
       <c r="CF35" t="n">
         <v>15.03391666666667</v>
@@ -23961,7 +23961,7 @@
         <v>79.30503918682102</v>
       </c>
       <c r="CI35" t="n">
-        <v>22.46273579269512</v>
+        <v>22.46273578574444</v>
       </c>
       <c r="CJ35" t="n">
         <v>20.05535426892732</v>
@@ -23982,7 +23982,7 @@
         <v>-45.89382940108894</v>
       </c>
       <c r="CP35" t="n">
-        <v>-32.66566132578257</v>
+        <v>-32.66566134661797</v>
       </c>
       <c r="CQ35" t="inlineStr">
         <is>
@@ -24274,10 +24274,10 @@
         <v>34.68999862670898</v>
       </c>
       <c r="CA36" t="n">
-        <v>3.441715129974142</v>
+        <v>3.441715135618347</v>
       </c>
       <c r="CB36" t="n">
-        <v>6.384381566102033</v>
+        <v>6.384381576572033</v>
       </c>
       <c r="CC36" t="n">
         <v>32.87857523633004</v>
@@ -24286,7 +24286,7 @@
         <v>23.03538757661248</v>
       </c>
       <c r="CE36" t="n">
-        <v>40.66766746926129</v>
+        <v>40.66766747491356</v>
       </c>
       <c r="CF36" t="n">
         <v>10.59424454785779</v>
@@ -24577,35 +24577,35 @@
         <v>12.84000015258789</v>
       </c>
       <c r="CA37" t="n">
-        <v>8.620453608860551</v>
+        <v>8.620453699055004</v>
       </c>
       <c r="CB37" t="n">
-        <v>13.75172347439505</v>
+        <v>13.75172337055989</v>
       </c>
       <c r="CC37" t="n">
-        <v>18.28832866588292</v>
+        <v>18.2883283364453</v>
       </c>
       <c r="CD37" t="n">
         <v>17.29599079072038</v>
       </c>
       <c r="CE37" t="n">
-        <v>22.79371672331302</v>
+        <v>22.79371663669027</v>
       </c>
       <c r="CF37" t="n">
-        <v>17.32775209408891</v>
+        <v>17.32775206890582</v>
       </c>
       <c r="CG37" t="n">
-        <v>9.132623021575037</v>
+        <v>9.13262286791255</v>
       </c>
       <c r="CH37" t="inlineStr"/>
       <c r="CI37" t="n">
-        <v>14.49706446080686</v>
+        <v>14.4970643687415</v>
       </c>
       <c r="CJ37" t="n">
-        <v>15.53973778424198</v>
+        <v>15.53973771973286</v>
       </c>
       <c r="CK37" t="n">
-        <v>13.98576400581778</v>
+        <v>13.98576394775957</v>
       </c>
       <c r="CL37" t="n">
         <v>4</v>
@@ -24617,10 +24617,10 @@
         <v>2.1</v>
       </c>
       <c r="CO37" t="n">
-        <v>8.923394389516147</v>
+        <v>8.923393937349399</v>
       </c>
       <c r="CP37" t="n">
-        <v>12.90548511313676</v>
+        <v>12.90548439611687</v>
       </c>
       <c r="CQ37" t="inlineStr">
         <is>
@@ -24894,10 +24894,10 @@
         <v>39.09999847412109</v>
       </c>
       <c r="CA38" t="n">
-        <v>19.98811954040033</v>
+        <v>19.9881195590459</v>
       </c>
       <c r="CB38" t="n">
-        <v>37.07796174744261</v>
+        <v>37.07796178203014</v>
       </c>
       <c r="CC38" t="n">
         <v>55.88726858490879</v>
@@ -24906,23 +24906,23 @@
         <v>42.23733079208057</v>
       </c>
       <c r="CE38" t="n">
-        <v>62.05637365125566</v>
+        <v>62.05637362081207</v>
       </c>
       <c r="CF38" t="n">
-        <v>45.20951665016102</v>
+        <v>45.20951664432093</v>
       </c>
       <c r="CG38" t="n">
-        <v>31.30000271636338</v>
+        <v>31.3000026795272</v>
       </c>
       <c r="CH38" t="inlineStr"/>
       <c r="CI38" t="n">
-        <v>39.54071663072818</v>
+        <v>39.54071664257643</v>
       </c>
       <c r="CJ38" t="n">
-        <v>41.14373919880181</v>
+        <v>41.14373921317554</v>
       </c>
       <c r="CK38" t="n">
-        <v>37.02936527892163</v>
+        <v>37.02936529185799</v>
       </c>
       <c r="CL38" t="n">
         <v>4</v>
@@ -24934,10 +24934,10 @@
         <v>2.8</v>
       </c>
       <c r="CO38" t="n">
-        <v>-5.295737278787726</v>
+        <v>-5.295737245702414</v>
       </c>
       <c r="CP38" t="n">
-        <v>1.127156454747147</v>
+        <v>1.127156485049574</v>
       </c>
       <c r="CQ38" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>-7.739505689776549</v>
       </c>
       <c r="DC38" t="n">
-        <v>-19.71089251072075</v>
+        <v>-19.71089883815426</v>
       </c>
       <c r="DD38" t="b">
         <v>1</v>
@@ -25233,10 +25233,10 @@
         <v>6.010000228881836</v>
       </c>
       <c r="CA39" t="n">
-        <v>7.129314286253146</v>
+        <v>7.129314335517792</v>
       </c>
       <c r="CB39" t="n">
-        <v>13.22487800099958</v>
+        <v>13.2248780923855</v>
       </c>
       <c r="CC39" t="n">
         <v>5.700250753950201</v>
@@ -25257,7 +25257,7 @@
         <v>5.504458217875779</v>
       </c>
       <c r="CI39" t="n">
-        <v>7.42796296784184</v>
+        <v>7.427962985423161</v>
       </c>
       <c r="CJ39" t="n">
         <v>5.916792043641768</v>
@@ -25278,7 +25278,7 @@
         <v>-11.39579639802557</v>
       </c>
       <c r="CP39" t="n">
-        <v>23.59338910081565</v>
+        <v>23.59338939335012</v>
       </c>
       <c r="CQ39" t="inlineStr">
         <is>
@@ -25550,10 +25550,10 @@
         <v>14.96000003814697</v>
       </c>
       <c r="CA40" t="n">
-        <v>9.298791796674807</v>
+        <v>9.298791826816277</v>
       </c>
       <c r="CB40" t="n">
-        <v>17.24925878283177</v>
+        <v>17.24925883874419</v>
       </c>
       <c r="CC40" t="n">
         <v>30.82737177378653</v>
@@ -25562,23 +25562,23 @@
         <v>29.3357145487105</v>
       </c>
       <c r="CE40" t="n">
-        <v>34.72610762496628</v>
+        <v>34.72610763096726</v>
       </c>
       <c r="CF40" t="n">
-        <v>25.49561712208956</v>
+        <v>25.49561711593838</v>
       </c>
       <c r="CG40" t="n">
-        <v>15.31698429157356</v>
+        <v>15.31698425409445</v>
       </c>
       <c r="CH40" t="inlineStr"/>
       <c r="CI40" t="n">
-        <v>20.71775986884566</v>
+        <v>20.71775988882134</v>
       </c>
       <c r="CJ40" t="n">
-        <v>21.37243795246066</v>
+        <v>21.37243797734128</v>
       </c>
       <c r="CK40" t="n">
-        <v>19.2351941572146</v>
+        <v>19.23519417960716</v>
       </c>
       <c r="CL40" t="n">
         <v>4</v>
@@ -25590,10 +25590,10 @@
         <v>3.3</v>
       </c>
       <c r="CO40" t="n">
-        <v>28.57750072303591</v>
+        <v>28.5775008727188</v>
       </c>
       <c r="CP40" t="n">
-        <v>38.48769930492513</v>
+        <v>38.48769943845238</v>
       </c>
       <c r="CQ40" t="inlineStr">
         <is>
@@ -25632,7 +25632,7 @@
         <v>-5.015872773670016</v>
       </c>
       <c r="DC40" t="n">
-        <v>-17.75793314155376</v>
+        <v>-17.75794205146741</v>
       </c>
       <c r="DD40" t="b">
         <v>1</v>
@@ -25881,10 +25881,10 @@
         <v>12.75</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.570253746011598</v>
+        <v>1.570253759332672</v>
       </c>
       <c r="CB41" t="n">
-        <v>2.912820698851514</v>
+        <v>2.912820723562107</v>
       </c>
       <c r="CC41" t="n">
         <v>12.56040892193308</v>
@@ -25893,7 +25893,7 @@
         <v>9.175696506445684</v>
       </c>
       <c r="CE41" t="n">
-        <v>15.85379572075557</v>
+        <v>15.85379573462137</v>
       </c>
       <c r="CF41" t="n">
         <v>6.104046666666666</v>
@@ -25951,7 +25951,7 @@
         <v>-14.19919048066149</v>
       </c>
       <c r="DC41" t="n">
-        <v>-29.85972104196217</v>
+        <v>-29.85973582521294</v>
       </c>
       <c r="DD41" t="b">
         <v>0</v>
@@ -26200,37 +26200,37 @@
         <v>26.64999961853027</v>
       </c>
       <c r="CA42" t="n">
-        <v>17.04026343140696</v>
+        <v>17.04026358136929</v>
       </c>
       <c r="CB42" t="n">
-        <v>28.24459566395387</v>
+        <v>28.24459568212314</v>
       </c>
       <c r="CC42" t="n">
-        <v>47.30449332245774</v>
+        <v>47.30449293658613</v>
       </c>
       <c r="CD42" t="n">
         <v>53.09041087001181</v>
       </c>
       <c r="CE42" t="n">
-        <v>56.22805797747338</v>
+        <v>56.22805802539393</v>
       </c>
       <c r="CF42" t="n">
-        <v>42.93955285992938</v>
+        <v>42.93955283264891</v>
       </c>
       <c r="CG42" t="n">
-        <v>23.53514266469771</v>
+        <v>23.53514249696784</v>
       </c>
       <c r="CH42" t="n">
         <v>30.99183173163939</v>
       </c>
       <c r="CI42" t="n">
-        <v>37.42179356519628</v>
+        <v>37.42179351959255</v>
       </c>
       <c r="CJ42" t="n">
-        <v>36.96569229578439</v>
+        <v>36.96569228214415</v>
       </c>
       <c r="CK42" t="n">
-        <v>33.26912306620595</v>
+        <v>33.26912305392973</v>
       </c>
       <c r="CL42" t="n">
         <v>8</v>
@@ -26242,10 +26242,10 @@
         <v>3.3</v>
       </c>
       <c r="CO42" t="n">
-        <v>24.8372365569314</v>
+        <v>24.83723651086678</v>
       </c>
       <c r="CP42" t="n">
-        <v>40.41949005949015</v>
+        <v>40.41948988836923</v>
       </c>
       <c r="CQ42" t="inlineStr">
         <is>
@@ -26533,37 +26533,37 @@
         <v>15.11999988555908</v>
       </c>
       <c r="CA43" t="n">
-        <v>5.865830787236021</v>
+        <v>5.865830805980611</v>
       </c>
       <c r="CB43" t="n">
-        <v>8.474845215612692</v>
+        <v>8.474845200009646</v>
       </c>
       <c r="CC43" t="n">
-        <v>10.77599632720064</v>
+        <v>10.77599627292565</v>
       </c>
       <c r="CD43" t="n">
         <v>11.55627711976371</v>
       </c>
       <c r="CE43" t="n">
-        <v>9.774262772991017</v>
+        <v>9.774262742828176</v>
       </c>
       <c r="CF43" t="n">
-        <v>14.9164232401739</v>
+        <v>14.916423233537</v>
       </c>
       <c r="CG43" t="n">
-        <v>5.368455516564914</v>
+        <v>5.368455486213674</v>
       </c>
       <c r="CH43" t="n">
         <v>10.8369287109083</v>
       </c>
       <c r="CI43" t="n">
-        <v>9.6961274613064</v>
+        <v>9.696127446520844</v>
       </c>
       <c r="CJ43" t="n">
-        <v>10.27512955009583</v>
+        <v>10.27512950787691</v>
       </c>
       <c r="CK43" t="n">
-        <v>9.247616595086248</v>
+        <v>9.247616557089222</v>
       </c>
       <c r="CL43" t="n">
         <v>8</v>
@@ -26575,10 +26575,10 @@
         <v>2.8</v>
       </c>
       <c r="CO43" t="n">
-        <v>-38.83851411984119</v>
+        <v>-38.83851437114426</v>
       </c>
       <c r="CP43" t="n">
-        <v>-35.87217238958416</v>
+        <v>-35.87217248737223</v>
       </c>
       <c r="CQ43" t="inlineStr">
         <is>
@@ -26866,10 +26866,10 @@
         <v>11.77000045776367</v>
       </c>
       <c r="CA44" t="n">
-        <v>4.784269071605902</v>
+        <v>4.784269049165137</v>
       </c>
       <c r="CB44" t="n">
-        <v>8.874819127828946</v>
+        <v>8.874819086201329</v>
       </c>
       <c r="CC44" t="n">
         <v>25.44086558978281</v>
@@ -26878,25 +26878,25 @@
         <v>28.63793221437547</v>
       </c>
       <c r="CE44" t="n">
-        <v>23.61676925263853</v>
+        <v>23.61676923327552</v>
       </c>
       <c r="CF44" t="n">
-        <v>14.24977379771474</v>
+        <v>14.24977379993462</v>
       </c>
       <c r="CG44" t="n">
-        <v>13.10602502986306</v>
+        <v>13.10602504990715</v>
       </c>
       <c r="CH44" t="n">
         <v>4.870861694358507</v>
       </c>
       <c r="CI44" t="n">
-        <v>18.98769750203393</v>
+        <v>18.98769749557948</v>
       </c>
       <c r="CJ44" t="n">
-        <v>18.93327152517664</v>
+        <v>18.93327151660507</v>
       </c>
       <c r="CK44" t="n">
-        <v>17.03994437265897</v>
+        <v>17.03994436494456</v>
       </c>
       <c r="CL44" t="n">
         <v>6</v>
@@ -26908,10 +26908,10 @@
         <v>6</v>
       </c>
       <c r="CO44" t="n">
-        <v>44.77437306656318</v>
+        <v>44.77437300102017</v>
       </c>
       <c r="CP44" t="n">
-        <v>61.32282721798327</v>
+        <v>61.32282716314516</v>
       </c>
       <c r="CQ44" t="inlineStr">
         <is>
@@ -27195,10 +27195,10 @@
         <v>9.069999694824219</v>
       </c>
       <c r="CA45" t="n">
-        <v>2.472824447569588</v>
+        <v>2.472824451553216</v>
       </c>
       <c r="CB45" t="n">
-        <v>4.587089350241586</v>
+        <v>4.587089357631216</v>
       </c>
       <c r="CC45" t="n">
         <v>13.23540704365869</v>
@@ -27207,19 +27207,19 @@
         <v>14.96700525293176</v>
       </c>
       <c r="CE45" t="n">
-        <v>10.35281120504992</v>
+        <v>10.35281120560385</v>
       </c>
       <c r="CF45" t="n">
-        <v>7.309831174710438</v>
+        <v>7.309831174326628</v>
       </c>
       <c r="CG45" t="n">
-        <v>6.779397759393971</v>
+        <v>6.779397755881368</v>
       </c>
       <c r="CH45" t="n">
         <v>10.12863973392969</v>
       </c>
       <c r="CI45" t="n">
-        <v>9.622883074273725</v>
+        <v>9.622883074851885</v>
       </c>
       <c r="CJ45" t="n">
         <v>10.12863973392969</v>
@@ -27240,7 +27240,7 @@
         <v>0.5046975441313828</v>
       </c>
       <c r="CP45" t="n">
-        <v>6.095737574996929</v>
+        <v>6.095737581371341</v>
       </c>
       <c r="CQ45" t="inlineStr">
         <is>
@@ -27524,37 +27524,37 @@
         <v>38.70000076293945</v>
       </c>
       <c r="CA46" t="n">
-        <v>30.84756125820635</v>
+        <v>30.84756156679863</v>
       </c>
       <c r="CB46" t="n">
-        <v>35.74245458360979</v>
+        <v>35.74245434017883</v>
       </c>
       <c r="CC46" t="n">
-        <v>39.0600346478168</v>
+        <v>39.06003399104274</v>
       </c>
       <c r="CD46" t="n">
         <v>49.9060657389037</v>
       </c>
       <c r="CE46" t="n">
-        <v>60.73976176178693</v>
+        <v>60.739761418545</v>
       </c>
       <c r="CF46" t="n">
-        <v>16.6127311962797</v>
+        <v>16.61273116616696</v>
       </c>
       <c r="CG46" t="n">
-        <v>17.68241890464684</v>
+        <v>17.68241835772257</v>
       </c>
       <c r="CH46" t="n">
         <v>28.82212409504474</v>
       </c>
       <c r="CI46" t="n">
-        <v>34.92664402328685</v>
+        <v>34.9266438343004</v>
       </c>
       <c r="CJ46" t="n">
-        <v>33.29500792090807</v>
+        <v>33.29500795348874</v>
       </c>
       <c r="CK46" t="n">
-        <v>29.96550712881726</v>
+        <v>29.96550715813986</v>
       </c>
       <c r="CL46" t="n">
         <v>8</v>
@@ -27566,10 +27566,10 @@
         <v>3.7</v>
       </c>
       <c r="CO46" t="n">
-        <v>-22.56975054761927</v>
+        <v>-22.56975047185029</v>
       </c>
       <c r="CP46" t="n">
-        <v>-9.750275620836945</v>
+        <v>-9.750276109174028</v>
       </c>
       <c r="CQ46" t="inlineStr">
         <is>
@@ -27857,10 +27857,10 @@
         <v>33.34999847412109</v>
       </c>
       <c r="CA47" t="n">
-        <v>14.44287256759654</v>
+        <v>14.44287259822253</v>
       </c>
       <c r="CB47" t="n">
-        <v>26.79152861289158</v>
+        <v>26.79152866970278</v>
       </c>
       <c r="CC47" t="n">
         <v>55.86440958054417</v>
@@ -27869,25 +27869,25 @@
         <v>43.13942726989067</v>
       </c>
       <c r="CE47" t="n">
-        <v>72.71552797431916</v>
+        <v>72.71552793638311</v>
       </c>
       <c r="CF47" t="n">
-        <v>38.50512723627332</v>
+        <v>38.50512722870478</v>
       </c>
       <c r="CG47" t="n">
-        <v>40.90220799928341</v>
+        <v>40.90220794136599</v>
       </c>
       <c r="CH47" t="n">
         <v>21.66331906695809</v>
       </c>
       <c r="CI47" t="n">
-        <v>42.79736396288006</v>
+        <v>42.79736395622137</v>
       </c>
       <c r="CJ47" t="n">
-        <v>40.90220799928341</v>
+        <v>40.90220794136599</v>
       </c>
       <c r="CK47" t="n">
-        <v>36.81198719935507</v>
+        <v>36.8119871472294</v>
       </c>
       <c r="CL47" t="n">
         <v>7</v>
@@ -27899,10 +27899,10 @@
         <v>5</v>
       </c>
       <c r="CO47" t="n">
-        <v>10.38077626276477</v>
+        <v>10.38077610646588</v>
       </c>
       <c r="CP47" t="n">
-        <v>28.32793379612873</v>
+        <v>28.32793377616263</v>
       </c>
       <c r="CQ47" t="inlineStr">
         <is>
@@ -28184,10 +28184,10 @@
         <v>6.570000171661377</v>
       </c>
       <c r="CA48" t="n">
-        <v>7.812280645065718</v>
+        <v>7.81228064065644</v>
       </c>
       <c r="CB48" t="n">
-        <v>11.37468061921569</v>
+        <v>11.37468061279578</v>
       </c>
       <c r="CC48" t="n">
         <v>8.114964582574622</v>
@@ -28206,7 +28206,7 @@
         <v>5.379803695646386</v>
       </c>
       <c r="CI48" t="n">
-        <v>8.397726691153572</v>
+        <v>8.397726689348707</v>
       </c>
       <c r="CJ48" t="n">
         <v>8.471557624874304</v>
@@ -28227,7 +28227,7 @@
         <v>16.04873155519062</v>
       </c>
       <c r="CP48" t="n">
-        <v>27.8192765865638</v>
+        <v>27.81927655909249</v>
       </c>
       <c r="CQ48" t="inlineStr">
         <is>
@@ -28493,35 +28493,35 @@
         <v>16.93000030517578</v>
       </c>
       <c r="CA49" t="n">
-        <v>10.07551305271984</v>
+        <v>10.07551297601118</v>
       </c>
       <c r="CB49" t="n">
-        <v>17.56141117258434</v>
+        <v>17.56141118553893</v>
       </c>
       <c r="CC49" t="n">
-        <v>28.83392700366752</v>
+        <v>28.83392724446106</v>
       </c>
       <c r="CD49" t="n">
         <v>29.26650917734455</v>
       </c>
       <c r="CE49" t="n">
-        <v>32.09024621456947</v>
+        <v>32.0902462194033</v>
       </c>
       <c r="CF49" t="n">
-        <v>27.8843817471833</v>
+        <v>27.88438176449679</v>
       </c>
       <c r="CG49" t="n">
-        <v>14.22884660747816</v>
+        <v>14.22884670286078</v>
       </c>
       <c r="CH49" t="inlineStr"/>
       <c r="CI49" t="n">
-        <v>21.08880824403875</v>
+        <v>21.08880829262699</v>
       </c>
       <c r="CJ49" t="n">
-        <v>22.72289645988382</v>
+        <v>22.72289647501785</v>
       </c>
       <c r="CK49" t="n">
-        <v>20.45060681389544</v>
+        <v>20.45060682751607</v>
       </c>
       <c r="CL49" t="n">
         <v>4</v>
@@ -28533,10 +28533,10 @@
         <v>2.9</v>
       </c>
       <c r="CO49" t="n">
-        <v>20.7950764634266</v>
+        <v>20.7950765438792</v>
       </c>
       <c r="CP49" t="n">
-        <v>24.5647245357199</v>
+        <v>24.56472482271479</v>
       </c>
       <c r="CQ49" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>-6.204980494321388</v>
       </c>
       <c r="DC49" t="n">
-        <v>-20.28805503364547</v>
+        <v>-20.28806233739286</v>
       </c>
       <c r="DD49" t="b">
         <v>1</v>
@@ -28828,10 +28828,10 @@
         <v>32.52999877929688</v>
       </c>
       <c r="CA50" t="n">
-        <v>11.0539601622437</v>
+        <v>11.05396012563881</v>
       </c>
       <c r="CB50" t="n">
-        <v>20.50509610096207</v>
+        <v>20.50509603305999</v>
       </c>
       <c r="CC50" t="n">
         <v>55.47264914101462</v>
@@ -28840,19 +28840,19 @@
         <v>52.30651498008846</v>
       </c>
       <c r="CE50" t="n">
-        <v>57.86673686310854</v>
+        <v>57.86673687084676</v>
       </c>
       <c r="CF50" t="n">
-        <v>28.13054892367068</v>
+        <v>28.13054883505714</v>
       </c>
       <c r="CG50" t="n">
-        <v>35.03833482358144</v>
+        <v>35.03833486990275</v>
       </c>
       <c r="CH50" t="n">
         <v>54.48085949640561</v>
       </c>
       <c r="CI50" t="n">
-        <v>43.40010576126163</v>
+        <v>43.40010574662504</v>
       </c>
       <c r="CJ50" t="n">
         <v>52.30651498008846</v>
@@ -28873,7 +28873,7 @@
         <v>44.71523285774048</v>
       </c>
       <c r="CP50" t="n">
-        <v>33.41563907122811</v>
+        <v>33.41563902623399</v>
       </c>
       <c r="CQ50" t="inlineStr">
         <is>
@@ -29157,37 +29157,37 @@
         <v>44.06000137329102</v>
       </c>
       <c r="CA51" t="n">
-        <v>31.96096257437985</v>
+        <v>31.96096264123675</v>
       </c>
       <c r="CB51" t="n">
-        <v>43.40679471696702</v>
+        <v>43.40679459074402</v>
       </c>
       <c r="CC51" t="n">
-        <v>49.69994250523287</v>
+        <v>49.69994225674613</v>
       </c>
       <c r="CD51" t="n">
         <v>47.301358204649</v>
       </c>
       <c r="CE51" t="n">
-        <v>69.17517562383775</v>
+        <v>69.17517548529065</v>
       </c>
       <c r="CF51" t="n">
-        <v>59.81377114128137</v>
+        <v>59.81377111333469</v>
       </c>
       <c r="CG51" t="n">
-        <v>24.46371057649108</v>
+        <v>24.46371042099262</v>
       </c>
       <c r="CH51" t="n">
         <v>76.33330481362214</v>
       </c>
       <c r="CI51" t="n">
-        <v>50.26937751955764</v>
+        <v>50.269377440827</v>
       </c>
       <c r="CJ51" t="n">
-        <v>48.50065035494093</v>
+        <v>48.50065023069757</v>
       </c>
       <c r="CK51" t="n">
-        <v>43.65058531944684</v>
+        <v>43.65058520762781</v>
       </c>
       <c r="CL51" t="n">
         <v>8</v>
@@ -29199,10 +29199,10 @@
         <v>3.1</v>
       </c>
       <c r="CO51" t="n">
-        <v>-0.9292238789905261</v>
+        <v>-0.9292241327785944</v>
       </c>
       <c r="CP51" t="n">
-        <v>14.09300034663803</v>
+        <v>14.09300016794843</v>
       </c>
       <c r="CQ51" t="inlineStr">
         <is>
@@ -29490,37 +29490,37 @@
         <v>10.65999984741211</v>
       </c>
       <c r="CA52" t="n">
-        <v>8.155913734330436</v>
+        <v>8.155913700357743</v>
       </c>
       <c r="CB52" t="n">
-        <v>11.52280745547566</v>
+        <v>11.52280744616852</v>
       </c>
       <c r="CC52" t="n">
-        <v>17.21213829351711</v>
+        <v>17.21213835131017</v>
       </c>
       <c r="CD52" t="n">
         <v>24.17460734763337</v>
       </c>
       <c r="CE52" t="n">
-        <v>24.61732007919933</v>
+        <v>24.61732005665505</v>
       </c>
       <c r="CF52" t="n">
-        <v>21.03193964128703</v>
+        <v>21.03193964765394</v>
       </c>
       <c r="CG52" t="n">
-        <v>8.546606018053332</v>
+        <v>8.546606051716193</v>
       </c>
       <c r="CH52" t="n">
         <v>9.746272614957581</v>
       </c>
       <c r="CI52" t="n">
-        <v>15.62595064805673</v>
+        <v>15.62595065205657</v>
       </c>
       <c r="CJ52" t="n">
-        <v>14.36747287449639</v>
+        <v>14.36747289873935</v>
       </c>
       <c r="CK52" t="n">
-        <v>12.93072558704675</v>
+        <v>12.93072560886541</v>
       </c>
       <c r="CL52" t="n">
         <v>8</v>
@@ -29532,10 +29532,10 @@
         <v>3</v>
       </c>
       <c r="CO52" t="n">
-        <v>21.30136746846107</v>
+        <v>21.30136767313893</v>
       </c>
       <c r="CP52" t="n">
-        <v>46.58490498806329</v>
+        <v>46.58490502558523</v>
       </c>
       <c r="CQ52" t="inlineStr">
         <is>
@@ -29809,10 +29809,10 @@
         <v>53.7400016784668</v>
       </c>
       <c r="CA53" t="n">
-        <v>10.50731955363538</v>
+        <v>10.50731958635367</v>
       </c>
       <c r="CB53" t="n">
-        <v>19.49107777199363</v>
+        <v>19.49107783268605</v>
       </c>
       <c r="CC53" t="n">
         <v>62.18821154931746</v>
@@ -29821,7 +29821,7 @@
         <v>46.54098234247379</v>
       </c>
       <c r="CE53" t="n">
-        <v>83.24912654392116</v>
+        <v>83.24912658392606</v>
       </c>
       <c r="CF53" t="n">
         <v>11.76833333333333</v>
@@ -29831,7 +29831,7 @@
       </c>
       <c r="CH53" t="inlineStr"/>
       <c r="CI53" t="n">
-        <v>13.92224355298745</v>
+        <v>13.92224358412435</v>
       </c>
       <c r="CJ53" t="n">
         <v>11.76833333333333</v>
@@ -29852,7 +29852,7 @@
         <v>-80.29121758616556</v>
       </c>
       <c r="CP53" t="n">
-        <v>-74.09333249320314</v>
+        <v>-74.09333243526324</v>
       </c>
       <c r="CQ53" t="inlineStr">
         <is>
@@ -29971,12 +29971,12 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Bandeira de alta</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>Fundo duplo (pré-confirmação) — pescoço R$27.67, preço 6.5% acima do pescoço; falta fechar acima e segurar</t>
+          <t>Bandeira de alta (pré-confirmação) — pescoço R$29.65, preço 0.6% abaixo do pescoço; falta fechar acima e segurar</t>
         </is>
       </c>
       <c r="U54" t="b">
@@ -30130,10 +30130,10 @@
         <v>29.46999931335449</v>
       </c>
       <c r="CA54" t="n">
-        <v>15.40499609631564</v>
+        <v>15.4049961404869</v>
       </c>
       <c r="CB54" t="n">
-        <v>28.57626775866552</v>
+        <v>28.57626784060319</v>
       </c>
       <c r="CC54" t="n">
         <v>53.78477836114972</v>
@@ -30142,23 +30142,23 @@
         <v>48.59041952862963</v>
       </c>
       <c r="CE54" t="n">
-        <v>59.55728565402742</v>
+        <v>59.55728564217956</v>
       </c>
       <c r="CF54" t="n">
-        <v>36.60763963896498</v>
+        <v>36.60763963081416</v>
       </c>
       <c r="CG54" t="n">
-        <v>29.60722472567762</v>
+        <v>29.60722466468949</v>
       </c>
       <c r="CH54" t="inlineStr"/>
       <c r="CI54" t="n">
-        <v>33.59342046377397</v>
+        <v>33.59342049326349</v>
       </c>
       <c r="CJ54" t="n">
-        <v>32.59195369881525</v>
+        <v>32.59195373570867</v>
       </c>
       <c r="CK54" t="n">
-        <v>29.33275832893373</v>
+        <v>29.33275836213781</v>
       </c>
       <c r="CL54" t="n">
         <v>4</v>
@@ -30170,10 +30170,10 @@
         <v>3.5</v>
       </c>
       <c r="CO54" t="n">
-        <v>-0.4656972772936974</v>
+        <v>-0.4656971646229247</v>
       </c>
       <c r="CP54" t="n">
-        <v>13.99192822020503</v>
+        <v>13.9919283202713</v>
       </c>
       <c r="CQ54" t="inlineStr">
         <is>
@@ -30463,10 +30463,10 @@
         <v>10.39999961853027</v>
       </c>
       <c r="CA55" t="n">
-        <v>12.95046613209858</v>
+        <v>12.95046604910022</v>
       </c>
       <c r="CB55" t="n">
-        <v>18.85587868833553</v>
+        <v>18.85587856748992</v>
       </c>
       <c r="CC55" t="n">
         <v>16.51297649354425</v>
@@ -30485,7 +30485,7 @@
         <v>14.71449508364002</v>
       </c>
       <c r="CI55" t="n">
-        <v>16.0256887432667</v>
+        <v>16.0256887092927</v>
       </c>
       <c r="CJ55" t="n">
         <v>15.61373578859213</v>
@@ -30506,7 +30506,7 @@
         <v>35.11887235740878</v>
       </c>
       <c r="CP55" t="n">
-        <v>54.09316664505266</v>
+        <v>54.09316631837959</v>
       </c>
       <c r="CQ55" t="inlineStr">
         <is>
@@ -30794,10 +30794,10 @@
         <v>33.16999816894531</v>
       </c>
       <c r="CA56" t="n">
-        <v>11.72159151149348</v>
+        <v>11.72159147728659</v>
       </c>
       <c r="CB56" t="n">
-        <v>21.74355225382041</v>
+        <v>21.74355219036662</v>
       </c>
       <c r="CC56" t="n">
         <v>40.50714062106224</v>
@@ -30806,25 +30806,25 @@
         <v>33.04065851780371</v>
       </c>
       <c r="CE56" t="n">
-        <v>42.38494183625834</v>
+        <v>42.38494188430799</v>
       </c>
       <c r="CF56" t="n">
-        <v>23.85594021977225</v>
+        <v>23.85594022637702</v>
       </c>
       <c r="CG56" t="n">
-        <v>25.30198883363071</v>
+        <v>25.30198889157718</v>
       </c>
       <c r="CH56" t="n">
         <v>26.88952120736854</v>
       </c>
       <c r="CI56" t="n">
-        <v>28.18066687515121</v>
+        <v>28.18066687701874</v>
       </c>
       <c r="CJ56" t="n">
-        <v>26.09575502049962</v>
+        <v>26.09575504947286</v>
       </c>
       <c r="CK56" t="n">
-        <v>23.48617951844966</v>
+        <v>23.48617954452557</v>
       </c>
       <c r="CL56" t="n">
         <v>8</v>
@@ -30836,10 +30836,10 @@
         <v>3.6</v>
       </c>
       <c r="CO56" t="n">
-        <v>-29.19451065741062</v>
+        <v>-29.19451057879769</v>
       </c>
       <c r="CP56" t="n">
-        <v>-15.04169903290876</v>
+        <v>-15.0416990272786</v>
       </c>
       <c r="CQ56" t="inlineStr">
         <is>
@@ -31119,10 +31119,10 @@
         <v>24.18000030517578</v>
       </c>
       <c r="CA57" t="n">
-        <v>4.240146146784672</v>
+        <v>4.240146154692025</v>
       </c>
       <c r="CB57" t="n">
-        <v>7.865471102285565</v>
+        <v>7.865471116953705</v>
       </c>
       <c r="CC57" t="n">
         <v>28.58028582012302</v>
@@ -31131,13 +31131,13 @@
         <v>28.44859048200662</v>
       </c>
       <c r="CE57" t="n">
-        <v>25.50998699914107</v>
+        <v>25.50998699470256</v>
       </c>
       <c r="CF57" t="n">
-        <v>2.971261370080653</v>
+        <v>2.971261369900375</v>
       </c>
       <c r="CG57" t="n">
-        <v>18.4685561591753</v>
+        <v>18.468556150178</v>
       </c>
       <c r="CH57" t="n">
         <v>17.91045698312367</v>
@@ -31446,10 +31446,10 @@
         <v>50.25</v>
       </c>
       <c r="CA58" t="n">
-        <v>8.363274355972894</v>
+        <v>8.363274420658357</v>
       </c>
       <c r="CB58" t="n">
-        <v>15.51387393032972</v>
+        <v>15.51387405032125</v>
       </c>
       <c r="CC58" t="n">
         <v>19.85129695885509</v>
@@ -31458,25 +31458,25 @@
         <v>12.34222338033302</v>
       </c>
       <c r="CE58" t="n">
-        <v>14.34594636965315</v>
+        <v>14.34594609635785</v>
       </c>
       <c r="CF58" t="n">
-        <v>20.65459860509735</v>
+        <v>20.65459856649491</v>
       </c>
       <c r="CG58" t="n">
-        <v>10.82551614754239</v>
+        <v>10.82551595878504</v>
       </c>
       <c r="CH58" t="n">
         <v>13.23570535215743</v>
       </c>
       <c r="CI58" t="n">
-        <v>14.39155438749263</v>
+        <v>14.39155434799537</v>
       </c>
       <c r="CJ58" t="n">
-        <v>13.79082586090529</v>
+        <v>13.79082572425764</v>
       </c>
       <c r="CK58" t="n">
-        <v>12.41174327481476</v>
+        <v>12.41174315183188</v>
       </c>
       <c r="CL58" t="n">
         <v>8</v>
@@ -31488,10 +31488,10 @@
         <v>2.5</v>
       </c>
       <c r="CO58" t="n">
-        <v>-75.30001338345321</v>
+        <v>-75.30001362819526</v>
       </c>
       <c r="CP58" t="n">
-        <v>-71.36009077115895</v>
+        <v>-71.36009084976045</v>
       </c>
       <c r="CQ58" t="inlineStr">
         <is>
@@ -31793,10 +31793,10 @@
         <v>4.760000228881836</v>
       </c>
       <c r="CA59" t="n">
-        <v>1.10125696998279</v>
+        <v>1.10125696805712</v>
       </c>
       <c r="CB59" t="n">
-        <v>2.042831679318076</v>
+        <v>2.042831675745957</v>
       </c>
       <c r="CC59" t="n">
         <v>9.302360329304472</v>
@@ -31805,13 +31805,13 @@
         <v>8.759319099989012</v>
       </c>
       <c r="CE59" t="n">
-        <v>10.22932956639293</v>
+        <v>10.22932956633112</v>
       </c>
       <c r="CF59" t="n">
-        <v>4.217909909997017</v>
+        <v>4.217909910208259</v>
       </c>
       <c r="CG59" t="n">
-        <v>6.876020534213742</v>
+        <v>6.876020536674287</v>
       </c>
       <c r="CH59" t="n">
         <v>6.539351670742607</v>
@@ -31863,7 +31863,7 @@
         <v>2.586214781232954</v>
       </c>
       <c r="DC59" t="n">
-        <v>-34.27075641632828</v>
+        <v>-34.27075202300205</v>
       </c>
       <c r="DD59" t="b">
         <v>0</v>
@@ -32112,37 +32112,37 @@
         <v>24.3700008392334</v>
       </c>
       <c r="CA60" t="n">
-        <v>10.76553943353114</v>
+        <v>10.76553941748</v>
       </c>
       <c r="CB60" t="n">
-        <v>14.15877733084953</v>
+        <v>14.15877733942185</v>
       </c>
       <c r="CC60" t="n">
-        <v>17.23929054560065</v>
+        <v>17.23929058174138</v>
       </c>
       <c r="CD60" t="n">
         <v>21.14737695048065</v>
       </c>
       <c r="CE60" t="n">
-        <v>16.91392917821632</v>
+        <v>16.91392919942924</v>
       </c>
       <c r="CF60" t="n">
-        <v>23.15616101947027</v>
+        <v>23.15616102414064</v>
       </c>
       <c r="CG60" t="n">
-        <v>8.400134426954418</v>
+        <v>8.400134450924549</v>
       </c>
       <c r="CH60" t="n">
         <v>18.63306280322801</v>
       </c>
       <c r="CI60" t="n">
-        <v>16.30178396104137</v>
+        <v>16.30178397085579</v>
       </c>
       <c r="CJ60" t="n">
-        <v>17.07660986190849</v>
+        <v>17.07660989058531</v>
       </c>
       <c r="CK60" t="n">
-        <v>15.36894887571764</v>
+        <v>15.36894890152678</v>
       </c>
       <c r="CL60" t="n">
         <v>8</v>
@@ -32154,10 +32154,10 @@
         <v>2.8</v>
       </c>
       <c r="CO60" t="n">
-        <v>-36.93496780281155</v>
+        <v>-36.93496769690617</v>
       </c>
       <c r="CP60" t="n">
-        <v>-33.10716701003538</v>
+        <v>-33.10716696976286</v>
       </c>
       <c r="CQ60" t="inlineStr">
         <is>
@@ -32441,10 +32441,10 @@
         <v>4.409999847412109</v>
       </c>
       <c r="CA61" t="n">
-        <v>2.864148128039998</v>
+        <v>2.864148113397083</v>
       </c>
       <c r="CB61" t="n">
-        <v>5.312994777514196</v>
+        <v>5.312994750351589</v>
       </c>
       <c r="CC61" t="n">
         <v>13.62062889934975</v>
@@ -32453,13 +32453,13 @@
         <v>15.2256151851382</v>
       </c>
       <c r="CE61" t="n">
-        <v>15.79234044395151</v>
+        <v>15.79234041723986</v>
       </c>
       <c r="CF61" t="n">
-        <v>9.476368784790324</v>
+        <v>9.476368786618419</v>
       </c>
       <c r="CG61" t="n">
-        <v>6.797592097215164</v>
+        <v>6.797592110461729</v>
       </c>
       <c r="CH61" t="n">
         <v>1.534123064462555</v>
@@ -32760,37 +32760,37 @@
         <v>29.38999938964844</v>
       </c>
       <c r="CA62" t="n">
-        <v>13.71649366433329</v>
+        <v>13.71649361441833</v>
       </c>
       <c r="CB62" t="n">
-        <v>14.34579127273152</v>
+        <v>14.34579126234659</v>
       </c>
       <c r="CC62" t="n">
-        <v>15.1629736397064</v>
+        <v>15.16297368390866</v>
       </c>
       <c r="CD62" t="n">
         <v>30.32006495022776</v>
       </c>
       <c r="CE62" t="n">
-        <v>14.36114238987925</v>
+        <v>14.36114241184928</v>
       </c>
       <c r="CF62" t="n">
-        <v>30.46947462497202</v>
+        <v>30.46947463545809</v>
       </c>
       <c r="CG62" t="n">
-        <v>6.113201290523697</v>
+        <v>6.113201334668482</v>
       </c>
       <c r="CH62" t="n">
         <v>37.5668789909021</v>
       </c>
       <c r="CI62" t="n">
-        <v>17.78416311891056</v>
+        <v>17.78416312755389</v>
       </c>
       <c r="CJ62" t="n">
-        <v>14.36114238987925</v>
+        <v>14.36114241184928</v>
       </c>
       <c r="CK62" t="n">
-        <v>12.92502815089133</v>
+        <v>12.92502817066435</v>
       </c>
       <c r="CL62" t="n">
         <v>7</v>
@@ -32802,10 +32802,10 @@
         <v>6.1</v>
       </c>
       <c r="CO62" t="n">
-        <v>-56.02235992068888</v>
+        <v>-56.02235985341082</v>
       </c>
       <c r="CP62" t="n">
-        <v>-39.48906604886018</v>
+        <v>-39.48906601945112</v>
       </c>
       <c r="CQ62" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>-5.487098157636739</v>
       </c>
       <c r="DC62" t="n">
-        <v>-28.45092417641193</v>
+        <v>-28.45091748718991</v>
       </c>
       <c r="DD62" t="b">
         <v>0</v>
@@ -33097,35 +33097,35 @@
         <v>3.430000066757202</v>
       </c>
       <c r="CA63" t="n">
-        <v>2.632869213008068</v>
+        <v>2.632869211411867</v>
       </c>
       <c r="CB63" t="n">
-        <v>3.088140474957044</v>
+        <v>3.08814047442369</v>
       </c>
       <c r="CC63" t="n">
-        <v>3.82134293203847</v>
+        <v>3.821342933695207</v>
       </c>
       <c r="CD63" t="n">
         <v>6.992141669127824</v>
       </c>
       <c r="CE63" t="n">
-        <v>5.742640636304274</v>
+        <v>5.742640635480152</v>
       </c>
       <c r="CF63" t="n">
-        <v>8.486989516030206</v>
+        <v>8.486989516422565</v>
       </c>
       <c r="CG63" t="n">
-        <v>1.747126730643968</v>
+        <v>1.747126731993843</v>
       </c>
       <c r="CH63" t="inlineStr"/>
       <c r="CI63" t="n">
-        <v>4.64446445315855</v>
+        <v>4.644464453222163</v>
       </c>
       <c r="CJ63" t="n">
-        <v>3.82134293203847</v>
+        <v>3.821342933695207</v>
       </c>
       <c r="CK63" t="n">
-        <v>3.439208638834623</v>
+        <v>3.439208640325686</v>
       </c>
       <c r="CL63" t="n">
         <v>7</v>
@@ -33137,10 +33137,10 @@
         <v>4.9</v>
       </c>
       <c r="CO63" t="n">
-        <v>0.2684714839124469</v>
+        <v>0.2684715273836735</v>
       </c>
       <c r="CP63" t="n">
-        <v>35.40712427884962</v>
+        <v>35.40712428070422</v>
       </c>
       <c r="CQ63" t="inlineStr">
         <is>
@@ -33440,37 +33440,37 @@
         <v>18.73999977111816</v>
       </c>
       <c r="CA64" t="n">
-        <v>8.791279506096567</v>
+        <v>8.791279524812904</v>
       </c>
       <c r="CB64" t="n">
-        <v>9.149669700004923</v>
+        <v>9.149669699019631</v>
       </c>
       <c r="CC64" t="n">
-        <v>9.503003816599623</v>
+        <v>9.503003795344707</v>
       </c>
       <c r="CD64" t="n">
         <v>16.79875791329259</v>
       </c>
       <c r="CE64" t="n">
-        <v>9.013371306400025</v>
+        <v>9.01337129021001</v>
       </c>
       <c r="CF64" t="n">
-        <v>17.5186208391091</v>
+        <v>17.51862083446328</v>
       </c>
       <c r="CG64" t="n">
-        <v>3.803290595326335</v>
+        <v>3.803290573914844</v>
       </c>
       <c r="CH64" t="n">
         <v>16.19033501601518</v>
       </c>
       <c r="CI64" t="n">
-        <v>11.34604108660554</v>
+        <v>11.34604108088414</v>
       </c>
       <c r="CJ64" t="n">
-        <v>9.326336758302272</v>
+        <v>9.326336747182168</v>
       </c>
       <c r="CK64" t="n">
-        <v>8.393703082472046</v>
+        <v>8.393703072463952</v>
       </c>
       <c r="CL64" t="n">
         <v>8</v>
@@ -33482,10 +33482,10 @@
         <v>4.6</v>
       </c>
       <c r="CO64" t="n">
-        <v>-55.20969485064611</v>
+        <v>-55.2096949040511</v>
       </c>
       <c r="CP64" t="n">
-        <v>-39.45548972688939</v>
+        <v>-39.45548975741979</v>
       </c>
       <c r="CQ64" t="inlineStr">
         <is>
@@ -33773,10 +33773,10 @@
         <v>8.199999809265137</v>
       </c>
       <c r="CA65" t="n">
-        <v>0.4878164973801171</v>
+        <v>0.4878164979387967</v>
       </c>
       <c r="CB65" t="n">
-        <v>0.9048996026401172</v>
+        <v>0.904899603676468</v>
       </c>
       <c r="CC65" t="n">
         <v>9.48908274871293</v>
@@ -33785,13 +33785,13 @@
         <v>8.714204226367567</v>
       </c>
       <c r="CE65" t="n">
-        <v>10.45045124150449</v>
+        <v>10.45045124099794</v>
       </c>
       <c r="CF65" t="n">
-        <v>0.736098748070976</v>
+        <v>0.7360987480602271</v>
       </c>
       <c r="CG65" t="n">
-        <v>8.107102105323007</v>
+        <v>8.107102104575226</v>
       </c>
       <c r="CH65" t="inlineStr"/>
       <c r="CI65" t="inlineStr"/>
@@ -34098,10 +34098,10 @@
         <v>35.31000137329102</v>
       </c>
       <c r="CA66" t="n">
-        <v>10.10979899599965</v>
+        <v>10.10979899813031</v>
       </c>
       <c r="CB66" t="n">
-        <v>18.75367713757934</v>
+        <v>18.75367714153173</v>
       </c>
       <c r="CC66" t="n">
         <v>28.42390754532843</v>
@@ -34110,25 +34110,25 @@
         <v>21.09476497433801</v>
       </c>
       <c r="CE66" t="n">
-        <v>25.57467277826903</v>
+        <v>25.57467277314297</v>
       </c>
       <c r="CF66" t="n">
-        <v>22.87196697739428</v>
+        <v>22.87196697670876</v>
       </c>
       <c r="CG66" t="n">
-        <v>16.40126287814893</v>
+        <v>16.40126287378772</v>
       </c>
       <c r="CH66" t="n">
         <v>26.23735511627599</v>
       </c>
       <c r="CI66" t="n">
-        <v>21.18342580041671</v>
+        <v>21.18342579990549</v>
       </c>
       <c r="CJ66" t="n">
-        <v>21.98336597586614</v>
+        <v>21.98336597552338</v>
       </c>
       <c r="CK66" t="n">
-        <v>19.78502937827953</v>
+        <v>19.78502937797105</v>
       </c>
       <c r="CL66" t="n">
         <v>8</v>
@@ -34140,10 +34140,10 @@
         <v>2.8</v>
       </c>
       <c r="CO66" t="n">
-        <v>-43.96763350667779</v>
+        <v>-43.96763350755143</v>
       </c>
       <c r="CP66" t="n">
-        <v>-40.00729261811882</v>
+        <v>-40.00729261956661</v>
       </c>
       <c r="CQ66" t="inlineStr">
         <is>
@@ -34433,25 +34433,25 @@
         <v>2.230000019073486</v>
       </c>
       <c r="CA67" t="n">
-        <v>0.6400794702570614</v>
+        <v>0.6400794708725257</v>
       </c>
       <c r="CB67" t="n">
-        <v>0.9077006535035311</v>
+        <v>0.9077006542496393</v>
       </c>
       <c r="CC67" t="n">
-        <v>3.427679180657432</v>
+        <v>3.427679180179039</v>
       </c>
       <c r="CD67" t="n">
         <v>7.066656151822504</v>
       </c>
       <c r="CE67" t="n">
-        <v>2.631072379309566</v>
+        <v>2.631072380176775</v>
       </c>
       <c r="CF67" t="n">
-        <v>2.231186133897674</v>
+        <v>2.231186133869693</v>
       </c>
       <c r="CG67" t="n">
-        <v>1.703071313663547</v>
+        <v>1.703071313386785</v>
       </c>
       <c r="CH67" t="n">
         <v>7.171516514635575</v>
@@ -34730,10 +34730,10 @@
         <v>12.86999988555908</v>
       </c>
       <c r="CA68" t="n">
-        <v>10.88409499738454</v>
+        <v>10.88409501666247</v>
       </c>
       <c r="CB68" t="n">
-        <v>15.84724231619188</v>
+        <v>15.84724234426056</v>
       </c>
       <c r="CC68" t="n">
         <v>15.47375708783982</v>
@@ -34750,13 +34750,13 @@
       </c>
       <c r="CH68" t="inlineStr"/>
       <c r="CI68" t="n">
-        <v>12.38460693368739</v>
+        <v>12.38460694552405</v>
       </c>
       <c r="CJ68" t="n">
-        <v>13.17892604261218</v>
+        <v>13.17892605225115</v>
       </c>
       <c r="CK68" t="n">
-        <v>11.86103343835096</v>
+        <v>11.86103344702603</v>
       </c>
       <c r="CL68" t="n">
         <v>4</v>
@@ -34768,10 +34768,10 @@
         <v>2.2</v>
       </c>
       <c r="CO68" t="n">
-        <v>-7.839677204195183</v>
+        <v>-7.839677136789813</v>
       </c>
       <c r="CP68" t="n">
-        <v>-3.771507041086519</v>
+        <v>-3.771506949115622</v>
       </c>
       <c r="CQ68" t="inlineStr">
         <is>
@@ -35055,10 +35055,10 @@
         <v>8.329999923706055</v>
       </c>
       <c r="CA69" t="n">
-        <v>1.604458792248442</v>
+        <v>1.604458791774183</v>
       </c>
       <c r="CB69" t="n">
-        <v>2.976271059620859</v>
+        <v>2.97627105874111</v>
       </c>
       <c r="CC69" t="n">
         <v>24.04629607605778</v>
@@ -35067,13 +35067,13 @@
         <v>23.80972001921325</v>
       </c>
       <c r="CE69" t="n">
-        <v>25.6775648083308</v>
+        <v>25.67756480775206</v>
       </c>
       <c r="CF69" t="n">
-        <v>6.709198121092105</v>
+        <v>6.709198121120889</v>
       </c>
       <c r="CG69" t="n">
-        <v>17.91224512417828</v>
+        <v>17.91224512472375</v>
       </c>
       <c r="CH69" t="n">
         <v>14.80472650453005</v>
@@ -35382,10 +35382,10 @@
         <v>21.25</v>
       </c>
       <c r="CA70" t="n">
-        <v>5.876551492718586</v>
+        <v>5.876551498223663</v>
       </c>
       <c r="CB70" t="n">
-        <v>10.90100301899298</v>
+        <v>10.90100302920489</v>
       </c>
       <c r="CC70" t="n">
         <v>32.70180023228804</v>
@@ -35394,25 +35394,25 @@
         <v>33.68464293302805</v>
       </c>
       <c r="CE70" t="n">
-        <v>29.46402083034288</v>
+        <v>29.46402082996862</v>
       </c>
       <c r="CF70" t="n">
-        <v>25.30919493824348</v>
+        <v>25.30919493735855</v>
       </c>
       <c r="CG70" t="n">
-        <v>19.10725722889073</v>
+        <v>19.10725722302893</v>
       </c>
       <c r="CH70" t="n">
         <v>13.22580990542387</v>
       </c>
       <c r="CI70" t="n">
-        <v>23.48481844103</v>
+        <v>23.48481844147156</v>
       </c>
       <c r="CJ70" t="n">
-        <v>25.30919493824348</v>
+        <v>25.30919493735855</v>
       </c>
       <c r="CK70" t="n">
-        <v>22.77827544441913</v>
+        <v>22.77827544362269</v>
       </c>
       <c r="CL70" t="n">
         <v>7</v>
@@ -35424,10 +35424,10 @@
         <v>5.7</v>
       </c>
       <c r="CO70" t="n">
-        <v>7.191884444325325</v>
+        <v>7.19188444057739</v>
       </c>
       <c r="CP70" t="n">
-        <v>10.5167926636706</v>
+        <v>10.51679266574854</v>
       </c>
       <c r="CQ70" t="inlineStr">
         <is>
@@ -35711,25 +35711,25 @@
         <v>17.14999961853027</v>
       </c>
       <c r="CA71" t="n">
-        <v>3.99182555156599</v>
+        <v>3.991825572160829</v>
       </c>
       <c r="CB71" t="n">
-        <v>6.867699811339862</v>
+        <v>6.867699836818201</v>
       </c>
       <c r="CC71" t="n">
-        <v>23.57427309545418</v>
+        <v>23.57427306128624</v>
       </c>
       <c r="CD71" t="n">
         <v>32.99378636564864</v>
       </c>
       <c r="CE71" t="n">
-        <v>16.65127103155252</v>
+        <v>16.65127104174687</v>
       </c>
       <c r="CF71" t="n">
-        <v>20.30231638007159</v>
+        <v>20.30231637785728</v>
       </c>
       <c r="CG71" t="n">
-        <v>11.66191972175137</v>
+        <v>11.66191970788693</v>
       </c>
       <c r="CH71" t="n">
         <v>22.29340682675621</v>
@@ -36030,10 +36030,10 @@
         <v>3.970000028610229</v>
       </c>
       <c r="CA72" t="n">
-        <v>0.9629806176100767</v>
+        <v>0.9629806215909222</v>
       </c>
       <c r="CB72" t="n">
-        <v>1.786329045666692</v>
+        <v>1.786329053051161</v>
       </c>
       <c r="CC72" t="n">
         <v>6.217789642917912</v>
@@ -36042,7 +36042,7 @@
         <v>4.127898727162465</v>
       </c>
       <c r="CE72" t="n">
-        <v>8.632592089325593</v>
+        <v>8.63259209591328</v>
       </c>
       <c r="CF72" t="n">
         <v>3.760485277130923</v>
@@ -36349,35 +36349,35 @@
         <v>24.02000045776367</v>
       </c>
       <c r="CA73" t="n">
-        <v>23.07830347085615</v>
+        <v>23.07830342341049</v>
       </c>
       <c r="CB73" t="n">
-        <v>28.9011396282845</v>
+        <v>28.90113961550622</v>
       </c>
       <c r="CC73" t="n">
-        <v>37.96117379809366</v>
+        <v>37.96117385935231</v>
       </c>
       <c r="CD73" t="n">
         <v>61.82732111992195</v>
       </c>
       <c r="CE73" t="n">
-        <v>67.85077927962134</v>
+        <v>67.85077923287321</v>
       </c>
       <c r="CF73" t="n">
-        <v>41.68738825980374</v>
+        <v>41.68738826656808</v>
       </c>
       <c r="CG73" t="n">
-        <v>18.10465224470297</v>
+        <v>18.10465228908553</v>
       </c>
       <c r="CH73" t="inlineStr"/>
       <c r="CI73" t="n">
-        <v>39.91582254304062</v>
+        <v>39.91582254381683</v>
       </c>
       <c r="CJ73" t="n">
-        <v>37.96117379809366</v>
+        <v>37.96117385935231</v>
       </c>
       <c r="CK73" t="n">
-        <v>34.16505641828429</v>
+        <v>34.16505647341708</v>
       </c>
       <c r="CL73" t="n">
         <v>7</v>
@@ -36389,10 +36389,10 @@
         <v>3.7</v>
       </c>
       <c r="CO73" t="n">
-        <v>42.23586913896818</v>
+        <v>42.23586936849686</v>
       </c>
       <c r="CP73" t="n">
-        <v>66.17744289067717</v>
+        <v>66.17744289390868</v>
       </c>
       <c r="CQ73" t="inlineStr">
         <is>
@@ -36680,10 +36680,10 @@
         <v>25.07999992370605</v>
       </c>
       <c r="CA74" t="n">
-        <v>4.600567039586476</v>
+        <v>4.600567046626805</v>
       </c>
       <c r="CB74" t="n">
-        <v>8.534051858432912</v>
+        <v>8.534051871492723</v>
       </c>
       <c r="CC74" t="n">
         <v>30.04611202433139</v>
@@ -36692,19 +36692,19 @@
         <v>25.48637760632342</v>
       </c>
       <c r="CE74" t="n">
-        <v>34.72272303103752</v>
+        <v>34.72272302240483</v>
       </c>
       <c r="CF74" t="n">
-        <v>11.77819857462634</v>
+        <v>11.77819857381808</v>
       </c>
       <c r="CG74" t="n">
-        <v>24.22303878219047</v>
+        <v>24.2230387711625</v>
       </c>
       <c r="CH74" t="n">
         <v>25.07999992370605</v>
       </c>
       <c r="CI74" t="n">
-        <v>25.22274165703587</v>
+        <v>25.22274165362437</v>
       </c>
       <c r="CJ74" t="n">
         <v>25.28318876501474</v>
@@ -36725,7 +36725,7 @@
         <v>-9.270853438061765</v>
       </c>
       <c r="CP74" t="n">
-        <v>0.569145668915616</v>
+        <v>0.5691456553131635</v>
       </c>
       <c r="CQ74" t="inlineStr">
         <is>
@@ -37017,10 +37017,10 @@
         <v>12.42000007629395</v>
       </c>
       <c r="CA75" t="n">
-        <v>2.054914839828541</v>
+        <v>2.05491484000739</v>
       </c>
       <c r="CB75" t="n">
-        <v>3.811867027881944</v>
+        <v>3.811867028213709</v>
       </c>
       <c r="CC75" t="n">
         <v>15.91537727378093</v>
@@ -37029,7 +37029,7 @@
         <v>12.64279048217724</v>
       </c>
       <c r="CE75" t="n">
-        <v>20.79969138317299</v>
+        <v>20.79969138341515</v>
       </c>
       <c r="CF75" t="n">
         <v>9.294207014285712</v>
@@ -37334,10 +37334,10 @@
         <v>55.20000076293945</v>
       </c>
       <c r="CA76" t="n">
-        <v>40.14526250141495</v>
+        <v>40.14526248618796</v>
       </c>
       <c r="CB76" t="n">
-        <v>58.45150220206018</v>
+        <v>58.45150217988967</v>
       </c>
       <c r="CC76" t="n">
         <v>35.6793044086122</v>
@@ -37356,13 +37356,13 @@
         <v>48.81663041531538</v>
       </c>
       <c r="CI76" t="n">
-        <v>43.24590265021568</v>
+        <v>43.24590264398276</v>
       </c>
       <c r="CJ76" t="n">
-        <v>41.3632554329257</v>
+        <v>41.3632554253122</v>
       </c>
       <c r="CK76" t="n">
-        <v>37.22692988963313</v>
+        <v>37.22692988278099</v>
       </c>
       <c r="CL76" t="n">
         <v>6</v>
@@ -37374,10 +37374,10 @@
         <v>6.4</v>
       </c>
       <c r="CO76" t="n">
-        <v>-32.55991055234406</v>
+        <v>-32.55991056475737</v>
       </c>
       <c r="CP76" t="n">
-        <v>-21.65597454257573</v>
+        <v>-21.65597455386724</v>
       </c>
       <c r="CQ76" t="inlineStr">
         <is>
@@ -37661,10 +37661,10 @@
         <v>28.85000038146973</v>
       </c>
       <c r="CA77" t="n">
-        <v>13.47749129618646</v>
+        <v>13.47749121228908</v>
       </c>
       <c r="CB77" t="n">
-        <v>25.00074635442588</v>
+        <v>25.00074619879625</v>
       </c>
       <c r="CC77" t="n">
         <v>37.07686760955129</v>
@@ -37673,19 +37673,19 @@
         <v>25.84183193227743</v>
       </c>
       <c r="CE77" t="n">
-        <v>42.33491191071817</v>
+        <v>42.33491210652584</v>
       </c>
       <c r="CF77" t="n">
-        <v>42.16443460078658</v>
+        <v>42.16443464376599</v>
       </c>
       <c r="CG77" t="n">
-        <v>22.58227084946955</v>
+        <v>22.58227104415844</v>
       </c>
       <c r="CH77" t="n">
         <v>25.39446734308974</v>
       </c>
       <c r="CI77" t="n">
-        <v>29.23412773706314</v>
+        <v>29.23412776130676</v>
       </c>
       <c r="CJ77" t="n">
         <v>25.61814963768359</v>
@@ -37706,7 +37706,7 @@
         <v>-20.08202991662958</v>
       </c>
       <c r="CP77" t="n">
-        <v>1.33146395325574</v>
+        <v>1.331464037289076</v>
       </c>
       <c r="CQ77" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>-1.619472460532234</v>
       </c>
       <c r="DC77" t="n">
-        <v>-24.19493061245316</v>
+        <v>-24.19493858539801</v>
       </c>
       <c r="DD77" t="b">
         <v>0</v>
@@ -37998,10 +37998,10 @@
         <v>15.07999992370605</v>
       </c>
       <c r="CA78" t="n">
-        <v>2.433410658140781</v>
+        <v>2.433410667533303</v>
       </c>
       <c r="CB78" t="n">
-        <v>4.51397677085115</v>
+        <v>4.513976788274277</v>
       </c>
       <c r="CC78" t="n">
         <v>25.45350305593697</v>
@@ -38010,7 +38010,7 @@
         <v>19.52359161971606</v>
       </c>
       <c r="CE78" t="n">
-        <v>33.15512714261934</v>
+        <v>33.15512715937033</v>
       </c>
       <c r="CF78" t="n">
         <v>10.38593205872702</v>
@@ -38317,10 +38317,10 @@
         <v>14.56999969482422</v>
       </c>
       <c r="CA79" t="n">
-        <v>9.522007341680045</v>
+        <v>9.522007349588284</v>
       </c>
       <c r="CB79" t="n">
-        <v>17.66332361881648</v>
+        <v>17.66332363348626</v>
       </c>
       <c r="CC79" t="n">
         <v>13.81907630325131</v>
@@ -38341,7 +38341,7 @@
         <v>12.2203515982404</v>
       </c>
       <c r="CI79" t="n">
-        <v>14.92966932762521</v>
+        <v>14.92966933044746</v>
       </c>
       <c r="CJ79" t="n">
         <v>13.18184499442705</v>
@@ -38362,7 +38362,7 @@
         <v>-18.57473751904922</v>
       </c>
       <c r="CP79" t="n">
-        <v>2.468563077106678</v>
+        <v>2.468563096477006</v>
       </c>
       <c r="CQ79" t="inlineStr">
         <is>
@@ -38646,25 +38646,25 @@
         <v>26.20999908447266</v>
       </c>
       <c r="CA80" t="n">
-        <v>11.93854599254916</v>
+        <v>11.93854600600278</v>
       </c>
       <c r="CB80" t="n">
-        <v>12.61580797129651</v>
+        <v>12.61580797753781</v>
       </c>
       <c r="CC80" t="n">
-        <v>13.88314113709398</v>
+        <v>13.88314112831726</v>
       </c>
       <c r="CD80" t="n">
         <v>32.29491627828039</v>
       </c>
       <c r="CE80" t="n">
-        <v>12.94974348455922</v>
+        <v>12.94974348408371</v>
       </c>
       <c r="CF80" t="n">
-        <v>24.67209426849052</v>
+        <v>24.67209426666586</v>
       </c>
       <c r="CG80" t="n">
-        <v>5.68081670396464</v>
+        <v>5.680816695357558</v>
       </c>
       <c r="CH80" t="n">
         <v>61.56724104958222</v>
@@ -38965,10 +38965,10 @@
         <v>6.960000038146973</v>
       </c>
       <c r="CA81" t="n">
-        <v>1.253753091415094</v>
+        <v>1.253753091961851</v>
       </c>
       <c r="CB81" t="n">
-        <v>2.325711984574998</v>
+        <v>2.325711985589234</v>
       </c>
       <c r="CC81" t="n">
         <v>10.46765045464783</v>
@@ -38977,13 +38977,13 @@
         <v>10.28299479481327</v>
       </c>
       <c r="CE81" t="n">
-        <v>10.1527162123052</v>
+        <v>10.15271621215752</v>
       </c>
       <c r="CF81" t="n">
-        <v>1.873743398219951</v>
+        <v>1.873743398198098</v>
       </c>
       <c r="CG81" t="n">
-        <v>7.239836249975311</v>
+        <v>7.239836249336348</v>
       </c>
       <c r="CH81" t="n">
         <v>11.45586349250206</v>
@@ -39284,10 +39284,10 @@
         <v>10.44999980926514</v>
       </c>
       <c r="CA82" t="n">
-        <v>6.405733354885149</v>
+        <v>6.405733375838899</v>
       </c>
       <c r="CB82" t="n">
-        <v>11.88263537331195</v>
+        <v>11.88263541218116</v>
       </c>
       <c r="CC82" t="n">
         <v>7.980547404770202</v>
@@ -39308,7 +39308,7 @@
         <v>39.67377387971943</v>
       </c>
       <c r="CI82" t="n">
-        <v>10.25169813784719</v>
+        <v>10.25169814639333</v>
       </c>
       <c r="CJ82" t="n">
         <v>7.980547404770202</v>
@@ -39329,7 +39329,7 @@
         <v>-31.26801152737755</v>
       </c>
       <c r="CP82" t="n">
-        <v>-1.897623684568162</v>
+        <v>-1.897623602786935</v>
       </c>
       <c r="CQ82" t="inlineStr">
         <is>
@@ -39613,35 +39613,35 @@
         <v>2.779999971389771</v>
       </c>
       <c r="CA83" t="n">
-        <v>1.278070013488336</v>
+        <v>1.278070010016566</v>
       </c>
       <c r="CB83" t="n">
-        <v>1.746225328181497</v>
+        <v>1.746225324896744</v>
       </c>
       <c r="CC83" t="n">
-        <v>3.757726746318252</v>
+        <v>3.757726749457295</v>
       </c>
       <c r="CD83" t="n">
         <v>7.235833015165504</v>
       </c>
       <c r="CE83" t="n">
-        <v>3.789122804432596</v>
+        <v>3.789122800791896</v>
       </c>
       <c r="CF83" t="n">
-        <v>1.340415119442803</v>
+        <v>1.340415119546873</v>
       </c>
       <c r="CG83" t="n">
-        <v>1.852586859622515</v>
+        <v>1.852586861565595</v>
       </c>
       <c r="CH83" t="inlineStr"/>
       <c r="CI83" t="n">
-        <v>2.294024478581</v>
+        <v>2.294024477712494</v>
       </c>
       <c r="CJ83" t="n">
-        <v>1.799406093902006</v>
+        <v>1.79940609323117</v>
       </c>
       <c r="CK83" t="n">
-        <v>1.619465484511806</v>
+        <v>1.619465483908053</v>
       </c>
       <c r="CL83" t="n">
         <v>6</v>
@@ -39653,10 +39653,10 @@
         <v>5.7</v>
       </c>
       <c r="CO83" t="n">
-        <v>-41.7458452813506</v>
+        <v>-41.74584530306834</v>
       </c>
       <c r="CP83" t="n">
-        <v>-17.48113301475406</v>
+        <v>-17.48113304599527</v>
       </c>
       <c r="CQ83" t="inlineStr">
         <is>
@@ -39938,10 +39938,10 @@
         <v>5.269999980926514</v>
       </c>
       <c r="CA84" t="n">
-        <v>3.116563119736672</v>
+        <v>3.116563121612964</v>
       </c>
       <c r="CB84" t="n">
-        <v>4.537715902336594</v>
+        <v>4.537715905068476</v>
       </c>
       <c r="CC84" t="n">
         <v>4.409332244701186</v>
@@ -40263,10 +40263,10 @@
         <v>18.8700008392334</v>
       </c>
       <c r="CA85" t="n">
-        <v>4.583372131445171</v>
+        <v>4.583372138659932</v>
       </c>
       <c r="CB85" t="n">
-        <v>8.502155303830792</v>
+        <v>8.502155317214175</v>
       </c>
       <c r="CC85" t="n">
         <v>32.85512629695696</v>
@@ -40275,13 +40275,13 @@
         <v>35.40227792012859</v>
       </c>
       <c r="CE85" t="n">
-        <v>28.64952006761382</v>
+        <v>28.64952006977598</v>
       </c>
       <c r="CF85" t="n">
-        <v>11.13130675711154</v>
+        <v>11.13130675665037</v>
       </c>
       <c r="CG85" t="n">
-        <v>19.33234132420919</v>
+        <v>19.3323413172253</v>
       </c>
       <c r="CH85" t="n">
         <v>44.34329506457097</v>
@@ -40726,8 +40726,16 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Bandeira de alta</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Bandeira de alta (pré-confirmação) — pescoço R$1.63, preço 4.4% abaixo do pescoço; falta fechar acima e segurar</t>
+        </is>
+      </c>
       <c r="U87" t="b">
         <v>0</v>
       </c>
@@ -40899,25 +40907,25 @@
         <v>1.559999942779541</v>
       </c>
       <c r="CA87" t="n">
-        <v>0.1391065134769551</v>
+        <v>0.1391065133551693</v>
       </c>
       <c r="CB87" t="n">
-        <v>0.1588447641643512</v>
+        <v>0.15884476403043</v>
       </c>
       <c r="CC87" t="n">
-        <v>0.7587329111159103</v>
+        <v>0.758732911140487</v>
       </c>
       <c r="CD87" t="n">
         <v>3.145519198624604</v>
       </c>
       <c r="CE87" t="n">
-        <v>0.2602842160248378</v>
+        <v>0.2602842159565861</v>
       </c>
       <c r="CF87" t="n">
-        <v>0.5416073431986184</v>
+        <v>0.5416073432005343</v>
       </c>
       <c r="CG87" t="n">
-        <v>0.3391165297882078</v>
+        <v>0.3391165298092135</v>
       </c>
       <c r="CH87" t="inlineStr"/>
       <c r="CI87" t="inlineStr"/>
@@ -41216,10 +41224,10 @@
         <v>23.96999931335449</v>
       </c>
       <c r="CA88" t="n">
-        <v>12.08006953884126</v>
+        <v>12.08006959686802</v>
       </c>
       <c r="CB88" t="n">
-        <v>22.40852899455054</v>
+        <v>22.40852910219017</v>
       </c>
       <c r="CC88" t="n">
         <v>15.09517542309634</v>
@@ -41240,13 +41248,13 @@
         <v>23.16277622804454</v>
       </c>
       <c r="CI88" t="n">
-        <v>19.87755694330279</v>
+        <v>19.87755696401108</v>
       </c>
       <c r="CJ88" t="n">
-        <v>18.75185220882344</v>
+        <v>18.75185226264325</v>
       </c>
       <c r="CK88" t="n">
-        <v>16.8766669879411</v>
+        <v>16.87666703637893</v>
       </c>
       <c r="CL88" t="n">
         <v>8</v>
@@ -41258,10 +41266,10 @@
         <v>2.9</v>
       </c>
       <c r="CO88" t="n">
-        <v>-29.59254288114001</v>
+        <v>-29.5925426790631</v>
       </c>
       <c r="CP88" t="n">
-        <v>-17.07318517848964</v>
+        <v>-17.07318509209707</v>
       </c>
       <c r="CQ88" t="inlineStr">
         <is>
@@ -41543,10 +41551,10 @@
         <v>14.03999996185303</v>
       </c>
       <c r="CA89" t="n">
-        <v>6.06089647247348</v>
+        <v>6.060896464684133</v>
       </c>
       <c r="CB89" t="n">
-        <v>8.824665263921387</v>
+        <v>8.824665252580099</v>
       </c>
       <c r="CC89" t="n">
         <v>3.751695776034725</v>
@@ -41860,10 +41868,10 @@
         <v>7.210000038146973</v>
       </c>
       <c r="CA90" t="n">
-        <v>3.000514736313903</v>
+        <v>3.000514739231277</v>
       </c>
       <c r="CB90" t="n">
-        <v>5.565954835862288</v>
+        <v>5.565954841274017</v>
       </c>
       <c r="CC90" t="n">
         <v>14.71995385291947</v>
@@ -41872,17 +41880,17 @@
         <v>15.82114567812849</v>
       </c>
       <c r="CE90" t="n">
-        <v>14.12742075999183</v>
+        <v>14.12742076175965</v>
       </c>
       <c r="CF90" t="n">
-        <v>15.00312294986183</v>
+        <v>15.00312294929008</v>
       </c>
       <c r="CG90" t="n">
-        <v>7.779395117295591</v>
+        <v>7.779395114451034</v>
       </c>
       <c r="CH90" t="inlineStr"/>
       <c r="CI90" t="n">
-        <v>13.49020767163944</v>
+        <v>13.49020767130974</v>
       </c>
       <c r="CJ90" t="n">
         <v>14.71995385291947</v>
@@ -41903,7 +41911,7 @@
         <v>83.74422187981506</v>
       </c>
       <c r="CP90" t="n">
-        <v>87.10412760422861</v>
+        <v>87.1041275996558</v>
       </c>
       <c r="CQ90" t="inlineStr">
         <is>
@@ -42171,10 +42179,10 @@
         <v>55.22999954223633</v>
       </c>
       <c r="CA91" t="n">
-        <v>11.59198337960933</v>
+        <v>11.59198338465607</v>
       </c>
       <c r="CB91" t="n">
-        <v>16.87792780071118</v>
+        <v>16.87792780805924</v>
       </c>
       <c r="CC91" t="inlineStr"/>
       <c r="CD91" t="inlineStr"/>
@@ -42185,13 +42193,13 @@
       <c r="CG91" t="inlineStr"/>
       <c r="CH91" t="inlineStr"/>
       <c r="CI91" t="n">
-        <v>18.26587039344017</v>
+        <v>18.26587039757177</v>
       </c>
       <c r="CJ91" t="n">
-        <v>16.87792780071118</v>
+        <v>16.87792780805924</v>
       </c>
       <c r="CK91" t="n">
-        <v>15.19013502064006</v>
+        <v>15.19013502725332</v>
       </c>
       <c r="CL91" t="n">
         <v>3</v>
@@ -42203,10 +42211,10 @@
         <v>2.3</v>
       </c>
       <c r="CO91" t="n">
-        <v>-72.49658673449086</v>
+        <v>-72.49658672251684</v>
       </c>
       <c r="CP91" t="n">
-        <v>-66.92762892479908</v>
+        <v>-66.92762891731836</v>
       </c>
       <c r="CQ91" t="inlineStr">
         <is>
@@ -42504,10 +42512,10 @@
         <v>3.660000085830688</v>
       </c>
       <c r="CA92" t="n">
-        <v>33.40407228883803</v>
+        <v>33.40407232276198</v>
       </c>
       <c r="CB92" t="n">
-        <v>61.96455409579454</v>
+        <v>61.96455415872346</v>
       </c>
       <c r="CC92" t="n">
         <v>4.712828098858758</v>
@@ -42821,10 +42829,10 @@
         <v>7.739999771118164</v>
       </c>
       <c r="CA93" t="n">
-        <v>4.98233916783806</v>
+        <v>4.982339148458794</v>
       </c>
       <c r="CB93" t="n">
-        <v>7.254285828372216</v>
+        <v>7.254285800156005</v>
       </c>
       <c r="CC93" t="n">
         <v>5.854254372336648</v>
@@ -42843,13 +42851,13 @@
         <v>7.739999771118164</v>
       </c>
       <c r="CI93" t="n">
-        <v>6.60602519877425</v>
+        <v>6.60602519084167</v>
       </c>
       <c r="CJ93" t="n">
-        <v>6.554270100354432</v>
+        <v>6.554270086246326</v>
       </c>
       <c r="CK93" t="n">
-        <v>5.898843090318989</v>
+        <v>5.898843077621694</v>
       </c>
       <c r="CL93" t="n">
         <v>6</v>
@@ -42861,10 +42869,10 @@
         <v>5.9</v>
       </c>
       <c r="CO93" t="n">
-        <v>-23.78755471892206</v>
+        <v>-23.7875548829698</v>
       </c>
       <c r="CP93" t="n">
-        <v>-14.6508347012534</v>
+        <v>-14.65083480374152</v>
       </c>
       <c r="CQ93" t="inlineStr">
         <is>
@@ -43148,10 +43156,10 @@
         <v>35.06000137329102</v>
       </c>
       <c r="CA94" t="n">
-        <v>8.678975663064849</v>
+        <v>8.678975692313651</v>
       </c>
       <c r="CB94" t="n">
-        <v>16.09949985498529</v>
+        <v>16.09949990924182</v>
       </c>
       <c r="CC94" t="n">
         <v>40.64260876606351</v>
@@ -43160,19 +43168,19 @@
         <v>40.99197343130513</v>
       </c>
       <c r="CE94" t="n">
-        <v>34.02509303025669</v>
+        <v>34.02509301436427</v>
       </c>
       <c r="CF94" t="n">
-        <v>50.06624561540897</v>
+        <v>50.06624560756568</v>
       </c>
       <c r="CG94" t="n">
-        <v>22.89947635937279</v>
+        <v>22.89947632686451</v>
       </c>
       <c r="CH94" t="n">
         <v>54.19026455668205</v>
       </c>
       <c r="CI94" t="n">
-        <v>36.98788023058206</v>
+        <v>36.98788023029814</v>
       </c>
       <c r="CJ94" t="n">
         <v>40.64260876606351</v>
@@ -43193,7 +43201,7 @@
         <v>4.330708661417315</v>
       </c>
       <c r="CP94" t="n">
-        <v>5.498798578940511</v>
+        <v>5.49879857813067</v>
       </c>
       <c r="CQ94" t="inlineStr">
         <is>
@@ -43475,10 +43483,10 @@
         <v>79.11000061035156</v>
       </c>
       <c r="CA95" t="n">
-        <v>59.14478700616458</v>
+        <v>59.14478698533546</v>
       </c>
       <c r="CB95" t="n">
-        <v>86.11480988097563</v>
+        <v>86.11480985064844</v>
       </c>
       <c r="CC95" t="n">
         <v>24.45731291164257</v>
@@ -43782,35 +43790,35 @@
         <v>19.96999931335449</v>
       </c>
       <c r="CA96" t="n">
-        <v>11.90564909445598</v>
+        <v>11.9056491440227</v>
       </c>
       <c r="CB96" t="n">
-        <v>15.10153845941968</v>
+        <v>15.10153848950621</v>
       </c>
       <c r="CC96" t="n">
-        <v>22.67332628438679</v>
+        <v>22.67332623516273</v>
       </c>
       <c r="CD96" t="n">
         <v>41.91581127865282</v>
       </c>
       <c r="CE96" t="n">
-        <v>27.56446897257639</v>
+        <v>27.56446900409021</v>
       </c>
       <c r="CF96" t="n">
-        <v>15.76134638081548</v>
+        <v>15.76134637741417</v>
       </c>
       <c r="CG96" t="n">
-        <v>10.88246755292415</v>
+        <v>10.8824675180728</v>
       </c>
       <c r="CH96" t="inlineStr"/>
       <c r="CI96" t="n">
-        <v>16.36046505476948</v>
+        <v>16.36046506152645</v>
       </c>
       <c r="CJ96" t="n">
-        <v>15.43144242011758</v>
+        <v>15.43144243346019</v>
       </c>
       <c r="CK96" t="n">
-        <v>13.88829817810583</v>
+        <v>13.88829819011417</v>
       </c>
       <c r="CL96" t="n">
         <v>4</v>
@@ -43822,10 +43830,10 @@
         <v>1.9</v>
       </c>
       <c r="CO96" t="n">
-        <v>-30.45418800381061</v>
+        <v>-30.4541879436787</v>
       </c>
       <c r="CP96" t="n">
-        <v>-18.07478408960792</v>
+        <v>-18.07478405577233</v>
       </c>
       <c r="CQ96" t="inlineStr">
         <is>
@@ -44121,10 +44129,10 @@
         <v>19.39999961853027</v>
       </c>
       <c r="CA97" t="n">
-        <v>2.002086983194392</v>
+        <v>2.002086996799187</v>
       </c>
       <c r="CB97" t="n">
-        <v>3.713871353825597</v>
+        <v>3.713871379062493</v>
       </c>
       <c r="CC97" t="n">
         <v>10.17214067849332</v>
@@ -44133,19 +44141,19 @@
         <v>8.489143658487551</v>
       </c>
       <c r="CE97" t="n">
-        <v>10.08252820151572</v>
+        <v>10.082528173988</v>
       </c>
       <c r="CF97" t="n">
-        <v>7.542883472971194</v>
+        <v>7.542883469886538</v>
       </c>
       <c r="CG97" t="n">
-        <v>7.691263386126244</v>
+        <v>7.691263364085387</v>
       </c>
       <c r="CH97" t="n">
         <v>13.63549921457183</v>
       </c>
       <c r="CI97" t="n">
-        <v>8.761047137998778</v>
+        <v>8.76104713408216</v>
       </c>
       <c r="CJ97" t="n">
         <v>8.489143658487551</v>
@@ -44166,7 +44174,7 @@
         <v>-60.61737400581654</v>
       </c>
       <c r="CP97" t="n">
-        <v>-54.83996231819253</v>
+        <v>-54.83996233838128</v>
       </c>
       <c r="CQ97" t="inlineStr">
         <is>
@@ -44458,10 +44466,10 @@
         <v>16.01000022888184</v>
       </c>
       <c r="CA98" t="n">
-        <v>8.061612827900362</v>
+        <v>8.061612859093621</v>
       </c>
       <c r="CB98" t="n">
-        <v>14.95429179575517</v>
+        <v>14.95429185361867</v>
       </c>
       <c r="CC98" t="n">
         <v>10.47567916210787</v>
@@ -44482,7 +44490,7 @@
         <v>10.00660187036776</v>
       </c>
       <c r="CI98" t="n">
-        <v>12.47880699380619</v>
+        <v>12.47880700493828</v>
       </c>
       <c r="CJ98" t="n">
         <v>10.24114051623781</v>
@@ -44503,7 +44511,7 @@
         <v>-42.4295669403762</v>
       </c>
       <c r="CP98" t="n">
-        <v>-22.05617229602172</v>
+        <v>-22.05617222648958</v>
       </c>
       <c r="CQ98" t="inlineStr">
         <is>
@@ -44787,10 +44795,10 @@
         <v>7.170000076293945</v>
       </c>
       <c r="CA99" t="n">
-        <v>3.214416914576922</v>
+        <v>3.214416911077948</v>
       </c>
       <c r="CB99" t="n">
-        <v>5.96274337654019</v>
+        <v>5.962743370049593</v>
       </c>
       <c r="CC99" t="inlineStr"/>
       <c r="CD99" t="inlineStr"/>
@@ -44801,13 +44809,13 @@
         <v>9.809989751681186</v>
       </c>
       <c r="CI99" t="n">
-        <v>6.329050014266099</v>
+        <v>6.329050010936243</v>
       </c>
       <c r="CJ99" t="n">
-        <v>5.96274337654019</v>
+        <v>5.962743370049593</v>
       </c>
       <c r="CK99" t="n">
-        <v>5.366469038886171</v>
+        <v>5.366469033044634</v>
       </c>
       <c r="CL99" t="n">
         <v>3</v>
@@ -44819,10 +44827,10 @@
         <v>3.1</v>
       </c>
       <c r="CO99" t="n">
-        <v>-25.1538496264562</v>
+        <v>-25.15384970792813</v>
       </c>
       <c r="CP99" t="n">
-        <v>-11.72873156317342</v>
+        <v>-11.72873160961493</v>
       </c>
       <c r="CQ99" t="inlineStr">
         <is>
@@ -45114,37 +45122,37 @@
         <v>23.05999946594238</v>
       </c>
       <c r="CA100" t="n">
-        <v>5.050688947852107</v>
+        <v>5.050688901453313</v>
       </c>
       <c r="CB100" t="n">
-        <v>7.175729503170489</v>
+        <v>7.175729492811916</v>
       </c>
       <c r="CC100" t="n">
-        <v>10.62745754962625</v>
+        <v>10.6274576319154</v>
       </c>
       <c r="CD100" t="n">
         <v>14.56873729010693</v>
       </c>
       <c r="CE100" t="n">
-        <v>7.163504663057443</v>
+        <v>7.163504709039312</v>
       </c>
       <c r="CF100" t="n">
-        <v>8.436256188434387</v>
+        <v>8.436256194293875</v>
       </c>
       <c r="CG100" t="n">
-        <v>5.281933246527457</v>
+        <v>5.281933293973007</v>
       </c>
       <c r="CH100" t="n">
         <v>10.72687534044447</v>
       </c>
       <c r="CI100" t="n">
-        <v>8.628897841152442</v>
+        <v>8.628897856754779</v>
       </c>
       <c r="CJ100" t="n">
-        <v>7.805992845802438</v>
+        <v>7.805992843552896</v>
       </c>
       <c r="CK100" t="n">
-        <v>7.025393561222194</v>
+        <v>7.025393559197607</v>
       </c>
       <c r="CL100" t="n">
         <v>8</v>
@@ -45156,10 +45164,10 @@
         <v>2.9</v>
       </c>
       <c r="CO100" t="n">
-        <v>-69.53428567247761</v>
+        <v>-69.53428568125726</v>
       </c>
       <c r="CP100" t="n">
-        <v>-62.58066764530253</v>
+        <v>-62.58066757764278</v>
       </c>
       <c r="CQ100" t="inlineStr">
         <is>
@@ -45443,10 +45451,10 @@
         <v>46.40000152587891</v>
       </c>
       <c r="CA101" t="n">
-        <v>10.15177417024026</v>
+        <v>10.15177418318714</v>
       </c>
       <c r="CB101" t="n">
-        <v>18.83154108579569</v>
+        <v>18.83154110981214</v>
       </c>
       <c r="CC101" t="n">
         <v>86.34831744633361</v>
@@ -45455,13 +45463,13 @@
         <v>76.25640482050953</v>
       </c>
       <c r="CE101" t="n">
-        <v>103.7331124502263</v>
+        <v>103.7331124458851</v>
       </c>
       <c r="CF101" t="n">
-        <v>16.00171173209397</v>
+        <v>16.00171173144562</v>
       </c>
       <c r="CG101" t="n">
-        <v>70.06584443193867</v>
+        <v>70.06584441320817</v>
       </c>
       <c r="CH101" t="n">
         <v>22.72912505392368</v>
@@ -45774,25 +45782,25 @@
         <v>47.5</v>
       </c>
       <c r="CA102" t="n">
-        <v>18.25668183966376</v>
+        <v>18.25668176857641</v>
       </c>
       <c r="CB102" t="n">
-        <v>20.19873859991595</v>
+        <v>20.19873856683065</v>
       </c>
       <c r="CC102" t="n">
-        <v>23.86378090129652</v>
+        <v>23.86378095512804</v>
       </c>
       <c r="CD102" t="n">
         <v>51.4328502242105</v>
       </c>
       <c r="CE102" t="n">
-        <v>19.85694202296504</v>
+        <v>19.85694203712428</v>
       </c>
       <c r="CF102" t="n">
-        <v>23.27481926360353</v>
+        <v>23.27481926950097</v>
       </c>
       <c r="CG102" t="n">
-        <v>10.33491117945844</v>
+        <v>10.33491122812768</v>
       </c>
       <c r="CH102" t="n">
         <v>120.2965411332743</v>
@@ -46101,37 +46109,37 @@
         <v>52.59999847412109</v>
       </c>
       <c r="CA103" t="n">
-        <v>16.06764462676261</v>
+        <v>16.06764458927408</v>
       </c>
       <c r="CB103" t="n">
-        <v>24.44956362623018</v>
+        <v>24.44956360462806</v>
       </c>
       <c r="CC103" t="n">
-        <v>44.11350736119449</v>
+        <v>44.11350742514281</v>
       </c>
       <c r="CD103" t="n">
         <v>61.25894385652082</v>
       </c>
       <c r="CE103" t="n">
-        <v>35.19545558943221</v>
+        <v>35.1954556006845</v>
       </c>
       <c r="CF103" t="n">
-        <v>26.76297346985695</v>
+        <v>26.76297347312566</v>
       </c>
       <c r="CG103" t="n">
-        <v>22.0551005510281</v>
+        <v>22.05510058355615</v>
       </c>
       <c r="CH103" t="n">
         <v>21.52547978006953</v>
       </c>
       <c r="CI103" t="n">
-        <v>31.42858360763686</v>
+        <v>31.4285836141252</v>
       </c>
       <c r="CJ103" t="n">
-        <v>25.60626854804357</v>
+        <v>25.60626853887686</v>
       </c>
       <c r="CK103" t="n">
-        <v>23.04564169323921</v>
+        <v>23.04564168498917</v>
       </c>
       <c r="CL103" t="n">
         <v>8</v>
@@ -46143,10 +46151,10 @@
         <v>3.8</v>
       </c>
       <c r="CO103" t="n">
-        <v>-56.18699170765653</v>
+        <v>-56.18699172334102</v>
       </c>
       <c r="CP103" t="n">
-        <v>-40.24983931682137</v>
+        <v>-40.24983930448612</v>
       </c>
       <c r="CQ103" t="inlineStr">
         <is>
@@ -46450,10 +46458,10 @@
         <v>11.97000026702881</v>
       </c>
       <c r="CA104" t="n">
-        <v>2.129461196662962</v>
+        <v>2.129461178522574</v>
       </c>
       <c r="CB104" t="n">
-        <v>3.950150519809794</v>
+        <v>3.950150486159375</v>
       </c>
       <c r="CC104" t="n">
         <v>12.16276867623709</v>
@@ -46462,25 +46470,25 @@
         <v>13.48270925178679</v>
       </c>
       <c r="CE104" t="n">
-        <v>8.763352835519244</v>
+        <v>8.763352842582755</v>
       </c>
       <c r="CF104" t="n">
-        <v>5.737636414944148</v>
+        <v>5.737636416493662</v>
       </c>
       <c r="CG104" t="n">
-        <v>6.523557488713325</v>
+        <v>6.523557505395226</v>
       </c>
       <c r="CH104" t="n">
         <v>11.97000026702881</v>
       </c>
       <c r="CI104" t="n">
-        <v>8.941453636291316</v>
+        <v>8.941453635097673</v>
       </c>
       <c r="CJ104" t="n">
-        <v>8.763352835519244</v>
+        <v>8.763352842582755</v>
       </c>
       <c r="CK104" t="n">
-        <v>7.88701755196732</v>
+        <v>7.887017558324479</v>
       </c>
       <c r="CL104" t="n">
         <v>7</v>
@@ -46492,10 +46500,10 @@
         <v>6.3</v>
       </c>
       <c r="CO104" t="n">
-        <v>-34.11013052612877</v>
+        <v>-34.11013047301967</v>
       </c>
       <c r="CP104" t="n">
-        <v>-25.30114087866464</v>
+        <v>-25.3011408886366</v>
       </c>
       <c r="CQ104" t="inlineStr">
         <is>
@@ -46530,7 +46538,7 @@
         <v>-3.623186847833049</v>
       </c>
       <c r="DC104" t="n">
-        <v>-26.54313590288396</v>
+        <v>-26.54314462197242</v>
       </c>
       <c r="DD104" t="b">
         <v>0</v>
@@ -46779,10 +46787,10 @@
         <v>3.029999971389771</v>
       </c>
       <c r="CA105" t="n">
-        <v>0.634393400160509</v>
+        <v>0.6343934004828935</v>
       </c>
       <c r="CB105" t="n">
-        <v>1.176799757297744</v>
+        <v>1.176799757895767</v>
       </c>
       <c r="CC105" t="n">
         <v>3.469965395066072</v>
@@ -46791,13 +46799,13 @@
         <v>4.010566432856011</v>
       </c>
       <c r="CE105" t="n">
-        <v>2.423903795796604</v>
+        <v>2.423903795754766</v>
       </c>
       <c r="CF105" t="n">
-        <v>2.635949510293158</v>
+        <v>2.635949510252269</v>
       </c>
       <c r="CG105" t="n">
-        <v>1.740689720354548</v>
+        <v>1.740689720083049</v>
       </c>
       <c r="CH105" t="n">
         <v>9.095071583324174</v>
@@ -47096,10 +47104,10 @@
         <v>55.18999862670898</v>
       </c>
       <c r="CA106" t="n">
-        <v>62.46314045632767</v>
+        <v>62.46314027029702</v>
       </c>
       <c r="CB106" t="n">
-        <v>90.94633250441309</v>
+        <v>90.94633223355248</v>
       </c>
       <c r="CC106" t="n">
         <v>24.38300703983744</v>
@@ -48021,10 +48029,10 @@
         <v>97.61000061035156</v>
       </c>
       <c r="CA109" t="n">
-        <v>4.983317724542968</v>
+        <v>4.983317747697623</v>
       </c>
       <c r="CB109" t="n">
-        <v>9.244054379027206</v>
+        <v>9.244054421979092</v>
       </c>
       <c r="CC109" t="n">
         <v>42.72654470059987</v>
@@ -48033,13 +48041,13 @@
         <v>42.39662181432417</v>
       </c>
       <c r="CE109" t="n">
-        <v>35.18082005139934</v>
+        <v>35.18082001993458</v>
       </c>
       <c r="CF109" t="n">
-        <v>17.64642630819762</v>
+        <v>17.64642630610324</v>
       </c>
       <c r="CG109" t="n">
-        <v>29.27933220344284</v>
+        <v>29.27933217693354</v>
       </c>
       <c r="CH109" t="n">
         <v>44.08436660991484</v>
@@ -48659,10 +48667,10 @@
         <v>17.03000068664551</v>
       </c>
       <c r="CA111" t="n">
-        <v>3.197432134508171</v>
+        <v>3.197432151873655</v>
       </c>
       <c r="CB111" t="n">
-        <v>5.931236609512657</v>
+        <v>5.931236641725629</v>
       </c>
       <c r="CC111" t="n">
         <v>14.94354364887768</v>
@@ -48671,23 +48679,23 @@
         <v>15.89715452361429</v>
       </c>
       <c r="CE111" t="n">
-        <v>10.65047412759275</v>
+        <v>10.65047411622101</v>
       </c>
       <c r="CF111" t="n">
-        <v>13.0312705535162</v>
+        <v>13.03127055054446</v>
       </c>
       <c r="CG111" t="n">
-        <v>7.844055765296405</v>
+        <v>7.844055748028169</v>
       </c>
       <c r="CH111" t="inlineStr"/>
       <c r="CI111" t="n">
-        <v>11.38295587140166</v>
+        <v>11.38295587150187</v>
       </c>
       <c r="CJ111" t="n">
-        <v>11.84087234055447</v>
+        <v>11.84087233338273</v>
       </c>
       <c r="CK111" t="n">
-        <v>10.65678510649903</v>
+        <v>10.65678510004446</v>
       </c>
       <c r="CL111" t="n">
         <v>6</v>
@@ -48699,10 +48707,10 @@
         <v>5</v>
       </c>
       <c r="CO111" t="n">
-        <v>-37.423460500176</v>
+        <v>-37.42346053807716</v>
       </c>
       <c r="CP111" t="n">
-        <v>-33.15939276310255</v>
+        <v>-33.15939276251413</v>
       </c>
       <c r="CQ111" t="inlineStr">
         <is>
@@ -48986,25 +48994,25 @@
         <v>14.78999996185303</v>
       </c>
       <c r="CA112" t="n">
-        <v>3.734050399658269</v>
+        <v>3.734050392041933</v>
       </c>
       <c r="CB112" t="n">
-        <v>4.750965491165045</v>
+        <v>4.750965482740938</v>
       </c>
       <c r="CC112" t="n">
-        <v>14.39113215676547</v>
+        <v>14.39113216060161</v>
       </c>
       <c r="CD112" t="n">
         <v>37.23867291481046</v>
       </c>
       <c r="CE112" t="n">
-        <v>9.871878897433948</v>
+        <v>9.871878890314735</v>
       </c>
       <c r="CF112" t="n">
-        <v>48.41104884002601</v>
+        <v>48.41104884130521</v>
       </c>
       <c r="CG112" t="n">
-        <v>6.917256497960351</v>
+        <v>6.917256500661409</v>
       </c>
       <c r="CH112" t="n">
         <v>27.46854012923095</v>
@@ -49305,25 +49313,25 @@
         <v>14.8100004196167</v>
       </c>
       <c r="CA113" t="n">
-        <v>1.386019546155701</v>
+        <v>1.386019545581671</v>
       </c>
       <c r="CB113" t="n">
-        <v>2.562681322591672</v>
+        <v>2.56268132188664</v>
       </c>
       <c r="CC113" t="n">
-        <v>8.67757492518764</v>
+        <v>8.677574926394195</v>
       </c>
       <c r="CD113" t="n">
         <v>10.7066274318662</v>
       </c>
       <c r="CE113" t="n">
-        <v>4.787218446823891</v>
+        <v>4.787218447148839</v>
       </c>
       <c r="CF113" t="n">
-        <v>7.688860391467219</v>
+        <v>7.68886039154247</v>
       </c>
       <c r="CG113" t="n">
-        <v>4.223256309328479</v>
+        <v>4.223256309756843</v>
       </c>
       <c r="CH113" t="n">
         <v>11.50778129173654</v>
@@ -49624,10 +49632,10 @@
         <v>11.21000003814697</v>
       </c>
       <c r="CA114" t="n">
-        <v>2.436068241905331</v>
+        <v>2.436068244442286</v>
       </c>
       <c r="CB114" t="n">
-        <v>4.518906588734389</v>
+        <v>4.51890659344044</v>
       </c>
       <c r="CC114" t="n">
         <v>12.15486910846541</v>
@@ -49636,13 +49644,13 @@
         <v>12.67593560098585</v>
       </c>
       <c r="CE114" t="n">
-        <v>9.597004755510515</v>
+        <v>9.597004754222409</v>
       </c>
       <c r="CF114" t="n">
-        <v>0.7922532027798349</v>
+        <v>0.792253202746111</v>
       </c>
       <c r="CG114" t="n">
-        <v>6.728746185483628</v>
+        <v>6.728746182847019</v>
       </c>
       <c r="CH114" t="n">
         <v>7.42587936633825</v>
@@ -49943,10 +49951,10 @@
         <v>18.32999992370605</v>
       </c>
       <c r="CA115" t="n">
-        <v>11.72124070694724</v>
+        <v>11.72124063954529</v>
       </c>
       <c r="CB115" t="n">
-        <v>14.62606992562547</v>
+        <v>14.62606984151956</v>
       </c>
       <c r="CC115" t="inlineStr"/>
       <c r="CD115" t="inlineStr"/>
@@ -50254,25 +50262,25 @@
         <v>8.859999656677246</v>
       </c>
       <c r="CA116" t="n">
-        <v>2.278494624794862</v>
+        <v>2.278494622371153</v>
       </c>
       <c r="CB116" t="n">
-        <v>2.457217336596655</v>
+        <v>2.457217334656649</v>
       </c>
       <c r="CC116" t="n">
-        <v>3.19820882036864</v>
+        <v>3.19820882124565</v>
       </c>
       <c r="CD116" t="n">
         <v>9.985934437661033</v>
       </c>
       <c r="CE116" t="n">
-        <v>1.868987657308722</v>
+        <v>1.868987657038611</v>
       </c>
       <c r="CF116" t="n">
-        <v>5.906665058472821</v>
+        <v>5.906665058658929</v>
       </c>
       <c r="CG116" t="n">
-        <v>1.344337861582278</v>
+        <v>1.344337862411962</v>
       </c>
       <c r="CH116" t="n">
         <v>14.36284499478099</v>
@@ -50585,10 +50593,10 @@
         <v>4.820000171661377</v>
       </c>
       <c r="CA117" t="n">
-        <v>1.482729244006164</v>
+        <v>1.482729236456806</v>
       </c>
       <c r="CB117" t="n">
-        <v>1.54533336764198</v>
+        <v>1.545333359773871</v>
       </c>
       <c r="CC117" t="inlineStr"/>
       <c r="CD117" t="inlineStr"/>
@@ -50894,10 +50902,10 @@
         <v>3.339999914169312</v>
       </c>
       <c r="CA118" t="n">
-        <v>1.645463648520525</v>
+        <v>1.645463648893405</v>
       </c>
       <c r="CB118" t="n">
-        <v>3.052335068005573</v>
+        <v>3.052335068697266</v>
       </c>
       <c r="CC118" t="n">
         <v>1.157901592431799</v>
@@ -50906,7 +50914,7 @@
         <v>4.60268789222791</v>
       </c>
       <c r="CE118" t="n">
-        <v>1.607705130618378</v>
+        <v>1.607705130754965</v>
       </c>
       <c r="CF118" t="n">
         <v>0.7445919647652398</v>
@@ -51213,10 +51221,10 @@
         <v>6.53000020980835</v>
       </c>
       <c r="CA119" t="n">
-        <v>1.049728088214408</v>
+        <v>1.049728088477062</v>
       </c>
       <c r="CB119" t="n">
-        <v>1.947245603637726</v>
+        <v>1.94724560412495</v>
       </c>
       <c r="CC119" t="inlineStr"/>
       <c r="CD119" t="inlineStr"/>
@@ -51522,25 +51530,25 @@
         <v>3.680000066757202</v>
       </c>
       <c r="CA120" t="n">
-        <v>1.260300728021352</v>
+        <v>1.260300725970805</v>
       </c>
       <c r="CB120" t="n">
-        <v>1.270282442500588</v>
+        <v>1.270282441180997</v>
       </c>
       <c r="CC120" t="n">
-        <v>1.298084291593951</v>
+        <v>1.2980842923575</v>
       </c>
       <c r="CD120" t="n">
         <v>4.028317282462615</v>
       </c>
       <c r="CE120" t="n">
-        <v>0.8819046452353982</v>
+        <v>0.881904645123565</v>
       </c>
       <c r="CF120" t="n">
-        <v>2.295577887496407</v>
+        <v>2.295577887661088</v>
       </c>
       <c r="CG120" t="n">
-        <v>0.4926159527050053</v>
+        <v>0.4926159535188262</v>
       </c>
       <c r="CH120" t="n">
         <v>5.189162701709523</v>
@@ -51845,10 +51853,10 @@
         <v>5.369999885559082</v>
       </c>
       <c r="CA121" t="n">
-        <v>5.323748909303515</v>
+        <v>5.323748905683608</v>
       </c>
       <c r="CB121" t="n">
-        <v>7.751378411945918</v>
+        <v>7.751378406675334</v>
       </c>
       <c r="CC121" t="inlineStr"/>
       <c r="CD121" t="inlineStr"/>
@@ -51857,13 +51865,13 @@
       <c r="CG121" t="inlineStr"/>
       <c r="CH121" t="inlineStr"/>
       <c r="CI121" t="n">
-        <v>6.537563660624716</v>
+        <v>6.537563656179471</v>
       </c>
       <c r="CJ121" t="n">
-        <v>6.537563660624716</v>
+        <v>6.537563656179471</v>
       </c>
       <c r="CK121" t="n">
-        <v>5.883807294562245</v>
+        <v>5.883807290561524</v>
       </c>
       <c r="CL121" t="n">
         <v>2</v>
@@ -51875,10 +51883,10 @@
         <v>1.5</v>
       </c>
       <c r="CO121" t="n">
-        <v>9.568108379012919</v>
+        <v>9.568108304511602</v>
       </c>
       <c r="CP121" t="n">
-        <v>21.74234264334769</v>
+        <v>21.74234256056844</v>
       </c>
       <c r="CQ121" t="inlineStr">
         <is>
@@ -52162,10 +52170,10 @@
         <v>5.369999885559082</v>
       </c>
       <c r="CA122" t="n">
-        <v>5.911211500743264</v>
+        <v>5.911211516683818</v>
       </c>
       <c r="CB122" t="n">
-        <v>10.53904913108419</v>
+        <v>10.53904915950447</v>
       </c>
       <c r="CC122" t="inlineStr"/>
       <c r="CD122" t="inlineStr"/>
@@ -52174,13 +52182,13 @@
       <c r="CG122" t="inlineStr"/>
       <c r="CH122" t="inlineStr"/>
       <c r="CI122" t="n">
-        <v>8.225130315913727</v>
+        <v>8.225130338094145</v>
       </c>
       <c r="CJ122" t="n">
-        <v>8.225130315913727</v>
+        <v>8.225130338094145</v>
       </c>
       <c r="CK122" t="n">
-        <v>7.402617284322354</v>
+        <v>7.40261730428473</v>
       </c>
       <c r="CL122" t="n">
         <v>2</v>
@@ -52192,10 +52200,10 @@
         <v>1.8</v>
       </c>
       <c r="CO122" t="n">
-        <v>37.85134901453824</v>
+        <v>37.8513493862771</v>
       </c>
       <c r="CP122" t="n">
-        <v>53.16816557170916</v>
+        <v>53.16816598475233</v>
       </c>
       <c r="CQ122" t="inlineStr">
         <is>
@@ -52465,10 +52473,10 @@
         <v>22.35000038146973</v>
       </c>
       <c r="CA123" t="n">
-        <v>38.78271012112215</v>
+        <v>38.78271054460242</v>
       </c>
       <c r="CB123" t="n">
-        <v>71.94192727468157</v>
+        <v>71.94192806023747</v>
       </c>
       <c r="CC123" t="n">
         <v>19.80852876618554</v>
@@ -52487,7 +52495,7 @@
       </c>
       <c r="CH123" t="inlineStr"/>
       <c r="CI123" t="n">
-        <v>25.97687178624113</v>
+        <v>25.97687185682118</v>
       </c>
       <c r="CJ123" t="n">
         <v>23.0354806164258</v>
@@ -52508,7 +52516,7 @@
         <v>-7.239676953330354</v>
       </c>
       <c r="CP123" t="n">
-        <v>16.22761227233995</v>
+        <v>16.22761258813432</v>
       </c>
       <c r="CQ123" t="inlineStr">
         <is>
@@ -52796,25 +52804,25 @@
         <v>9.090000152587891</v>
       </c>
       <c r="CA124" t="n">
-        <v>3.513201112167974</v>
+        <v>3.513201115858493</v>
       </c>
       <c r="CB124" t="n">
-        <v>3.627571357153372</v>
+        <v>3.627571360378641</v>
       </c>
       <c r="CC124" t="n">
-        <v>4.393334529221852</v>
+        <v>4.393334528512885</v>
       </c>
       <c r="CD124" t="n">
         <v>18.92946868244077</v>
       </c>
       <c r="CE124" t="n">
-        <v>3.454654098405184</v>
+        <v>3.454654100638801</v>
       </c>
       <c r="CF124" t="n">
-        <v>7.742523562394612</v>
+        <v>7.742523562245433</v>
       </c>
       <c r="CG124" t="n">
-        <v>1.736838692446771</v>
+        <v>1.736838691722543</v>
       </c>
       <c r="CH124" t="n">
         <v>21.77146113239846</v>
@@ -52946,8 +52954,16 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr"/>
-      <c r="T125" t="inlineStr"/>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Bandeira de alta</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Bandeira de alta (pré-confirmação) — pescoço R$5.71, preço 3.5% acima do pescoço; falta fechar acima e segurar</t>
+        </is>
+      </c>
       <c r="U125" t="b">
         <v>0</v>
       </c>
@@ -53414,10 +53430,10 @@
         <v>11.25</v>
       </c>
       <c r="CA126" t="n">
-        <v>0.7653059288413692</v>
+        <v>0.7653059283421771</v>
       </c>
       <c r="CB126" t="n">
-        <v>1.41964249800074</v>
+        <v>1.419642497074739</v>
       </c>
       <c r="CC126" t="n">
         <v>15.28846153846153</v>
@@ -53426,13 +53442,13 @@
         <v>15.93648555693364</v>
       </c>
       <c r="CE126" t="n">
-        <v>13.40813190888677</v>
+        <v>13.40813190899185</v>
       </c>
       <c r="CF126" t="n">
-        <v>1.648085085144817</v>
+        <v>1.648085085155425</v>
       </c>
       <c r="CG126" t="n">
-        <v>10.819648552009</v>
+        <v>10.8196485525256</v>
       </c>
       <c r="CH126" t="inlineStr"/>
       <c r="CI126" t="inlineStr"/>
@@ -53731,25 +53747,25 @@
         <v>18.46054267883301</v>
       </c>
       <c r="CA127" t="n">
-        <v>0.5760472926900004</v>
+        <v>0.576047294188069</v>
       </c>
       <c r="CB127" t="n">
-        <v>0.7744861400199492</v>
+        <v>0.7744861418973076</v>
       </c>
       <c r="CC127" t="n">
-        <v>4.579823771719387</v>
+        <v>4.579823770910615</v>
       </c>
       <c r="CD127" t="n">
         <v>11.45343257282958</v>
       </c>
       <c r="CE127" t="n">
-        <v>1.757660189684854</v>
+        <v>1.757660189406608</v>
       </c>
       <c r="CF127" t="n">
-        <v>0.674236713360962</v>
+        <v>0.6742367133497329</v>
       </c>
       <c r="CG127" t="n">
-        <v>2.247847913098706</v>
+        <v>2.24784791258325</v>
       </c>
       <c r="CH127" t="n">
         <v>18.46054267883301</v>
@@ -54058,10 +54074,10 @@
         <v>5.239999771118164</v>
       </c>
       <c r="CA128" t="n">
-        <v>1.294299775305172</v>
+        <v>1.294299766464892</v>
       </c>
       <c r="CB128" t="n">
-        <v>2.16618716939711</v>
+        <v>2.166187154601696</v>
       </c>
       <c r="CC128" t="inlineStr"/>
       <c r="CD128" t="inlineStr"/>
@@ -54072,13 +54088,13 @@
         <v>6.020931258896678</v>
       </c>
       <c r="CI128" t="n">
-        <v>1.730243472351141</v>
+        <v>1.730243460533294</v>
       </c>
       <c r="CJ128" t="n">
-        <v>1.730243472351141</v>
+        <v>1.730243460533294</v>
       </c>
       <c r="CK128" t="n">
-        <v>1.557219125116027</v>
+        <v>1.557219114479965</v>
       </c>
       <c r="CL128" t="n">
         <v>2</v>
@@ -54090,10 +54106,10 @@
         <v>4.7</v>
       </c>
       <c r="CO128" t="n">
-        <v>-70.28207646689015</v>
+        <v>-70.28207666986846</v>
       </c>
       <c r="CP128" t="n">
-        <v>-66.98008496321128</v>
+        <v>-66.98008518874272</v>
       </c>
       <c r="CQ128" t="inlineStr">
         <is>
@@ -54373,10 +54389,10 @@
         <v>17.5</v>
       </c>
       <c r="CA129" t="n">
-        <v>1.348184136393147</v>
+        <v>1.348184136113585</v>
       </c>
       <c r="CB129" t="n">
-        <v>1.962956102588422</v>
+        <v>1.96295610218138</v>
       </c>
       <c r="CC129" t="n">
         <v>1.254999310439939</v>
@@ -54688,37 +54704,37 @@
         <v>17.54999923706055</v>
       </c>
       <c r="CA130" t="n">
-        <v>2.114176576482695</v>
+        <v>2.11417657887995</v>
       </c>
       <c r="CB130" t="n">
-        <v>3.73012510077437</v>
+        <v>3.730125103069732</v>
       </c>
       <c r="CC130" t="n">
-        <v>9.632950376779688</v>
+        <v>9.632950371784643</v>
       </c>
       <c r="CD130" t="n">
         <v>11.96027571768681</v>
       </c>
       <c r="CE130" t="n">
-        <v>5.584250645719657</v>
+        <v>5.584250644103803</v>
       </c>
       <c r="CF130" t="n">
-        <v>5.535381010962628</v>
+        <v>5.535381010751614</v>
       </c>
       <c r="CG130" t="n">
-        <v>4.741756133990051</v>
+        <v>4.741756132055563</v>
       </c>
       <c r="CH130" t="n">
         <v>15.78993633088096</v>
       </c>
       <c r="CI130" t="n">
-        <v>6.864123164318868</v>
+        <v>6.864123163242028</v>
       </c>
       <c r="CJ130" t="n">
-        <v>5.559815828341143</v>
+        <v>5.559815827427709</v>
       </c>
       <c r="CK130" t="n">
-        <v>5.003834245507028</v>
+        <v>5.003834244684938</v>
       </c>
       <c r="CL130" t="n">
         <v>6</v>
@@ -54730,10 +54746,10 @@
         <v>7.5</v>
       </c>
       <c r="CO130" t="n">
-        <v>-71.48812271774707</v>
+        <v>-71.48812272243134</v>
       </c>
       <c r="CP130" t="n">
-        <v>-60.88818539761633</v>
+        <v>-60.88818540375218</v>
       </c>
       <c r="CQ130" t="inlineStr">
         <is>
@@ -55009,10 +55025,10 @@
         <v>4.329999923706055</v>
       </c>
       <c r="CA131" t="n">
-        <v>0.9105843953547605</v>
+        <v>0.9105843974141412</v>
       </c>
       <c r="CB131" t="n">
-        <v>1.689134053383081</v>
+        <v>1.689134057203232</v>
       </c>
       <c r="CC131" t="inlineStr"/>
       <c r="CD131" t="inlineStr"/>
@@ -55021,13 +55037,13 @@
       <c r="CG131" t="inlineStr"/>
       <c r="CH131" t="inlineStr"/>
       <c r="CI131" t="n">
-        <v>1.299859224368921</v>
+        <v>1.299859227308687</v>
       </c>
       <c r="CJ131" t="n">
-        <v>1.299859224368921</v>
+        <v>1.299859227308687</v>
       </c>
       <c r="CK131" t="n">
-        <v>1.169873301932029</v>
+        <v>1.169873304577818</v>
       </c>
       <c r="CL131" t="n">
         <v>2</v>
@@ -55039,10 +55055,10 @@
         <v>1.9</v>
       </c>
       <c r="CO131" t="n">
-        <v>-72.98214035692794</v>
+        <v>-72.98214029582427</v>
       </c>
       <c r="CP131" t="n">
-        <v>-69.98015595214217</v>
+        <v>-69.9801558842492</v>
       </c>
       <c r="CQ131" t="inlineStr">
         <is>
@@ -55328,10 +55344,10 @@
         <v>1.179999947547913</v>
       </c>
       <c r="CA132" t="n">
-        <v>0.3468781107904809</v>
+        <v>0.3468781106801614</v>
       </c>
       <c r="CB132" t="n">
-        <v>0.6434588955163419</v>
+        <v>0.6434588953116993</v>
       </c>
       <c r="CC132" t="inlineStr"/>
       <c r="CD132" t="inlineStr"/>
@@ -55340,13 +55356,13 @@
       <c r="CG132" t="inlineStr"/>
       <c r="CH132" t="inlineStr"/>
       <c r="CI132" t="n">
-        <v>0.4951685031534114</v>
+        <v>0.4951685029959303</v>
       </c>
       <c r="CJ132" t="n">
-        <v>0.4951685031534114</v>
+        <v>0.4951685029959303</v>
       </c>
       <c r="CK132" t="n">
-        <v>0.4456516528380703</v>
+        <v>0.4456516526963373</v>
       </c>
       <c r="CL132" t="n">
         <v>2</v>
@@ -55358,10 +55374,10 @@
         <v>1.9</v>
       </c>
       <c r="CO132" t="n">
-        <v>-62.23290909765274</v>
+        <v>-62.23290910966399</v>
       </c>
       <c r="CP132" t="n">
-        <v>-58.03656566405859</v>
+        <v>-58.03656567740444</v>
       </c>
       <c r="CQ132" t="inlineStr">
         <is>
@@ -55643,10 +55659,10 @@
         <v>5.46999979019165</v>
       </c>
       <c r="CA133" t="n">
-        <v>1.043475835227301</v>
+        <v>1.043475834682479</v>
       </c>
       <c r="CB133" t="n">
-        <v>1.935647674346644</v>
+        <v>1.935647673335999</v>
       </c>
       <c r="CC133" t="inlineStr"/>
       <c r="CD133" t="inlineStr"/>
@@ -55657,13 +55673,13 @@
         <v>3.086391414577443</v>
       </c>
       <c r="CI133" t="n">
-        <v>2.021838308050463</v>
+        <v>2.021838307531974</v>
       </c>
       <c r="CJ133" t="n">
-        <v>1.935647674346644</v>
+        <v>1.935647673335999</v>
       </c>
       <c r="CK133" t="n">
-        <v>1.742082906911979</v>
+        <v>1.742082906002399</v>
       </c>
       <c r="CL133" t="n">
         <v>3</v>
@@ -55675,10 +55691,10 @@
         <v>3</v>
       </c>
       <c r="CO133" t="n">
-        <v>-68.15204801221861</v>
+        <v>-68.15204802884713</v>
       </c>
       <c r="CP133" t="n">
-        <v>-63.03768947713937</v>
+        <v>-63.03768948661814</v>
       </c>
       <c r="CQ133" t="inlineStr">
         <is>
@@ -56275,10 +56291,10 @@
         <v>36.70999908447266</v>
       </c>
       <c r="CA135" t="n">
-        <v>8.268344958859641</v>
+        <v>8.268344974597303</v>
       </c>
       <c r="CB135" t="n">
-        <v>12.03871026009964</v>
+        <v>12.03871028301367</v>
       </c>
       <c r="CC135" t="n">
         <v>7.906067311627989</v>
@@ -56592,25 +56608,25 @@
         <v>4.920000076293945</v>
       </c>
       <c r="CA136" t="n">
-        <v>1.527407294560709</v>
+        <v>1.527407283632557</v>
       </c>
       <c r="CB136" t="n">
-        <v>1.686264662902466</v>
+        <v>1.686264653507533</v>
       </c>
       <c r="CC136" t="n">
-        <v>2.46962929140277</v>
+        <v>2.469629295312837</v>
       </c>
       <c r="CD136" t="n">
         <v>7.731331217553538</v>
       </c>
       <c r="CE136" t="n">
-        <v>1.727714300947225</v>
+        <v>1.727714296854062</v>
       </c>
       <c r="CF136" t="n">
-        <v>1.781877002054284</v>
+        <v>1.781877002371779</v>
       </c>
       <c r="CG136" t="n">
-        <v>1.067038605259917</v>
+        <v>1.067038608808507</v>
       </c>
       <c r="CH136" t="n">
         <v>0.3081571864153818</v>
@@ -56909,10 +56925,10 @@
         <v>2.220000028610229</v>
       </c>
       <c r="CA137" t="n">
-        <v>0.6232610201799459</v>
+        <v>0.6232610189298263</v>
       </c>
       <c r="CB137" t="n">
-        <v>0.9074680453820013</v>
+        <v>0.9074680435618272</v>
       </c>
       <c r="CC137" t="n">
         <v>0.3656057054243292</v>
@@ -57513,10 +57529,10 @@
         <v>6.869999885559082</v>
       </c>
       <c r="CA139" t="n">
-        <v>1.885299348071089</v>
+        <v>1.885299343805755</v>
       </c>
       <c r="CB139" t="n">
-        <v>2.744995850791506</v>
+        <v>2.74499584458118</v>
       </c>
       <c r="CC139" t="n">
         <v>1.690276763894357</v>
@@ -58739,10 +58755,10 @@
         <v>18.76000022888184</v>
       </c>
       <c r="CA143" t="n">
-        <v>28.4898616584154</v>
+        <v>28.48986172269697</v>
       </c>
       <c r="CB143" t="n">
-        <v>38.11310381859127</v>
+        <v>38.11310390458573</v>
       </c>
       <c r="CC143" t="n">
         <v>2.597626784658967</v>
@@ -58751,7 +58767,7 @@
         <v>7.205629833517744</v>
       </c>
       <c r="CE143" t="n">
-        <v>6.649616924362229</v>
+        <v>6.649616937402977</v>
       </c>
       <c r="CF143" t="n">
         <v>3.046690502845772</v>
@@ -59058,10 +59074,10 @@
         <v>3.710000038146973</v>
       </c>
       <c r="CA144" t="n">
-        <v>0.6711165078802589</v>
+        <v>0.6711165070072428</v>
       </c>
       <c r="CB144" t="n">
-        <v>1.24492112211788</v>
+        <v>1.244921120498435</v>
       </c>
       <c r="CC144" t="inlineStr"/>
       <c r="CD144" t="inlineStr"/>
@@ -59072,13 +59088,13 @@
         <v>3.383752809074293</v>
       </c>
       <c r="CI144" t="n">
-        <v>0.9580188149990696</v>
+        <v>0.9580188137528391</v>
       </c>
       <c r="CJ144" t="n">
-        <v>0.9580188149990696</v>
+        <v>0.9580188137528391</v>
       </c>
       <c r="CK144" t="n">
-        <v>0.8622169334991626</v>
+        <v>0.8622169323775553</v>
       </c>
       <c r="CL144" t="n">
         <v>2</v>
@@ -59090,10 +59106,10 @@
         <v>5</v>
       </c>
       <c r="CO144" t="n">
-        <v>-76.7596516271247</v>
+        <v>-76.75965165735673</v>
       </c>
       <c r="CP144" t="n">
-        <v>-74.17739069680523</v>
+        <v>-74.17739073039635</v>
       </c>
       <c r="CQ144" t="inlineStr">
         <is>
@@ -59375,10 +59391,10 @@
         <v>18.79000091552734</v>
       </c>
       <c r="CA145" t="n">
-        <v>9.525161241221076</v>
+        <v>9.525161233132909</v>
       </c>
       <c r="CB145" t="n">
-        <v>13.86863476721789</v>
+        <v>13.86863475544152</v>
       </c>
       <c r="CC145" t="n">
         <v>4.657197557709351</v>
@@ -60326,10 +60342,10 @@
         <v>10.85999965667725</v>
       </c>
       <c r="CA148" t="n">
-        <v>5.802515947022678</v>
+        <v>5.802515941114286</v>
       </c>
       <c r="CB148" t="n">
-        <v>10.62075326303188</v>
+        <v>10.62075325221733</v>
       </c>
       <c r="CC148" t="inlineStr"/>
       <c r="CD148" t="inlineStr"/>
@@ -60340,13 +60356,13 @@
         <v>3.332701500657688</v>
       </c>
       <c r="CI148" t="n">
-        <v>6.585323570237414</v>
+        <v>6.585323564663102</v>
       </c>
       <c r="CJ148" t="n">
-        <v>5.802515947022678</v>
+        <v>5.802515941114286</v>
       </c>
       <c r="CK148" t="n">
-        <v>5.22226435232041</v>
+        <v>5.222264347002858</v>
       </c>
       <c r="CL148" t="n">
         <v>3</v>
@@ -60358,10 +60374,10 @@
         <v>3.2</v>
       </c>
       <c r="CO148" t="n">
-        <v>-51.9128497475641</v>
+        <v>-51.91284979652868</v>
       </c>
       <c r="CP148" t="n">
-        <v>-39.36165949887076</v>
+        <v>-39.36165955019961</v>
       </c>
       <c r="CQ148" t="inlineStr">
         <is>
@@ -60964,10 +60980,10 @@
         <v>15.42000007629395</v>
       </c>
       <c r="CA150" t="n">
-        <v>3.945356585556625</v>
+        <v>3.945356597309724</v>
       </c>
       <c r="CB150" t="n">
-        <v>5.744439188570447</v>
+        <v>5.744439205682959</v>
       </c>
       <c r="CC150" t="inlineStr"/>
       <c r="CD150" t="inlineStr"/>
@@ -60978,7 +60994,7 @@
         <v>5.488479853420727</v>
       </c>
       <c r="CI150" t="n">
-        <v>5.059425209182599</v>
+        <v>5.059425218804471</v>
       </c>
       <c r="CJ150" t="n">
         <v>5.488479853420727</v>
@@ -60999,7 +61015,7 @@
         <v>-67.96607105292668</v>
       </c>
       <c r="CP150" t="n">
-        <v>-67.18920114040242</v>
+        <v>-67.18920107800376</v>
       </c>
       <c r="CQ150" t="inlineStr">
         <is>

--- a/reports/screener_2026-08-29.xlsx
+++ b/reports/screener_2026-08-29.xlsx
@@ -1206,10 +1206,10 @@
         <v>10.35999965667725</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.851607480570364</v>
+        <v>5.851607491869938</v>
       </c>
       <c r="CB2" t="n">
-        <v>10.85473187645802</v>
+        <v>10.85473189741873</v>
       </c>
       <c r="CC2" t="n">
         <v>41.59696831847682</v>
@@ -1218,7 +1218,7 @@
         <v>27.90166392450355</v>
       </c>
       <c r="CE2" t="n">
-        <v>71.91590896307387</v>
+        <v>71.91590901101146</v>
       </c>
       <c r="CF2" t="n">
         <v>19.57807411896471</v>
@@ -1529,10 +1529,10 @@
         <v>13.46000003814697</v>
       </c>
       <c r="CA3" t="n">
-        <v>14.84732055865599</v>
+        <v>14.84732050446674</v>
       </c>
       <c r="CB3" t="n">
-        <v>27.54177963630687</v>
+        <v>27.54177953578581</v>
       </c>
       <c r="CC3" t="n">
         <v>38.93995644223742</v>
@@ -1541,13 +1541,13 @@
         <v>23.51205793312256</v>
       </c>
       <c r="CE3" t="n">
-        <v>75.54482861675247</v>
+        <v>75.54482871709098</v>
       </c>
       <c r="CF3" t="n">
-        <v>48.52515938780768</v>
+        <v>48.5251594276379</v>
       </c>
       <c r="CG3" t="n">
-        <v>26.80868498393435</v>
+        <v>26.80868515112335</v>
       </c>
       <c r="CH3" t="n">
         <v>8.920136085713818</v>
@@ -1852,10 +1852,10 @@
         <v>24.61000061035156</v>
       </c>
       <c r="CA4" t="n">
-        <v>16.31411909286777</v>
+        <v>16.31411910363583</v>
       </c>
       <c r="CB4" t="n">
-        <v>30.26269091726972</v>
+        <v>30.26269093724446</v>
       </c>
       <c r="CC4" t="n">
         <v>72.30210822331667</v>
@@ -1864,19 +1864,19 @@
         <v>52.41049602817493</v>
       </c>
       <c r="CE4" t="n">
-        <v>127.9950261358423</v>
+        <v>127.9950261325152</v>
       </c>
       <c r="CF4" t="n">
-        <v>25.73142365748924</v>
+        <v>25.7314236559713</v>
       </c>
       <c r="CG4" t="n">
-        <v>63.19894120787374</v>
+        <v>63.19894118477155</v>
       </c>
       <c r="CH4" t="n">
         <v>42.85100954601229</v>
       </c>
       <c r="CI4" t="n">
-        <v>47.7927782633561</v>
+        <v>47.79277826258186</v>
       </c>
       <c r="CJ4" t="n">
         <v>47.63075278709361</v>
@@ -1897,7 +1897,7 @@
         <v>74.18803919229917</v>
       </c>
       <c r="CP4" t="n">
-        <v>94.20063826919736</v>
+        <v>94.20063826605134</v>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
@@ -2183,10 +2183,10 @@
         <v>4.119999885559082</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.742641502759139</v>
+        <v>3.742641509775883</v>
       </c>
       <c r="CB5" t="n">
-        <v>6.942599987618202</v>
+        <v>6.942600000634262</v>
       </c>
       <c r="CC5" t="n">
         <v>12.63657372306894</v>
@@ -2195,19 +2195,19 @@
         <v>8.512687176725057</v>
       </c>
       <c r="CE5" t="n">
-        <v>24.29899390450435</v>
+        <v>24.29899389942381</v>
       </c>
       <c r="CF5" t="n">
-        <v>11.19276559323877</v>
+        <v>11.19276559034328</v>
       </c>
       <c r="CG5" t="n">
-        <v>10.19750520591305</v>
+        <v>10.1975051884262</v>
       </c>
       <c r="CH5" t="n">
         <v>5.258139118319559</v>
       </c>
       <c r="CI5" t="n">
-        <v>8.354701758234674</v>
+        <v>8.35470175818474</v>
       </c>
       <c r="CJ5" t="n">
         <v>8.512687176725057</v>
@@ -2228,7 +2228,7 @@
         <v>85.95676388017426</v>
       </c>
       <c r="CP5" t="n">
-        <v>102.7840288908393</v>
+        <v>102.7840288896273</v>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>-0.4233949874864695</v>
       </c>
       <c r="DC5" t="n">
-        <v>-36.92337647573303</v>
+        <v>-36.92338129060463</v>
       </c>
       <c r="DD5" t="b">
         <v>1</v>
@@ -2516,10 +2516,10 @@
         <v>4.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.282970774499373</v>
+        <v>3.282970791652486</v>
       </c>
       <c r="CB6" t="n">
-        <v>6.089910786696336</v>
+        <v>6.089910818515362</v>
       </c>
       <c r="CC6" t="n">
         <v>12.96195652173913</v>
@@ -2528,7 +2528,7 @@
         <v>8.728772626887835</v>
       </c>
       <c r="CE6" t="n">
-        <v>24.66556322673722</v>
+        <v>24.66556327894235</v>
       </c>
       <c r="CF6" t="n">
         <v>11.57513776217851</v>
@@ -2540,7 +2540,7 @@
         <v>5.383571029035719</v>
       </c>
       <c r="CI6" t="n">
-        <v>11.60598121071627</v>
+        <v>11.60598122271972</v>
       </c>
       <c r="CJ6" t="n">
         <v>11.57513776217851</v>
@@ -2561,7 +2561,7 @@
         <v>131.5027552435702</v>
       </c>
       <c r="CP6" t="n">
-        <v>157.9106935714727</v>
+        <v>157.910693838216</v>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
@@ -2839,10 +2839,10 @@
         <v>48.34000015258789</v>
       </c>
       <c r="CA7" t="n">
-        <v>18.42191766567338</v>
+        <v>18.4219176096249</v>
       </c>
       <c r="CB7" t="n">
-        <v>34.17265726982411</v>
+        <v>34.17265716585418</v>
       </c>
       <c r="CC7" t="n">
         <v>74.65093263657221</v>
@@ -2851,23 +2851,23 @@
         <v>55.91472932652801</v>
       </c>
       <c r="CE7" t="n">
-        <v>99.8344549538902</v>
+        <v>99.83445504165644</v>
       </c>
       <c r="CF7" t="n">
-        <v>48.37202136328627</v>
+        <v>48.37202137697793</v>
       </c>
       <c r="CG7" t="n">
-        <v>58.90972724054575</v>
+        <v>58.9097273531987</v>
       </c>
       <c r="CH7" t="inlineStr"/>
       <c r="CI7" t="n">
-        <v>43.90438223383899</v>
+        <v>43.90438219725731</v>
       </c>
       <c r="CJ7" t="n">
-        <v>41.27233931655519</v>
+        <v>41.27233927141606</v>
       </c>
       <c r="CK7" t="n">
-        <v>37.14510538489967</v>
+        <v>37.14510534427446</v>
       </c>
       <c r="CL7" t="n">
         <v>4</v>
@@ -2879,10 +2879,10 @@
         <v>4.1</v>
       </c>
       <c r="CO7" t="n">
-        <v>-23.15865687288149</v>
+        <v>-23.15865695692207</v>
       </c>
       <c r="CP7" t="n">
-        <v>-9.175874854670296</v>
+        <v>-9.175874930346117</v>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         <v>15.69999980926514</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.403272784300161</v>
+        <v>6.403272785622092</v>
       </c>
       <c r="CB8" t="n">
-        <v>11.8780710148768</v>
+        <v>11.87807101732898</v>
       </c>
       <c r="CC8" t="n">
         <v>25.39987759130195</v>
@@ -3182,19 +3182,19 @@
         <v>18.63509665364473</v>
       </c>
       <c r="CE8" t="n">
-        <v>35.24419673265818</v>
+        <v>35.24419673051138</v>
       </c>
       <c r="CF8" t="n">
-        <v>12.29886962111222</v>
+        <v>12.29886962086131</v>
       </c>
       <c r="CG8" t="n">
-        <v>20.39435315503992</v>
+        <v>20.3943531522701</v>
       </c>
       <c r="CH8" t="n">
         <v>18.40902666520164</v>
       </c>
       <c r="CI8" t="n">
-        <v>20.32278449054792</v>
+        <v>20.32278449016001</v>
       </c>
       <c r="CJ8" t="n">
         <v>18.63509665364473</v>
@@ -3215,7 +3215,7 @@
         <v>6.825396127602112</v>
       </c>
       <c r="CP8" t="n">
-        <v>29.44448877352668</v>
+        <v>29.44448877105594</v>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
@@ -3505,10 +3505,10 @@
         <v>42.70000076293945</v>
       </c>
       <c r="CA9" t="n">
-        <v>125.1015273012702</v>
+        <v>125.1015273821003</v>
       </c>
       <c r="CB9" t="n">
-        <v>232.0633331438562</v>
+        <v>232.0633332937961</v>
       </c>
       <c r="CC9" t="n">
         <v>134.3883634463059</v>
@@ -3529,13 +3529,13 @@
         <v>54.40212095818906</v>
       </c>
       <c r="CI9" t="n">
-        <v>140.0386116444515</v>
+        <v>140.0386116732977</v>
       </c>
       <c r="CJ9" t="n">
-        <v>123.9129975261182</v>
+        <v>123.9129975665332</v>
       </c>
       <c r="CK9" t="n">
-        <v>111.5216977735063</v>
+        <v>111.5216978098799</v>
       </c>
       <c r="CL9" t="n">
         <v>8</v>
@@ -3547,10 +3547,10 @@
         <v>5.6</v>
       </c>
       <c r="CO9" t="n">
-        <v>161.1749315711938</v>
+        <v>161.1749316563777</v>
       </c>
       <c r="CP9" t="n">
-        <v>227.9592719960674</v>
+        <v>227.9592720636231</v>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>32.47999954223633</v>
       </c>
       <c r="CA10" t="n">
-        <v>45.35763192753625</v>
+        <v>45.35763236666469</v>
       </c>
       <c r="CB10" t="n">
-        <v>84.13840722557973</v>
+        <v>84.13840804016299</v>
       </c>
       <c r="CC10" t="n">
         <v>68.20285165366582</v>
@@ -3862,7 +3862,7 @@
         <v>25.67266223983068</v>
       </c>
       <c r="CI10" t="n">
-        <v>77.37745275702851</v>
+        <v>77.37745293613018</v>
       </c>
       <c r="CJ10" t="n">
         <v>68.20285165366582</v>
@@ -3883,7 +3883,7 @@
         <v>88.98573692551506</v>
       </c>
       <c r="CP10" t="n">
-        <v>138.2310771168837</v>
+        <v>138.2310776683051</v>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
@@ -4179,37 +4179,37 @@
         <v>32.84999847412109</v>
       </c>
       <c r="CA11" t="n">
-        <v>24.40198167129093</v>
+        <v>24.40198158437201</v>
       </c>
       <c r="CB11" t="n">
-        <v>32.23832874511812</v>
+        <v>32.23832936630178</v>
       </c>
       <c r="CC11" t="n">
-        <v>33.8053475634636</v>
+        <v>33.80534833525467</v>
       </c>
       <c r="CD11" t="n">
         <v>20.85130777065122</v>
       </c>
       <c r="CE11" t="n">
-        <v>48.27773753216625</v>
+        <v>48.27773820722045</v>
       </c>
       <c r="CF11" t="n">
-        <v>50.84601668507388</v>
+        <v>50.8460167963005</v>
       </c>
       <c r="CG11" t="n">
-        <v>16.4985676034022</v>
+        <v>16.49856811113381</v>
       </c>
       <c r="CH11" t="n">
         <v>24.29339039885633</v>
       </c>
       <c r="CI11" t="n">
-        <v>31.40158474625282</v>
+        <v>31.40158507126135</v>
       </c>
       <c r="CJ11" t="n">
-        <v>28.32015520820453</v>
+        <v>28.3201554753369</v>
       </c>
       <c r="CK11" t="n">
-        <v>25.48813968738407</v>
+        <v>25.48813992780321</v>
       </c>
       <c r="CL11" t="n">
         <v>8</v>
@@ -4221,10 +4221,10 @@
         <v>3.1</v>
       </c>
       <c r="CO11" t="n">
-        <v>-22.4105300721296</v>
+        <v>-22.41052934026006</v>
       </c>
       <c r="CP11" t="n">
-        <v>-4.409174414450357</v>
+        <v>-4.409173425078827</v>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
@@ -4341,8 +4341,16 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Bandeira de alta</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Bandeira de alta (pré-confirmação) — pescoço R$48.12, preço 1.7% abaixo do pescoço; falta fechar acima e segurar</t>
+        </is>
+      </c>
       <c r="U12" t="b">
         <v>0</v>
       </c>
@@ -4514,10 +4522,10 @@
         <v>47.31000137329102</v>
       </c>
       <c r="CA12" t="n">
-        <v>131.3186533008917</v>
+        <v>131.3186532722856</v>
       </c>
       <c r="CB12" t="n">
-        <v>243.5961018731541</v>
+        <v>243.5961018200898</v>
       </c>
       <c r="CC12" t="n">
         <v>134.5187807287781</v>
@@ -4538,13 +4546,13 @@
         <v>53.17581509382557</v>
       </c>
       <c r="CI12" t="n">
-        <v>142.2124817469415</v>
+        <v>142.2124817367327</v>
       </c>
       <c r="CJ12" t="n">
-        <v>127.0811095492464</v>
+        <v>127.0811095349434</v>
       </c>
       <c r="CK12" t="n">
-        <v>114.3729985943218</v>
+        <v>114.372998581449</v>
       </c>
       <c r="CL12" t="n">
         <v>8</v>
@@ -4556,10 +4564,10 @@
         <v>5.7</v>
       </c>
       <c r="CO12" t="n">
-        <v>141.7522622582111</v>
+        <v>141.7522622310018</v>
       </c>
       <c r="CP12" t="n">
-        <v>200.5970780360788</v>
+        <v>200.5970780145003</v>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
@@ -4847,10 +4855,10 @@
         <v>7.239999771118164</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.268913162743343</v>
+        <v>3.268913181465356</v>
       </c>
       <c r="CB13" t="n">
-        <v>6.0638339168889</v>
+        <v>6.063833951618235</v>
       </c>
       <c r="CC13" t="n">
         <v>20.4541571358882</v>
@@ -4859,7 +4867,7 @@
         <v>14.0164620450613</v>
       </c>
       <c r="CE13" t="n">
-        <v>32.91359932733033</v>
+        <v>32.91359938321693</v>
       </c>
       <c r="CF13" t="n">
         <v>10.95072400487419</v>
@@ -5152,10 +5160,10 @@
         <v>19.30999946594238</v>
       </c>
       <c r="CA14" t="n">
-        <v>13.27286329671517</v>
+        <v>13.27286328520698</v>
       </c>
       <c r="CB14" t="n">
-        <v>24.62116141540664</v>
+        <v>24.62116139405894</v>
       </c>
       <c r="CC14" t="n">
         <v>19.98886663466692</v>
@@ -5164,7 +5172,7 @@
         <v>12.49234273346821</v>
       </c>
       <c r="CE14" t="n">
-        <v>33.8271936967246</v>
+        <v>33.82719368413751</v>
       </c>
       <c r="CF14" t="n">
         <v>22.8984489302328</v>
@@ -5174,7 +5182,7 @@
       </c>
       <c r="CH14" t="inlineStr"/>
       <c r="CI14" t="n">
-        <v>20.19533506925538</v>
+        <v>20.1953350610414</v>
       </c>
       <c r="CJ14" t="n">
         <v>21.44365778244985</v>
@@ -5195,7 +5203,7 @@
         <v>-0.05545034714474761</v>
       </c>
       <c r="CP14" t="n">
-        <v>4.584855659237519</v>
+        <v>4.584855616700123</v>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
@@ -5491,10 +5499,10 @@
         <v>17.21999931335449</v>
       </c>
       <c r="CA15" t="n">
-        <v>10.55474915901828</v>
+        <v>10.55474910382358</v>
       </c>
       <c r="CB15" t="n">
-        <v>19.57905968997891</v>
+        <v>19.57905958759274</v>
       </c>
       <c r="CC15" t="n">
         <v>37.03977125031607</v>
@@ -5503,25 +5511,25 @@
         <v>36.56718452753732</v>
       </c>
       <c r="CE15" t="n">
-        <v>41.35653256221261</v>
+        <v>41.35653253861537</v>
       </c>
       <c r="CF15" t="n">
-        <v>34.51133418750026</v>
+        <v>34.51133419933809</v>
       </c>
       <c r="CG15" t="n">
-        <v>18.38517851415616</v>
+        <v>18.38517857817317</v>
       </c>
       <c r="CH15" t="n">
         <v>31.59171947190627</v>
       </c>
       <c r="CI15" t="n">
-        <v>31.29011145765823</v>
+        <v>31.290111450497</v>
       </c>
       <c r="CJ15" t="n">
-        <v>34.51133418750026</v>
+        <v>34.51133419933809</v>
       </c>
       <c r="CK15" t="n">
-        <v>31.06020076875024</v>
+        <v>31.06020077940428</v>
       </c>
       <c r="CL15" t="n">
         <v>7</v>
@@ -5533,10 +5541,10 @@
         <v>3.9</v>
       </c>
       <c r="CO15" t="n">
-        <v>80.37283395628454</v>
+        <v>80.37283401815472</v>
       </c>
       <c r="CP15" t="n">
-        <v>81.70797157577152</v>
+        <v>81.70797153418481</v>
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
@@ -5824,37 +5832,37 @@
         <v>10.10999965667725</v>
       </c>
       <c r="CA16" t="n">
-        <v>10.1314312053109</v>
+        <v>10.13143126652837</v>
       </c>
       <c r="CB16" t="n">
-        <v>18.70783454234331</v>
+        <v>18.70783436878482</v>
       </c>
       <c r="CC16" t="n">
-        <v>24.60234696522342</v>
+        <v>24.60234658832414</v>
       </c>
       <c r="CD16" t="n">
         <v>17.7286584153084</v>
       </c>
       <c r="CE16" t="n">
-        <v>37.29788770493122</v>
+        <v>37.29788764965343</v>
       </c>
       <c r="CF16" t="n">
-        <v>24.22484089934649</v>
+        <v>24.22484087319202</v>
       </c>
       <c r="CG16" t="n">
-        <v>11.97788237532717</v>
+        <v>11.97788224118745</v>
       </c>
       <c r="CH16" t="n">
         <v>10.10999965667725</v>
       </c>
       <c r="CI16" t="n">
-        <v>19.34761022055851</v>
+        <v>19.34761013245699</v>
       </c>
       <c r="CJ16" t="n">
-        <v>18.21824647882585</v>
+        <v>18.21824639204661</v>
       </c>
       <c r="CK16" t="n">
-        <v>16.39642183094327</v>
+        <v>16.39642175284195</v>
       </c>
       <c r="CL16" t="n">
         <v>8</v>
@@ -5866,10 +5874,10 @@
         <v>3.7</v>
       </c>
       <c r="CO16" t="n">
-        <v>62.18024122398555</v>
+        <v>62.18024045146999</v>
       </c>
       <c r="CP16" t="n">
-        <v>91.37102747357859</v>
+        <v>91.371026602149</v>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
@@ -6159,10 +6167,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="CA17" t="n">
-        <v>5.04484953672942</v>
+        <v>5.044849568253714</v>
       </c>
       <c r="CB17" t="n">
-        <v>9.358195890633075</v>
+        <v>9.358195949110639</v>
       </c>
       <c r="CC17" t="n">
         <v>8.579313567043014</v>
@@ -6482,10 +6490,10 @@
         <v>10.97000026702881</v>
       </c>
       <c r="CA18" t="n">
-        <v>9.497073368273673</v>
+        <v>9.497073350591037</v>
       </c>
       <c r="CB18" t="n">
-        <v>17.61707109814766</v>
+        <v>17.61707106534638</v>
       </c>
       <c r="CC18" t="n">
         <v>21.98978873496697</v>
@@ -6494,25 +6502,25 @@
         <v>12.98356721691296</v>
       </c>
       <c r="CE18" t="n">
-        <v>32.25283425643481</v>
+        <v>32.25283431003437</v>
       </c>
       <c r="CF18" t="n">
-        <v>25.36723517344997</v>
+        <v>25.36723518641875</v>
       </c>
       <c r="CG18" t="n">
-        <v>12.0631233417318</v>
+        <v>12.06312339896413</v>
       </c>
       <c r="CH18" t="n">
         <v>9.632374997322403</v>
       </c>
       <c r="CI18" t="n">
-        <v>17.67538352340503</v>
+        <v>17.67538353256962</v>
       </c>
       <c r="CJ18" t="n">
-        <v>15.30031915753031</v>
+        <v>15.30031914112967</v>
       </c>
       <c r="CK18" t="n">
-        <v>13.77028724177728</v>
+        <v>13.7702872270167</v>
       </c>
       <c r="CL18" t="n">
         <v>8</v>
@@ -6524,10 +6532,10 @@
         <v>3.4</v>
       </c>
       <c r="CO18" t="n">
-        <v>25.52677216576697</v>
+        <v>25.52677203121294</v>
       </c>
       <c r="CP18" t="n">
-        <v>61.12473193396153</v>
+        <v>61.12473201750384</v>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
@@ -6815,10 +6823,10 @@
         <v>10.63000011444092</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.315435262656715</v>
+        <v>3.315435255587584</v>
       </c>
       <c r="CB19" t="n">
-        <v>6.150132412228205</v>
+        <v>6.150132399114969</v>
       </c>
       <c r="CC19" t="n">
         <v>19.53502101474926</v>
@@ -6827,13 +6835,13 @@
         <v>18.41366451165369</v>
       </c>
       <c r="CE19" t="n">
-        <v>20.99443609200229</v>
+        <v>20.99443609253708</v>
       </c>
       <c r="CF19" t="n">
-        <v>15.9343722529959</v>
+        <v>15.93437225439872</v>
       </c>
       <c r="CG19" t="n">
-        <v>13.08852150867985</v>
+        <v>13.08852151764407</v>
       </c>
       <c r="CH19" t="n">
         <v>29.73646810990179</v>
@@ -7138,10 +7146,10 @@
         <v>27.42000007629395</v>
       </c>
       <c r="CA20" t="n">
-        <v>7.265285082105257</v>
+        <v>7.265285107589708</v>
       </c>
       <c r="CB20" t="n">
-        <v>13.47710382730525</v>
+        <v>13.47710387457891</v>
       </c>
       <c r="CC20" t="n">
         <v>35.82988175649849</v>
@@ -7150,19 +7158,19 @@
         <v>28.32096620307184</v>
       </c>
       <c r="CE20" t="n">
-        <v>44.64824884995695</v>
+        <v>44.64824881193085</v>
       </c>
       <c r="CF20" t="n">
-        <v>26.46426766182362</v>
+        <v>26.46426765547184</v>
       </c>
       <c r="CG20" t="n">
-        <v>28.98335743954201</v>
+        <v>28.98335739352322</v>
       </c>
       <c r="CH20" t="n">
         <v>24.27856406616775</v>
       </c>
       <c r="CI20" t="n">
-        <v>28.85748425776656</v>
+        <v>28.85748425160613</v>
       </c>
       <c r="CJ20" t="n">
         <v>28.32096620307184</v>
@@ -7183,7 +7191,7 @@
         <v>-7.042780773727464</v>
       </c>
       <c r="CP20" t="n">
-        <v>5.242466000995383</v>
+        <v>5.242465978528443</v>
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
@@ -7479,10 +7487,10 @@
         <v>22.60000038146973</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.184692833654026</v>
+        <v>3.184692830772003</v>
       </c>
       <c r="CB21" t="n">
-        <v>5.907605206428219</v>
+        <v>5.907605201082066</v>
       </c>
       <c r="CC21" t="n">
         <v>33.79796896777358</v>
@@ -7491,7 +7499,7 @@
         <v>28.20908778885038</v>
       </c>
       <c r="CE21" t="n">
-        <v>43.29409767417634</v>
+        <v>43.29409766962235</v>
       </c>
       <c r="CF21" t="n">
         <v>10.85340539909456</v>
@@ -7782,10 +7790,10 @@
         <v>39.45000076293945</v>
       </c>
       <c r="CA22" t="n">
-        <v>36.119665776403</v>
+        <v>36.11966575775509</v>
       </c>
       <c r="CB22" t="n">
-        <v>52.59023337044277</v>
+        <v>52.59023334329141</v>
       </c>
       <c r="CC22" t="n">
         <v>48.55384709284856</v>
@@ -7802,13 +7810,13 @@
       </c>
       <c r="CH22" t="inlineStr"/>
       <c r="CI22" t="n">
-        <v>49.19197780587801</v>
+        <v>49.19197779442819</v>
       </c>
       <c r="CJ22" t="n">
-        <v>50.57204023164567</v>
+        <v>50.57204021806999</v>
       </c>
       <c r="CK22" t="n">
-        <v>45.5148362084811</v>
+        <v>45.51483619626299</v>
       </c>
       <c r="CL22" t="n">
         <v>4</v>
@@ -7820,10 +7828,10 @@
         <v>1.6</v>
       </c>
       <c r="CO22" t="n">
-        <v>15.37347358238619</v>
+        <v>15.37347355141507</v>
       </c>
       <c r="CP22" t="n">
-        <v>24.69449139298996</v>
+        <v>24.69449136396633</v>
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
@@ -8119,10 +8127,10 @@
         <v>34.68999862670898</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.441930984802076</v>
+        <v>3.441930999778089</v>
       </c>
       <c r="CB23" t="n">
-        <v>6.384781976807851</v>
+        <v>6.384782004588356</v>
       </c>
       <c r="CC23" t="n">
         <v>32.87857523633004</v>
@@ -8131,7 +8139,7 @@
         <v>23.03538757661248</v>
       </c>
       <c r="CE23" t="n">
-        <v>40.66788363289441</v>
+        <v>40.66788364789184</v>
       </c>
       <c r="CF23" t="n">
         <v>10.59424454785779</v>
@@ -8422,35 +8430,35 @@
         <v>12.84000015258789</v>
       </c>
       <c r="CA24" t="n">
-        <v>8.620481287043701</v>
+        <v>8.620481286504914</v>
       </c>
       <c r="CB24" t="n">
-        <v>13.75169161039808</v>
+        <v>13.75169161101834</v>
       </c>
       <c r="CC24" t="n">
-        <v>18.28822757110052</v>
+        <v>18.28822757306843</v>
       </c>
       <c r="CD24" t="n">
         <v>17.29599079072038</v>
       </c>
       <c r="CE24" t="n">
-        <v>22.79369014118592</v>
+        <v>22.79369014170337</v>
       </c>
       <c r="CF24" t="n">
-        <v>17.32774436609555</v>
+        <v>17.32774436624598</v>
       </c>
       <c r="CG24" t="n">
-        <v>9.132575866807965</v>
+        <v>9.132575867725885</v>
       </c>
       <c r="CH24" t="inlineStr"/>
       <c r="CI24" t="n">
-        <v>14.49703620865946</v>
+        <v>14.49703620920942</v>
       </c>
       <c r="CJ24" t="n">
-        <v>15.53971798824681</v>
+        <v>15.53971798863216</v>
       </c>
       <c r="CK24" t="n">
-        <v>13.98574618942213</v>
+        <v>13.98574618976895</v>
       </c>
       <c r="CL24" t="n">
         <v>4</v>
@@ -8462,10 +8470,10 @@
         <v>2.1</v>
       </c>
       <c r="CO24" t="n">
-        <v>8.923255632542325</v>
+        <v>8.923255635243388</v>
       </c>
       <c r="CP24" t="n">
-        <v>12.90526508083876</v>
+        <v>12.90526508512191</v>
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
@@ -8739,10 +8747,10 @@
         <v>39.09999847412109</v>
       </c>
       <c r="CA25" t="n">
-        <v>19.98838175923153</v>
+        <v>19.98838182642474</v>
       </c>
       <c r="CB25" t="n">
-        <v>37.07844816337448</v>
+        <v>37.0784482880179</v>
       </c>
       <c r="CC25" t="n">
         <v>55.88726858490879</v>
@@ -8751,23 +8759,23 @@
         <v>42.23733079208057</v>
       </c>
       <c r="CE25" t="n">
-        <v>62.05594551296399</v>
+        <v>62.05594540325415</v>
       </c>
       <c r="CF25" t="n">
-        <v>45.209434519073</v>
+        <v>45.20943449802702</v>
       </c>
       <c r="CG25" t="n">
-        <v>31.29948467684047</v>
+        <v>31.29948454409355</v>
       </c>
       <c r="CH25" t="inlineStr"/>
       <c r="CI25" t="n">
-        <v>39.54088325664695</v>
+        <v>39.54088329934461</v>
       </c>
       <c r="CJ25" t="n">
-        <v>41.14394134122374</v>
+        <v>41.14394139302246</v>
       </c>
       <c r="CK25" t="n">
-        <v>37.02954720710137</v>
+        <v>37.02954725372022</v>
       </c>
       <c r="CL25" t="n">
         <v>4</v>
@@ -8779,10 +8787,10 @@
         <v>2.8</v>
       </c>
       <c r="CO25" t="n">
-        <v>-5.295271989307326</v>
+        <v>-5.295271870077523</v>
       </c>
       <c r="CP25" t="n">
-        <v>1.127582608008693</v>
+        <v>1.127582717209874</v>
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
@@ -9078,10 +9086,10 @@
         <v>6.010000228881836</v>
       </c>
       <c r="CA26" t="n">
-        <v>7.129143010811095</v>
+        <v>7.12914305894854</v>
       </c>
       <c r="CB26" t="n">
-        <v>13.22456028505458</v>
+        <v>13.22456037434954</v>
       </c>
       <c r="CC26" t="n">
         <v>5.700250753950201</v>
@@ -9102,7 +9110,7 @@
         <v>5.504458217875779</v>
       </c>
       <c r="CI26" t="n">
-        <v>7.427901843918459</v>
+        <v>7.427901861097509</v>
       </c>
       <c r="CJ26" t="n">
         <v>5.916792043641768</v>
@@ -9123,7 +9131,7 @@
         <v>-11.39579639802557</v>
       </c>
       <c r="CP26" t="n">
-        <v>23.59237206385971</v>
+        <v>23.5923723497008</v>
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
@@ -9395,10 +9403,10 @@
         <v>14.96000003814697</v>
       </c>
       <c r="CA27" t="n">
-        <v>9.299118729791529</v>
+        <v>9.299118859309983</v>
       </c>
       <c r="CB27" t="n">
-        <v>17.24986524376328</v>
+        <v>17.24986548402002</v>
       </c>
       <c r="CC27" t="n">
         <v>30.82737177378653</v>
@@ -9407,23 +9415,23 @@
         <v>29.3357145487105</v>
       </c>
       <c r="CE27" t="n">
-        <v>34.72617271536686</v>
+        <v>34.7261727411532</v>
       </c>
       <c r="CF27" t="n">
-        <v>25.49555040258641</v>
+        <v>25.49555037615469</v>
       </c>
       <c r="CG27" t="n">
-        <v>15.31657776985891</v>
+        <v>15.31657760881048</v>
       </c>
       <c r="CH27" t="inlineStr"/>
       <c r="CI27" t="n">
-        <v>20.71797653748194</v>
+        <v>20.7179766233178</v>
       </c>
       <c r="CJ27" t="n">
-        <v>21.37270782317485</v>
+        <v>21.37270793008735</v>
       </c>
       <c r="CK27" t="n">
-        <v>19.23543704085737</v>
+        <v>19.23543713707862</v>
       </c>
       <c r="CL27" t="n">
         <v>4</v>
@@ -9435,10 +9443,10 @@
         <v>3.3</v>
       </c>
       <c r="CO27" t="n">
-        <v>28.57912427679361</v>
+        <v>28.57912491998378</v>
       </c>
       <c r="CP27" t="n">
-        <v>38.48914762468263</v>
+        <v>38.48914819845177</v>
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
@@ -9477,7 +9485,7 @@
         <v>-3.17151959331623</v>
       </c>
       <c r="DC27" t="n">
-        <v>-17.75794205146741</v>
+        <v>-17.75793314155376</v>
       </c>
       <c r="DD27" t="b">
         <v>1</v>
@@ -9726,37 +9734,37 @@
         <v>26.64999961853027</v>
       </c>
       <c r="CA28" t="n">
-        <v>17.0408192720678</v>
+        <v>17.04081911348038</v>
       </c>
       <c r="CB28" t="n">
-        <v>28.24466300494045</v>
+        <v>28.24466298572847</v>
       </c>
       <c r="CC28" t="n">
-        <v>47.30306311562731</v>
+        <v>47.30306352366961</v>
       </c>
       <c r="CD28" t="n">
         <v>53.09041087001181</v>
       </c>
       <c r="CE28" t="n">
-        <v>56.22823559664822</v>
+        <v>56.22823554597153</v>
       </c>
       <c r="CF28" t="n">
-        <v>42.93945174387274</v>
+        <v>42.93945177272226</v>
       </c>
       <c r="CG28" t="n">
-        <v>23.53452096803537</v>
+        <v>23.53452114541224</v>
       </c>
       <c r="CH28" t="n">
         <v>30.99183173163939</v>
       </c>
       <c r="CI28" t="n">
-        <v>37.42162453785539</v>
+        <v>37.42162458607946</v>
       </c>
       <c r="CJ28" t="n">
-        <v>36.96564173775607</v>
+        <v>36.96564175218083</v>
       </c>
       <c r="CK28" t="n">
-        <v>33.26907756398046</v>
+        <v>33.26907757696275</v>
       </c>
       <c r="CL28" t="n">
         <v>8</v>
@@ -9768,10 +9776,10 @@
         <v>3.3</v>
       </c>
       <c r="CO28" t="n">
-        <v>24.83706581687082</v>
+        <v>24.83706586558485</v>
       </c>
       <c r="CP28" t="n">
-        <v>40.41885581054714</v>
+        <v>40.4188559915005</v>
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
@@ -10059,37 +10067,37 @@
         <v>15.11999988555908</v>
       </c>
       <c r="CA29" t="n">
-        <v>5.865830791501525</v>
+        <v>5.865830794046077</v>
       </c>
       <c r="CB29" t="n">
-        <v>8.474845212062075</v>
+        <v>8.474845209943982</v>
       </c>
       <c r="CC29" t="n">
-        <v>10.77599631484987</v>
+        <v>10.77599630748211</v>
       </c>
       <c r="CD29" t="n">
         <v>11.55627711976371</v>
       </c>
       <c r="CE29" t="n">
-        <v>9.774262766127185</v>
+        <v>9.774262762032622</v>
       </c>
       <c r="CF29" t="n">
-        <v>14.91642323866362</v>
+        <v>14.91642323776266</v>
       </c>
       <c r="CG29" t="n">
-        <v>5.368455509658211</v>
+        <v>5.368455505538072</v>
       </c>
       <c r="CH29" t="n">
         <v>10.8369287109083</v>
       </c>
       <c r="CI29" t="n">
-        <v>9.69612745794181</v>
+        <v>9.696127455934691</v>
       </c>
       <c r="CJ29" t="n">
-        <v>10.27512954048852</v>
+        <v>10.27512953475737</v>
       </c>
       <c r="CK29" t="n">
-        <v>9.247616586439673</v>
+        <v>9.24761658128163</v>
       </c>
       <c r="CL29" t="n">
         <v>8</v>
@@ -10101,10 +10109,10 @@
         <v>2.8</v>
       </c>
       <c r="CO29" t="n">
-        <v>-38.83851417702753</v>
+        <v>-38.83851421114156</v>
       </c>
       <c r="CP29" t="n">
-        <v>-35.87217241183674</v>
+        <v>-35.87217242511134</v>
       </c>
       <c r="CQ29" t="inlineStr">
         <is>
@@ -10392,37 +10400,37 @@
         <v>38.70000076293945</v>
       </c>
       <c r="CA30" t="n">
-        <v>30.84756158724255</v>
+        <v>30.84756146352459</v>
       </c>
       <c r="CB30" t="n">
-        <v>35.74245432405178</v>
+        <v>35.74245442164587</v>
       </c>
       <c r="CC30" t="n">
-        <v>39.06003394753215</v>
+        <v>39.06003421083991</v>
       </c>
       <c r="CD30" t="n">
         <v>49.9060657389037</v>
       </c>
       <c r="CE30" t="n">
-        <v>60.73976139580559</v>
+        <v>60.73976153341496</v>
       </c>
       <c r="CF30" t="n">
-        <v>16.61273116417203</v>
+        <v>16.61273117624454</v>
       </c>
       <c r="CG30" t="n">
-        <v>17.68241832148942</v>
+        <v>17.68241854075722</v>
       </c>
       <c r="CH30" t="n">
         <v>28.82212409504474</v>
       </c>
       <c r="CI30" t="n">
-        <v>34.92664382178025</v>
+        <v>34.92664389754694</v>
       </c>
       <c r="CJ30" t="n">
-        <v>33.29500795564716</v>
+        <v>33.29500794258523</v>
       </c>
       <c r="CK30" t="n">
-        <v>29.96550716008245</v>
+        <v>29.96550714832671</v>
       </c>
       <c r="CL30" t="n">
         <v>8</v>
@@ -10434,10 +10442,10 @@
         <v>3.7</v>
       </c>
       <c r="CO30" t="n">
-        <v>-22.56975046683068</v>
+        <v>-22.56975049720727</v>
       </c>
       <c r="CP30" t="n">
-        <v>-9.750276141525848</v>
+        <v>-9.750275945746289</v>
       </c>
       <c r="CQ30" t="inlineStr">
         <is>
@@ -10476,7 +10484,7 @@
         <v>-0.61632735550462</v>
       </c>
       <c r="DC30" t="n">
-        <v>-11.66799814233929</v>
+        <v>-11.66799026158288</v>
       </c>
       <c r="DD30" t="b">
         <v>1</v>
@@ -10707,35 +10715,35 @@
         <v>16.93000030517578</v>
       </c>
       <c r="CA31" t="n">
-        <v>10.07593953728143</v>
+        <v>10.07593953517678</v>
       </c>
       <c r="CB31" t="n">
-        <v>17.56133914827641</v>
+        <v>17.56133914863183</v>
       </c>
       <c r="CC31" t="n">
-        <v>28.83258829819589</v>
+        <v>28.83258830480192</v>
       </c>
       <c r="CD31" t="n">
         <v>29.26650917734455</v>
       </c>
       <c r="CE31" t="n">
-        <v>32.09021933950772</v>
+        <v>32.09021933964034</v>
       </c>
       <c r="CF31" t="n">
-        <v>27.88428548772638</v>
+        <v>27.8842854882014</v>
       </c>
       <c r="CG31" t="n">
-        <v>14.2283162995149</v>
+        <v>14.2283163021319</v>
       </c>
       <c r="CH31" t="inlineStr"/>
       <c r="CI31" t="n">
-        <v>21.08853811787003</v>
+        <v>21.08853811920299</v>
       </c>
       <c r="CJ31" t="n">
-        <v>22.7228123180014</v>
+        <v>22.72281231841662</v>
       </c>
       <c r="CK31" t="n">
-        <v>20.45053108620126</v>
+        <v>20.45053108657496</v>
       </c>
       <c r="CL31" t="n">
         <v>4</v>
@@ -10747,10 +10755,10 @@
         <v>2.9</v>
       </c>
       <c r="CO31" t="n">
-        <v>20.79462916459127</v>
+        <v>20.79462916679862</v>
       </c>
       <c r="CP31" t="n">
-        <v>24.56312898838469</v>
+        <v>24.56312899625803</v>
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
@@ -10793,7 +10801,7 @@
         <v>-4.350284884596789</v>
       </c>
       <c r="DC31" t="n">
-        <v>-20.28806233739286</v>
+        <v>-20.28805503364547</v>
       </c>
       <c r="DD31" t="b">
         <v>1</v>
@@ -11042,37 +11050,37 @@
         <v>44.06000137329102</v>
       </c>
       <c r="CA32" t="n">
-        <v>31.96233894589389</v>
+        <v>31.96233917907316</v>
       </c>
       <c r="CB32" t="n">
-        <v>43.40419641010975</v>
+        <v>43.40419596995319</v>
       </c>
       <c r="CC32" t="n">
-        <v>49.69482742877578</v>
+        <v>49.69482656228118</v>
       </c>
       <c r="CD32" t="n">
         <v>47.301358204649</v>
       </c>
       <c r="CE32" t="n">
-        <v>69.1723233787518</v>
+        <v>69.17232289553603</v>
       </c>
       <c r="CF32" t="n">
-        <v>59.81319580781662</v>
+        <v>59.81319571034596</v>
       </c>
       <c r="CG32" t="n">
-        <v>24.46050935656888</v>
+        <v>24.4605088142312</v>
       </c>
       <c r="CH32" t="n">
         <v>76.33330481362214</v>
       </c>
       <c r="CI32" t="n">
-        <v>50.26775679327348</v>
+        <v>50.26775651871148</v>
       </c>
       <c r="CJ32" t="n">
-        <v>48.49809281671239</v>
+        <v>48.49809238346509</v>
       </c>
       <c r="CK32" t="n">
-        <v>43.64828353504115</v>
+        <v>43.64828314511858</v>
       </c>
       <c r="CL32" t="n">
         <v>8</v>
@@ -11084,10 +11092,10 @@
         <v>3.1</v>
       </c>
       <c r="CO32" t="n">
-        <v>-0.9344480831075197</v>
+        <v>-0.9344489680883528</v>
       </c>
       <c r="CP32" t="n">
-        <v>14.08932189399699</v>
+        <v>14.08932127084221</v>
       </c>
       <c r="CQ32" t="inlineStr">
         <is>
@@ -11365,10 +11373,10 @@
         <v>53.7400016784668</v>
       </c>
       <c r="CA33" t="n">
-        <v>10.50731957800449</v>
+        <v>10.50731956132986</v>
       </c>
       <c r="CB33" t="n">
-        <v>19.49107781719833</v>
+        <v>19.4910777862669</v>
       </c>
       <c r="CC33" t="n">
         <v>62.18821154931746</v>
@@ -11377,7 +11385,7 @@
         <v>46.54098234247379</v>
       </c>
       <c r="CE33" t="n">
-        <v>83.24912657371745</v>
+        <v>83.24912655332926</v>
       </c>
       <c r="CF33" t="n">
         <v>11.76833333333333</v>
@@ -11387,7 +11395,7 @@
       </c>
       <c r="CH33" t="inlineStr"/>
       <c r="CI33" t="n">
-        <v>13.92224357617872</v>
+        <v>13.92224356031003</v>
       </c>
       <c r="CJ33" t="n">
         <v>11.76833333333333</v>
@@ -11408,7 +11416,7 @@
         <v>-80.29121758616556</v>
       </c>
       <c r="CP33" t="n">
-        <v>-74.09333245004856</v>
+        <v>-74.09333247957719</v>
       </c>
       <c r="CQ33" t="inlineStr">
         <is>
@@ -11686,10 +11694,10 @@
         <v>29.46999931335449</v>
       </c>
       <c r="CA34" t="n">
-        <v>15.40499610351113</v>
+        <v>15.40499612269137</v>
       </c>
       <c r="CB34" t="n">
-        <v>28.57626777201315</v>
+        <v>28.57626780759248</v>
       </c>
       <c r="CC34" t="n">
         <v>53.78477836114972</v>
@@ -11698,23 +11706,23 @@
         <v>48.59041952862963</v>
       </c>
       <c r="CE34" t="n">
-        <v>59.5572856520974</v>
+        <v>59.55728564695277</v>
       </c>
       <c r="CF34" t="n">
-        <v>36.60763963763722</v>
+        <v>36.60763963409793</v>
       </c>
       <c r="CG34" t="n">
-        <v>29.60722471574267</v>
+        <v>29.60722468926014</v>
       </c>
       <c r="CH34" t="inlineStr"/>
       <c r="CI34" t="n">
-        <v>33.5934204685778</v>
+        <v>33.59342048138287</v>
       </c>
       <c r="CJ34" t="n">
-        <v>32.59195370482519</v>
+        <v>32.5919537208452</v>
       </c>
       <c r="CK34" t="n">
-        <v>29.33275833434267</v>
+        <v>29.33275834876068</v>
       </c>
       <c r="CL34" t="n">
         <v>4</v>
@@ -11726,10 +11734,10 @@
         <v>3.5</v>
       </c>
       <c r="CO34" t="n">
-        <v>-0.4656972589396458</v>
+        <v>-0.465697210015259</v>
       </c>
       <c r="CP34" t="n">
-        <v>13.99192823650579</v>
+        <v>13.99192827995699</v>
       </c>
       <c r="CQ34" t="inlineStr">
         <is>
@@ -12019,10 +12027,10 @@
         <v>10.39999961853027</v>
       </c>
       <c r="CA35" t="n">
-        <v>12.95070199893063</v>
+        <v>12.95070196961655</v>
       </c>
       <c r="CB35" t="n">
-        <v>18.85622211044299</v>
+        <v>18.8562220677617</v>
       </c>
       <c r="CC35" t="n">
         <v>16.51297649354425</v>
@@ -12041,7 +12049,7 @@
         <v>14.71449508364002</v>
       </c>
       <c r="CI35" t="n">
-        <v>16.02578529142328</v>
+        <v>16.02578527942405</v>
       </c>
       <c r="CJ35" t="n">
         <v>15.61373578859213</v>
@@ -12062,7 +12070,7 @@
         <v>35.11887235740878</v>
       </c>
       <c r="CP35" t="n">
-        <v>54.09409499274618</v>
+        <v>54.09409487736892</v>
       </c>
       <c r="CQ35" t="inlineStr">
         <is>
@@ -12350,37 +12358,37 @@
         <v>18.73999977111816</v>
       </c>
       <c r="CA36" t="n">
-        <v>8.790659671350621</v>
+        <v>8.790659630785338</v>
       </c>
       <c r="CB36" t="n">
-        <v>9.149702326742997</v>
+        <v>9.149702328878035</v>
       </c>
       <c r="CC36" t="n">
-        <v>9.503707768242267</v>
+        <v>9.503707814315618</v>
       </c>
       <c r="CD36" t="n">
         <v>16.79875791329259</v>
       </c>
       <c r="CE36" t="n">
-        <v>9.013907476139471</v>
+        <v>9.01390751122927</v>
       </c>
       <c r="CF36" t="n">
-        <v>17.51877469618424</v>
+        <v>17.51877470625346</v>
       </c>
       <c r="CG36" t="n">
-        <v>3.803999686275694</v>
+        <v>3.803999732682379</v>
       </c>
       <c r="CH36" t="n">
         <v>16.19033501601518</v>
       </c>
       <c r="CI36" t="n">
-        <v>11.34623056928038</v>
+        <v>11.34623058168148</v>
       </c>
       <c r="CJ36" t="n">
-        <v>9.326705047492631</v>
+        <v>9.326705071596827</v>
       </c>
       <c r="CK36" t="n">
-        <v>8.394034542743368</v>
+        <v>8.394034564437144</v>
       </c>
       <c r="CL36" t="n">
         <v>8</v>
@@ -12392,10 +12400,10 @@
         <v>4.6</v>
       </c>
       <c r="CO36" t="n">
-        <v>-55.20792611918736</v>
+        <v>-55.20792600342548</v>
       </c>
       <c r="CP36" t="n">
-        <v>-39.45447861335067</v>
+        <v>-39.45447854717617</v>
       </c>
       <c r="CQ36" t="inlineStr">
         <is>
@@ -12455,7 +12463,7 @@
       </c>
       <c r="DG36" t="inlineStr">
         <is>
-          <t>Bandeira de alta — mastro +17%, recuo 18%, bandeira 14d (candidato)</t>
+          <t>Bandeira de alta — mastro +30%, recuo 12%, bandeira 14d (candidato)</t>
         </is>
       </c>
     </row>
@@ -13262,10 +13270,10 @@
         <v>10.35999965667725</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.851607480570364</v>
+        <v>5.851607491869938</v>
       </c>
       <c r="CB2" t="n">
-        <v>10.85473187645802</v>
+        <v>10.85473189741873</v>
       </c>
       <c r="CC2" t="n">
         <v>41.59696831847682</v>
@@ -13274,7 +13282,7 @@
         <v>27.90166392450355</v>
       </c>
       <c r="CE2" t="n">
-        <v>71.91590896307387</v>
+        <v>71.91590901101146</v>
       </c>
       <c r="CF2" t="n">
         <v>19.57807411896471</v>
@@ -13585,10 +13593,10 @@
         <v>13.46000003814697</v>
       </c>
       <c r="CA3" t="n">
-        <v>14.84732055865599</v>
+        <v>14.84732050446674</v>
       </c>
       <c r="CB3" t="n">
-        <v>27.54177963630687</v>
+        <v>27.54177953578581</v>
       </c>
       <c r="CC3" t="n">
         <v>38.93995644223742</v>
@@ -13597,13 +13605,13 @@
         <v>23.51205793312256</v>
       </c>
       <c r="CE3" t="n">
-        <v>75.54482861675247</v>
+        <v>75.54482871709098</v>
       </c>
       <c r="CF3" t="n">
-        <v>48.52515938780768</v>
+        <v>48.5251594276379</v>
       </c>
       <c r="CG3" t="n">
-        <v>26.80868498393435</v>
+        <v>26.80868515112335</v>
       </c>
       <c r="CH3" t="n">
         <v>8.920136085713818</v>
@@ -13908,10 +13916,10 @@
         <v>24.61000061035156</v>
       </c>
       <c r="CA4" t="n">
-        <v>16.31411909286777</v>
+        <v>16.31411910363583</v>
       </c>
       <c r="CB4" t="n">
-        <v>30.26269091726972</v>
+        <v>30.26269093724446</v>
       </c>
       <c r="CC4" t="n">
         <v>72.30210822331667</v>
@@ -13920,19 +13928,19 @@
         <v>52.41049602817493</v>
       </c>
       <c r="CE4" t="n">
-        <v>127.9950261358423</v>
+        <v>127.9950261325152</v>
       </c>
       <c r="CF4" t="n">
-        <v>25.73142365748924</v>
+        <v>25.7314236559713</v>
       </c>
       <c r="CG4" t="n">
-        <v>63.19894120787374</v>
+        <v>63.19894118477155</v>
       </c>
       <c r="CH4" t="n">
         <v>42.85100954601229</v>
       </c>
       <c r="CI4" t="n">
-        <v>47.7927782633561</v>
+        <v>47.79277826258186</v>
       </c>
       <c r="CJ4" t="n">
         <v>47.63075278709361</v>
@@ -13953,7 +13961,7 @@
         <v>74.18803919229917</v>
       </c>
       <c r="CP4" t="n">
-        <v>94.20063826919736</v>
+        <v>94.20063826605134</v>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
@@ -14239,10 +14247,10 @@
         <v>4.119999885559082</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.742641502759139</v>
+        <v>3.742641509775883</v>
       </c>
       <c r="CB5" t="n">
-        <v>6.942599987618202</v>
+        <v>6.942600000634262</v>
       </c>
       <c r="CC5" t="n">
         <v>12.63657372306894</v>
@@ -14251,19 +14259,19 @@
         <v>8.512687176725057</v>
       </c>
       <c r="CE5" t="n">
-        <v>24.29899390450435</v>
+        <v>24.29899389942381</v>
       </c>
       <c r="CF5" t="n">
-        <v>11.19276559323877</v>
+        <v>11.19276559034328</v>
       </c>
       <c r="CG5" t="n">
-        <v>10.19750520591305</v>
+        <v>10.1975051884262</v>
       </c>
       <c r="CH5" t="n">
         <v>5.258139118319559</v>
       </c>
       <c r="CI5" t="n">
-        <v>8.354701758234674</v>
+        <v>8.35470175818474</v>
       </c>
       <c r="CJ5" t="n">
         <v>8.512687176725057</v>
@@ -14284,7 +14292,7 @@
         <v>85.95676388017426</v>
       </c>
       <c r="CP5" t="n">
-        <v>102.7840288908393</v>
+        <v>102.7840288896273</v>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
@@ -14323,7 +14331,7 @@
         <v>-0.4233949874864695</v>
       </c>
       <c r="DC5" t="n">
-        <v>-36.92337647573303</v>
+        <v>-36.92338129060463</v>
       </c>
       <c r="DD5" t="b">
         <v>1</v>
@@ -14572,10 +14580,10 @@
         <v>4.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.282970774499373</v>
+        <v>3.282970791652486</v>
       </c>
       <c r="CB6" t="n">
-        <v>6.089910786696336</v>
+        <v>6.089910818515362</v>
       </c>
       <c r="CC6" t="n">
         <v>12.96195652173913</v>
@@ -14584,7 +14592,7 @@
         <v>8.728772626887835</v>
       </c>
       <c r="CE6" t="n">
-        <v>24.66556322673722</v>
+        <v>24.66556327894235</v>
       </c>
       <c r="CF6" t="n">
         <v>11.57513776217851</v>
@@ -14596,7 +14604,7 @@
         <v>5.383571029035719</v>
       </c>
       <c r="CI6" t="n">
-        <v>11.60598121071627</v>
+        <v>11.60598122271972</v>
       </c>
       <c r="CJ6" t="n">
         <v>11.57513776217851</v>
@@ -14617,7 +14625,7 @@
         <v>131.5027552435702</v>
       </c>
       <c r="CP6" t="n">
-        <v>157.9106935714727</v>
+        <v>157.910693838216</v>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
@@ -14895,10 +14903,10 @@
         <v>48.34000015258789</v>
       </c>
       <c r="CA7" t="n">
-        <v>18.42191766567338</v>
+        <v>18.4219176096249</v>
       </c>
       <c r="CB7" t="n">
-        <v>34.17265726982411</v>
+        <v>34.17265716585418</v>
       </c>
       <c r="CC7" t="n">
         <v>74.65093263657221</v>
@@ -14907,23 +14915,23 @@
         <v>55.91472932652801</v>
       </c>
       <c r="CE7" t="n">
-        <v>99.8344549538902</v>
+        <v>99.83445504165644</v>
       </c>
       <c r="CF7" t="n">
-        <v>48.37202136328627</v>
+        <v>48.37202137697793</v>
       </c>
       <c r="CG7" t="n">
-        <v>58.90972724054575</v>
+        <v>58.9097273531987</v>
       </c>
       <c r="CH7" t="inlineStr"/>
       <c r="CI7" t="n">
-        <v>43.90438223383899</v>
+        <v>43.90438219725731</v>
       </c>
       <c r="CJ7" t="n">
-        <v>41.27233931655519</v>
+        <v>41.27233927141606</v>
       </c>
       <c r="CK7" t="n">
-        <v>37.14510538489967</v>
+        <v>37.14510534427446</v>
       </c>
       <c r="CL7" t="n">
         <v>4</v>
@@ -14935,10 +14943,10 @@
         <v>4.1</v>
       </c>
       <c r="CO7" t="n">
-        <v>-23.15865687288149</v>
+        <v>-23.15865695692207</v>
       </c>
       <c r="CP7" t="n">
-        <v>-9.175874854670296</v>
+        <v>-9.175874930346117</v>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
@@ -15441,10 +15449,10 @@
         <v>15.69999980926514</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.403272784300161</v>
+        <v>6.403272785622092</v>
       </c>
       <c r="CB9" t="n">
-        <v>11.8780710148768</v>
+        <v>11.87807101732898</v>
       </c>
       <c r="CC9" t="n">
         <v>25.39987759130195</v>
@@ -15453,19 +15461,19 @@
         <v>18.63509665364473</v>
       </c>
       <c r="CE9" t="n">
-        <v>35.24419673265818</v>
+        <v>35.24419673051138</v>
       </c>
       <c r="CF9" t="n">
-        <v>12.29886962111222</v>
+        <v>12.29886962086131</v>
       </c>
       <c r="CG9" t="n">
-        <v>20.39435315503992</v>
+        <v>20.3943531522701</v>
       </c>
       <c r="CH9" t="n">
         <v>18.40902666520164</v>
       </c>
       <c r="CI9" t="n">
-        <v>20.32278449054792</v>
+        <v>20.32278449016001</v>
       </c>
       <c r="CJ9" t="n">
         <v>18.63509665364473</v>
@@ -15486,7 +15494,7 @@
         <v>6.825396127602112</v>
       </c>
       <c r="CP9" t="n">
-        <v>29.44448877352668</v>
+        <v>29.44448877105594</v>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
@@ -15776,10 +15784,10 @@
         <v>42.70000076293945</v>
       </c>
       <c r="CA10" t="n">
-        <v>125.1015273012702</v>
+        <v>125.1015273821003</v>
       </c>
       <c r="CB10" t="n">
-        <v>232.0633331438562</v>
+        <v>232.0633332937961</v>
       </c>
       <c r="CC10" t="n">
         <v>134.3883634463059</v>
@@ -15800,13 +15808,13 @@
         <v>54.40212095818906</v>
       </c>
       <c r="CI10" t="n">
-        <v>140.0386116444515</v>
+        <v>140.0386116732977</v>
       </c>
       <c r="CJ10" t="n">
-        <v>123.9129975261182</v>
+        <v>123.9129975665332</v>
       </c>
       <c r="CK10" t="n">
-        <v>111.5216977735063</v>
+        <v>111.5216978098799</v>
       </c>
       <c r="CL10" t="n">
         <v>8</v>
@@ -15818,10 +15826,10 @@
         <v>5.6</v>
       </c>
       <c r="CO10" t="n">
-        <v>161.1749315711938</v>
+        <v>161.1749316563777</v>
       </c>
       <c r="CP10" t="n">
-        <v>227.9592719960674</v>
+        <v>227.9592720636231</v>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
@@ -16109,10 +16117,10 @@
         <v>32.47999954223633</v>
       </c>
       <c r="CA11" t="n">
-        <v>45.35763192753625</v>
+        <v>45.35763236666469</v>
       </c>
       <c r="CB11" t="n">
-        <v>84.13840722557973</v>
+        <v>84.13840804016299</v>
       </c>
       <c r="CC11" t="n">
         <v>68.20285165366582</v>
@@ -16133,7 +16141,7 @@
         <v>25.67266223983068</v>
       </c>
       <c r="CI11" t="n">
-        <v>77.37745275702851</v>
+        <v>77.37745293613018</v>
       </c>
       <c r="CJ11" t="n">
         <v>68.20285165366582</v>
@@ -16154,7 +16162,7 @@
         <v>88.98573692551506</v>
       </c>
       <c r="CP11" t="n">
-        <v>138.2310771168837</v>
+        <v>138.2310776683051</v>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
@@ -16442,10 +16450,10 @@
         <v>6.920000076293945</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.500811674042849</v>
+        <v>6.500811666242972</v>
       </c>
       <c r="CB12" t="n">
-        <v>12.05900565534948</v>
+        <v>12.05900564088071</v>
       </c>
       <c r="CC12" t="n">
         <v>40.39207092990959</v>
@@ -16454,7 +16462,7 @@
         <v>27.23293457569906</v>
       </c>
       <c r="CE12" t="n">
-        <v>85.8199843969203</v>
+        <v>85.81998434881532</v>
       </c>
       <c r="CF12" t="n">
         <v>51.88018214566937</v>
@@ -16769,37 +16777,37 @@
         <v>32.84999847412109</v>
       </c>
       <c r="CA13" t="n">
-        <v>24.40198167129093</v>
+        <v>24.40198158437201</v>
       </c>
       <c r="CB13" t="n">
-        <v>32.23832874511812</v>
+        <v>32.23832936630178</v>
       </c>
       <c r="CC13" t="n">
-        <v>33.8053475634636</v>
+        <v>33.80534833525467</v>
       </c>
       <c r="CD13" t="n">
         <v>20.85130777065122</v>
       </c>
       <c r="CE13" t="n">
-        <v>48.27773753216625</v>
+        <v>48.27773820722045</v>
       </c>
       <c r="CF13" t="n">
-        <v>50.84601668507388</v>
+        <v>50.8460167963005</v>
       </c>
       <c r="CG13" t="n">
-        <v>16.4985676034022</v>
+        <v>16.49856811113381</v>
       </c>
       <c r="CH13" t="n">
         <v>24.29339039885633</v>
       </c>
       <c r="CI13" t="n">
-        <v>31.40158474625282</v>
+        <v>31.40158507126135</v>
       </c>
       <c r="CJ13" t="n">
-        <v>28.32015520820453</v>
+        <v>28.3201554753369</v>
       </c>
       <c r="CK13" t="n">
-        <v>25.48813968738407</v>
+        <v>25.48813992780321</v>
       </c>
       <c r="CL13" t="n">
         <v>8</v>
@@ -16811,10 +16819,10 @@
         <v>3.1</v>
       </c>
       <c r="CO13" t="n">
-        <v>-22.4105300721296</v>
+        <v>-22.41052934026006</v>
       </c>
       <c r="CP13" t="n">
-        <v>-4.409174414450357</v>
+        <v>-4.409173425078827</v>
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
@@ -16931,8 +16939,16 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Bandeira de alta</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Bandeira de alta (pré-confirmação) — pescoço R$48.12, preço 1.7% abaixo do pescoço; falta fechar acima e segurar</t>
+        </is>
+      </c>
       <c r="U14" t="b">
         <v>0</v>
       </c>
@@ -17104,10 +17120,10 @@
         <v>47.31000137329102</v>
       </c>
       <c r="CA14" t="n">
-        <v>131.3186533008917</v>
+        <v>131.3186532722856</v>
       </c>
       <c r="CB14" t="n">
-        <v>243.5961018731541</v>
+        <v>243.5961018200898</v>
       </c>
       <c r="CC14" t="n">
         <v>134.5187807287781</v>
@@ -17128,13 +17144,13 @@
         <v>53.17581509382557</v>
       </c>
       <c r="CI14" t="n">
-        <v>142.2124817469415</v>
+        <v>142.2124817367327</v>
       </c>
       <c r="CJ14" t="n">
-        <v>127.0811095492464</v>
+        <v>127.0811095349434</v>
       </c>
       <c r="CK14" t="n">
-        <v>114.3729985943218</v>
+        <v>114.372998581449</v>
       </c>
       <c r="CL14" t="n">
         <v>8</v>
@@ -17146,10 +17162,10 @@
         <v>5.7</v>
       </c>
       <c r="CO14" t="n">
-        <v>141.7522622582111</v>
+        <v>141.7522622310018</v>
       </c>
       <c r="CP14" t="n">
-        <v>200.5970780360788</v>
+        <v>200.5970780145003</v>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
@@ -17435,10 +17451,10 @@
         <v>13.64999961853027</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.2010593269434413</v>
+        <v>0.2010593269665734</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.2927423800296505</v>
+        <v>0.2927423800633308</v>
       </c>
       <c r="CC15" t="n">
         <v>75.91443638113093</v>
@@ -17746,10 +17762,10 @@
         <v>13.80000019073486</v>
       </c>
       <c r="CA16" t="n">
-        <v>10.01824947315738</v>
+        <v>10.01824952713163</v>
       </c>
       <c r="CB16" t="n">
-        <v>18.58385277270694</v>
+        <v>18.58385287282918</v>
       </c>
       <c r="CC16" t="n">
         <v>49.41891960195592</v>
@@ -17758,23 +17774,23 @@
         <v>48.6151297750832</v>
       </c>
       <c r="CE16" t="n">
-        <v>68.76522847623269</v>
+        <v>68.76522858026181</v>
       </c>
       <c r="CF16" t="n">
-        <v>33.93504904318902</v>
+        <v>33.93504903476912</v>
       </c>
       <c r="CG16" t="n">
-        <v>29.36037666460678</v>
+        <v>29.36037660162531</v>
       </c>
       <c r="CH16" t="inlineStr"/>
       <c r="CI16" t="n">
-        <v>33.97927380595063</v>
+        <v>33.97927383651808</v>
       </c>
       <c r="CJ16" t="n">
-        <v>33.93504904318902</v>
+        <v>33.93504903476912</v>
       </c>
       <c r="CK16" t="n">
-        <v>30.54154413887012</v>
+        <v>30.54154413129221</v>
       </c>
       <c r="CL16" t="n">
         <v>3</v>
@@ -17786,10 +17802,10 @@
         <v>4.9</v>
       </c>
       <c r="CO16" t="n">
-        <v>121.3155341793061</v>
+        <v>121.3155341243937</v>
       </c>
       <c r="CP16" t="n">
-        <v>146.2266183790626</v>
+        <v>146.2266186005657</v>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
@@ -18073,10 +18089,10 @@
         <v>7.239999771118164</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.268913162743343</v>
+        <v>3.268913181465356</v>
       </c>
       <c r="CB17" t="n">
-        <v>6.0638339168889</v>
+        <v>6.063833951618235</v>
       </c>
       <c r="CC17" t="n">
         <v>20.4541571358882</v>
@@ -18085,7 +18101,7 @@
         <v>14.0164620450613</v>
       </c>
       <c r="CE17" t="n">
-        <v>32.91359932733033</v>
+        <v>32.91359938321693</v>
       </c>
       <c r="CF17" t="n">
         <v>10.95072400487419</v>
@@ -18378,10 +18394,10 @@
         <v>19.30999946594238</v>
       </c>
       <c r="CA18" t="n">
-        <v>13.27286329671517</v>
+        <v>13.27286328520698</v>
       </c>
       <c r="CB18" t="n">
-        <v>24.62116141540664</v>
+        <v>24.62116139405894</v>
       </c>
       <c r="CC18" t="n">
         <v>19.98886663466692</v>
@@ -18390,7 +18406,7 @@
         <v>12.49234273346821</v>
       </c>
       <c r="CE18" t="n">
-        <v>33.8271936967246</v>
+        <v>33.82719368413751</v>
       </c>
       <c r="CF18" t="n">
         <v>22.8984489302328</v>
@@ -18400,7 +18416,7 @@
       </c>
       <c r="CH18" t="inlineStr"/>
       <c r="CI18" t="n">
-        <v>20.19533506925538</v>
+        <v>20.1953350610414</v>
       </c>
       <c r="CJ18" t="n">
         <v>21.44365778244985</v>
@@ -18421,7 +18437,7 @@
         <v>-0.05545034714474761</v>
       </c>
       <c r="CP18" t="n">
-        <v>4.584855659237519</v>
+        <v>4.584855616700123</v>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
@@ -18717,10 +18733,10 @@
         <v>17.21999931335449</v>
       </c>
       <c r="CA19" t="n">
-        <v>10.55474915901828</v>
+        <v>10.55474910382358</v>
       </c>
       <c r="CB19" t="n">
-        <v>19.57905968997891</v>
+        <v>19.57905958759274</v>
       </c>
       <c r="CC19" t="n">
         <v>37.03977125031607</v>
@@ -18729,25 +18745,25 @@
         <v>36.56718452753732</v>
       </c>
       <c r="CE19" t="n">
-        <v>41.35653256221261</v>
+        <v>41.35653253861537</v>
       </c>
       <c r="CF19" t="n">
-        <v>34.51133418750026</v>
+        <v>34.51133419933809</v>
       </c>
       <c r="CG19" t="n">
-        <v>18.38517851415616</v>
+        <v>18.38517857817317</v>
       </c>
       <c r="CH19" t="n">
         <v>31.59171947190627</v>
       </c>
       <c r="CI19" t="n">
-        <v>31.29011145765823</v>
+        <v>31.290111450497</v>
       </c>
       <c r="CJ19" t="n">
-        <v>34.51133418750026</v>
+        <v>34.51133419933809</v>
       </c>
       <c r="CK19" t="n">
-        <v>31.06020076875024</v>
+        <v>31.06020077940428</v>
       </c>
       <c r="CL19" t="n">
         <v>7</v>
@@ -18759,10 +18775,10 @@
         <v>3.9</v>
       </c>
       <c r="CO19" t="n">
-        <v>80.37283395628454</v>
+        <v>80.37283401815472</v>
       </c>
       <c r="CP19" t="n">
-        <v>81.70797157577152</v>
+        <v>81.70797153418481</v>
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
@@ -19050,37 +19066,37 @@
         <v>10.10999965667725</v>
       </c>
       <c r="CA20" t="n">
-        <v>10.1314312053109</v>
+        <v>10.13143126652837</v>
       </c>
       <c r="CB20" t="n">
-        <v>18.70783454234331</v>
+        <v>18.70783436878482</v>
       </c>
       <c r="CC20" t="n">
-        <v>24.60234696522342</v>
+        <v>24.60234658832414</v>
       </c>
       <c r="CD20" t="n">
         <v>17.7286584153084</v>
       </c>
       <c r="CE20" t="n">
-        <v>37.29788770493122</v>
+        <v>37.29788764965343</v>
       </c>
       <c r="CF20" t="n">
-        <v>24.22484089934649</v>
+        <v>24.22484087319202</v>
       </c>
       <c r="CG20" t="n">
-        <v>11.97788237532717</v>
+        <v>11.97788224118745</v>
       </c>
       <c r="CH20" t="n">
         <v>10.10999965667725</v>
       </c>
       <c r="CI20" t="n">
-        <v>19.34761022055851</v>
+        <v>19.34761013245699</v>
       </c>
       <c r="CJ20" t="n">
-        <v>18.21824647882585</v>
+        <v>18.21824639204661</v>
       </c>
       <c r="CK20" t="n">
-        <v>16.39642183094327</v>
+        <v>16.39642175284195</v>
       </c>
       <c r="CL20" t="n">
         <v>8</v>
@@ -19092,10 +19108,10 @@
         <v>3.7</v>
       </c>
       <c r="CO20" t="n">
-        <v>62.18024122398555</v>
+        <v>62.18024045146999</v>
       </c>
       <c r="CP20" t="n">
-        <v>91.37102747357859</v>
+        <v>91.371026602149</v>
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
@@ -19385,10 +19401,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="CA21" t="n">
-        <v>5.04484953672942</v>
+        <v>5.044849568253714</v>
       </c>
       <c r="CB21" t="n">
-        <v>9.358195890633075</v>
+        <v>9.358195949110639</v>
       </c>
       <c r="CC21" t="n">
         <v>8.579313567043014</v>
@@ -19708,37 +19724,37 @@
         <v>35.20000076293945</v>
       </c>
       <c r="CA22" t="n">
-        <v>25.30945529590517</v>
+        <v>25.30945525840963</v>
       </c>
       <c r="CB22" t="n">
-        <v>31.05670936255197</v>
+        <v>31.056709418514</v>
       </c>
       <c r="CC22" t="n">
-        <v>34.16642401084461</v>
+        <v>34.16642412302713</v>
       </c>
       <c r="CD22" t="n">
         <v>36.55813791194976</v>
       </c>
       <c r="CE22" t="n">
-        <v>48.30444536510483</v>
+        <v>48.30444544109378</v>
       </c>
       <c r="CF22" t="n">
-        <v>48.45169425830761</v>
+        <v>48.45169427459941</v>
       </c>
       <c r="CG22" t="n">
-        <v>16.11152968336583</v>
+        <v>16.11152976767082</v>
       </c>
       <c r="CH22" t="n">
         <v>30.9183777534985</v>
       </c>
       <c r="CI22" t="n">
-        <v>33.85959670519104</v>
+        <v>33.85959674359538</v>
       </c>
       <c r="CJ22" t="n">
-        <v>32.61156668669829</v>
+        <v>32.61156677077057</v>
       </c>
       <c r="CK22" t="n">
-        <v>29.35041001802846</v>
+        <v>29.35041009369351</v>
       </c>
       <c r="CL22" t="n">
         <v>8</v>
@@ -19750,10 +19766,10 @@
         <v>3</v>
       </c>
       <c r="CO22" t="n">
-        <v>-16.6181551651265</v>
+        <v>-16.618154950169</v>
       </c>
       <c r="CP22" t="n">
-        <v>-3.807965990613471</v>
+        <v>-3.807965881510234</v>
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
@@ -20037,10 +20053,10 @@
         <v>10.97000026702881</v>
       </c>
       <c r="CA23" t="n">
-        <v>9.497073368273673</v>
+        <v>9.497073350591037</v>
       </c>
       <c r="CB23" t="n">
-        <v>17.61707109814766</v>
+        <v>17.61707106534638</v>
       </c>
       <c r="CC23" t="n">
         <v>21.98978873496697</v>
@@ -20049,25 +20065,25 @@
         <v>12.98356721691296</v>
       </c>
       <c r="CE23" t="n">
-        <v>32.25283425643481</v>
+        <v>32.25283431003437</v>
       </c>
       <c r="CF23" t="n">
-        <v>25.36723517344997</v>
+        <v>25.36723518641875</v>
       </c>
       <c r="CG23" t="n">
-        <v>12.0631233417318</v>
+        <v>12.06312339896413</v>
       </c>
       <c r="CH23" t="n">
         <v>9.632374997322403</v>
       </c>
       <c r="CI23" t="n">
-        <v>17.67538352340503</v>
+        <v>17.67538353256962</v>
       </c>
       <c r="CJ23" t="n">
-        <v>15.30031915753031</v>
+        <v>15.30031914112967</v>
       </c>
       <c r="CK23" t="n">
-        <v>13.77028724177728</v>
+        <v>13.7702872270167</v>
       </c>
       <c r="CL23" t="n">
         <v>8</v>
@@ -20079,10 +20095,10 @@
         <v>3.4</v>
       </c>
       <c r="CO23" t="n">
-        <v>25.52677216576697</v>
+        <v>25.52677203121294</v>
       </c>
       <c r="CP23" t="n">
-        <v>61.12473193396153</v>
+        <v>61.12473201750384</v>
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
@@ -20370,10 +20386,10 @@
         <v>10.63000011444092</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.315435262656715</v>
+        <v>3.315435255587584</v>
       </c>
       <c r="CB24" t="n">
-        <v>6.150132412228205</v>
+        <v>6.150132399114969</v>
       </c>
       <c r="CC24" t="n">
         <v>19.53502101474926</v>
@@ -20382,13 +20398,13 @@
         <v>18.41366451165369</v>
       </c>
       <c r="CE24" t="n">
-        <v>20.99443609200229</v>
+        <v>20.99443609253708</v>
       </c>
       <c r="CF24" t="n">
-        <v>15.9343722529959</v>
+        <v>15.93437225439872</v>
       </c>
       <c r="CG24" t="n">
-        <v>13.08852150867985</v>
+        <v>13.08852151764407</v>
       </c>
       <c r="CH24" t="n">
         <v>29.73646810990179</v>
@@ -20701,10 +20717,10 @@
         <v>14.72999954223633</v>
       </c>
       <c r="CA25" t="n">
-        <v>4.523502096555866</v>
+        <v>4.523502097171789</v>
       </c>
       <c r="CB25" t="n">
-        <v>8.391096389111132</v>
+        <v>8.391096390253667</v>
       </c>
       <c r="CC25" t="n">
         <v>24.2149496196813</v>
@@ -20713,25 +20729,25 @@
         <v>20.36807772582785</v>
       </c>
       <c r="CE25" t="n">
-        <v>29.43735271871269</v>
+        <v>29.43735271822437</v>
       </c>
       <c r="CF25" t="n">
-        <v>16.70161176006436</v>
+        <v>16.70161175993701</v>
       </c>
       <c r="CG25" t="n">
-        <v>18.4468191972422</v>
+        <v>18.44681919626278</v>
       </c>
       <c r="CH25" t="n">
         <v>14.61024983224005</v>
       </c>
       <c r="CI25" t="n">
-        <v>18.88145103469708</v>
+        <v>18.88145103463243</v>
       </c>
       <c r="CJ25" t="n">
-        <v>18.4468191972422</v>
+        <v>18.44681919626278</v>
       </c>
       <c r="CK25" t="n">
-        <v>16.60213727751798</v>
+        <v>16.6021372766365</v>
       </c>
       <c r="CL25" t="n">
         <v>7</v>
@@ -20743,10 +20759,10 @@
         <v>6.5</v>
       </c>
       <c r="CO25" t="n">
-        <v>12.70969309885952</v>
+        <v>12.70969309287533</v>
       </c>
       <c r="CP25" t="n">
-        <v>28.18364984029371</v>
+        <v>28.18364983985479</v>
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
@@ -21028,10 +21044,10 @@
         <v>8.140000343322754</v>
       </c>
       <c r="CA26" t="n">
-        <v>3.771663348271938</v>
+        <v>3.771663344142528</v>
       </c>
       <c r="CB26" t="n">
-        <v>6.996435511044444</v>
+        <v>6.996435503384389</v>
       </c>
       <c r="CC26" t="n">
         <v>23.80905177682704</v>
@@ -21040,13 +21056,13 @@
         <v>22.16303232632007</v>
       </c>
       <c r="CE26" t="n">
-        <v>30.42304110143251</v>
+        <v>30.42304109722089</v>
       </c>
       <c r="CF26" t="n">
-        <v>9.586527744618676</v>
+        <v>9.586527745031702</v>
       </c>
       <c r="CG26" t="n">
-        <v>16.59651842952813</v>
+        <v>16.59651843490264</v>
       </c>
       <c r="CH26" t="inlineStr"/>
       <c r="CI26" t="inlineStr"/>
@@ -21353,10 +21369,10 @@
         <v>14.31999969482422</v>
       </c>
       <c r="CA27" t="n">
-        <v>8.981535428991007</v>
+        <v>8.981535404762363</v>
       </c>
       <c r="CB27" t="n">
-        <v>16.66074822077832</v>
+        <v>16.66074817583418</v>
       </c>
       <c r="CC27" t="n">
         <v>13.52387711735003</v>
@@ -21377,7 +21393,7 @@
         <v>6.210695553020633</v>
       </c>
       <c r="CI27" t="n">
-        <v>11.29322925904286</v>
+        <v>11.29322924916103</v>
       </c>
       <c r="CJ27" t="n">
         <v>10.99565184259889</v>
@@ -21398,7 +21414,7 @@
         <v>-30.89324811985986</v>
       </c>
       <c r="CP27" t="n">
-        <v>-21.13666550478591</v>
+        <v>-21.13666557379309</v>
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
@@ -21682,10 +21698,10 @@
         <v>27.42000007629395</v>
       </c>
       <c r="CA28" t="n">
-        <v>7.265285082105257</v>
+        <v>7.265285107589708</v>
       </c>
       <c r="CB28" t="n">
-        <v>13.47710382730525</v>
+        <v>13.47710387457891</v>
       </c>
       <c r="CC28" t="n">
         <v>35.82988175649849</v>
@@ -21694,19 +21710,19 @@
         <v>28.32096620307184</v>
       </c>
       <c r="CE28" t="n">
-        <v>44.64824884995695</v>
+        <v>44.64824881193085</v>
       </c>
       <c r="CF28" t="n">
-        <v>26.46426766182362</v>
+        <v>26.46426765547184</v>
       </c>
       <c r="CG28" t="n">
-        <v>28.98335743954201</v>
+        <v>28.98335739352322</v>
       </c>
       <c r="CH28" t="n">
         <v>24.27856406616775</v>
       </c>
       <c r="CI28" t="n">
-        <v>28.85748425776656</v>
+        <v>28.85748425160613</v>
       </c>
       <c r="CJ28" t="n">
         <v>28.32096620307184</v>
@@ -21727,7 +21743,7 @@
         <v>-7.042780773727464</v>
       </c>
       <c r="CP28" t="n">
-        <v>5.242466000995383</v>
+        <v>5.242465978528443</v>
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
@@ -22015,10 +22031,10 @@
         <v>23.79999923706055</v>
       </c>
       <c r="CA29" t="n">
-        <v>12.34802658170191</v>
+        <v>12.34802659991777</v>
       </c>
       <c r="CB29" t="n">
-        <v>22.90558930905705</v>
+        <v>22.90558934284746</v>
       </c>
       <c r="CC29" t="n">
         <v>61.59179490059613</v>
@@ -22027,13 +22043,13 @@
         <v>51.73586889978424</v>
       </c>
       <c r="CE29" t="n">
-        <v>87.07810605992637</v>
+        <v>87.07810606316832</v>
       </c>
       <c r="CF29" t="n">
-        <v>33.74455761054283</v>
+        <v>33.74455760751021</v>
       </c>
       <c r="CG29" t="n">
-        <v>45.92960718800826</v>
+        <v>45.92960715873755</v>
       </c>
       <c r="CH29" t="n">
         <v>5.609791711095563</v>
@@ -22354,10 +22370,10 @@
         <v>22.60000038146973</v>
       </c>
       <c r="CA30" t="n">
-        <v>3.184692833654026</v>
+        <v>3.184692830772003</v>
       </c>
       <c r="CB30" t="n">
-        <v>5.907605206428219</v>
+        <v>5.907605201082066</v>
       </c>
       <c r="CC30" t="n">
         <v>33.79796896777358</v>
@@ -22366,7 +22382,7 @@
         <v>28.20908778885038</v>
       </c>
       <c r="CE30" t="n">
-        <v>43.29409767417634</v>
+        <v>43.29409766962235</v>
       </c>
       <c r="CF30" t="n">
         <v>10.85340539909456</v>
@@ -22657,10 +22673,10 @@
         <v>39.45000076293945</v>
       </c>
       <c r="CA31" t="n">
-        <v>36.119665776403</v>
+        <v>36.11966575775509</v>
       </c>
       <c r="CB31" t="n">
-        <v>52.59023337044277</v>
+        <v>52.59023334329141</v>
       </c>
       <c r="CC31" t="n">
         <v>48.55384709284856</v>
@@ -22677,13 +22693,13 @@
       </c>
       <c r="CH31" t="inlineStr"/>
       <c r="CI31" t="n">
-        <v>49.19197780587801</v>
+        <v>49.19197779442819</v>
       </c>
       <c r="CJ31" t="n">
-        <v>50.57204023164567</v>
+        <v>50.57204021806999</v>
       </c>
       <c r="CK31" t="n">
-        <v>45.5148362084811</v>
+        <v>45.51483619626299</v>
       </c>
       <c r="CL31" t="n">
         <v>4</v>
@@ -22695,10 +22711,10 @@
         <v>1.6</v>
       </c>
       <c r="CO31" t="n">
-        <v>15.37347358238619</v>
+        <v>15.37347355141507</v>
       </c>
       <c r="CP31" t="n">
-        <v>24.69449139298996</v>
+        <v>24.69449136396633</v>
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
@@ -22986,10 +23002,10 @@
         <v>11.92000007629395</v>
       </c>
       <c r="CA32" t="n">
-        <v>2.06341019438997</v>
+        <v>2.063410193362865</v>
       </c>
       <c r="CB32" t="n">
-        <v>3.827625910593393</v>
+        <v>3.827625908688114</v>
       </c>
       <c r="CC32" t="n">
         <v>27.37261715960048</v>
@@ -22998,7 +23014,7 @@
         <v>23.19321737174429</v>
       </c>
       <c r="CE32" t="n">
-        <v>35.9944096821263</v>
+        <v>35.9944096796342</v>
       </c>
       <c r="CF32" t="n">
         <v>9.158754146</v>
@@ -23287,35 +23303,35 @@
         <v>23.04999923706055</v>
       </c>
       <c r="CA33" t="n">
-        <v>16.54461548176287</v>
+        <v>16.54461545509324</v>
       </c>
       <c r="CB33" t="n">
-        <v>29.57431142363072</v>
+        <v>29.5743114276749</v>
       </c>
       <c r="CC33" t="n">
-        <v>49.88257127327497</v>
+        <v>49.88257136050604</v>
       </c>
       <c r="CD33" t="n">
         <v>49.40798271639872</v>
       </c>
       <c r="CE33" t="n">
-        <v>61.60540338557257</v>
+        <v>61.60540337474787</v>
       </c>
       <c r="CF33" t="n">
-        <v>45.75579822008942</v>
+        <v>45.75579822590096</v>
       </c>
       <c r="CG33" t="n">
-        <v>24.48336426019137</v>
+        <v>24.4833642931657</v>
       </c>
       <c r="CH33" t="inlineStr"/>
       <c r="CI33" t="n">
-        <v>35.43932409968949</v>
+        <v>35.43932411729379</v>
       </c>
       <c r="CJ33" t="n">
-        <v>37.66505482186007</v>
+        <v>37.66505482678793</v>
       </c>
       <c r="CK33" t="n">
-        <v>33.89854933967406</v>
+        <v>33.89854934410914</v>
       </c>
       <c r="CL33" t="n">
         <v>4</v>
@@ -23327,10 +23343,10 @@
         <v>3</v>
       </c>
       <c r="CO33" t="n">
-        <v>47.06529484465604</v>
+        <v>47.06529486389714</v>
       </c>
       <c r="CP33" t="n">
-        <v>53.74978426337205</v>
+        <v>53.74978433974642</v>
       </c>
       <c r="CQ33" t="inlineStr">
         <is>
@@ -23614,10 +23630,10 @@
         <v>33.38999938964844</v>
       </c>
       <c r="CA34" t="n">
-        <v>7.919773873548435</v>
+        <v>7.91977388125787</v>
       </c>
       <c r="CB34" t="n">
-        <v>14.69118053543234</v>
+        <v>14.69118054973335</v>
       </c>
       <c r="CC34" t="n">
         <v>63.74891814306077</v>
@@ -23626,7 +23642,7 @@
         <v>37.2141137927402</v>
       </c>
       <c r="CE34" t="n">
-        <v>88.14507565913613</v>
+        <v>88.14507567468829</v>
       </c>
       <c r="CF34" t="n">
         <v>22.51480113099953</v>
@@ -23937,10 +23953,10 @@
         <v>33.36000061035156</v>
       </c>
       <c r="CA35" t="n">
-        <v>15.11688471736868</v>
+        <v>15.11688470009254</v>
       </c>
       <c r="CB35" t="n">
-        <v>28.04182115071889</v>
+        <v>28.04182111867167</v>
       </c>
       <c r="CC35" t="n">
         <v>20.05535426892732</v>
@@ -23949,7 +23965,7 @@
         <v>36.99750756788258</v>
       </c>
       <c r="CE35" t="n">
-        <v>27.00891075599839</v>
+        <v>27.00891074502444</v>
       </c>
       <c r="CF35" t="n">
         <v>15.03391666666667</v>
@@ -23961,7 +23977,7 @@
         <v>79.30503918682102</v>
       </c>
       <c r="CI35" t="n">
-        <v>22.46273577037826</v>
+        <v>22.46273576176436</v>
       </c>
       <c r="CJ35" t="n">
         <v>20.05535426892732</v>
@@ -23982,7 +23998,7 @@
         <v>-45.89382940108894</v>
       </c>
       <c r="CP35" t="n">
-        <v>-32.66566139267965</v>
+        <v>-32.66566141850069</v>
       </c>
       <c r="CQ35" t="inlineStr">
         <is>
@@ -24274,10 +24290,10 @@
         <v>34.68999862670898</v>
       </c>
       <c r="CA36" t="n">
-        <v>3.441930984802076</v>
+        <v>3.441930999778089</v>
       </c>
       <c r="CB36" t="n">
-        <v>6.384781976807851</v>
+        <v>6.384782004588356</v>
       </c>
       <c r="CC36" t="n">
         <v>32.87857523633004</v>
@@ -24286,7 +24302,7 @@
         <v>23.03538757661248</v>
       </c>
       <c r="CE36" t="n">
-        <v>40.66788363289441</v>
+        <v>40.66788364789184</v>
       </c>
       <c r="CF36" t="n">
         <v>10.59424454785779</v>
@@ -24577,35 +24593,35 @@
         <v>12.84000015258789</v>
       </c>
       <c r="CA37" t="n">
-        <v>8.620481287043701</v>
+        <v>8.620481286504914</v>
       </c>
       <c r="CB37" t="n">
-        <v>13.75169161039808</v>
+        <v>13.75169161101834</v>
       </c>
       <c r="CC37" t="n">
-        <v>18.28822757110052</v>
+        <v>18.28822757306843</v>
       </c>
       <c r="CD37" t="n">
         <v>17.29599079072038</v>
       </c>
       <c r="CE37" t="n">
-        <v>22.79369014118592</v>
+        <v>22.79369014170337</v>
       </c>
       <c r="CF37" t="n">
-        <v>17.32774436609555</v>
+        <v>17.32774436624598</v>
       </c>
       <c r="CG37" t="n">
-        <v>9.132575866807965</v>
+        <v>9.132575867725885</v>
       </c>
       <c r="CH37" t="inlineStr"/>
       <c r="CI37" t="n">
-        <v>14.49703620865946</v>
+        <v>14.49703620920942</v>
       </c>
       <c r="CJ37" t="n">
-        <v>15.53971798824681</v>
+        <v>15.53971798863216</v>
       </c>
       <c r="CK37" t="n">
-        <v>13.98574618942213</v>
+        <v>13.98574618976895</v>
       </c>
       <c r="CL37" t="n">
         <v>4</v>
@@ -24617,10 +24633,10 @@
         <v>2.1</v>
       </c>
       <c r="CO37" t="n">
-        <v>8.923255632542325</v>
+        <v>8.923255635243388</v>
       </c>
       <c r="CP37" t="n">
-        <v>12.90526508083876</v>
+        <v>12.90526508512191</v>
       </c>
       <c r="CQ37" t="inlineStr">
         <is>
@@ -24894,10 +24910,10 @@
         <v>39.09999847412109</v>
       </c>
       <c r="CA38" t="n">
-        <v>19.98838175923153</v>
+        <v>19.98838182642474</v>
       </c>
       <c r="CB38" t="n">
-        <v>37.07844816337448</v>
+        <v>37.0784482880179</v>
       </c>
       <c r="CC38" t="n">
         <v>55.88726858490879</v>
@@ -24906,23 +24922,23 @@
         <v>42.23733079208057</v>
       </c>
       <c r="CE38" t="n">
-        <v>62.05594551296399</v>
+        <v>62.05594540325415</v>
       </c>
       <c r="CF38" t="n">
-        <v>45.209434519073</v>
+        <v>45.20943449802702</v>
       </c>
       <c r="CG38" t="n">
-        <v>31.29948467684047</v>
+        <v>31.29948454409355</v>
       </c>
       <c r="CH38" t="inlineStr"/>
       <c r="CI38" t="n">
-        <v>39.54088325664695</v>
+        <v>39.54088329934461</v>
       </c>
       <c r="CJ38" t="n">
-        <v>41.14394134122374</v>
+        <v>41.14394139302246</v>
       </c>
       <c r="CK38" t="n">
-        <v>37.02954720710137</v>
+        <v>37.02954725372022</v>
       </c>
       <c r="CL38" t="n">
         <v>4</v>
@@ -24934,10 +24950,10 @@
         <v>2.8</v>
       </c>
       <c r="CO38" t="n">
-        <v>-5.295271989307326</v>
+        <v>-5.295271870077523</v>
       </c>
       <c r="CP38" t="n">
-        <v>1.127582608008693</v>
+        <v>1.127582717209874</v>
       </c>
       <c r="CQ38" t="inlineStr">
         <is>
@@ -25233,10 +25249,10 @@
         <v>6.010000228881836</v>
       </c>
       <c r="CA39" t="n">
-        <v>7.129143010811095</v>
+        <v>7.12914305894854</v>
       </c>
       <c r="CB39" t="n">
-        <v>13.22456028505458</v>
+        <v>13.22456037434954</v>
       </c>
       <c r="CC39" t="n">
         <v>5.700250753950201</v>
@@ -25257,7 +25273,7 @@
         <v>5.504458217875779</v>
       </c>
       <c r="CI39" t="n">
-        <v>7.427901843918459</v>
+        <v>7.427901861097509</v>
       </c>
       <c r="CJ39" t="n">
         <v>5.916792043641768</v>
@@ -25278,7 +25294,7 @@
         <v>-11.39579639802557</v>
       </c>
       <c r="CP39" t="n">
-        <v>23.59237206385971</v>
+        <v>23.5923723497008</v>
       </c>
       <c r="CQ39" t="inlineStr">
         <is>
@@ -25550,10 +25566,10 @@
         <v>14.96000003814697</v>
       </c>
       <c r="CA40" t="n">
-        <v>9.299118729791529</v>
+        <v>9.299118859309983</v>
       </c>
       <c r="CB40" t="n">
-        <v>17.24986524376328</v>
+        <v>17.24986548402002</v>
       </c>
       <c r="CC40" t="n">
         <v>30.82737177378653</v>
@@ -25562,23 +25578,23 @@
         <v>29.3357145487105</v>
       </c>
       <c r="CE40" t="n">
-        <v>34.72617271536686</v>
+        <v>34.7261727411532</v>
       </c>
       <c r="CF40" t="n">
-        <v>25.49555040258641</v>
+        <v>25.49555037615469</v>
       </c>
       <c r="CG40" t="n">
-        <v>15.31657776985891</v>
+        <v>15.31657760881048</v>
       </c>
       <c r="CH40" t="inlineStr"/>
       <c r="CI40" t="n">
-        <v>20.71797653748194</v>
+        <v>20.7179766233178</v>
       </c>
       <c r="CJ40" t="n">
-        <v>21.37270782317485</v>
+        <v>21.37270793008735</v>
       </c>
       <c r="CK40" t="n">
-        <v>19.23543704085737</v>
+        <v>19.23543713707862</v>
       </c>
       <c r="CL40" t="n">
         <v>4</v>
@@ -25590,10 +25606,10 @@
         <v>3.3</v>
       </c>
       <c r="CO40" t="n">
-        <v>28.57912427679361</v>
+        <v>28.57912491998378</v>
       </c>
       <c r="CP40" t="n">
-        <v>38.48914762468263</v>
+        <v>38.48914819845177</v>
       </c>
       <c r="CQ40" t="inlineStr">
         <is>
@@ -25632,7 +25648,7 @@
         <v>-3.17151959331623</v>
       </c>
       <c r="DC40" t="n">
-        <v>-17.75794205146741</v>
+        <v>-17.75793314155376</v>
       </c>
       <c r="DD40" t="b">
         <v>1</v>
@@ -25881,10 +25897,10 @@
         <v>12.75</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.570253763036984</v>
+        <v>1.570253751563669</v>
       </c>
       <c r="CB41" t="n">
-        <v>2.912820730433605</v>
+        <v>2.912820709150606</v>
       </c>
       <c r="CC41" t="n">
         <v>12.56040892193308</v>
@@ -25893,7 +25909,7 @@
         <v>9.175696506445684</v>
       </c>
       <c r="CE41" t="n">
-        <v>15.85379573847716</v>
+        <v>15.85379572653467</v>
       </c>
       <c r="CF41" t="n">
         <v>6.104046666666666</v>
@@ -26200,37 +26216,37 @@
         <v>26.64999961853027</v>
       </c>
       <c r="CA42" t="n">
-        <v>17.0408192720678</v>
+        <v>17.04081911348038</v>
       </c>
       <c r="CB42" t="n">
-        <v>28.24466300494045</v>
+        <v>28.24466298572847</v>
       </c>
       <c r="CC42" t="n">
-        <v>47.30306311562731</v>
+        <v>47.30306352366961</v>
       </c>
       <c r="CD42" t="n">
         <v>53.09041087001181</v>
       </c>
       <c r="CE42" t="n">
-        <v>56.22823559664822</v>
+        <v>56.22823554597153</v>
       </c>
       <c r="CF42" t="n">
-        <v>42.93945174387274</v>
+        <v>42.93945177272226</v>
       </c>
       <c r="CG42" t="n">
-        <v>23.53452096803537</v>
+        <v>23.53452114541224</v>
       </c>
       <c r="CH42" t="n">
         <v>30.99183173163939</v>
       </c>
       <c r="CI42" t="n">
-        <v>37.42162453785539</v>
+        <v>37.42162458607946</v>
       </c>
       <c r="CJ42" t="n">
-        <v>36.96564173775607</v>
+        <v>36.96564175218083</v>
       </c>
       <c r="CK42" t="n">
-        <v>33.26907756398046</v>
+        <v>33.26907757696275</v>
       </c>
       <c r="CL42" t="n">
         <v>8</v>
@@ -26242,10 +26258,10 @@
         <v>3.3</v>
       </c>
       <c r="CO42" t="n">
-        <v>24.83706581687082</v>
+        <v>24.83706586558485</v>
       </c>
       <c r="CP42" t="n">
-        <v>40.41885581054714</v>
+        <v>40.4188559915005</v>
       </c>
       <c r="CQ42" t="inlineStr">
         <is>
@@ -26533,37 +26549,37 @@
         <v>15.11999988555908</v>
       </c>
       <c r="CA43" t="n">
-        <v>5.865830791501525</v>
+        <v>5.865830794046077</v>
       </c>
       <c r="CB43" t="n">
-        <v>8.474845212062075</v>
+        <v>8.474845209943982</v>
       </c>
       <c r="CC43" t="n">
-        <v>10.77599631484987</v>
+        <v>10.77599630748211</v>
       </c>
       <c r="CD43" t="n">
         <v>11.55627711976371</v>
       </c>
       <c r="CE43" t="n">
-        <v>9.774262766127185</v>
+        <v>9.774262762032622</v>
       </c>
       <c r="CF43" t="n">
-        <v>14.91642323866362</v>
+        <v>14.91642323776266</v>
       </c>
       <c r="CG43" t="n">
-        <v>5.368455509658211</v>
+        <v>5.368455505538072</v>
       </c>
       <c r="CH43" t="n">
         <v>10.8369287109083</v>
       </c>
       <c r="CI43" t="n">
-        <v>9.69612745794181</v>
+        <v>9.696127455934691</v>
       </c>
       <c r="CJ43" t="n">
-        <v>10.27512954048852</v>
+        <v>10.27512953475737</v>
       </c>
       <c r="CK43" t="n">
-        <v>9.247616586439673</v>
+        <v>9.24761658128163</v>
       </c>
       <c r="CL43" t="n">
         <v>8</v>
@@ -26575,10 +26591,10 @@
         <v>2.8</v>
       </c>
       <c r="CO43" t="n">
-        <v>-38.83851417702753</v>
+        <v>-38.83851421114156</v>
       </c>
       <c r="CP43" t="n">
-        <v>-35.87217241183674</v>
+        <v>-35.87217242511134</v>
       </c>
       <c r="CQ43" t="inlineStr">
         <is>
@@ -26866,10 +26882,10 @@
         <v>11.77000045776367</v>
       </c>
       <c r="CA44" t="n">
-        <v>4.784269064699458</v>
+        <v>4.784269052954928</v>
       </c>
       <c r="CB44" t="n">
-        <v>8.874819115017496</v>
+        <v>8.874819093231391</v>
       </c>
       <c r="CC44" t="n">
         <v>25.44086558978281</v>
@@ -26878,25 +26894,25 @@
         <v>28.63793221437547</v>
       </c>
       <c r="CE44" t="n">
-        <v>23.61676924667931</v>
+        <v>23.61676923654554</v>
       </c>
       <c r="CF44" t="n">
-        <v>14.24977379839794</v>
+        <v>14.24977379955972</v>
       </c>
       <c r="CG44" t="n">
-        <v>13.10602503603189</v>
+        <v>13.10602504652211</v>
       </c>
       <c r="CH44" t="n">
         <v>4.870861694358507</v>
       </c>
       <c r="CI44" t="n">
-        <v>18.98769750004749</v>
+        <v>18.98769749666951</v>
       </c>
       <c r="CJ44" t="n">
-        <v>18.93327152253863</v>
+        <v>18.93327151805263</v>
       </c>
       <c r="CK44" t="n">
-        <v>17.03994437028476</v>
+        <v>17.03994436624737</v>
       </c>
       <c r="CL44" t="n">
         <v>6</v>
@@ -26908,10 +26924,10 @@
         <v>6</v>
       </c>
       <c r="CO44" t="n">
-        <v>44.77437304639149</v>
+        <v>44.77437301208909</v>
       </c>
       <c r="CP44" t="n">
-        <v>61.32282720110609</v>
+        <v>61.3228271724062</v>
       </c>
       <c r="CQ44" t="inlineStr">
         <is>
@@ -26946,7 +26962,7 @@
         <v>0.08503595822453303</v>
       </c>
       <c r="DC44" t="n">
-        <v>-28.42166457816909</v>
+        <v>-28.42166002413473</v>
       </c>
       <c r="DD44" t="b">
         <v>0</v>
@@ -27195,10 +27211,10 @@
         <v>9.069999694824219</v>
       </c>
       <c r="CA45" t="n">
-        <v>2.472824446146039</v>
+        <v>2.472824426255773</v>
       </c>
       <c r="CB45" t="n">
-        <v>4.587089347600902</v>
+        <v>4.587089310704459</v>
       </c>
       <c r="CC45" t="n">
         <v>13.23540704365869</v>
@@ -27207,19 +27223,19 @@
         <v>14.96700525293176</v>
       </c>
       <c r="CE45" t="n">
-        <v>10.35281120485198</v>
+        <v>10.35281120208623</v>
       </c>
       <c r="CF45" t="n">
-        <v>7.309831174847594</v>
+        <v>7.309831176763966</v>
       </c>
       <c r="CG45" t="n">
-        <v>6.779397760649198</v>
+        <v>6.779397778187641</v>
       </c>
       <c r="CH45" t="n">
         <v>10.12863973392969</v>
       </c>
       <c r="CI45" t="n">
-        <v>9.622883074067117</v>
+        <v>9.622883071180349</v>
       </c>
       <c r="CJ45" t="n">
         <v>10.12863973392969</v>
@@ -27240,7 +27256,7 @@
         <v>0.5046975441313828</v>
       </c>
       <c r="CP45" t="n">
-        <v>6.095737572718996</v>
+        <v>6.095737540891344</v>
       </c>
       <c r="CQ45" t="inlineStr">
         <is>
@@ -27524,37 +27540,37 @@
         <v>38.70000076293945</v>
       </c>
       <c r="CA46" t="n">
-        <v>30.84756158724255</v>
+        <v>30.84756146352459</v>
       </c>
       <c r="CB46" t="n">
-        <v>35.74245432405178</v>
+        <v>35.74245442164587</v>
       </c>
       <c r="CC46" t="n">
-        <v>39.06003394753215</v>
+        <v>39.06003421083991</v>
       </c>
       <c r="CD46" t="n">
         <v>49.9060657389037</v>
       </c>
       <c r="CE46" t="n">
-        <v>60.73976139580559</v>
+        <v>60.73976153341496</v>
       </c>
       <c r="CF46" t="n">
-        <v>16.61273116417203</v>
+        <v>16.61273117624454</v>
       </c>
       <c r="CG46" t="n">
-        <v>17.68241832148942</v>
+        <v>17.68241854075722</v>
       </c>
       <c r="CH46" t="n">
         <v>28.82212409504474</v>
       </c>
       <c r="CI46" t="n">
-        <v>34.92664382178025</v>
+        <v>34.92664389754694</v>
       </c>
       <c r="CJ46" t="n">
-        <v>33.29500795564716</v>
+        <v>33.29500794258523</v>
       </c>
       <c r="CK46" t="n">
-        <v>29.96550716008245</v>
+        <v>29.96550714832671</v>
       </c>
       <c r="CL46" t="n">
         <v>8</v>
@@ -27566,10 +27582,10 @@
         <v>3.7</v>
       </c>
       <c r="CO46" t="n">
-        <v>-22.56975046683068</v>
+        <v>-22.56975049720727</v>
       </c>
       <c r="CP46" t="n">
-        <v>-9.750276141525848</v>
+        <v>-9.750275945746289</v>
       </c>
       <c r="CQ46" t="inlineStr">
         <is>
@@ -27608,7 +27624,7 @@
         <v>-0.61632735550462</v>
       </c>
       <c r="DC46" t="n">
-        <v>-11.66799814233929</v>
+        <v>-11.66799026158288</v>
       </c>
       <c r="DD46" t="b">
         <v>1</v>
@@ -27684,8 +27700,16 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Bandeira de alta</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Bandeira de alta (pré-confirmação) — pescoço R$34.16, preço 2.4% abaixo do pescoço; falta fechar acima e segurar</t>
+        </is>
+      </c>
       <c r="U47" t="b">
         <v>0</v>
       </c>
@@ -27857,10 +27881,10 @@
         <v>33.34999847412109</v>
       </c>
       <c r="CA47" t="n">
-        <v>14.4422310896216</v>
+        <v>14.44223110656149</v>
       </c>
       <c r="CB47" t="n">
-        <v>26.79033867124808</v>
+        <v>26.79033870267156</v>
       </c>
       <c r="CC47" t="n">
         <v>55.86440958054417</v>
@@ -27869,25 +27893,25 @@
         <v>43.13942726989067</v>
       </c>
       <c r="CE47" t="n">
-        <v>72.71632256570689</v>
+        <v>72.71632254472365</v>
       </c>
       <c r="CF47" t="n">
-        <v>38.5052857635239</v>
+        <v>38.50528575933758</v>
       </c>
       <c r="CG47" t="n">
-        <v>40.90342111111136</v>
+        <v>40.903421079076</v>
       </c>
       <c r="CH47" t="n">
         <v>21.66331906695809</v>
       </c>
       <c r="CI47" t="n">
-        <v>42.79750343271188</v>
+        <v>42.79750342902881</v>
       </c>
       <c r="CJ47" t="n">
-        <v>40.90342111111136</v>
+        <v>40.903421079076</v>
       </c>
       <c r="CK47" t="n">
-        <v>36.81307900000023</v>
+        <v>36.8130789711684</v>
       </c>
       <c r="CL47" t="n">
         <v>7</v>
@@ -27899,10 +27923,10 @@
         <v>5</v>
       </c>
       <c r="CO47" t="n">
-        <v>10.38405002796752</v>
+        <v>10.38404994151525</v>
       </c>
       <c r="CP47" t="n">
-        <v>28.32835199654313</v>
+        <v>28.32835198549946</v>
       </c>
       <c r="CQ47" t="inlineStr">
         <is>
@@ -28184,10 +28208,10 @@
         <v>6.570000171661377</v>
       </c>
       <c r="CA48" t="n">
-        <v>7.812280629767995</v>
+        <v>7.812280716514052</v>
       </c>
       <c r="CB48" t="n">
-        <v>11.3746805969422</v>
+        <v>11.37468072324446</v>
       </c>
       <c r="CC48" t="n">
         <v>8.114964582574622</v>
@@ -28206,7 +28230,7 @@
         <v>5.379803695646386</v>
       </c>
       <c r="CI48" t="n">
-        <v>8.397726684891705</v>
+        <v>8.397726720399756</v>
       </c>
       <c r="CJ48" t="n">
         <v>8.471557624874304</v>
@@ -28227,7 +28251,7 @@
         <v>16.04873155519062</v>
       </c>
       <c r="CP48" t="n">
-        <v>27.8192764912538</v>
+        <v>27.81927703171119</v>
       </c>
       <c r="CQ48" t="inlineStr">
         <is>
@@ -28493,35 +28517,35 @@
         <v>16.93000030517578</v>
       </c>
       <c r="CA49" t="n">
-        <v>10.07593953728143</v>
+        <v>10.07593953517678</v>
       </c>
       <c r="CB49" t="n">
-        <v>17.56133914827641</v>
+        <v>17.56133914863183</v>
       </c>
       <c r="CC49" t="n">
-        <v>28.83258829819589</v>
+        <v>28.83258830480192</v>
       </c>
       <c r="CD49" t="n">
         <v>29.26650917734455</v>
       </c>
       <c r="CE49" t="n">
-        <v>32.09021933950772</v>
+        <v>32.09021933964034</v>
       </c>
       <c r="CF49" t="n">
-        <v>27.88428548772638</v>
+        <v>27.8842854882014</v>
       </c>
       <c r="CG49" t="n">
-        <v>14.2283162995149</v>
+        <v>14.2283163021319</v>
       </c>
       <c r="CH49" t="inlineStr"/>
       <c r="CI49" t="n">
-        <v>21.08853811787003</v>
+        <v>21.08853811920299</v>
       </c>
       <c r="CJ49" t="n">
-        <v>22.7228123180014</v>
+        <v>22.72281231841662</v>
       </c>
       <c r="CK49" t="n">
-        <v>20.45053108620126</v>
+        <v>20.45053108657496</v>
       </c>
       <c r="CL49" t="n">
         <v>4</v>
@@ -28533,10 +28557,10 @@
         <v>2.9</v>
       </c>
       <c r="CO49" t="n">
-        <v>20.79462916459127</v>
+        <v>20.79462916679862</v>
       </c>
       <c r="CP49" t="n">
-        <v>24.56312898838469</v>
+        <v>24.56312899625803</v>
       </c>
       <c r="CQ49" t="inlineStr">
         <is>
@@ -28579,7 +28603,7 @@
         <v>-4.350284884596789</v>
       </c>
       <c r="DC49" t="n">
-        <v>-20.28806233739286</v>
+        <v>-20.28805503364547</v>
       </c>
       <c r="DD49" t="b">
         <v>1</v>
@@ -28828,10 +28852,10 @@
         <v>32.52999877929688</v>
       </c>
       <c r="CA50" t="n">
-        <v>11.05396020911095</v>
+        <v>11.05396023052786</v>
       </c>
       <c r="CB50" t="n">
-        <v>20.50509618790082</v>
+        <v>20.50509622762917</v>
       </c>
       <c r="CC50" t="n">
         <v>55.47264914101462</v>
@@ -28840,19 +28864,19 @@
         <v>52.30651498008846</v>
       </c>
       <c r="CE50" t="n">
-        <v>57.8667368532009</v>
+        <v>57.8667368486734</v>
       </c>
       <c r="CF50" t="n">
-        <v>28.13054903712746</v>
+        <v>28.13054908897375</v>
       </c>
       <c r="CG50" t="n">
-        <v>35.03833476427376</v>
+        <v>35.03833473717194</v>
       </c>
       <c r="CH50" t="n">
         <v>54.48085949640561</v>
       </c>
       <c r="CI50" t="n">
-        <v>43.40010578000166</v>
+        <v>43.40010578856528</v>
       </c>
       <c r="CJ50" t="n">
         <v>52.30651498008846</v>
@@ -28873,7 +28897,7 @@
         <v>44.71523285774048</v>
       </c>
       <c r="CP50" t="n">
-        <v>33.41563912883656</v>
+        <v>33.41563915516186</v>
       </c>
       <c r="CQ50" t="inlineStr">
         <is>
@@ -29157,37 +29181,37 @@
         <v>44.06000137329102</v>
       </c>
       <c r="CA51" t="n">
-        <v>31.96233894589389</v>
+        <v>31.96233917907316</v>
       </c>
       <c r="CB51" t="n">
-        <v>43.40419641010975</v>
+        <v>43.40419596995319</v>
       </c>
       <c r="CC51" t="n">
-        <v>49.69482742877578</v>
+        <v>49.69482656228118</v>
       </c>
       <c r="CD51" t="n">
         <v>47.301358204649</v>
       </c>
       <c r="CE51" t="n">
-        <v>69.1723233787518</v>
+        <v>69.17232289553603</v>
       </c>
       <c r="CF51" t="n">
-        <v>59.81319580781662</v>
+        <v>59.81319571034596</v>
       </c>
       <c r="CG51" t="n">
-        <v>24.46050935656888</v>
+        <v>24.4605088142312</v>
       </c>
       <c r="CH51" t="n">
         <v>76.33330481362214</v>
       </c>
       <c r="CI51" t="n">
-        <v>50.26775679327348</v>
+        <v>50.26775651871148</v>
       </c>
       <c r="CJ51" t="n">
-        <v>48.49809281671239</v>
+        <v>48.49809238346509</v>
       </c>
       <c r="CK51" t="n">
-        <v>43.64828353504115</v>
+        <v>43.64828314511858</v>
       </c>
       <c r="CL51" t="n">
         <v>8</v>
@@ -29199,10 +29223,10 @@
         <v>3.1</v>
       </c>
       <c r="CO51" t="n">
-        <v>-0.9344480831075197</v>
+        <v>-0.9344489680883528</v>
       </c>
       <c r="CP51" t="n">
-        <v>14.08932189399699</v>
+        <v>14.08932127084221</v>
       </c>
       <c r="CQ51" t="inlineStr">
         <is>
@@ -29490,37 +29514,37 @@
         <v>10.65999984741211</v>
       </c>
       <c r="CA52" t="n">
-        <v>8.15591370413131</v>
+        <v>8.155913709013452</v>
       </c>
       <c r="CB52" t="n">
-        <v>11.52280744720233</v>
+        <v>11.52280744853984</v>
       </c>
       <c r="CC52" t="n">
-        <v>17.21213834489071</v>
+        <v>17.2121383365854</v>
       </c>
       <c r="CD52" t="n">
         <v>24.17460734763337</v>
       </c>
       <c r="CE52" t="n">
-        <v>24.61732005915919</v>
+        <v>24.61732006239898</v>
       </c>
       <c r="CF52" t="n">
-        <v>21.03193964694672</v>
+        <v>21.03193964603175</v>
       </c>
       <c r="CG52" t="n">
-        <v>8.54660604797704</v>
+        <v>8.546606043139425</v>
       </c>
       <c r="CH52" t="n">
         <v>9.746272614957581</v>
       </c>
       <c r="CI52" t="n">
-        <v>15.62595065161228</v>
+        <v>15.62595065103747</v>
       </c>
       <c r="CJ52" t="n">
-        <v>14.36747289604652</v>
+        <v>14.36747289256262</v>
       </c>
       <c r="CK52" t="n">
-        <v>12.93072560644187</v>
+        <v>12.93072560330636</v>
       </c>
       <c r="CL52" t="n">
         <v>8</v>
@@ -29532,10 +29556,10 @@
         <v>3</v>
       </c>
       <c r="CO52" t="n">
-        <v>21.30136765040402</v>
+        <v>21.3013676209902</v>
       </c>
       <c r="CP52" t="n">
-        <v>46.58490502141741</v>
+        <v>46.58490501602521</v>
       </c>
       <c r="CQ52" t="inlineStr">
         <is>
@@ -29809,10 +29833,10 @@
         <v>53.7400016784668</v>
       </c>
       <c r="CA53" t="n">
-        <v>10.50731957800449</v>
+        <v>10.50731956132986</v>
       </c>
       <c r="CB53" t="n">
-        <v>19.49107781719833</v>
+        <v>19.4910777862669</v>
       </c>
       <c r="CC53" t="n">
         <v>62.18821154931746</v>
@@ -29821,7 +29845,7 @@
         <v>46.54098234247379</v>
       </c>
       <c r="CE53" t="n">
-        <v>83.24912657371745</v>
+        <v>83.24912655332926</v>
       </c>
       <c r="CF53" t="n">
         <v>11.76833333333333</v>
@@ -29831,7 +29855,7 @@
       </c>
       <c r="CH53" t="inlineStr"/>
       <c r="CI53" t="n">
-        <v>13.92224357617872</v>
+        <v>13.92224356031003</v>
       </c>
       <c r="CJ53" t="n">
         <v>11.76833333333333</v>
@@ -29852,7 +29876,7 @@
         <v>-80.29121758616556</v>
       </c>
       <c r="CP53" t="n">
-        <v>-74.09333245004856</v>
+        <v>-74.09333247957719</v>
       </c>
       <c r="CQ53" t="inlineStr">
         <is>
@@ -30130,10 +30154,10 @@
         <v>29.46999931335449</v>
       </c>
       <c r="CA54" t="n">
-        <v>15.40499610351113</v>
+        <v>15.40499612269137</v>
       </c>
       <c r="CB54" t="n">
-        <v>28.57626777201315</v>
+        <v>28.57626780759248</v>
       </c>
       <c r="CC54" t="n">
         <v>53.78477836114972</v>
@@ -30142,23 +30166,23 @@
         <v>48.59041952862963</v>
       </c>
       <c r="CE54" t="n">
-        <v>59.5572856520974</v>
+        <v>59.55728564695277</v>
       </c>
       <c r="CF54" t="n">
-        <v>36.60763963763722</v>
+        <v>36.60763963409793</v>
       </c>
       <c r="CG54" t="n">
-        <v>29.60722471574267</v>
+        <v>29.60722468926014</v>
       </c>
       <c r="CH54" t="inlineStr"/>
       <c r="CI54" t="n">
-        <v>33.5934204685778</v>
+        <v>33.59342048138287</v>
       </c>
       <c r="CJ54" t="n">
-        <v>32.59195370482519</v>
+        <v>32.5919537208452</v>
       </c>
       <c r="CK54" t="n">
-        <v>29.33275833434267</v>
+        <v>29.33275834876068</v>
       </c>
       <c r="CL54" t="n">
         <v>4</v>
@@ -30170,10 +30194,10 @@
         <v>3.5</v>
       </c>
       <c r="CO54" t="n">
-        <v>-0.4656972589396458</v>
+        <v>-0.465697210015259</v>
       </c>
       <c r="CP54" t="n">
-        <v>13.99192823650579</v>
+        <v>13.99192827995699</v>
       </c>
       <c r="CQ54" t="inlineStr">
         <is>
@@ -30463,10 +30487,10 @@
         <v>10.39999961853027</v>
       </c>
       <c r="CA55" t="n">
-        <v>12.95070199893063</v>
+        <v>12.95070196961655</v>
       </c>
       <c r="CB55" t="n">
-        <v>18.85622211044299</v>
+        <v>18.8562220677617</v>
       </c>
       <c r="CC55" t="n">
         <v>16.51297649354425</v>
@@ -30485,7 +30509,7 @@
         <v>14.71449508364002</v>
       </c>
       <c r="CI55" t="n">
-        <v>16.02578529142328</v>
+        <v>16.02578527942405</v>
       </c>
       <c r="CJ55" t="n">
         <v>15.61373578859213</v>
@@ -30506,7 +30530,7 @@
         <v>35.11887235740878</v>
       </c>
       <c r="CP55" t="n">
-        <v>54.09409499274618</v>
+        <v>54.09409487736892</v>
       </c>
       <c r="CQ55" t="inlineStr">
         <is>
@@ -30794,10 +30818,10 @@
         <v>33.16999816894531</v>
       </c>
       <c r="CA56" t="n">
-        <v>11.72042510465507</v>
+        <v>11.72042512663754</v>
       </c>
       <c r="CB56" t="n">
-        <v>21.74138856913515</v>
+        <v>21.74138860991263</v>
       </c>
       <c r="CC56" t="n">
         <v>40.50714062106224</v>
@@ -30806,25 +30830,25 @@
         <v>33.04065851780371</v>
       </c>
       <c r="CE56" t="n">
-        <v>42.38658026160604</v>
+        <v>42.38658023072776</v>
       </c>
       <c r="CF56" t="n">
-        <v>23.85616543320452</v>
+        <v>23.85616542896008</v>
       </c>
       <c r="CG56" t="n">
-        <v>25.30396472681499</v>
+        <v>25.30396468957667</v>
       </c>
       <c r="CH56" t="n">
         <v>26.88952120736854</v>
       </c>
       <c r="CI56" t="n">
-        <v>28.18073055520628</v>
+        <v>28.18073055400615</v>
       </c>
       <c r="CJ56" t="n">
-        <v>26.09674296709176</v>
+        <v>26.0967429484726</v>
       </c>
       <c r="CK56" t="n">
-        <v>23.48706867038258</v>
+        <v>23.48706865362534</v>
       </c>
       <c r="CL56" t="n">
         <v>8</v>
@@ -30836,10 +30860,10 @@
         <v>3.6</v>
       </c>
       <c r="CO56" t="n">
-        <v>-29.19183006656949</v>
+        <v>-29.19183011708877</v>
       </c>
       <c r="CP56" t="n">
-        <v>-15.04150705202668</v>
+        <v>-15.04150705564482</v>
       </c>
       <c r="CQ56" t="inlineStr">
         <is>
@@ -31119,10 +31143,10 @@
         <v>24.18000030517578</v>
       </c>
       <c r="CA57" t="n">
-        <v>4.240146146670714</v>
+        <v>4.24014614487791</v>
       </c>
       <c r="CB57" t="n">
-        <v>7.865471102074174</v>
+        <v>7.865471098748522</v>
       </c>
       <c r="CC57" t="n">
         <v>28.58028582012302</v>
@@ -31131,13 +31155,13 @@
         <v>28.44859048200662</v>
       </c>
       <c r="CE57" t="n">
-        <v>25.50998699920504</v>
+        <v>25.50998700021137</v>
       </c>
       <c r="CF57" t="n">
-        <v>2.971261370083251</v>
+        <v>2.971261370124125</v>
       </c>
       <c r="CG57" t="n">
-        <v>18.46855615930497</v>
+        <v>18.46855616134489</v>
       </c>
       <c r="CH57" t="n">
         <v>17.91045698312367</v>
@@ -31446,10 +31470,10 @@
         <v>50.25</v>
       </c>
       <c r="CA58" t="n">
-        <v>8.363254076184065</v>
+        <v>8.363254055170597</v>
       </c>
       <c r="CB58" t="n">
-        <v>15.51383631132144</v>
+        <v>15.51383627234146</v>
       </c>
       <c r="CC58" t="n">
         <v>19.85129695885509</v>
@@ -31458,25 +31482,25 @@
         <v>12.34222338033302</v>
       </c>
       <c r="CE58" t="n">
-        <v>14.34603205151667</v>
+        <v>14.34603214029834</v>
       </c>
       <c r="CF58" t="n">
-        <v>20.65461070749445</v>
+        <v>20.65461072003468</v>
       </c>
       <c r="CG58" t="n">
-        <v>10.82557532558858</v>
+        <v>10.82557538690757</v>
       </c>
       <c r="CH58" t="n">
         <v>13.23570535215743</v>
       </c>
       <c r="CI58" t="n">
-        <v>14.39156677043134</v>
+        <v>14.39156678326227</v>
       </c>
       <c r="CJ58" t="n">
-        <v>13.79086870183705</v>
+        <v>13.79086874622788</v>
       </c>
       <c r="CK58" t="n">
-        <v>12.41178183165335</v>
+        <v>12.4117818716051</v>
       </c>
       <c r="CL58" t="n">
         <v>8</v>
@@ -31488,10 +31512,10 @@
         <v>2.5</v>
       </c>
       <c r="CO58" t="n">
-        <v>-75.29993665342617</v>
+        <v>-75.29993657392021</v>
       </c>
       <c r="CP58" t="n">
-        <v>-71.36006612849484</v>
+        <v>-71.36006610296064</v>
       </c>
       <c r="CQ58" t="inlineStr">
         <is>
@@ -31793,10 +31817,10 @@
         <v>4.760000228881836</v>
       </c>
       <c r="CA59" t="n">
-        <v>1.101256971682966</v>
+        <v>1.101256969808371</v>
       </c>
       <c r="CB59" t="n">
-        <v>2.042831682471901</v>
+        <v>2.042831678994529</v>
       </c>
       <c r="CC59" t="n">
         <v>9.302360329304472</v>
@@ -31805,13 +31829,13 @@
         <v>8.759319099989012</v>
       </c>
       <c r="CE59" t="n">
-        <v>10.2293295664475</v>
+        <v>10.22932956638733</v>
       </c>
       <c r="CF59" t="n">
-        <v>4.217909909810512</v>
+        <v>4.217909910016151</v>
       </c>
       <c r="CG59" t="n">
-        <v>6.876020532041325</v>
+        <v>6.876020534436607</v>
       </c>
       <c r="CH59" t="n">
         <v>6.539351670742607</v>
@@ -32112,37 +32136,37 @@
         <v>24.3700008392334</v>
       </c>
       <c r="CA60" t="n">
-        <v>10.76553943495779</v>
+        <v>10.76553939602004</v>
       </c>
       <c r="CB60" t="n">
-        <v>14.1587773300876</v>
+        <v>14.15877735088281</v>
       </c>
       <c r="CC60" t="n">
-        <v>17.2392905423884</v>
+        <v>17.23929063006058</v>
       </c>
       <c r="CD60" t="n">
         <v>21.14737695048065</v>
       </c>
       <c r="CE60" t="n">
-        <v>16.91392917633088</v>
+        <v>16.91392922779036</v>
       </c>
       <c r="CF60" t="n">
-        <v>23.15616101905515</v>
+        <v>23.1561610303848</v>
       </c>
       <c r="CG60" t="n">
-        <v>8.400134424823909</v>
+        <v>8.400134482971987</v>
       </c>
       <c r="CH60" t="n">
         <v>18.63306280322801</v>
       </c>
       <c r="CI60" t="n">
-        <v>16.30178396016905</v>
+        <v>16.3017839839774</v>
       </c>
       <c r="CJ60" t="n">
-        <v>17.07660985935964</v>
+        <v>17.07660992892547</v>
       </c>
       <c r="CK60" t="n">
-        <v>15.36894887342368</v>
+        <v>15.36894893603292</v>
       </c>
       <c r="CL60" t="n">
         <v>8</v>
@@ -32154,10 +32178,10 @@
         <v>2.8</v>
       </c>
       <c r="CO60" t="n">
-        <v>-36.93496781222461</v>
+        <v>-36.93496755531347</v>
       </c>
       <c r="CP60" t="n">
-        <v>-33.10716701361488</v>
+        <v>-33.10716691591954</v>
       </c>
       <c r="CQ60" t="inlineStr">
         <is>
@@ -32441,10 +32465,10 @@
         <v>4.409999847412109</v>
       </c>
       <c r="CA61" t="n">
-        <v>2.864148125883506</v>
+        <v>2.86414812572561</v>
       </c>
       <c r="CB61" t="n">
-        <v>5.312994773513904</v>
+        <v>5.312994773221006</v>
       </c>
       <c r="CC61" t="n">
         <v>13.62062889934975</v>
@@ -32453,13 +32477,13 @@
         <v>15.2256151851382</v>
       </c>
       <c r="CE61" t="n">
-        <v>15.79234044001764</v>
+        <v>15.7923404397296</v>
       </c>
       <c r="CF61" t="n">
-        <v>9.476368785059551</v>
+        <v>9.476368785079263</v>
       </c>
       <c r="CG61" t="n">
-        <v>6.797592099166012</v>
+        <v>6.797592099308851</v>
       </c>
       <c r="CH61" t="n">
         <v>1.534123064462555</v>
@@ -32760,37 +32784,37 @@
         <v>29.38999938964844</v>
       </c>
       <c r="CA62" t="n">
-        <v>13.71847504287397</v>
+        <v>13.71847501346808</v>
       </c>
       <c r="CB62" t="n">
-        <v>14.34620343332856</v>
+        <v>14.34620342721268</v>
       </c>
       <c r="CC62" t="n">
-        <v>15.16121920588184</v>
+        <v>15.16121923191696</v>
       </c>
       <c r="CD62" t="n">
         <v>30.32006495022776</v>
       </c>
       <c r="CE62" t="n">
-        <v>14.3602702877566</v>
+        <v>14.36027030069958</v>
       </c>
       <c r="CF62" t="n">
-        <v>30.46905837943275</v>
+        <v>30.4690583856103</v>
       </c>
       <c r="CG62" t="n">
-        <v>6.11144895934232</v>
+        <v>6.111448985348889</v>
       </c>
       <c r="CH62" t="n">
         <v>37.5668789909021</v>
       </c>
       <c r="CI62" t="n">
-        <v>17.78382003697768</v>
+        <v>17.78382004206918</v>
       </c>
       <c r="CJ62" t="n">
-        <v>14.3602702877566</v>
+        <v>14.36027030069958</v>
       </c>
       <c r="CK62" t="n">
-        <v>12.92424325898094</v>
+        <v>12.92424327062962</v>
       </c>
       <c r="CL62" t="n">
         <v>7</v>
@@ -32802,10 +32826,10 @@
         <v>6.1</v>
       </c>
       <c r="CO62" t="n">
-        <v>-56.02503052949012</v>
+        <v>-56.02503048985528</v>
       </c>
       <c r="CP62" t="n">
-        <v>-39.49023339128959</v>
+        <v>-39.49023337396569</v>
       </c>
       <c r="CQ62" t="inlineStr">
         <is>
@@ -33097,35 +33121,35 @@
         <v>3.430000066757202</v>
       </c>
       <c r="CA63" t="n">
-        <v>2.632869212470826</v>
+        <v>2.632869213176799</v>
       </c>
       <c r="CB63" t="n">
-        <v>3.08814047477753</v>
+        <v>3.088140475013425</v>
       </c>
       <c r="CC63" t="n">
-        <v>3.821342932596086</v>
+        <v>3.82134293186334</v>
       </c>
       <c r="CD63" t="n">
         <v>6.992141669127824</v>
       </c>
       <c r="CE63" t="n">
-        <v>5.742640636026894</v>
+        <v>5.742640636391389</v>
       </c>
       <c r="CF63" t="n">
-        <v>8.486989516162264</v>
+        <v>8.486989515988732</v>
       </c>
       <c r="CG63" t="n">
-        <v>1.747126731098302</v>
+        <v>1.747126730501275</v>
       </c>
       <c r="CH63" t="inlineStr"/>
       <c r="CI63" t="n">
-        <v>4.644464453179962</v>
+        <v>4.644464453151826</v>
       </c>
       <c r="CJ63" t="n">
-        <v>3.821342932596086</v>
+        <v>3.82134293186334</v>
       </c>
       <c r="CK63" t="n">
-        <v>3.439208639336478</v>
+        <v>3.439208638677006</v>
       </c>
       <c r="CL63" t="n">
         <v>7</v>
@@ -33137,10 +33161,10 @@
         <v>4.9</v>
       </c>
       <c r="CO63" t="n">
-        <v>0.2684714985437875</v>
+        <v>0.2684714793172116</v>
       </c>
       <c r="CP63" t="n">
-        <v>35.4071242794739</v>
+        <v>35.4071242786536</v>
       </c>
       <c r="CQ63" t="inlineStr">
         <is>
@@ -33432,37 +33456,37 @@
         <v>18.73999977111816</v>
       </c>
       <c r="CA64" t="n">
-        <v>8.790659671350621</v>
+        <v>8.790659630785338</v>
       </c>
       <c r="CB64" t="n">
-        <v>9.149702326742997</v>
+        <v>9.149702328878035</v>
       </c>
       <c r="CC64" t="n">
-        <v>9.503707768242267</v>
+        <v>9.503707814315618</v>
       </c>
       <c r="CD64" t="n">
         <v>16.79875791329259</v>
       </c>
       <c r="CE64" t="n">
-        <v>9.013907476139471</v>
+        <v>9.01390751122927</v>
       </c>
       <c r="CF64" t="n">
-        <v>17.51877469618424</v>
+        <v>17.51877470625346</v>
       </c>
       <c r="CG64" t="n">
-        <v>3.803999686275694</v>
+        <v>3.803999732682379</v>
       </c>
       <c r="CH64" t="n">
         <v>16.19033501601518</v>
       </c>
       <c r="CI64" t="n">
-        <v>11.34623056928038</v>
+        <v>11.34623058168148</v>
       </c>
       <c r="CJ64" t="n">
-        <v>9.326705047492631</v>
+        <v>9.326705071596827</v>
       </c>
       <c r="CK64" t="n">
-        <v>8.394034542743368</v>
+        <v>8.394034564437144</v>
       </c>
       <c r="CL64" t="n">
         <v>8</v>
@@ -33474,10 +33498,10 @@
         <v>4.6</v>
       </c>
       <c r="CO64" t="n">
-        <v>-55.20792611918736</v>
+        <v>-55.20792600342548</v>
       </c>
       <c r="CP64" t="n">
-        <v>-39.45447861335067</v>
+        <v>-39.45447854717617</v>
       </c>
       <c r="CQ64" t="inlineStr">
         <is>
@@ -33537,7 +33561,7 @@
       </c>
       <c r="DG64" t="inlineStr">
         <is>
-          <t>Bandeira de alta — mastro +17%, recuo 18%, bandeira 14d (candidato)</t>
+          <t>Bandeira de alta — mastro +30%, recuo 12%, bandeira 14d (candidato)</t>
         </is>
       </c>
     </row>
@@ -33773,10 +33797,10 @@
         <v>8.199999809265137</v>
       </c>
       <c r="CA65" t="n">
-        <v>0.4878659170204635</v>
+        <v>0.4878659183183344</v>
       </c>
       <c r="CB65" t="n">
-        <v>0.9049912760729597</v>
+        <v>0.9049912784805101</v>
       </c>
       <c r="CC65" t="n">
         <v>9.48908274871293</v>
@@ -33785,13 +33809,13 @@
         <v>8.714204226367567</v>
       </c>
       <c r="CE65" t="n">
-        <v>10.45040643308346</v>
+        <v>10.45040643190669</v>
       </c>
       <c r="CF65" t="n">
-        <v>0.7360977972544498</v>
+        <v>0.7360977972294792</v>
       </c>
       <c r="CG65" t="n">
-        <v>8.107035958122797</v>
+        <v>8.107035956385623</v>
       </c>
       <c r="CH65" t="inlineStr"/>
       <c r="CI65" t="inlineStr"/>
@@ -34098,10 +34122,10 @@
         <v>35.31000137329102</v>
       </c>
       <c r="CA66" t="n">
-        <v>10.1100512409775</v>
+        <v>10.11005122874284</v>
       </c>
       <c r="CB66" t="n">
-        <v>18.75414505201327</v>
+        <v>18.75414502931797</v>
       </c>
       <c r="CC66" t="n">
         <v>28.42390754532843</v>
@@ -34110,25 +34134,25 @@
         <v>21.09476497433801</v>
       </c>
       <c r="CE66" t="n">
-        <v>25.57406591387685</v>
+        <v>25.57406594331166</v>
       </c>
       <c r="CF66" t="n">
-        <v>22.87188582141228</v>
+        <v>22.87188582534859</v>
       </c>
       <c r="CG66" t="n">
-        <v>16.40074656294866</v>
+        <v>16.40074658799155</v>
       </c>
       <c r="CH66" t="n">
         <v>26.23735511627599</v>
       </c>
       <c r="CI66" t="n">
-        <v>21.18336527839637</v>
+        <v>21.18336528133188</v>
       </c>
       <c r="CJ66" t="n">
-        <v>21.98332539787514</v>
+        <v>21.9833253998433</v>
       </c>
       <c r="CK66" t="n">
-        <v>19.78499285808763</v>
+        <v>19.78499285985897</v>
       </c>
       <c r="CL66" t="n">
         <v>8</v>
@@ -34140,10 +34164,10 @@
         <v>2.8</v>
       </c>
       <c r="CO66" t="n">
-        <v>-43.96773693400851</v>
+        <v>-43.96773692899198</v>
       </c>
       <c r="CP66" t="n">
-        <v>-40.0074640200389</v>
+        <v>-40.00746401172537</v>
       </c>
       <c r="CQ66" t="inlineStr">
         <is>
@@ -34178,7 +34202,7 @@
         <v>-2.107009503640933</v>
       </c>
       <c r="DC66" t="n">
-        <v>-21.44954253181865</v>
+        <v>-21.44953582303043</v>
       </c>
       <c r="DD66" t="b">
         <v>0</v>
@@ -34433,25 +34457,25 @@
         <v>2.230000019073486</v>
       </c>
       <c r="CA67" t="n">
-        <v>0.6401421964625412</v>
+        <v>0.6401421988013057</v>
       </c>
       <c r="CB67" t="n">
-        <v>0.9077766934169418</v>
+        <v>0.9077766962520706</v>
       </c>
       <c r="CC67" t="n">
-        <v>3.427630424944842</v>
+        <v>3.427630423126994</v>
       </c>
       <c r="CD67" t="n">
         <v>7.066656151822504</v>
       </c>
       <c r="CE67" t="n">
-        <v>2.63116076247484</v>
+        <v>2.631160765770231</v>
       </c>
       <c r="CF67" t="n">
-        <v>2.231183282237624</v>
+        <v>2.231183282131298</v>
       </c>
       <c r="CG67" t="n">
-        <v>1.703043106943466</v>
+        <v>1.703043105891771</v>
       </c>
       <c r="CH67" t="n">
         <v>7.171516514635575</v>
@@ -34730,10 +34754,10 @@
         <v>12.86999988555908</v>
       </c>
       <c r="CA68" t="n">
-        <v>10.88409503335791</v>
+        <v>10.88409500833714</v>
       </c>
       <c r="CB68" t="n">
-        <v>15.84724236856911</v>
+        <v>15.84724233213888</v>
       </c>
       <c r="CC68" t="n">
         <v>15.47375708783982</v>
@@ -34750,13 +34774,13 @@
       </c>
       <c r="CH68" t="inlineStr"/>
       <c r="CI68" t="n">
-        <v>12.38460695577504</v>
+        <v>12.3846069404123</v>
       </c>
       <c r="CJ68" t="n">
-        <v>13.17892606059886</v>
+        <v>13.17892604808848</v>
       </c>
       <c r="CK68" t="n">
-        <v>11.86103345453898</v>
+        <v>11.86103344327963</v>
       </c>
       <c r="CL68" t="n">
         <v>4</v>
@@ -34768,10 +34792,10 @@
         <v>2.2</v>
       </c>
       <c r="CO68" t="n">
-        <v>-7.839677078414176</v>
+        <v>-7.83967716589935</v>
       </c>
       <c r="CP68" t="n">
-        <v>-3.771506869465313</v>
+        <v>-3.771506988833984</v>
       </c>
       <c r="CQ68" t="inlineStr">
         <is>
@@ -35055,10 +35079,10 @@
         <v>8.329999923706055</v>
       </c>
       <c r="CA69" t="n">
-        <v>1.605082993036848</v>
+        <v>1.605082990780117</v>
       </c>
       <c r="CB69" t="n">
-        <v>2.977428952083353</v>
+        <v>2.977428947897116</v>
       </c>
       <c r="CC69" t="n">
         <v>24.04629607605778</v>
@@ -35067,13 +35091,13 @@
         <v>23.80972001921325</v>
       </c>
       <c r="CE69" t="n">
-        <v>25.67832652612854</v>
+        <v>25.67832652337463</v>
       </c>
       <c r="CF69" t="n">
-        <v>6.709160235224862</v>
+        <v>6.709160235361832</v>
       </c>
       <c r="CG69" t="n">
-        <v>17.91152719339948</v>
+        <v>17.91152719599509</v>
       </c>
       <c r="CH69" t="n">
         <v>14.80472650453005</v>
@@ -35382,10 +35406,10 @@
         <v>21.25</v>
       </c>
       <c r="CA70" t="n">
-        <v>5.876635879329978</v>
+        <v>5.876635896280653</v>
       </c>
       <c r="CB70" t="n">
-        <v>10.90115955615711</v>
+        <v>10.90115958760061</v>
       </c>
       <c r="CC70" t="n">
         <v>32.70180023228804</v>
@@ -35394,25 +35418,25 @@
         <v>33.68464293302805</v>
       </c>
       <c r="CE70" t="n">
-        <v>29.46401509342543</v>
+        <v>29.46401509227307</v>
       </c>
       <c r="CF70" t="n">
-        <v>25.30918137328886</v>
+        <v>25.30918137056408</v>
       </c>
       <c r="CG70" t="n">
-        <v>19.10716737402692</v>
+        <v>19.10716735597785</v>
       </c>
       <c r="CH70" t="n">
         <v>13.22580990542387</v>
       </c>
       <c r="CI70" t="n">
-        <v>23.48482520966261</v>
+        <v>23.48482521102223</v>
       </c>
       <c r="CJ70" t="n">
-        <v>25.30918137328886</v>
+        <v>25.30918137056408</v>
       </c>
       <c r="CK70" t="n">
-        <v>22.77826323595997</v>
+        <v>22.77826323350767</v>
       </c>
       <c r="CL70" t="n">
         <v>7</v>
@@ -35424,10 +35448,10 @@
         <v>5.7</v>
       </c>
       <c r="CO70" t="n">
-        <v>7.191826992752803</v>
+        <v>7.191826981212568</v>
       </c>
       <c r="CP70" t="n">
-        <v>10.51682451605935</v>
+        <v>10.51682452245755</v>
       </c>
       <c r="CQ70" t="inlineStr">
         <is>
@@ -35711,25 +35735,25 @@
         <v>17.14999961853027</v>
       </c>
       <c r="CA71" t="n">
-        <v>3.991825565518947</v>
+        <v>3.991825577807206</v>
       </c>
       <c r="CB71" t="n">
-        <v>6.867699828601378</v>
+        <v>6.867699843803461</v>
       </c>
       <c r="CC71" t="n">
-        <v>23.57427307230548</v>
+        <v>23.57427305191861</v>
       </c>
       <c r="CD71" t="n">
         <v>32.99378636564864</v>
       </c>
       <c r="CE71" t="n">
-        <v>16.65127103845917</v>
+        <v>16.6512710445418</v>
       </c>
       <c r="CF71" t="n">
-        <v>20.3023163785714</v>
+        <v>20.3023163772502</v>
       </c>
       <c r="CG71" t="n">
-        <v>11.66191971235824</v>
+        <v>11.66191970408579</v>
       </c>
       <c r="CH71" t="n">
         <v>22.29340682675621</v>
@@ -36030,10 +36054,10 @@
         <v>3.970000028610229</v>
       </c>
       <c r="CA72" t="n">
-        <v>0.9630390084920364</v>
+        <v>0.9630390070159548</v>
       </c>
       <c r="CB72" t="n">
-        <v>1.786437360752728</v>
+        <v>1.786437358014596</v>
       </c>
       <c r="CC72" t="n">
         <v>6.217789642917912</v>
@@ -36042,7 +36066,7 @@
         <v>4.127898727162465</v>
       </c>
       <c r="CE72" t="n">
-        <v>8.632688717262642</v>
+        <v>8.632688714819954</v>
       </c>
       <c r="CF72" t="n">
         <v>3.760485277130923</v>
@@ -36100,7 +36124,7 @@
         <v>-3.17072875722394</v>
       </c>
       <c r="DC72" t="n">
-        <v>-45.72659102148787</v>
+        <v>-45.72659463574499</v>
       </c>
       <c r="DD72" t="b">
         <v>0</v>
@@ -36349,35 +36373,35 @@
         <v>24.02000045776367</v>
       </c>
       <c r="CA73" t="n">
-        <v>23.07830350264929</v>
+        <v>23.07830346616155</v>
       </c>
       <c r="CB73" t="n">
-        <v>28.90113963684716</v>
+        <v>28.90113962702012</v>
       </c>
       <c r="CC73" t="n">
-        <v>37.9611737570445</v>
+        <v>37.96117380415502</v>
       </c>
       <c r="CD73" t="n">
         <v>61.82732111992195</v>
       </c>
       <c r="CE73" t="n">
-        <v>67.85077931094706</v>
+        <v>67.85077927499576</v>
       </c>
       <c r="CF73" t="n">
-        <v>41.68738825527099</v>
+        <v>41.68738826047305</v>
       </c>
       <c r="CG73" t="n">
-        <v>18.10465221496239</v>
+        <v>18.10465224909449</v>
       </c>
       <c r="CH73" t="inlineStr"/>
       <c r="CI73" t="n">
-        <v>39.91582254252048</v>
+        <v>39.91582254311742</v>
       </c>
       <c r="CJ73" t="n">
-        <v>37.9611737570445</v>
+        <v>37.96117380415502</v>
       </c>
       <c r="CK73" t="n">
-        <v>34.16505638134005</v>
+        <v>34.16505642373952</v>
       </c>
       <c r="CL73" t="n">
         <v>7</v>
@@ -36389,10 +36413,10 @@
         <v>3.7</v>
       </c>
       <c r="CO73" t="n">
-        <v>42.23586898516201</v>
+        <v>42.23586916167936</v>
       </c>
       <c r="CP73" t="n">
-        <v>66.17744288851173</v>
+        <v>66.17744289099691</v>
       </c>
       <c r="CQ73" t="inlineStr">
         <is>
@@ -36680,10 +36704,10 @@
         <v>25.07999992370605</v>
       </c>
       <c r="CA74" t="n">
-        <v>4.600671628347848</v>
+        <v>4.600671617619905</v>
       </c>
       <c r="CB74" t="n">
-        <v>8.534245870585258</v>
+        <v>8.534245850684922</v>
       </c>
       <c r="CC74" t="n">
         <v>30.04611202433139</v>
@@ -36692,19 +36716,19 @@
         <v>25.48637760632342</v>
       </c>
       <c r="CE74" t="n">
-        <v>34.72259478668136</v>
+        <v>34.72259479983572</v>
       </c>
       <c r="CF74" t="n">
-        <v>11.77818656733116</v>
+        <v>11.77818656856278</v>
       </c>
       <c r="CG74" t="n">
-        <v>24.22287495435466</v>
+        <v>24.22287497115891</v>
       </c>
       <c r="CH74" t="n">
         <v>25.07999992370605</v>
       </c>
       <c r="CI74" t="n">
-        <v>25.22269097712134</v>
+        <v>25.22269098231972</v>
       </c>
       <c r="CJ74" t="n">
         <v>25.28318876501474</v>
@@ -36725,7 +36749,7 @@
         <v>-9.270853438061765</v>
       </c>
       <c r="CP74" t="n">
-        <v>0.5689435958905698</v>
+        <v>0.5689436166177453</v>
       </c>
       <c r="CQ74" t="inlineStr">
         <is>
@@ -37017,10 +37041,10 @@
         <v>12.42000007629395</v>
       </c>
       <c r="CA75" t="n">
-        <v>2.054914846624271</v>
+        <v>2.054914844356821</v>
       </c>
       <c r="CB75" t="n">
-        <v>3.811867040488023</v>
+        <v>3.811867036281902</v>
       </c>
       <c r="CC75" t="n">
         <v>15.91537727378093</v>
@@ -37029,7 +37053,7 @@
         <v>12.64279048217724</v>
       </c>
       <c r="CE75" t="n">
-        <v>20.79969139237418</v>
+        <v>20.79969138930413</v>
       </c>
       <c r="CF75" t="n">
         <v>9.294207014285712</v>
@@ -37334,10 +37358,10 @@
         <v>55.20000076293945</v>
       </c>
       <c r="CA76" t="n">
-        <v>40.14457034350494</v>
+        <v>40.14457042915611</v>
       </c>
       <c r="CB76" t="n">
-        <v>58.45049442014319</v>
+        <v>58.4504945448513</v>
       </c>
       <c r="CC76" t="n">
         <v>35.6793044086122</v>
@@ -37356,13 +37380,13 @@
         <v>48.81663041531538</v>
       </c>
       <c r="CI76" t="n">
-        <v>43.24561932691118</v>
+        <v>43.24561936197106</v>
       </c>
       <c r="CJ76" t="n">
-        <v>41.36290935397069</v>
+        <v>41.36290939679628</v>
       </c>
       <c r="CK76" t="n">
-        <v>37.22661841857362</v>
+        <v>37.22661845711666</v>
       </c>
       <c r="CL76" t="n">
         <v>6</v>
@@ -37374,10 +37398,10 @@
         <v>6.4</v>
       </c>
       <c r="CO76" t="n">
-        <v>-32.56047481150204</v>
+        <v>-32.56047474167769</v>
       </c>
       <c r="CP76" t="n">
-        <v>-21.65648780942462</v>
+        <v>-21.65648774591034</v>
       </c>
       <c r="CQ76" t="inlineStr">
         <is>
@@ -37661,10 +37685,10 @@
         <v>28.85000038146973</v>
       </c>
       <c r="CA77" t="n">
-        <v>13.47826685979746</v>
+        <v>13.47826689531939</v>
       </c>
       <c r="CB77" t="n">
-        <v>25.00218502492428</v>
+        <v>25.00218509081748</v>
       </c>
       <c r="CC77" t="n">
         <v>37.07686760955129</v>
@@ -37673,19 +37697,19 @@
         <v>25.84183193227743</v>
       </c>
       <c r="CE77" t="n">
-        <v>42.33310182664291</v>
+        <v>42.33310174373844</v>
       </c>
       <c r="CF77" t="n">
-        <v>42.16403729076909</v>
+        <v>42.16403727257172</v>
       </c>
       <c r="CG77" t="n">
-        <v>22.58047110757641</v>
+        <v>22.58047102514563</v>
       </c>
       <c r="CH77" t="n">
         <v>25.39446734308974</v>
       </c>
       <c r="CI77" t="n">
-        <v>29.23390362432858</v>
+        <v>29.23390361406389</v>
       </c>
       <c r="CJ77" t="n">
         <v>25.61814963768359</v>
@@ -37706,7 +37730,7 @@
         <v>-20.08202991662958</v>
       </c>
       <c r="CP77" t="n">
-        <v>1.330687132695596</v>
+        <v>1.330687097116101</v>
       </c>
       <c r="CQ77" t="inlineStr">
         <is>
@@ -37998,10 +38022,10 @@
         <v>15.07999992370605</v>
       </c>
       <c r="CA78" t="n">
-        <v>2.433443124732141</v>
+        <v>2.433443111108075</v>
       </c>
       <c r="CB78" t="n">
-        <v>4.51403699637812</v>
+        <v>4.514036971105479</v>
       </c>
       <c r="CC78" t="n">
         <v>25.45350305593697</v>
@@ -38010,7 +38034,7 @@
         <v>19.52359161971606</v>
       </c>
       <c r="CE78" t="n">
-        <v>33.15518504482048</v>
+        <v>33.15518502052279</v>
       </c>
       <c r="CF78" t="n">
         <v>10.38593205872702</v>
@@ -38317,10 +38341,10 @@
         <v>14.56999969482422</v>
       </c>
       <c r="CA79" t="n">
-        <v>9.522149335578966</v>
+        <v>9.522149334652612</v>
       </c>
       <c r="CB79" t="n">
-        <v>17.66358701749898</v>
+        <v>17.66358701578059</v>
       </c>
       <c r="CC79" t="n">
         <v>13.81907630325131</v>
@@ -38341,7 +38365,7 @@
         <v>12.2203515982404</v>
       </c>
       <c r="CI79" t="n">
-        <v>14.92972000169788</v>
+        <v>14.92972000136729</v>
       </c>
       <c r="CJ79" t="n">
         <v>13.18184499442705</v>
@@ -38362,7 +38386,7 @@
         <v>-18.57473751904922</v>
       </c>
       <c r="CP79" t="n">
-        <v>2.468910874455621</v>
+        <v>2.468910872186614</v>
       </c>
       <c r="CQ79" t="inlineStr">
         <is>
@@ -38646,25 +38670,25 @@
         <v>26.20999908447266</v>
       </c>
       <c r="CA80" t="n">
-        <v>11.93854598679419</v>
+        <v>11.9385459919552</v>
       </c>
       <c r="CB80" t="n">
-        <v>12.61580796862671</v>
+        <v>12.61580797102097</v>
       </c>
       <c r="CC80" t="n">
-        <v>13.88314114084834</v>
+        <v>13.88314113748146</v>
       </c>
       <c r="CD80" t="n">
         <v>32.29491627828039</v>
       </c>
       <c r="CE80" t="n">
-        <v>12.94974348476262</v>
+        <v>12.94974348458021</v>
       </c>
       <c r="CF80" t="n">
-        <v>24.67209426927104</v>
+        <v>24.67209426857107</v>
       </c>
       <c r="CG80" t="n">
-        <v>5.680816707646442</v>
+        <v>5.680816704344635</v>
       </c>
       <c r="CH80" t="n">
         <v>61.56724104958222</v>
@@ -38716,7 +38740,7 @@
         <v>-2.04474013597955</v>
       </c>
       <c r="DC80" t="n">
-        <v>-19.17221039881886</v>
+        <v>-19.17220078617631</v>
       </c>
       <c r="DD80" t="b">
         <v>0</v>
@@ -38965,10 +38989,10 @@
         <v>6.960000038146973</v>
       </c>
       <c r="CA81" t="n">
-        <v>1.254324385072851</v>
+        <v>1.254324383550125</v>
       </c>
       <c r="CB81" t="n">
-        <v>2.326771734310139</v>
+        <v>2.326771731485482</v>
       </c>
       <c r="CC81" t="n">
         <v>10.46765045464783</v>
@@ -38977,13 +39001,13 @@
         <v>10.28299479481327</v>
       </c>
       <c r="CE81" t="n">
-        <v>10.15256190776878</v>
+        <v>10.15256190818006</v>
       </c>
       <c r="CF81" t="n">
-        <v>1.873720564803854</v>
+        <v>1.873720564864715</v>
       </c>
       <c r="CG81" t="n">
-        <v>7.23916861335511</v>
+        <v>7.239168615134628</v>
       </c>
       <c r="CH81" t="n">
         <v>11.45586349250206</v>
@@ -39284,10 +39308,10 @@
         <v>10.44999980926514</v>
       </c>
       <c r="CA82" t="n">
-        <v>6.405398473258392</v>
+        <v>6.405398367019009</v>
       </c>
       <c r="CB82" t="n">
-        <v>11.88201416789432</v>
+        <v>11.88201397082026</v>
       </c>
       <c r="CC82" t="n">
         <v>7.980547404770202</v>
@@ -39308,7 +39332,7 @@
         <v>39.67377387971943</v>
       </c>
       <c r="CI82" t="n">
-        <v>10.25156155398371</v>
+        <v>10.25156151065322</v>
       </c>
       <c r="CJ82" t="n">
         <v>7.980547404770202</v>
@@ -39329,7 +39353,7 @@
         <v>-31.26801152737755</v>
       </c>
       <c r="CP82" t="n">
-        <v>-1.89893070720909</v>
+        <v>-1.898931121854952</v>
       </c>
       <c r="CQ82" t="inlineStr">
         <is>
@@ -39613,35 +39637,35 @@
         <v>2.779999971389771</v>
       </c>
       <c r="CA83" t="n">
-        <v>1.278437330738012</v>
+        <v>1.278437324952654</v>
       </c>
       <c r="CB83" t="n">
-        <v>1.746572826835703</v>
+        <v>1.746572821362998</v>
       </c>
       <c r="CC83" t="n">
-        <v>3.757394658527694</v>
+        <v>3.757394663757759</v>
       </c>
       <c r="CD83" t="n">
         <v>7.235833015165504</v>
       </c>
       <c r="CE83" t="n">
-        <v>3.789507994668091</v>
+        <v>3.789507988601228</v>
       </c>
       <c r="CF83" t="n">
-        <v>1.340404108644795</v>
+        <v>1.340404108818218</v>
       </c>
       <c r="CG83" t="n">
-        <v>1.852381279504216</v>
+        <v>1.852381282742166</v>
       </c>
       <c r="CH83" t="inlineStr"/>
       <c r="CI83" t="n">
-        <v>2.294116366486418</v>
+        <v>2.29411636503917</v>
       </c>
       <c r="CJ83" t="n">
-        <v>1.79947705316996</v>
+        <v>1.799477052052582</v>
       </c>
       <c r="CK83" t="n">
-        <v>1.619529347852964</v>
+        <v>1.619529346847324</v>
       </c>
       <c r="CL83" t="n">
         <v>6</v>
@@ -39653,10 +39677,10 @@
         <v>5.7</v>
       </c>
       <c r="CO83" t="n">
-        <v>-41.74354803883926</v>
+        <v>-41.74354807501337</v>
       </c>
       <c r="CP83" t="n">
-        <v>-17.47782769438125</v>
+        <v>-17.47782774644053</v>
       </c>
       <c r="CQ83" t="inlineStr">
         <is>
@@ -39938,10 +39962,10 @@
         <v>5.269999980926514</v>
       </c>
       <c r="CA84" t="n">
-        <v>3.116563125408492</v>
+        <v>3.116563119576812</v>
       </c>
       <c r="CB84" t="n">
-        <v>4.537715910594764</v>
+        <v>4.537715902103838</v>
       </c>
       <c r="CC84" t="n">
         <v>4.409332244701186</v>
@@ -40263,10 +40287,10 @@
         <v>18.8700008392334</v>
       </c>
       <c r="CA85" t="n">
-        <v>4.583569617755083</v>
+        <v>4.583569634785647</v>
       </c>
       <c r="CB85" t="n">
-        <v>8.502521640935678</v>
+        <v>8.502521672527374</v>
       </c>
       <c r="CC85" t="n">
         <v>32.85512629695696</v>
@@ -40275,13 +40299,13 @@
         <v>35.40227792012859</v>
       </c>
       <c r="CE85" t="n">
-        <v>28.64957925122465</v>
+        <v>28.64957925632845</v>
       </c>
       <c r="CF85" t="n">
-        <v>11.13129413371513</v>
+        <v>11.13129413262653</v>
       </c>
       <c r="CG85" t="n">
-        <v>19.33215015746119</v>
+        <v>19.33215014097561</v>
       </c>
       <c r="CH85" t="n">
         <v>44.34329506457097</v>
@@ -40907,25 +40931,25 @@
         <v>1.559999942779541</v>
       </c>
       <c r="CA87" t="n">
-        <v>0.1391204194125289</v>
+        <v>0.139120419420455</v>
       </c>
       <c r="CB87" t="n">
-        <v>0.1588600556948569</v>
+        <v>0.1588600557035727</v>
       </c>
       <c r="CC87" t="n">
-        <v>0.7587301048710173</v>
+        <v>0.7587301048694177</v>
       </c>
       <c r="CD87" t="n">
         <v>3.145519198624604</v>
       </c>
       <c r="CE87" t="n">
-        <v>0.2602920092461362</v>
+        <v>0.2602920092505782</v>
       </c>
       <c r="CF87" t="n">
-        <v>0.5416071244230326</v>
+        <v>0.5416071244229079</v>
       </c>
       <c r="CG87" t="n">
-        <v>0.3391141312924401</v>
+        <v>0.339114131291073</v>
       </c>
       <c r="CH87" t="inlineStr"/>
       <c r="CI87" t="inlineStr"/>
@@ -41224,10 +41248,10 @@
         <v>23.96999931335449</v>
       </c>
       <c r="CA88" t="n">
-        <v>12.07935622959471</v>
+        <v>12.07935616962814</v>
       </c>
       <c r="CB88" t="n">
-        <v>22.40720580589818</v>
+        <v>22.4072056946602</v>
       </c>
       <c r="CC88" t="n">
         <v>15.09517542309634</v>
@@ -41248,13 +41272,13 @@
         <v>23.16277622804454</v>
       </c>
       <c r="CI88" t="n">
-        <v>19.87730238106542</v>
+        <v>19.87730235966485</v>
       </c>
       <c r="CJ88" t="n">
-        <v>18.75119061449726</v>
+        <v>18.75119055887827</v>
       </c>
       <c r="CK88" t="n">
-        <v>16.87607155304753</v>
+        <v>16.87607150299045</v>
       </c>
       <c r="CL88" t="n">
         <v>8</v>
@@ -41266,10 +41290,10 @@
         <v>2.9</v>
       </c>
       <c r="CO88" t="n">
-        <v>-29.59502696503914</v>
+        <v>-29.59502717387139</v>
       </c>
       <c r="CP88" t="n">
-        <v>-17.07424718201344</v>
+        <v>-17.07424727129408</v>
       </c>
       <c r="CQ88" t="inlineStr">
         <is>
@@ -41551,10 +41575,10 @@
         <v>14.03999996185303</v>
       </c>
       <c r="CA89" t="n">
-        <v>6.060896442980922</v>
+        <v>6.060896418544134</v>
       </c>
       <c r="CB89" t="n">
-        <v>8.824665220980222</v>
+        <v>8.82466518540026</v>
       </c>
       <c r="CC89" t="n">
         <v>3.751695776034725</v>
@@ -41868,10 +41892,10 @@
         <v>7.210000038146973</v>
       </c>
       <c r="CA90" t="n">
-        <v>3.000514740673769</v>
+        <v>3.000514726708099</v>
       </c>
       <c r="CB90" t="n">
-        <v>5.565954843949841</v>
+        <v>5.565954818043524</v>
       </c>
       <c r="CC90" t="n">
         <v>14.71995385291947</v>
@@ -41880,17 +41904,17 @@
         <v>15.82114567812849</v>
       </c>
       <c r="CE90" t="n">
-        <v>14.12742076263375</v>
+        <v>14.12742075417105</v>
       </c>
       <c r="CF90" t="n">
-        <v>15.00312294900737</v>
+        <v>15.00312295174442</v>
       </c>
       <c r="CG90" t="n">
-        <v>7.779395113044546</v>
+        <v>7.779395126661632</v>
       </c>
       <c r="CH90" t="inlineStr"/>
       <c r="CI90" t="n">
-        <v>13.49020767114673</v>
+        <v>13.49020767272501</v>
       </c>
       <c r="CJ90" t="n">
         <v>14.71995385291947</v>
@@ -41911,7 +41935,7 @@
         <v>83.74422187981506</v>
       </c>
       <c r="CP90" t="n">
-        <v>87.10412759739481</v>
+        <v>87.10412761928504</v>
       </c>
       <c r="CQ90" t="inlineStr">
         <is>
@@ -42179,10 +42203,10 @@
         <v>55.22999954223633</v>
       </c>
       <c r="CA91" t="n">
-        <v>11.59547551352601</v>
+        <v>11.59547547337404</v>
       </c>
       <c r="CB91" t="n">
-        <v>16.88301234769387</v>
+        <v>16.88301228923261</v>
       </c>
       <c r="CC91" t="inlineStr"/>
       <c r="CD91" t="inlineStr"/>
@@ -42193,13 +42217,13 @@
       <c r="CG91" t="inlineStr"/>
       <c r="CH91" t="inlineStr"/>
       <c r="CI91" t="n">
-        <v>18.2687292870733</v>
+        <v>18.26872925420222</v>
       </c>
       <c r="CJ91" t="n">
-        <v>16.88301234769387</v>
+        <v>16.88301228923261</v>
       </c>
       <c r="CK91" t="n">
-        <v>15.19471111292448</v>
+        <v>15.19471106030935</v>
       </c>
       <c r="CL91" t="n">
         <v>3</v>
@@ -42211,10 +42235,10 @@
         <v>2.3</v>
       </c>
       <c r="CO91" t="n">
-        <v>-72.48830121516741</v>
+        <v>-72.4883013104329</v>
       </c>
       <c r="CP91" t="n">
-        <v>-66.92245258285298</v>
+        <v>-66.92245264236971</v>
       </c>
       <c r="CQ91" t="inlineStr">
         <is>
@@ -42261,7 +42285,7 @@
         <v>3.426962479524587</v>
       </c>
       <c r="DC91" t="n">
-        <v>-14.66838871705677</v>
+        <v>-14.66839399830475</v>
       </c>
       <c r="DD91" t="b">
         <v>0</v>
@@ -42512,10 +42536,10 @@
         <v>3.660000085830688</v>
       </c>
       <c r="CA92" t="n">
-        <v>33.40407243222504</v>
+        <v>33.40407224899656</v>
       </c>
       <c r="CB92" t="n">
-        <v>61.96455436177743</v>
+        <v>61.9645540218886</v>
       </c>
       <c r="CC92" t="n">
         <v>4.712828098858758</v>
@@ -42735,7 +42759,7 @@
         <v>1</v>
       </c>
       <c r="AU93" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AV93" t="b">
         <v>1</v>
@@ -42829,10 +42853,10 @@
         <v>7.739999771118164</v>
       </c>
       <c r="CA93" t="n">
-        <v>4.982339141799269</v>
+        <v>4.982339140019103</v>
       </c>
       <c r="CB93" t="n">
-        <v>7.254285790459735</v>
+        <v>7.254285787867816</v>
       </c>
       <c r="CC93" t="n">
         <v>5.854254372336648</v>
@@ -42851,13 +42875,13 @@
         <v>7.739999771118164</v>
       </c>
       <c r="CI93" t="n">
-        <v>6.606025188115704</v>
+        <v>6.606025187387023</v>
       </c>
       <c r="CJ93" t="n">
-        <v>6.554270081398192</v>
+        <v>6.554270080102231</v>
       </c>
       <c r="CK93" t="n">
-        <v>5.898843073258373</v>
+        <v>5.898843072092008</v>
       </c>
       <c r="CL93" t="n">
         <v>6</v>
@@ -42869,10 +42893,10 @@
         <v>5.9</v>
       </c>
       <c r="CO93" t="n">
-        <v>-23.78755493934346</v>
+        <v>-23.78755495441277</v>
       </c>
       <c r="CP93" t="n">
-        <v>-14.65083483896072</v>
+        <v>-14.6508348483752</v>
       </c>
       <c r="CQ93" t="inlineStr">
         <is>
@@ -42907,7 +42931,7 @@
         <v>-6.469653146216814</v>
       </c>
       <c r="DC93" t="n">
-        <v>-20.2341272136166</v>
+        <v>-20.23411921596913</v>
       </c>
       <c r="DD93" t="b">
         <v>0</v>
@@ -43156,10 +43180,10 @@
         <v>35.06000137329102</v>
       </c>
       <c r="CA94" t="n">
-        <v>8.680155220767219</v>
+        <v>8.680155238892739</v>
       </c>
       <c r="CB94" t="n">
-        <v>16.10168793452319</v>
+        <v>16.10168796814603</v>
       </c>
       <c r="CC94" t="n">
         <v>40.64260876606351</v>
@@ -43168,19 +43192,19 @@
         <v>40.99197343130513</v>
       </c>
       <c r="CE94" t="n">
-        <v>34.02445211391557</v>
+        <v>34.02445210406701</v>
       </c>
       <c r="CF94" t="n">
-        <v>50.0659293083826</v>
+        <v>50.06592930352212</v>
       </c>
       <c r="CG94" t="n">
-        <v>22.89816535176007</v>
+        <v>22.89816533161465</v>
       </c>
       <c r="CH94" t="n">
         <v>54.19026455668205</v>
       </c>
       <c r="CI94" t="n">
-        <v>36.98786878037602</v>
+        <v>36.98786878020007</v>
       </c>
       <c r="CJ94" t="n">
         <v>40.64260876606351</v>
@@ -43201,7 +43225,7 @@
         <v>4.330708661417315</v>
       </c>
       <c r="CP94" t="n">
-        <v>5.498765920054027</v>
+        <v>5.498765919552207</v>
       </c>
       <c r="CQ94" t="inlineStr">
         <is>
@@ -43483,10 +43507,10 @@
         <v>79.11000061035156</v>
       </c>
       <c r="CA95" t="n">
-        <v>59.1458031552502</v>
+        <v>59.14580343791874</v>
       </c>
       <c r="CB95" t="n">
-        <v>86.1162893940443</v>
+        <v>86.1162898056097</v>
       </c>
       <c r="CC95" t="n">
         <v>24.45731291164257</v>
@@ -43790,35 +43814,35 @@
         <v>19.96999931335449</v>
       </c>
       <c r="CA96" t="n">
-        <v>11.90594417638589</v>
+        <v>11.90594416734853</v>
       </c>
       <c r="CB96" t="n">
-        <v>15.10171756875187</v>
+        <v>15.10171756326644</v>
       </c>
       <c r="CC96" t="n">
-        <v>22.67303324574936</v>
+        <v>22.67303325472404</v>
       </c>
       <c r="CD96" t="n">
         <v>41.91581127865282</v>
       </c>
       <c r="CE96" t="n">
-        <v>27.56465658152593</v>
+        <v>27.56465657578011</v>
       </c>
       <c r="CF96" t="n">
-        <v>15.76132613201339</v>
+        <v>15.76132613263354</v>
       </c>
       <c r="CG96" t="n">
-        <v>10.88226007491759</v>
+        <v>10.88226008127193</v>
       </c>
       <c r="CH96" t="inlineStr"/>
       <c r="CI96" t="n">
-        <v>16.36050528072513</v>
+        <v>16.36050527949314</v>
       </c>
       <c r="CJ96" t="n">
-        <v>15.43152185038263</v>
+        <v>15.43152184794999</v>
       </c>
       <c r="CK96" t="n">
-        <v>13.88836966534437</v>
+        <v>13.88836966315499</v>
       </c>
       <c r="CL96" t="n">
         <v>4</v>
@@ -43830,10 +43854,10 @@
         <v>1.9</v>
       </c>
       <c r="CO96" t="n">
-        <v>-30.45383003064587</v>
+        <v>-30.45383004160919</v>
       </c>
       <c r="CP96" t="n">
-        <v>-18.07458265767486</v>
+        <v>-18.07458266384408</v>
       </c>
       <c r="CQ96" t="inlineStr">
         <is>
@@ -44129,10 +44153,10 @@
         <v>19.39999961853027</v>
       </c>
       <c r="CA97" t="n">
-        <v>2.002220655048227</v>
+        <v>2.002220649267907</v>
       </c>
       <c r="CB97" t="n">
-        <v>3.714119315114461</v>
+        <v>3.714119304391967</v>
       </c>
       <c r="CC97" t="n">
         <v>10.17214067849332</v>
@@ -44141,19 +44165,19 @@
         <v>8.489143658487551</v>
       </c>
       <c r="CE97" t="n">
-        <v>10.08225773210836</v>
+        <v>10.08225774380416</v>
       </c>
       <c r="CF97" t="n">
-        <v>7.542853165173372</v>
+        <v>7.542853166483961</v>
       </c>
       <c r="CG97" t="n">
-        <v>7.691046827029282</v>
+        <v>7.691046836393862</v>
       </c>
       <c r="CH97" t="n">
         <v>13.63549921457183</v>
       </c>
       <c r="CI97" t="n">
-        <v>8.761008655854024</v>
+        <v>8.761008657518092</v>
       </c>
       <c r="CJ97" t="n">
         <v>8.489143658487551</v>
@@ -44174,7 +44198,7 @@
         <v>-60.61737400581654</v>
       </c>
       <c r="CP97" t="n">
-        <v>-54.84016067976732</v>
+        <v>-54.84016067118965</v>
       </c>
       <c r="CQ97" t="inlineStr">
         <is>
@@ -44466,10 +44490,10 @@
         <v>16.01000022888184</v>
       </c>
       <c r="CA98" t="n">
-        <v>8.061612831561469</v>
+        <v>8.061612835698385</v>
       </c>
       <c r="CB98" t="n">
-        <v>14.95429180254652</v>
+        <v>14.95429181022051</v>
       </c>
       <c r="CC98" t="n">
         <v>10.47567916210787</v>
@@ -44490,7 +44514,7 @@
         <v>10.00660187036776</v>
       </c>
       <c r="CI98" t="n">
-        <v>12.47880699511274</v>
+        <v>12.47880699658911</v>
       </c>
       <c r="CJ98" t="n">
         <v>10.24114051623781</v>
@@ -44511,7 +44535,7 @@
         <v>-42.4295669403762</v>
       </c>
       <c r="CP98" t="n">
-        <v>-22.05617228786083</v>
+        <v>-22.05617227863933</v>
       </c>
       <c r="CQ98" t="inlineStr">
         <is>
@@ -44795,10 +44819,10 @@
         <v>7.170000076293945</v>
       </c>
       <c r="CA99" t="n">
-        <v>3.21441692180567</v>
+        <v>3.214416914576922</v>
       </c>
       <c r="CB99" t="n">
-        <v>5.962743389949518</v>
+        <v>5.96274337654019</v>
       </c>
       <c r="CC99" t="inlineStr"/>
       <c r="CD99" t="inlineStr"/>
@@ -44809,13 +44833,13 @@
         <v>9.809989751681186</v>
       </c>
       <c r="CI99" t="n">
-        <v>6.329050021145458</v>
+        <v>6.329050014266099</v>
       </c>
       <c r="CJ99" t="n">
-        <v>5.962743389949518</v>
+        <v>5.96274337654019</v>
       </c>
       <c r="CK99" t="n">
-        <v>5.366469050954566</v>
+        <v>5.366469038886171</v>
       </c>
       <c r="CL99" t="n">
         <v>3</v>
@@ -44827,10 +44851,10 @@
         <v>3.1</v>
       </c>
       <c r="CO99" t="n">
-        <v>-25.15384945813828</v>
+        <v>-25.1538496264562</v>
       </c>
       <c r="CP99" t="n">
-        <v>-11.72873146722698</v>
+        <v>-11.72873156317342</v>
       </c>
       <c r="CQ99" t="inlineStr">
         <is>
@@ -45122,37 +45146,37 @@
         <v>23.05999946594238</v>
       </c>
       <c r="CA100" t="n">
-        <v>5.05068890057821</v>
+        <v>5.050688926532513</v>
       </c>
       <c r="CB100" t="n">
-        <v>7.175729492616548</v>
+        <v>7.175729498410869</v>
       </c>
       <c r="CC100" t="n">
-        <v>10.62745763346741</v>
+        <v>10.62745758743696</v>
       </c>
       <c r="CD100" t="n">
         <v>14.56873729010693</v>
       </c>
       <c r="CE100" t="n">
-        <v>7.163504709906552</v>
+        <v>7.163504684185467</v>
       </c>
       <c r="CF100" t="n">
-        <v>8.436256194404386</v>
+        <v>8.436256191126738</v>
       </c>
       <c r="CG100" t="n">
-        <v>5.281933294867852</v>
+        <v>5.281933268328021</v>
       </c>
       <c r="CH100" t="n">
         <v>10.72687534044447</v>
       </c>
       <c r="CI100" t="n">
-        <v>8.628897857049044</v>
+        <v>8.628897848321497</v>
       </c>
       <c r="CJ100" t="n">
-        <v>7.805992843510467</v>
+        <v>7.805992844768804</v>
       </c>
       <c r="CK100" t="n">
-        <v>7.02539355915942</v>
+        <v>7.025393560291924</v>
       </c>
       <c r="CL100" t="n">
         <v>8</v>
@@ -45164,10 +45188,10 @@
         <v>2.9</v>
       </c>
       <c r="CO100" t="n">
-        <v>-69.53428568142286</v>
+        <v>-69.53428567651174</v>
       </c>
       <c r="CP100" t="n">
-        <v>-62.5806675763667</v>
+        <v>-62.58066761421382</v>
       </c>
       <c r="CQ100" t="inlineStr">
         <is>
@@ -45451,10 +45475,10 @@
         <v>46.40000152587891</v>
       </c>
       <c r="CA101" t="n">
-        <v>10.15177884788909</v>
+        <v>10.15177886092706</v>
       </c>
       <c r="CB101" t="n">
-        <v>18.83154976283427</v>
+        <v>18.8315497870197</v>
       </c>
       <c r="CC101" t="n">
         <v>86.34831744633361</v>
@@ -45463,13 +45487,13 @@
         <v>76.25640482050953</v>
       </c>
       <c r="CE101" t="n">
-        <v>103.7331108817738</v>
+        <v>103.7331108774021</v>
       </c>
       <c r="CF101" t="n">
-        <v>16.00171149785102</v>
+        <v>16.00171149719812</v>
       </c>
       <c r="CG101" t="n">
-        <v>70.06583766469056</v>
+        <v>70.06583764582827</v>
       </c>
       <c r="CH101" t="n">
         <v>22.72912505392368</v>
@@ -45782,25 +45806,25 @@
         <v>47.5</v>
       </c>
       <c r="CA102" t="n">
-        <v>18.25668186205534</v>
+        <v>18.2566818854614</v>
       </c>
       <c r="CB102" t="n">
-        <v>20.19873861033739</v>
+        <v>20.19873862123098</v>
       </c>
       <c r="CC102" t="n">
-        <v>23.86378088434031</v>
+        <v>23.86378086661586</v>
       </c>
       <c r="CD102" t="n">
         <v>51.4328502242105</v>
       </c>
       <c r="CE102" t="n">
-        <v>19.85694201850506</v>
+        <v>19.85694201384302</v>
       </c>
       <c r="CF102" t="n">
-        <v>23.27481926174592</v>
+        <v>23.27481925980414</v>
       </c>
       <c r="CG102" t="n">
-        <v>10.33491116412826</v>
+        <v>10.33491114810354</v>
       </c>
       <c r="CH102" t="n">
         <v>120.2965411332743</v>
@@ -46109,37 +46133,37 @@
         <v>52.59999847412109</v>
       </c>
       <c r="CA103" t="n">
-        <v>16.06764461218517</v>
+        <v>16.06764462180982</v>
       </c>
       <c r="CB103" t="n">
-        <v>24.44956361783018</v>
+        <v>24.44956362337622</v>
       </c>
       <c r="CC103" t="n">
-        <v>44.11350738606083</v>
+        <v>44.11350736964302</v>
       </c>
       <c r="CD103" t="n">
         <v>61.25894385652082</v>
       </c>
       <c r="CE103" t="n">
-        <v>35.19545559380767</v>
+        <v>35.1954555909188</v>
       </c>
       <c r="CF103" t="n">
-        <v>26.76297347112799</v>
+        <v>26.7629734702888</v>
       </c>
       <c r="CG103" t="n">
-        <v>22.05510056367665</v>
+        <v>22.05510055532554</v>
       </c>
       <c r="CH103" t="n">
         <v>21.52547978006953</v>
       </c>
       <c r="CI103" t="n">
-        <v>31.42858361015985</v>
+        <v>31.42858360849407</v>
       </c>
       <c r="CJ103" t="n">
-        <v>25.60626854447909</v>
+        <v>25.60626854683251</v>
       </c>
       <c r="CK103" t="n">
-        <v>23.04564169003118</v>
+        <v>23.04564169214926</v>
       </c>
       <c r="CL103" t="n">
         <v>8</v>
@@ -46151,10 +46175,10 @@
         <v>3.8</v>
       </c>
       <c r="CO103" t="n">
-        <v>-56.18699171375545</v>
+        <v>-56.18699170972869</v>
       </c>
       <c r="CP103" t="n">
-        <v>-40.2498393120248</v>
+        <v>-40.24983931519169</v>
       </c>
       <c r="CQ103" t="inlineStr">
         <is>
@@ -46458,10 +46482,10 @@
         <v>11.97000026702881</v>
       </c>
       <c r="CA104" t="n">
-        <v>2.12963359208348</v>
+        <v>2.129633596371886</v>
       </c>
       <c r="CB104" t="n">
-        <v>3.950470313314854</v>
+        <v>3.950470321269849</v>
       </c>
       <c r="CC104" t="n">
         <v>12.16276867623709</v>
@@ -46470,25 +46494,25 @@
         <v>13.48270925178679</v>
       </c>
       <c r="CE104" t="n">
-        <v>8.763285708126944</v>
+        <v>8.763285706457124</v>
       </c>
       <c r="CF104" t="n">
-        <v>5.737621689274977</v>
+        <v>5.73762168890867</v>
       </c>
       <c r="CG104" t="n">
-        <v>6.523398953884617</v>
+        <v>6.523398949940999</v>
       </c>
       <c r="CH104" t="n">
         <v>11.97000026702881</v>
       </c>
       <c r="CI104" t="n">
-        <v>8.941464979950585</v>
+        <v>8.941464980232762</v>
       </c>
       <c r="CJ104" t="n">
-        <v>8.763285708126944</v>
+        <v>8.763285706457124</v>
       </c>
       <c r="CK104" t="n">
-        <v>7.88695713731425</v>
+        <v>7.886957135811412</v>
       </c>
       <c r="CL104" t="n">
         <v>7</v>
@@ -46500,10 +46524,10 @@
         <v>6.3</v>
       </c>
       <c r="CO104" t="n">
-        <v>-34.11063524335285</v>
+        <v>-34.11063525590789</v>
       </c>
       <c r="CP104" t="n">
-        <v>-25.30104611125432</v>
+        <v>-25.30104610889694</v>
       </c>
       <c r="CQ104" t="inlineStr">
         <is>
@@ -46787,10 +46811,10 @@
         <v>3.029999971389771</v>
       </c>
       <c r="CA105" t="n">
-        <v>0.6343933993611854</v>
+        <v>0.6343933978702244</v>
       </c>
       <c r="CB105" t="n">
-        <v>1.176799755814999</v>
+        <v>1.176799753049266</v>
       </c>
       <c r="CC105" t="n">
         <v>3.469965395066072</v>
@@ -46799,13 +46823,13 @@
         <v>4.010566432856011</v>
       </c>
       <c r="CE105" t="n">
-        <v>2.423903795900335</v>
+        <v>2.423903796093823</v>
       </c>
       <c r="CF105" t="n">
-        <v>2.63594951039454</v>
+        <v>2.635949510583644</v>
       </c>
       <c r="CG105" t="n">
-        <v>1.740689721027707</v>
+        <v>1.740689722283334</v>
       </c>
       <c r="CH105" t="n">
         <v>9.095071583324174</v>
@@ -47104,10 +47128,10 @@
         <v>55.18999862670898</v>
       </c>
       <c r="CA106" t="n">
-        <v>62.46314052596259</v>
+        <v>62.46314087046265</v>
       </c>
       <c r="CB106" t="n">
-        <v>90.94633260580153</v>
+        <v>90.94633310739363</v>
       </c>
       <c r="CC106" t="n">
         <v>24.38300703983744</v>
@@ -48029,10 +48053,10 @@
         <v>97.61000061035156</v>
       </c>
       <c r="CA109" t="n">
-        <v>4.982479625338173</v>
+        <v>4.982479577288823</v>
       </c>
       <c r="CB109" t="n">
-        <v>9.242499705002309</v>
+        <v>9.242499615870765</v>
       </c>
       <c r="CC109" t="n">
         <v>42.72654470059987</v>
@@ -48041,13 +48065,13 @@
         <v>42.39662181432417</v>
       </c>
       <c r="CE109" t="n">
-        <v>35.18195894094781</v>
+        <v>35.18195900624188</v>
       </c>
       <c r="CF109" t="n">
-        <v>17.64650211580932</v>
+        <v>17.64650212015547</v>
       </c>
       <c r="CG109" t="n">
-        <v>29.28029172646043</v>
+        <v>29.28029178147117</v>
       </c>
       <c r="CH109" t="n">
         <v>44.08436660991484</v>
@@ -48667,10 +48691,10 @@
         <v>17.03000068664551</v>
       </c>
       <c r="CA111" t="n">
-        <v>3.197534153255897</v>
+        <v>3.197534149963832</v>
       </c>
       <c r="CB111" t="n">
-        <v>5.931425854289688</v>
+        <v>5.931425848182909</v>
       </c>
       <c r="CC111" t="n">
         <v>14.94354364887768</v>
@@ -48679,23 +48703,23 @@
         <v>15.89715452361429</v>
       </c>
       <c r="CE111" t="n">
-        <v>10.65040732085227</v>
+        <v>10.65040732300807</v>
       </c>
       <c r="CF111" t="n">
-        <v>13.03125309515046</v>
+        <v>13.03125309571383</v>
       </c>
       <c r="CG111" t="n">
-        <v>7.843954317853668</v>
+        <v>7.843954321127297</v>
       </c>
       <c r="CH111" t="inlineStr"/>
       <c r="CI111" t="n">
-        <v>11.38295646010634</v>
+        <v>11.38295646008734</v>
       </c>
       <c r="CJ111" t="n">
-        <v>11.84083020800136</v>
+        <v>11.84083020936095</v>
       </c>
       <c r="CK111" t="n">
-        <v>10.65674718720123</v>
+        <v>10.65674718842485</v>
       </c>
       <c r="CL111" t="n">
         <v>6</v>
@@ -48707,10 +48731,10 @@
         <v>5</v>
       </c>
       <c r="CO111" t="n">
-        <v>-37.42368316192742</v>
+        <v>-37.42368315474231</v>
       </c>
       <c r="CP111" t="n">
-        <v>-33.15938930623435</v>
+        <v>-33.1593893063459</v>
       </c>
       <c r="CQ111" t="inlineStr">
         <is>
@@ -48994,25 +49018,25 @@
         <v>14.78999996185303</v>
       </c>
       <c r="CA112" t="n">
-        <v>3.734050393201275</v>
+        <v>3.734050399994813</v>
       </c>
       <c r="CB112" t="n">
-        <v>4.750965484023237</v>
+        <v>4.75096549153728</v>
       </c>
       <c r="CC112" t="n">
-        <v>14.39113216001768</v>
+        <v>14.39113215659596</v>
       </c>
       <c r="CD112" t="n">
         <v>37.23867291481046</v>
       </c>
       <c r="CE112" t="n">
-        <v>9.871878891398406</v>
+        <v>9.871878897748525</v>
       </c>
       <c r="CF112" t="n">
-        <v>48.41104884111049</v>
+        <v>48.41104883996949</v>
       </c>
       <c r="CG112" t="n">
-        <v>6.91725650025026</v>
+        <v>6.917256497841</v>
       </c>
       <c r="CH112" t="n">
         <v>27.46854012923095</v>
@@ -49313,25 +49337,25 @@
         <v>14.8100004196167</v>
       </c>
       <c r="CA113" t="n">
-        <v>1.386019549518147</v>
+        <v>1.386019545449728</v>
       </c>
       <c r="CB113" t="n">
-        <v>2.562681326721475</v>
+        <v>2.562681321724585</v>
       </c>
       <c r="CC113" t="n">
-        <v>8.677574918120134</v>
+        <v>8.677574926671523</v>
       </c>
       <c r="CD113" t="n">
         <v>10.7066274318662</v>
       </c>
       <c r="CE113" t="n">
-        <v>4.787218444920471</v>
+        <v>4.78721844722353</v>
       </c>
       <c r="CF113" t="n">
-        <v>7.688860391026426</v>
+        <v>7.688860391559766</v>
       </c>
       <c r="CG113" t="n">
-        <v>4.223256306819287</v>
+        <v>4.223256309855304</v>
       </c>
       <c r="CH113" t="n">
         <v>11.50778129173654</v>
@@ -49632,10 +49656,10 @@
         <v>11.21000003814697</v>
       </c>
       <c r="CA114" t="n">
-        <v>2.436021025519974</v>
+        <v>2.436021028890328</v>
       </c>
       <c r="CB114" t="n">
-        <v>4.51881900233955</v>
+        <v>4.518819008591558</v>
       </c>
       <c r="CC114" t="n">
         <v>12.15486910846541</v>
@@ -49644,13 +49668,13 @@
         <v>12.67593560098585</v>
       </c>
       <c r="CE114" t="n">
-        <v>9.597028729023554</v>
+        <v>9.597028727312301</v>
       </c>
       <c r="CF114" t="n">
-        <v>0.7922538304303869</v>
+        <v>0.7922538303855846</v>
       </c>
       <c r="CG114" t="n">
-        <v>6.728795256528601</v>
+        <v>6.728795253025859</v>
       </c>
       <c r="CH114" t="n">
         <v>7.42587936633825</v>
@@ -49951,10 +49975,10 @@
         <v>18.32999992370605</v>
       </c>
       <c r="CA115" t="n">
-        <v>11.72168815763747</v>
+        <v>11.72168816791328</v>
       </c>
       <c r="CB115" t="n">
-        <v>14.62662826626936</v>
+        <v>14.62662827909178</v>
       </c>
       <c r="CC115" t="inlineStr"/>
       <c r="CD115" t="inlineStr"/>
@@ -50262,25 +50286,25 @@
         <v>8.859999656677246</v>
       </c>
       <c r="CA116" t="n">
-        <v>2.278494628623395</v>
+        <v>2.278494627479795</v>
       </c>
       <c r="CB116" t="n">
-        <v>2.457217339661122</v>
+        <v>2.457217338745752</v>
       </c>
       <c r="CC116" t="n">
-        <v>3.198208818983299</v>
+        <v>3.198208819397106</v>
       </c>
       <c r="CD116" t="n">
         <v>9.985934437661033</v>
       </c>
       <c r="CE116" t="n">
-        <v>1.868987657735393</v>
+        <v>1.868987657607944</v>
       </c>
       <c r="CF116" t="n">
-        <v>5.906665058178842</v>
+        <v>5.906665058266654</v>
       </c>
       <c r="CG116" t="n">
-        <v>1.344337860271695</v>
+        <v>1.344337860663172</v>
       </c>
       <c r="CH116" t="n">
         <v>14.36284499478099</v>
@@ -50593,10 +50617,10 @@
         <v>4.820000171661377</v>
       </c>
       <c r="CA117" t="n">
-        <v>1.482729240334445</v>
+        <v>1.482729246311887</v>
       </c>
       <c r="CB117" t="n">
-        <v>1.545333363815232</v>
+        <v>1.545333370045055</v>
       </c>
       <c r="CC117" t="inlineStr"/>
       <c r="CD117" t="inlineStr"/>
@@ -50902,10 +50926,10 @@
         <v>3.339999914169312</v>
       </c>
       <c r="CA118" t="n">
-        <v>1.645463646645273</v>
+        <v>1.645463643602964</v>
       </c>
       <c r="CB118" t="n">
-        <v>3.052335064526982</v>
+        <v>3.052335058883498</v>
       </c>
       <c r="CC118" t="n">
         <v>1.157901592431799</v>
@@ -50914,7 +50938,7 @@
         <v>4.60268789222791</v>
       </c>
       <c r="CE118" t="n">
-        <v>1.607705129931474</v>
+        <v>1.607705128817075</v>
       </c>
       <c r="CF118" t="n">
         <v>0.7445919647652398</v>
@@ -51221,10 +51245,10 @@
         <v>6.53000020980835</v>
       </c>
       <c r="CA119" t="n">
-        <v>1.050039162546931</v>
+        <v>1.050039167604812</v>
       </c>
       <c r="CB119" t="n">
-        <v>1.947822646524558</v>
+        <v>1.947822655906926</v>
       </c>
       <c r="CC119" t="inlineStr"/>
       <c r="CD119" t="inlineStr"/>
@@ -51530,25 +51554,25 @@
         <v>3.680000066757202</v>
       </c>
       <c r="CA120" t="n">
-        <v>1.260908970505823</v>
+        <v>1.260908970841923</v>
       </c>
       <c r="CB120" t="n">
-        <v>1.270673792906873</v>
+        <v>1.270673793123084</v>
       </c>
       <c r="CC120" t="n">
-        <v>1.297857839050533</v>
+        <v>1.29785783892542</v>
       </c>
       <c r="CD120" t="n">
         <v>4.028317282462615</v>
       </c>
       <c r="CE120" t="n">
-        <v>0.8819378177255388</v>
+        <v>0.881937817743869</v>
       </c>
       <c r="CF120" t="n">
-        <v>2.295529039220201</v>
+        <v>2.295529039193208</v>
       </c>
       <c r="CG120" t="n">
-        <v>0.4923745534277685</v>
+        <v>0.4923745532943772</v>
       </c>
       <c r="CH120" t="n">
         <v>5.189162701709523</v>
@@ -51853,10 +51877,10 @@
         <v>5.369999885559082</v>
       </c>
       <c r="CA121" t="n">
-        <v>5.323748905168305</v>
+        <v>5.323748905251827</v>
       </c>
       <c r="CB121" t="n">
-        <v>7.751378405925052</v>
+        <v>7.751378406046661</v>
       </c>
       <c r="CC121" t="inlineStr"/>
       <c r="CD121" t="inlineStr"/>
@@ -51865,13 +51889,13 @@
       <c r="CG121" t="inlineStr"/>
       <c r="CH121" t="inlineStr"/>
       <c r="CI121" t="n">
-        <v>6.537563655546679</v>
+        <v>6.537563655649244</v>
       </c>
       <c r="CJ121" t="n">
-        <v>6.537563655546679</v>
+        <v>6.537563655649244</v>
       </c>
       <c r="CK121" t="n">
-        <v>5.883807289992011</v>
+        <v>5.883807290084319</v>
       </c>
       <c r="CL121" t="n">
         <v>2</v>
@@ -51883,10 +51907,10 @@
         <v>1.5</v>
       </c>
       <c r="CO121" t="n">
-        <v>9.568108293906153</v>
+        <v>9.568108295625111</v>
       </c>
       <c r="CP121" t="n">
-        <v>21.7423425487846</v>
+        <v>21.74234255069456</v>
       </c>
       <c r="CQ121" t="inlineStr">
         <is>
@@ -52170,10 +52194,10 @@
         <v>5.369999885559082</v>
       </c>
       <c r="CA122" t="n">
-        <v>5.9112115052234</v>
+        <v>5.911211507335186</v>
       </c>
       <c r="CB122" t="n">
-        <v>10.53904913907179</v>
+        <v>10.53904914283688</v>
       </c>
       <c r="CC122" t="inlineStr"/>
       <c r="CD122" t="inlineStr"/>
@@ -52182,13 +52206,13 @@
       <c r="CG122" t="inlineStr"/>
       <c r="CH122" t="inlineStr"/>
       <c r="CI122" t="n">
-        <v>8.225130322147594</v>
+        <v>8.225130325086031</v>
       </c>
       <c r="CJ122" t="n">
-        <v>8.225130322147594</v>
+        <v>8.225130325086031</v>
       </c>
       <c r="CK122" t="n">
-        <v>7.402617289932834</v>
+        <v>7.402617292577428</v>
       </c>
       <c r="CL122" t="n">
         <v>2</v>
@@ -52200,10 +52224,10 @@
         <v>1.8</v>
       </c>
       <c r="CO122" t="n">
-        <v>37.85134911901646</v>
+        <v>37.85134916826402</v>
       </c>
       <c r="CP122" t="n">
-        <v>53.16816568779608</v>
+        <v>53.16816574251557</v>
       </c>
       <c r="CQ122" t="inlineStr">
         <is>
@@ -52473,10 +52497,10 @@
         <v>22.35000038146973</v>
       </c>
       <c r="CA123" t="n">
-        <v>38.78271016943055</v>
+        <v>38.7827104273716</v>
       </c>
       <c r="CB123" t="n">
-        <v>71.94192736429368</v>
+        <v>71.94192784277432</v>
       </c>
       <c r="CC123" t="n">
         <v>19.80852876618554</v>
@@ -52495,7 +52519,7 @@
       </c>
       <c r="CH123" t="inlineStr"/>
       <c r="CI123" t="n">
-        <v>25.97687179429253</v>
+        <v>25.97687183728271</v>
       </c>
       <c r="CJ123" t="n">
         <v>23.0354806164258</v>
@@ -52516,7 +52540,7 @@
         <v>-7.239676953330354</v>
       </c>
       <c r="CP123" t="n">
-        <v>16.22761230836412</v>
+        <v>16.2276125007139</v>
       </c>
       <c r="CQ123" t="inlineStr">
         <is>
@@ -52804,25 +52828,25 @@
         <v>9.090000152587891</v>
       </c>
       <c r="CA124" t="n">
-        <v>3.51320112353287</v>
+        <v>3.513201113729493</v>
       </c>
       <c r="CB124" t="n">
-        <v>3.627571367085539</v>
+        <v>3.627571358518037</v>
       </c>
       <c r="CC124" t="n">
-        <v>4.393334527038602</v>
+        <v>4.393334528921876</v>
       </c>
       <c r="CD124" t="n">
         <v>18.92946868244077</v>
       </c>
       <c r="CE124" t="n">
-        <v>3.454654105283574</v>
+        <v>3.454654099350264</v>
       </c>
       <c r="CF124" t="n">
-        <v>7.742523561935217</v>
+        <v>7.742523562331491</v>
       </c>
       <c r="CG124" t="n">
-        <v>1.736838690216524</v>
+        <v>1.736838692140338</v>
       </c>
       <c r="CH124" t="n">
         <v>21.77146113239846</v>
@@ -53430,10 +53454,10 @@
         <v>11.25</v>
       </c>
       <c r="CA126" t="n">
-        <v>0.7656099600185554</v>
+        <v>0.7656099592395338</v>
       </c>
       <c r="CB126" t="n">
-        <v>1.42020647583442</v>
+        <v>1.420206474389335</v>
       </c>
       <c r="CC126" t="n">
         <v>15.28846153846153</v>
@@ -53442,13 +53466,13 @@
         <v>15.93648555693364</v>
       </c>
       <c r="CE126" t="n">
-        <v>13.4080679095444</v>
+        <v>13.40806790970839</v>
       </c>
       <c r="CF126" t="n">
-        <v>1.648078624689333</v>
+        <v>1.648078624705886</v>
       </c>
       <c r="CG126" t="n">
-        <v>10.81933391622435</v>
+        <v>10.81933391703054</v>
       </c>
       <c r="CH126" t="inlineStr"/>
       <c r="CI126" t="inlineStr"/>
@@ -53747,25 +53771,25 @@
         <v>18.46054267883301</v>
       </c>
       <c r="CA127" t="n">
-        <v>0.5760472920451851</v>
+        <v>0.5760472931370921</v>
       </c>
       <c r="CB127" t="n">
-        <v>0.7744861392118758</v>
+        <v>0.7744861405802382</v>
       </c>
       <c r="CC127" t="n">
-        <v>4.579823772067508</v>
+        <v>4.579823771478012</v>
       </c>
       <c r="CD127" t="n">
         <v>11.45343257282958</v>
       </c>
       <c r="CE127" t="n">
-        <v>1.75766018980462</v>
+        <v>1.757660189601812</v>
       </c>
       <c r="CF127" t="n">
-        <v>0.6742367133657954</v>
+        <v>0.6742367133576108</v>
       </c>
       <c r="CG127" t="n">
-        <v>2.247847913320574</v>
+        <v>2.247847912944871</v>
       </c>
       <c r="CH127" t="n">
         <v>18.46054267883301</v>
@@ -53894,19 +53918,11 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>Fundo duplo</t>
-        </is>
-      </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>Fundo duplo (pré-confirmação) — pescoço R$5.93, preço 11.6% abaixo do pescoço; falta fechar acima e segurar</t>
-        </is>
-      </c>
+          <t>Bandeira de alta</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
       <c r="U128" t="b">
         <v>0</v>
       </c>
@@ -54074,10 +54090,10 @@
         <v>5.239999771118164</v>
       </c>
       <c r="CA128" t="n">
-        <v>1.294299781628282</v>
+        <v>1.29429977328673</v>
       </c>
       <c r="CB128" t="n">
-        <v>2.166187179979698</v>
+        <v>2.166187166018972</v>
       </c>
       <c r="CC128" t="inlineStr"/>
       <c r="CD128" t="inlineStr"/>
@@ -54088,13 +54104,13 @@
         <v>6.020931258896678</v>
       </c>
       <c r="CI128" t="n">
-        <v>1.73024348080399</v>
+        <v>1.730243469652851</v>
       </c>
       <c r="CJ128" t="n">
-        <v>1.73024348080399</v>
+        <v>1.730243469652851</v>
       </c>
       <c r="CK128" t="n">
-        <v>1.557219132723591</v>
+        <v>1.557219122687566</v>
       </c>
       <c r="CL128" t="n">
         <v>2</v>
@@ -54106,10 +54122,10 @@
         <v>4.7</v>
       </c>
       <c r="CO128" t="n">
-        <v>-70.28207632170763</v>
+        <v>-70.28207651323484</v>
       </c>
       <c r="CP128" t="n">
-        <v>-66.98008480189736</v>
+        <v>-66.98008501470537</v>
       </c>
       <c r="CQ128" t="inlineStr">
         <is>
@@ -54123,7 +54139,11 @@
       </c>
       <c r="CS128" t="inlineStr"/>
       <c r="CT128" t="inlineStr"/>
-      <c r="CU128" t="inlineStr"/>
+      <c r="CU128" t="inlineStr">
+        <is>
+          <t>Bandeira de alta</t>
+        </is>
+      </c>
       <c r="CV128" t="b">
         <v>0</v>
       </c>
@@ -54150,14 +54170,14 @@
         <v>0</v>
       </c>
       <c r="DE128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF128" t="b">
         <v>0</v>
       </c>
       <c r="DG128" t="inlineStr">
         <is>
-          <t>sem sinal (Em Alta)</t>
+          <t>Bandeira de alta — mastro +14%, recuo 45%, bandeira 15d (candidato)</t>
         </is>
       </c>
     </row>
@@ -54389,10 +54409,10 @@
         <v>17.5</v>
       </c>
       <c r="CA129" t="n">
-        <v>1.348245199035097</v>
+        <v>1.348245199314659</v>
       </c>
       <c r="CB129" t="n">
-        <v>1.963045009795102</v>
+        <v>1.963045010202144</v>
       </c>
       <c r="CC129" t="n">
         <v>1.254999310439939</v>
@@ -54704,37 +54724,37 @@
         <v>17.54999923706055</v>
       </c>
       <c r="CA130" t="n">
-        <v>2.114176585745423</v>
+        <v>2.114176579589143</v>
       </c>
       <c r="CB130" t="n">
-        <v>3.730125109643394</v>
+        <v>3.730125103748781</v>
       </c>
       <c r="CC130" t="n">
-        <v>9.632950357479386</v>
+        <v>9.632950370306933</v>
       </c>
       <c r="CD130" t="n">
         <v>11.96027571768681</v>
       </c>
       <c r="CE130" t="n">
-        <v>5.584250639476172</v>
+        <v>5.584250643625776</v>
       </c>
       <c r="CF130" t="n">
-        <v>5.535381010147293</v>
+        <v>5.535381010689189</v>
       </c>
       <c r="CG130" t="n">
-        <v>4.7417561265154</v>
+        <v>4.741756131483272</v>
       </c>
       <c r="CH130" t="n">
         <v>15.78993633088096</v>
       </c>
       <c r="CI130" t="n">
-        <v>6.864123160158075</v>
+        <v>6.86412316292346</v>
       </c>
       <c r="CJ130" t="n">
-        <v>5.559815824811732</v>
+        <v>5.559815827157482</v>
       </c>
       <c r="CK130" t="n">
-        <v>5.00383424233056</v>
+        <v>5.003834244441735</v>
       </c>
       <c r="CL130" t="n">
         <v>6</v>
@@ -54746,10 +54766,10 @@
         <v>7.5</v>
       </c>
       <c r="CO130" t="n">
-        <v>-71.48812273584662</v>
+        <v>-71.48812272381713</v>
       </c>
       <c r="CP130" t="n">
-        <v>-60.88818542132456</v>
+        <v>-60.88818540556738</v>
       </c>
       <c r="CQ130" t="inlineStr">
         <is>
@@ -55025,10 +55045,10 @@
         <v>4.329999923706055</v>
       </c>
       <c r="CA131" t="n">
-        <v>0.910606041728659</v>
+        <v>0.9106060404411094</v>
       </c>
       <c r="CB131" t="n">
-        <v>1.689174207406663</v>
+        <v>1.689174205018258</v>
       </c>
       <c r="CC131" t="inlineStr"/>
       <c r="CD131" t="inlineStr"/>
@@ -55037,13 +55057,13 @@
       <c r="CG131" t="inlineStr"/>
       <c r="CH131" t="inlineStr"/>
       <c r="CI131" t="n">
-        <v>1.299890124567661</v>
+        <v>1.299890122729684</v>
       </c>
       <c r="CJ131" t="n">
-        <v>1.299890124567661</v>
+        <v>1.299890122729684</v>
       </c>
       <c r="CK131" t="n">
-        <v>1.169901112110895</v>
+        <v>1.169901110456715</v>
       </c>
       <c r="CL131" t="n">
         <v>2</v>
@@ -55055,10 +55075,10 @@
         <v>1.9</v>
       </c>
       <c r="CO131" t="n">
-        <v>-72.98149808950633</v>
+        <v>-72.98149812770909</v>
       </c>
       <c r="CP131" t="n">
-        <v>-69.9794423216737</v>
+        <v>-69.97944236412121</v>
       </c>
       <c r="CQ131" t="inlineStr">
         <is>
@@ -55344,10 +55364,10 @@
         <v>1.179999947547913</v>
       </c>
       <c r="CA132" t="n">
-        <v>0.3468781100550173</v>
+        <v>0.3468781106801614</v>
       </c>
       <c r="CB132" t="n">
-        <v>0.6434588941520571</v>
+        <v>0.6434588953116993</v>
       </c>
       <c r="CC132" t="inlineStr"/>
       <c r="CD132" t="inlineStr"/>
@@ -55356,13 +55376,13 @@
       <c r="CG132" t="inlineStr"/>
       <c r="CH132" t="inlineStr"/>
       <c r="CI132" t="n">
-        <v>0.4951685021035372</v>
+        <v>0.4951685029959303</v>
       </c>
       <c r="CJ132" t="n">
-        <v>0.4951685021035372</v>
+        <v>0.4951685029959303</v>
       </c>
       <c r="CK132" t="n">
-        <v>0.4456516518931835</v>
+        <v>0.4456516526963373</v>
       </c>
       <c r="CL132" t="n">
         <v>2</v>
@@ -55374,10 +55394,10 @@
         <v>1.9</v>
       </c>
       <c r="CO132" t="n">
-        <v>-62.23290917772788</v>
+        <v>-62.23290910966399</v>
       </c>
       <c r="CP132" t="n">
-        <v>-58.03656575303098</v>
+        <v>-58.03656567740444</v>
       </c>
       <c r="CQ132" t="inlineStr">
         <is>
@@ -55659,10 +55679,10 @@
         <v>5.46999979019165</v>
       </c>
       <c r="CA133" t="n">
-        <v>1.043475837353275</v>
+        <v>1.043475835173986</v>
       </c>
       <c r="CB133" t="n">
-        <v>1.935647678290324</v>
+        <v>1.935647674247744</v>
       </c>
       <c r="CC133" t="inlineStr"/>
       <c r="CD133" t="inlineStr"/>
@@ -55673,13 +55693,13 @@
         <v>3.086391414577443</v>
       </c>
       <c r="CI133" t="n">
-        <v>2.021838310073681</v>
+        <v>2.021838307999724</v>
       </c>
       <c r="CJ133" t="n">
-        <v>1.935647678290324</v>
+        <v>1.935647674247744</v>
       </c>
       <c r="CK133" t="n">
-        <v>1.742082910461292</v>
+        <v>1.74208290682297</v>
       </c>
       <c r="CL133" t="n">
         <v>3</v>
@@ -55691,10 +55711,10 @@
         <v>3</v>
       </c>
       <c r="CO133" t="n">
-        <v>-68.15204794733172</v>
+        <v>-68.15204801384584</v>
       </c>
       <c r="CP133" t="n">
-        <v>-63.03768944015184</v>
+        <v>-63.03768947806695</v>
       </c>
       <c r="CQ133" t="inlineStr">
         <is>
@@ -56291,10 +56311,10 @@
         <v>36.70999908447266</v>
       </c>
       <c r="CA135" t="n">
-        <v>8.268344969942197</v>
+        <v>8.268344963622502</v>
       </c>
       <c r="CB135" t="n">
-        <v>12.03871027623584</v>
+        <v>12.03871026703436</v>
       </c>
       <c r="CC135" t="n">
         <v>7.906067311627989</v>
@@ -56608,25 +56628,25 @@
         <v>4.920000076293945</v>
       </c>
       <c r="CA136" t="n">
-        <v>1.527637924590932</v>
+        <v>1.527637925308267</v>
       </c>
       <c r="CB136" t="n">
-        <v>1.686462928729987</v>
+        <v>1.686462929346638</v>
       </c>
       <c r="CC136" t="n">
-        <v>2.469546774974334</v>
+        <v>2.469546774717689</v>
       </c>
       <c r="CD136" t="n">
         <v>7.731331217553538</v>
       </c>
       <c r="CE136" t="n">
-        <v>1.72780068391684</v>
+        <v>1.72780068418552</v>
       </c>
       <c r="CF136" t="n">
-        <v>1.781870301583647</v>
+        <v>1.781870301562807</v>
       </c>
       <c r="CG136" t="n">
-        <v>1.066963715076503</v>
+        <v>1.06696371484357</v>
       </c>
       <c r="CH136" t="n">
         <v>0.3081571864153818</v>
@@ -56925,10 +56945,10 @@
         <v>2.220000028610229</v>
       </c>
       <c r="CA137" t="n">
-        <v>0.6232610166705995</v>
+        <v>0.6232610168887069</v>
       </c>
       <c r="CB137" t="n">
-        <v>0.907468040272393</v>
+        <v>0.9074680405899573</v>
       </c>
       <c r="CC137" t="n">
         <v>0.3656057054243292</v>
@@ -57529,10 +57549,10 @@
         <v>6.869999885559082</v>
       </c>
       <c r="CA139" t="n">
-        <v>1.88529934806184</v>
+        <v>1.8852993490839</v>
       </c>
       <c r="CB139" t="n">
-        <v>2.744995850778039</v>
+        <v>2.744995852266159</v>
       </c>
       <c r="CC139" t="n">
         <v>1.690276763894357</v>
@@ -58436,25 +58456,25 @@
         <v>4.840000152587891</v>
       </c>
       <c r="CA142" t="n">
-        <v>0.8111693300150393</v>
+        <v>0.8111693281433602</v>
       </c>
       <c r="CB142" t="n">
-        <v>0.8137713607003161</v>
+        <v>0.8137713589376933</v>
       </c>
       <c r="CC142" t="n">
-        <v>0.8563537348506844</v>
+        <v>0.8563537349717655</v>
       </c>
       <c r="CD142" t="n">
         <v>6.37726014905843</v>
       </c>
       <c r="CE142" t="n">
-        <v>0.2850987644646573</v>
+        <v>0.2850987640246648</v>
       </c>
       <c r="CF142" t="n">
-        <v>0.417430599539619</v>
+        <v>0.4174305995468469</v>
       </c>
       <c r="CG142" t="n">
-        <v>0.3222030756686739</v>
+        <v>0.322203075798793</v>
       </c>
       <c r="CH142" t="inlineStr"/>
       <c r="CI142" t="inlineStr"/>
@@ -58755,10 +58775,10 @@
         <v>18.76000022888184</v>
       </c>
       <c r="CA143" t="n">
-        <v>28.489861654669</v>
+        <v>28.48986178681072</v>
       </c>
       <c r="CB143" t="n">
-        <v>38.11310381357941</v>
+        <v>38.11310399035567</v>
       </c>
       <c r="CC143" t="n">
         <v>2.597626784658967</v>
@@ -58767,7 +58787,7 @@
         <v>7.205629833517744</v>
       </c>
       <c r="CE143" t="n">
-        <v>6.649616923602199</v>
+        <v>6.649616950409679</v>
       </c>
       <c r="CF143" t="n">
         <v>3.046690502845772</v>
@@ -59074,10 +59094,10 @@
         <v>3.710000038146973</v>
       </c>
       <c r="CA144" t="n">
-        <v>0.6711165052882461</v>
+        <v>0.6711165064974021</v>
       </c>
       <c r="CB144" t="n">
-        <v>1.244921117309697</v>
+        <v>1.244921119552681</v>
       </c>
       <c r="CC144" t="inlineStr"/>
       <c r="CD144" t="inlineStr"/>
@@ -59088,13 +59108,13 @@
         <v>3.383752809074293</v>
       </c>
       <c r="CI144" t="n">
-        <v>0.9580188112989714</v>
+        <v>0.9580188130250414</v>
       </c>
       <c r="CJ144" t="n">
-        <v>0.9580188112989714</v>
+        <v>0.9580188130250414</v>
       </c>
       <c r="CK144" t="n">
-        <v>0.8622169301690743</v>
+        <v>0.8622169317225373</v>
       </c>
       <c r="CL144" t="n">
         <v>2</v>
@@ -59106,10 +59126,10 @@
         <v>5</v>
       </c>
       <c r="CO144" t="n">
-        <v>-76.75965171688451</v>
+        <v>-76.75965167501218</v>
       </c>
       <c r="CP144" t="n">
-        <v>-74.17739079653833</v>
+        <v>-74.17739075001354</v>
       </c>
       <c r="CQ144" t="inlineStr">
         <is>
@@ -59391,10 +59411,10 @@
         <v>18.79000091552734</v>
       </c>
       <c r="CA145" t="n">
-        <v>9.525161243518408</v>
+        <v>9.525161207651804</v>
       </c>
       <c r="CB145" t="n">
-        <v>13.8686347705628</v>
+        <v>13.86863471834103</v>
       </c>
       <c r="CC145" t="n">
         <v>4.657197557709351</v>
@@ -60342,10 +60362,10 @@
         <v>10.85999965667725</v>
       </c>
       <c r="CA148" t="n">
-        <v>5.802515951874023</v>
+        <v>5.802515956281911</v>
       </c>
       <c r="CB148" t="n">
-        <v>10.62075327191164</v>
+        <v>10.6207532799797</v>
       </c>
       <c r="CC148" t="inlineStr"/>
       <c r="CD148" t="inlineStr"/>
@@ -60356,13 +60376,13 @@
         <v>3.332701500657688</v>
       </c>
       <c r="CI148" t="n">
-        <v>6.585323574814449</v>
+        <v>6.5853235789731</v>
       </c>
       <c r="CJ148" t="n">
-        <v>5.802515951874023</v>
+        <v>5.802515956281911</v>
       </c>
       <c r="CK148" t="n">
-        <v>5.222264356686621</v>
+        <v>5.22226436065372</v>
       </c>
       <c r="CL148" t="n">
         <v>3</v>
@@ -60374,10 +60394,10 @@
         <v>3.2</v>
       </c>
       <c r="CO148" t="n">
-        <v>-51.91284970735958</v>
+        <v>-51.91284967083012</v>
       </c>
       <c r="CP148" t="n">
-        <v>-39.36165945672495</v>
+        <v>-39.36165941843166</v>
       </c>
       <c r="CQ148" t="inlineStr">
         <is>
@@ -60980,10 +61000,10 @@
         <v>15.42000007629395</v>
       </c>
       <c r="CA150" t="n">
-        <v>3.945356587636522</v>
+        <v>3.945356590456175</v>
       </c>
       <c r="CB150" t="n">
-        <v>5.744439191598777</v>
+        <v>5.744439195704191</v>
       </c>
       <c r="CC150" t="inlineStr"/>
       <c r="CD150" t="inlineStr"/>
@@ -60994,7 +61014,7 @@
         <v>5.488479853420727</v>
       </c>
       <c r="CI150" t="n">
-        <v>5.059425210885341</v>
+        <v>5.059425213193698</v>
       </c>
       <c r="CJ150" t="n">
         <v>5.488479853420727</v>
@@ -61015,7 +61035,7 @@
         <v>-67.96607105292668</v>
       </c>
       <c r="CP150" t="n">
-        <v>-67.18920112936</v>
+        <v>-67.1892011143901</v>
       </c>
       <c r="CQ150" t="inlineStr">
         <is>

--- a/reports/screener_2026-08-29.xlsx
+++ b/reports/screener_2026-08-29.xlsx
@@ -1206,10 +1206,10 @@
         <v>10.35999965667725</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.851607491869938</v>
+        <v>5.851607495201637</v>
       </c>
       <c r="CB2" t="n">
-        <v>10.85473189741873</v>
+        <v>10.85473190359903</v>
       </c>
       <c r="CC2" t="n">
         <v>41.59696831847682</v>
@@ -1218,7 +1218,7 @@
         <v>27.90166392450355</v>
       </c>
       <c r="CE2" t="n">
-        <v>71.91590901101146</v>
+        <v>71.91590902514595</v>
       </c>
       <c r="CF2" t="n">
         <v>19.57807411896471</v>
@@ -1529,10 +1529,10 @@
         <v>13.46000003814697</v>
       </c>
       <c r="CA3" t="n">
-        <v>14.84732050446674</v>
+        <v>14.84732048606202</v>
       </c>
       <c r="CB3" t="n">
-        <v>27.54177953578581</v>
+        <v>27.54177950164504</v>
       </c>
       <c r="CC3" t="n">
         <v>38.93995644223742</v>
@@ -1541,13 +1541,13 @@
         <v>23.51205793312256</v>
       </c>
       <c r="CE3" t="n">
-        <v>75.54482871709098</v>
+        <v>75.54482875116977</v>
       </c>
       <c r="CF3" t="n">
-        <v>48.5251594276379</v>
+        <v>48.52515944116575</v>
       </c>
       <c r="CG3" t="n">
-        <v>26.80868515112335</v>
+        <v>26.80868520790709</v>
       </c>
       <c r="CH3" t="n">
         <v>8.920136085713818</v>
@@ -1756,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AV4" t="b">
         <v>1</v>
@@ -1852,10 +1852,10 @@
         <v>24.61000061035156</v>
       </c>
       <c r="CA4" t="n">
-        <v>16.31411910363583</v>
+        <v>16.31411911768027</v>
       </c>
       <c r="CB4" t="n">
-        <v>30.26269093724446</v>
+        <v>30.2626909632969</v>
       </c>
       <c r="CC4" t="n">
         <v>72.30210822331667</v>
@@ -1864,19 +1864,19 @@
         <v>52.41049602817493</v>
       </c>
       <c r="CE4" t="n">
-        <v>127.9950261325152</v>
+        <v>127.9950261281756</v>
       </c>
       <c r="CF4" t="n">
-        <v>25.7314236559713</v>
+        <v>25.73142365399151</v>
       </c>
       <c r="CG4" t="n">
-        <v>63.19894118477155</v>
+        <v>63.19894115464003</v>
       </c>
       <c r="CH4" t="n">
         <v>42.85100954601229</v>
       </c>
       <c r="CI4" t="n">
-        <v>47.79277826258186</v>
+        <v>47.79277826157206</v>
       </c>
       <c r="CJ4" t="n">
         <v>47.63075278709361</v>
@@ -1897,7 +1897,7 @@
         <v>74.18803919229917</v>
       </c>
       <c r="CP4" t="n">
-        <v>94.20063826605134</v>
+        <v>94.20063826194811</v>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
@@ -2183,10 +2183,10 @@
         <v>4.119999885559082</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.742641509775883</v>
+        <v>3.742641507761736</v>
       </c>
       <c r="CB5" t="n">
-        <v>6.942600000634262</v>
+        <v>6.942599996898021</v>
       </c>
       <c r="CC5" t="n">
         <v>12.63657372306894</v>
@@ -2195,19 +2195,19 @@
         <v>8.512687176725057</v>
       </c>
       <c r="CE5" t="n">
-        <v>24.29899389942381</v>
+        <v>24.29899390088217</v>
       </c>
       <c r="CF5" t="n">
-        <v>11.19276559034328</v>
+        <v>11.19276559117442</v>
       </c>
       <c r="CG5" t="n">
-        <v>10.1975051884262</v>
+        <v>10.19750519344577</v>
       </c>
       <c r="CH5" t="n">
         <v>5.258139118319559</v>
       </c>
       <c r="CI5" t="n">
-        <v>8.35470175818474</v>
+        <v>8.354701758199074</v>
       </c>
       <c r="CJ5" t="n">
         <v>8.512687176725057</v>
@@ -2228,7 +2228,7 @@
         <v>85.95676388017426</v>
       </c>
       <c r="CP5" t="n">
-        <v>102.7840288896273</v>
+        <v>102.7840288899752</v>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
         <v>4.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.282970791652486</v>
+        <v>3.282970777757609</v>
       </c>
       <c r="CB6" t="n">
-        <v>6.089910818515362</v>
+        <v>6.089910792740364</v>
       </c>
       <c r="CC6" t="n">
         <v>12.96195652173913</v>
@@ -2528,7 +2528,7 @@
         <v>8.728772626887835</v>
       </c>
       <c r="CE6" t="n">
-        <v>24.66556327894235</v>
+        <v>24.66556323665359</v>
       </c>
       <c r="CF6" t="n">
         <v>11.57513776217851</v>
@@ -2540,7 +2540,7 @@
         <v>5.383571029035719</v>
       </c>
       <c r="CI6" t="n">
-        <v>11.60598122271972</v>
+        <v>11.60598121299633</v>
       </c>
       <c r="CJ6" t="n">
         <v>11.57513776217851</v>
@@ -2561,7 +2561,7 @@
         <v>131.5027552435702</v>
       </c>
       <c r="CP6" t="n">
-        <v>157.910693838216</v>
+        <v>157.9106936221406</v>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>1.836517861131659</v>
       </c>
       <c r="DC6" t="n">
-        <v>-41.72318362747433</v>
+        <v>-41.72317990102352</v>
       </c>
       <c r="DD6" t="b">
         <v>1</v>
@@ -2839,10 +2839,10 @@
         <v>48.34000015258789</v>
       </c>
       <c r="CA7" t="n">
-        <v>18.4219176096249</v>
+        <v>18.42191767002555</v>
       </c>
       <c r="CB7" t="n">
-        <v>34.17265716585418</v>
+        <v>34.17265727789739</v>
       </c>
       <c r="CC7" t="n">
         <v>74.65093263657221</v>
@@ -2851,23 +2851,23 @@
         <v>55.91472932652801</v>
       </c>
       <c r="CE7" t="n">
-        <v>99.83445504165644</v>
+        <v>99.83445494707516</v>
       </c>
       <c r="CF7" t="n">
-        <v>48.37202137697793</v>
+        <v>48.37202136222312</v>
       </c>
       <c r="CG7" t="n">
-        <v>58.9097273531987</v>
+        <v>58.90972723179822</v>
       </c>
       <c r="CH7" t="inlineStr"/>
       <c r="CI7" t="n">
-        <v>43.90438219725731</v>
+        <v>43.90438223667957</v>
       </c>
       <c r="CJ7" t="n">
-        <v>41.27233927141606</v>
+        <v>41.27233932006025</v>
       </c>
       <c r="CK7" t="n">
-        <v>37.14510534427446</v>
+        <v>37.14510538805423</v>
       </c>
       <c r="CL7" t="n">
         <v>4</v>
@@ -2879,10 +2879,10 @@
         <v>4.1</v>
       </c>
       <c r="CO7" t="n">
-        <v>-23.15865695692207</v>
+        <v>-23.15865686635571</v>
       </c>
       <c r="CP7" t="n">
-        <v>-9.175874930346117</v>
+        <v>-9.175874848794063</v>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         <v>15.69999980926514</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.403272785622092</v>
+        <v>6.403272790282692</v>
       </c>
       <c r="CB8" t="n">
-        <v>11.87807101732898</v>
+        <v>11.87807102597439</v>
       </c>
       <c r="CC8" t="n">
         <v>25.39987759130195</v>
@@ -3182,19 +3182,19 @@
         <v>18.63509665364473</v>
       </c>
       <c r="CE8" t="n">
-        <v>35.24419673051138</v>
+        <v>35.24419672294257</v>
       </c>
       <c r="CF8" t="n">
-        <v>12.29886962086131</v>
+        <v>12.2988696199767</v>
       </c>
       <c r="CG8" t="n">
-        <v>20.3943531522701</v>
+        <v>20.39435314250484</v>
       </c>
       <c r="CH8" t="n">
         <v>18.40902666520164</v>
       </c>
       <c r="CI8" t="n">
-        <v>20.32278449016001</v>
+        <v>20.3227844887924</v>
       </c>
       <c r="CJ8" t="n">
         <v>18.63509665364473</v>
@@ -3215,7 +3215,7 @@
         <v>6.825396127602112</v>
       </c>
       <c r="CP8" t="n">
-        <v>29.44448877105594</v>
+        <v>29.44448876234502</v>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
@@ -3332,8 +3332,16 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Bandeira de alta</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Bandeira de alta (pré-confirmação) — pescoço R$43.15, preço 1.1% abaixo do pescoço; falta fechar acima e segurar</t>
+        </is>
+      </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
@@ -3505,10 +3513,10 @@
         <v>42.70000076293945</v>
       </c>
       <c r="CA9" t="n">
-        <v>125.1015273821003</v>
+        <v>125.1015279674615</v>
       </c>
       <c r="CB9" t="n">
-        <v>232.0633332937961</v>
+        <v>232.0633343796411</v>
       </c>
       <c r="CC9" t="n">
         <v>134.3883634463059</v>
@@ -3529,13 +3537,13 @@
         <v>54.40212095818906</v>
       </c>
       <c r="CI9" t="n">
-        <v>140.0386116732977</v>
+        <v>140.0386118821985</v>
       </c>
       <c r="CJ9" t="n">
-        <v>123.9129975665332</v>
+        <v>123.9129978592138</v>
       </c>
       <c r="CK9" t="n">
-        <v>111.5216978098799</v>
+        <v>111.5216980732924</v>
       </c>
       <c r="CL9" t="n">
         <v>8</v>
@@ -3547,10 +3555,10 @@
         <v>5.6</v>
       </c>
       <c r="CO9" t="n">
-        <v>161.1749316563777</v>
+        <v>161.174932273269</v>
       </c>
       <c r="CP9" t="n">
-        <v>227.9592720636231</v>
+        <v>227.959272552852</v>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
@@ -3838,10 +3846,10 @@
         <v>32.47999954223633</v>
       </c>
       <c r="CA10" t="n">
-        <v>45.35763236666469</v>
+        <v>45.3576324603114</v>
       </c>
       <c r="CB10" t="n">
-        <v>84.13840804016299</v>
+        <v>84.13840821387765</v>
       </c>
       <c r="CC10" t="n">
         <v>68.20285165366582</v>
@@ -3862,7 +3870,7 @@
         <v>25.67266223983068</v>
       </c>
       <c r="CI10" t="n">
-        <v>77.37745293613018</v>
+        <v>77.37745297432465</v>
       </c>
       <c r="CJ10" t="n">
         <v>68.20285165366582</v>
@@ -3883,7 +3891,7 @@
         <v>88.98573692551506</v>
       </c>
       <c r="CP10" t="n">
-        <v>138.2310776683051</v>
+        <v>138.2310777858989</v>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
@@ -4179,37 +4187,37 @@
         <v>32.84999847412109</v>
       </c>
       <c r="CA11" t="n">
-        <v>24.40198158437201</v>
+        <v>24.40198174522347</v>
       </c>
       <c r="CB11" t="n">
-        <v>32.23832936630178</v>
+        <v>32.23832821674423</v>
       </c>
       <c r="CC11" t="n">
-        <v>33.80534833525467</v>
+        <v>33.80534690698423</v>
       </c>
       <c r="CD11" t="n">
         <v>20.85130777065122</v>
       </c>
       <c r="CE11" t="n">
-        <v>48.27773820722045</v>
+        <v>48.27773695797047</v>
       </c>
       <c r="CF11" t="n">
-        <v>50.8460167963005</v>
+        <v>50.84601659046539</v>
       </c>
       <c r="CG11" t="n">
-        <v>16.49856811113381</v>
+        <v>16.4985671715297</v>
       </c>
       <c r="CH11" t="n">
         <v>24.29339039885633</v>
       </c>
       <c r="CI11" t="n">
-        <v>31.40158507126135</v>
+        <v>31.40158446980313</v>
       </c>
       <c r="CJ11" t="n">
-        <v>28.3201554753369</v>
+        <v>28.32015498098385</v>
       </c>
       <c r="CK11" t="n">
-        <v>25.48813992780321</v>
+        <v>25.48813948288546</v>
       </c>
       <c r="CL11" t="n">
         <v>8</v>
@@ -4221,10 +4229,10 @@
         <v>3.1</v>
       </c>
       <c r="CO11" t="n">
-        <v>-22.41052934026006</v>
+        <v>-22.41053069465203</v>
       </c>
       <c r="CP11" t="n">
-        <v>-4.409173425078827</v>
+        <v>-4.409175256001951</v>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
@@ -4522,10 +4530,10 @@
         <v>47.31000137329102</v>
       </c>
       <c r="CA12" t="n">
-        <v>131.3186532722856</v>
+        <v>131.3186531307394</v>
       </c>
       <c r="CB12" t="n">
-        <v>243.5961018200898</v>
+        <v>243.5961015575216</v>
       </c>
       <c r="CC12" t="n">
         <v>134.5187807287781</v>
@@ -4546,13 +4554,13 @@
         <v>53.17581509382557</v>
       </c>
       <c r="CI12" t="n">
-        <v>142.2124817367327</v>
+        <v>142.2124816862184</v>
       </c>
       <c r="CJ12" t="n">
-        <v>127.0811095349434</v>
+        <v>127.0811094641703</v>
       </c>
       <c r="CK12" t="n">
-        <v>114.372998581449</v>
+        <v>114.3729985177533</v>
       </c>
       <c r="CL12" t="n">
         <v>8</v>
@@ -4564,10 +4572,10 @@
         <v>5.7</v>
       </c>
       <c r="CO12" t="n">
-        <v>141.7522622310018</v>
+        <v>141.7522620963669</v>
       </c>
       <c r="CP12" t="n">
-        <v>200.5970780145003</v>
+        <v>200.5970779077273</v>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
@@ -4606,7 +4614,7 @@
         <v>-1.560432066163409</v>
       </c>
       <c r="DC12" t="n">
-        <v>-10.93847029890879</v>
+        <v>-10.93846372884365</v>
       </c>
       <c r="DD12" t="b">
         <v>1</v>
@@ -4759,7 +4767,7 @@
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="AV13" t="b">
         <v>1</v>
@@ -4855,10 +4863,10 @@
         <v>7.239999771118164</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.268913181465356</v>
+        <v>3.26891316777838</v>
       </c>
       <c r="CB13" t="n">
-        <v>6.063833951618235</v>
+        <v>6.063833926228895</v>
       </c>
       <c r="CC13" t="n">
         <v>20.4541571358882</v>
@@ -4867,7 +4875,7 @@
         <v>14.0164620450613</v>
       </c>
       <c r="CE13" t="n">
-        <v>32.91359938321693</v>
+        <v>32.91359934236029</v>
       </c>
       <c r="CF13" t="n">
         <v>10.95072400487419</v>
@@ -5160,10 +5168,10 @@
         <v>19.30999946594238</v>
       </c>
       <c r="CA14" t="n">
-        <v>13.27286328520698</v>
+        <v>13.27286328405224</v>
       </c>
       <c r="CB14" t="n">
-        <v>24.62116139405894</v>
+        <v>24.62116139191691</v>
       </c>
       <c r="CC14" t="n">
         <v>19.98886663466692</v>
@@ -5172,7 +5180,7 @@
         <v>12.49234273346821</v>
       </c>
       <c r="CE14" t="n">
-        <v>33.82719368413751</v>
+        <v>33.82719368287452</v>
       </c>
       <c r="CF14" t="n">
         <v>22.8984489302328</v>
@@ -5182,7 +5190,7 @@
       </c>
       <c r="CH14" t="inlineStr"/>
       <c r="CI14" t="n">
-        <v>20.1953350610414</v>
+        <v>20.19533506021722</v>
       </c>
       <c r="CJ14" t="n">
         <v>21.44365778244985</v>
@@ -5203,7 +5211,7 @@
         <v>-0.05545034714474761</v>
       </c>
       <c r="CP14" t="n">
-        <v>4.584855616700123</v>
+        <v>4.584855612431937</v>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
@@ -5499,10 +5507,10 @@
         <v>17.21999931335449</v>
       </c>
       <c r="CA15" t="n">
-        <v>10.55474910382358</v>
+        <v>10.55474909443632</v>
       </c>
       <c r="CB15" t="n">
-        <v>19.57905958759274</v>
+        <v>19.57905957017936</v>
       </c>
       <c r="CC15" t="n">
         <v>37.03977125031607</v>
@@ -5511,25 +5519,25 @@
         <v>36.56718452753732</v>
       </c>
       <c r="CE15" t="n">
-        <v>41.35653253861537</v>
+        <v>41.35653253460206</v>
       </c>
       <c r="CF15" t="n">
-        <v>34.51133419933809</v>
+        <v>34.51133420135141</v>
       </c>
       <c r="CG15" t="n">
-        <v>18.38517857817317</v>
+        <v>18.3851785890609</v>
       </c>
       <c r="CH15" t="n">
         <v>31.59171947190627</v>
       </c>
       <c r="CI15" t="n">
-        <v>31.290111450497</v>
+        <v>31.29011144927906</v>
       </c>
       <c r="CJ15" t="n">
-        <v>34.51133419933809</v>
+        <v>34.51133420135141</v>
       </c>
       <c r="CK15" t="n">
-        <v>31.06020077940428</v>
+        <v>31.06020078121627</v>
       </c>
       <c r="CL15" t="n">
         <v>7</v>
@@ -5541,10 +5549,10 @@
         <v>3.9</v>
       </c>
       <c r="CO15" t="n">
-        <v>80.37283401815472</v>
+        <v>80.3728340286773</v>
       </c>
       <c r="CP15" t="n">
-        <v>81.70797153418481</v>
+        <v>81.70797152711195</v>
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
@@ -5832,37 +5840,37 @@
         <v>10.10999965667725</v>
       </c>
       <c r="CA16" t="n">
-        <v>10.13143126652837</v>
+        <v>10.13143129308893</v>
       </c>
       <c r="CB16" t="n">
-        <v>18.70783436878482</v>
+        <v>18.70783429348263</v>
       </c>
       <c r="CC16" t="n">
-        <v>24.60234658832414</v>
+        <v>24.60234642479805</v>
       </c>
       <c r="CD16" t="n">
         <v>17.7286584153084</v>
       </c>
       <c r="CE16" t="n">
-        <v>37.29788764965343</v>
+        <v>37.29788762566994</v>
       </c>
       <c r="CF16" t="n">
-        <v>24.22484087319202</v>
+        <v>24.22484086184432</v>
       </c>
       <c r="CG16" t="n">
-        <v>11.97788224118745</v>
+        <v>11.97788218298796</v>
       </c>
       <c r="CH16" t="n">
         <v>10.10999965667725</v>
       </c>
       <c r="CI16" t="n">
-        <v>19.34761013245699</v>
+        <v>19.34761009423218</v>
       </c>
       <c r="CJ16" t="n">
-        <v>18.21824639204661</v>
+        <v>18.21824635439551</v>
       </c>
       <c r="CK16" t="n">
-        <v>16.39642175284195</v>
+        <v>16.39642171895596</v>
       </c>
       <c r="CL16" t="n">
         <v>8</v>
@@ -5874,10 +5882,10 @@
         <v>3.7</v>
       </c>
       <c r="CO16" t="n">
-        <v>62.18024045146999</v>
+        <v>62.18024011629704</v>
       </c>
       <c r="CP16" t="n">
-        <v>91.371026602149</v>
+        <v>91.37102622405995</v>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
@@ -6167,10 +6175,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="CA17" t="n">
-        <v>5.044849568253714</v>
+        <v>5.04484961288621</v>
       </c>
       <c r="CB17" t="n">
-        <v>9.358195949110639</v>
+        <v>9.358196031903919</v>
       </c>
       <c r="CC17" t="n">
         <v>8.579313567043014</v>
@@ -6490,10 +6498,10 @@
         <v>10.97000026702881</v>
       </c>
       <c r="CA18" t="n">
-        <v>9.497073350591037</v>
+        <v>9.497073383813341</v>
       </c>
       <c r="CB18" t="n">
-        <v>17.61707106534638</v>
+        <v>17.61707112697374</v>
       </c>
       <c r="CC18" t="n">
         <v>21.98978873496697</v>
@@ -6502,25 +6510,25 @@
         <v>12.98356721691296</v>
       </c>
       <c r="CE18" t="n">
-        <v>32.25283431003437</v>
+        <v>32.25283420933102</v>
       </c>
       <c r="CF18" t="n">
-        <v>25.36723518641875</v>
+        <v>25.36723516205288</v>
       </c>
       <c r="CG18" t="n">
-        <v>12.06312339896413</v>
+        <v>12.06312329143549</v>
       </c>
       <c r="CH18" t="n">
         <v>9.632374997322403</v>
       </c>
       <c r="CI18" t="n">
-        <v>17.67538353256962</v>
+        <v>17.6753835153511</v>
       </c>
       <c r="CJ18" t="n">
-        <v>15.30031914112967</v>
+        <v>15.30031917194335</v>
       </c>
       <c r="CK18" t="n">
-        <v>13.7702872270167</v>
+        <v>13.77028725474902</v>
       </c>
       <c r="CL18" t="n">
         <v>8</v>
@@ -6532,10 +6540,10 @@
         <v>3.4</v>
       </c>
       <c r="CO18" t="n">
-        <v>25.52677203121294</v>
+        <v>25.52677228401434</v>
       </c>
       <c r="CP18" t="n">
-        <v>61.12473201750384</v>
+        <v>61.12473186054375</v>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
@@ -6823,10 +6831,10 @@
         <v>10.63000011444092</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.315435255587584</v>
+        <v>3.315435210883541</v>
       </c>
       <c r="CB19" t="n">
-        <v>6.150132399114969</v>
+        <v>6.150132316188968</v>
       </c>
       <c r="CC19" t="n">
         <v>19.53502101474926</v>
@@ -6835,13 +6843,13 @@
         <v>18.41366451165369</v>
       </c>
       <c r="CE19" t="n">
-        <v>20.99443609253708</v>
+        <v>20.99443609591905</v>
       </c>
       <c r="CF19" t="n">
-        <v>15.93437225439872</v>
+        <v>15.93437226326995</v>
       </c>
       <c r="CG19" t="n">
-        <v>13.08852151764407</v>
+        <v>13.08852157433238</v>
       </c>
       <c r="CH19" t="n">
         <v>29.73646810990179</v>
@@ -6897,7 +6905,7 @@
         <v>-21.14242970755025</v>
       </c>
       <c r="DC19" t="n">
-        <v>-35.6218103618902</v>
+        <v>-35.62181802569307</v>
       </c>
       <c r="DD19" t="b">
         <v>1</v>
@@ -7146,10 +7154,10 @@
         <v>27.42000007629395</v>
       </c>
       <c r="CA20" t="n">
-        <v>7.265285107589708</v>
+        <v>7.265285056609213</v>
       </c>
       <c r="CB20" t="n">
-        <v>13.47710387457891</v>
+        <v>13.47710378001009</v>
       </c>
       <c r="CC20" t="n">
         <v>35.82988175649849</v>
@@ -7158,19 +7166,19 @@
         <v>28.32096620307184</v>
       </c>
       <c r="CE20" t="n">
-        <v>44.64824881193085</v>
+        <v>44.64824888800035</v>
       </c>
       <c r="CF20" t="n">
-        <v>26.46426765547184</v>
+        <v>26.4642676681783</v>
       </c>
       <c r="CG20" t="n">
-        <v>28.98335739352322</v>
+        <v>28.98335748558175</v>
       </c>
       <c r="CH20" t="n">
         <v>24.27856406616775</v>
       </c>
       <c r="CI20" t="n">
-        <v>28.85748425160613</v>
+        <v>28.8574842639298</v>
       </c>
       <c r="CJ20" t="n">
         <v>28.32096620307184</v>
@@ -7191,7 +7199,7 @@
         <v>-7.042780773727464</v>
       </c>
       <c r="CP20" t="n">
-        <v>5.242465978528443</v>
+        <v>5.242466023472536</v>
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
@@ -7487,10 +7495,10 @@
         <v>22.60000038146973</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.184692830772003</v>
+        <v>3.184692833531383</v>
       </c>
       <c r="CB21" t="n">
-        <v>5.907605201082066</v>
+        <v>5.907605206200714</v>
       </c>
       <c r="CC21" t="n">
         <v>33.79796896777358</v>
@@ -7499,7 +7507,7 @@
         <v>28.20908778885038</v>
       </c>
       <c r="CE21" t="n">
-        <v>43.29409766962235</v>
+        <v>43.29409767398253</v>
       </c>
       <c r="CF21" t="n">
         <v>10.85340539909456</v>
@@ -7790,10 +7798,10 @@
         <v>39.45000076293945</v>
       </c>
       <c r="CA22" t="n">
-        <v>36.11966575775509</v>
+        <v>36.1196657151245</v>
       </c>
       <c r="CB22" t="n">
-        <v>52.59023334329141</v>
+        <v>52.59023328122127</v>
       </c>
       <c r="CC22" t="n">
         <v>48.55384709284856</v>
@@ -7810,13 +7818,13 @@
       </c>
       <c r="CH22" t="inlineStr"/>
       <c r="CI22" t="n">
-        <v>49.19197779442819</v>
+        <v>49.19197776825301</v>
       </c>
       <c r="CJ22" t="n">
-        <v>50.57204021806999</v>
+        <v>50.57204018703491</v>
       </c>
       <c r="CK22" t="n">
-        <v>45.51483619626299</v>
+        <v>45.51483616833143</v>
       </c>
       <c r="CL22" t="n">
         <v>4</v>
@@ -7828,10 +7836,10 @@
         <v>1.6</v>
       </c>
       <c r="CO22" t="n">
-        <v>15.37347355141507</v>
+        <v>15.37347348061262</v>
       </c>
       <c r="CP22" t="n">
-        <v>24.69449136396633</v>
+        <v>24.69449129761607</v>
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
@@ -7948,12 +7956,12 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Bandeira de alta</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Fundo duplo (pré-confirmação) — pescoço R$30.00, preço 15.6% acima do pescoço; falta fechar acima e segurar</t>
+          <t>Bandeira de alta (pré-confirmação) — pescoço R$32.23, preço 7.6% acima do pescoço; falta fechar acima e segurar</t>
         </is>
       </c>
       <c r="U23" t="b">
@@ -8127,10 +8135,10 @@
         <v>34.68999862670898</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.441930999778089</v>
+        <v>3.44193098919063</v>
       </c>
       <c r="CB23" t="n">
-        <v>6.384782004588356</v>
+        <v>6.384781984948619</v>
       </c>
       <c r="CC23" t="n">
         <v>32.87857523633004</v>
@@ -8139,7 +8147,7 @@
         <v>23.03538757661248</v>
       </c>
       <c r="CE23" t="n">
-        <v>40.66788364789184</v>
+        <v>40.66788363728924</v>
       </c>
       <c r="CF23" t="n">
         <v>10.59424454785779</v>
@@ -8430,35 +8438,35 @@
         <v>12.84000015258789</v>
       </c>
       <c r="CA24" t="n">
-        <v>8.620481286504914</v>
+        <v>8.620481355714078</v>
       </c>
       <c r="CB24" t="n">
-        <v>13.75169161101834</v>
+        <v>13.75169153134293</v>
       </c>
       <c r="CC24" t="n">
-        <v>18.28822757306843</v>
+        <v>18.2882273202827</v>
       </c>
       <c r="CD24" t="n">
         <v>17.29599079072038</v>
       </c>
       <c r="CE24" t="n">
-        <v>22.79369014170337</v>
+        <v>22.7936900752349</v>
       </c>
       <c r="CF24" t="n">
-        <v>17.32774436624598</v>
+        <v>17.32774434692217</v>
       </c>
       <c r="CG24" t="n">
-        <v>9.132575867725885</v>
+        <v>9.132575749815619</v>
       </c>
       <c r="CH24" t="inlineStr"/>
       <c r="CI24" t="n">
-        <v>14.49703620920942</v>
+        <v>14.49703613856547</v>
       </c>
       <c r="CJ24" t="n">
-        <v>15.53971798863216</v>
+        <v>15.53971793913255</v>
       </c>
       <c r="CK24" t="n">
-        <v>13.98574618976895</v>
+        <v>13.9857461452193</v>
       </c>
       <c r="CL24" t="n">
         <v>4</v>
@@ -8470,10 +8478,10 @@
         <v>2.1</v>
       </c>
       <c r="CO24" t="n">
-        <v>8.923255635243388</v>
+        <v>8.923255288283482</v>
       </c>
       <c r="CP24" t="n">
-        <v>12.90526508512191</v>
+        <v>12.90526453493546</v>
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
@@ -8747,10 +8755,10 @@
         <v>39.09999847412109</v>
       </c>
       <c r="CA25" t="n">
-        <v>19.98838182642474</v>
+        <v>19.98838170689563</v>
       </c>
       <c r="CB25" t="n">
-        <v>37.0784482880179</v>
+        <v>37.0784480662914</v>
       </c>
       <c r="CC25" t="n">
         <v>55.88726858490879</v>
@@ -8759,23 +8767,23 @@
         <v>42.23733079208057</v>
       </c>
       <c r="CE25" t="n">
-        <v>62.05594540325415</v>
+        <v>62.05594559841553</v>
       </c>
       <c r="CF25" t="n">
-        <v>45.20943449802702</v>
+        <v>45.20943453546542</v>
       </c>
       <c r="CG25" t="n">
-        <v>31.29948454409355</v>
+        <v>31.29948478023526</v>
       </c>
       <c r="CH25" t="inlineStr"/>
       <c r="CI25" t="n">
-        <v>39.54088329934461</v>
+        <v>39.54088322339031</v>
       </c>
       <c r="CJ25" t="n">
-        <v>41.14394139302246</v>
+        <v>41.14394130087841</v>
       </c>
       <c r="CK25" t="n">
-        <v>37.02954725372022</v>
+        <v>37.02954717079057</v>
       </c>
       <c r="CL25" t="n">
         <v>4</v>
@@ -8787,10 +8795,10 @@
         <v>2.8</v>
       </c>
       <c r="CO25" t="n">
-        <v>-5.295271870077523</v>
+        <v>-5.295272082173819</v>
       </c>
       <c r="CP25" t="n">
-        <v>1.127582717209874</v>
+        <v>1.127582522953352</v>
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
@@ -8907,12 +8915,12 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Bandeira de alta</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Fundo duplo (pré-confirmação) — pescoço R$4.78, preço 25.7% acima do pescoço; falta fechar acima e segurar</t>
+          <t>Bandeira de alta (pré-confirmação) — pescoço R$6.04, preço 0.6% abaixo do pescoço; falta fechar acima e segurar</t>
         </is>
       </c>
       <c r="U26" t="b">
@@ -9086,10 +9094,10 @@
         <v>6.010000228881836</v>
       </c>
       <c r="CA26" t="n">
-        <v>7.12914305894854</v>
+        <v>7.129142969055732</v>
       </c>
       <c r="CB26" t="n">
-        <v>13.22456037434954</v>
+        <v>13.22456020759838</v>
       </c>
       <c r="CC26" t="n">
         <v>5.700250753950201</v>
@@ -9110,7 +9118,7 @@
         <v>5.504458217875779</v>
       </c>
       <c r="CI26" t="n">
-        <v>7.427901861097509</v>
+        <v>7.427901829017013</v>
       </c>
       <c r="CJ26" t="n">
         <v>5.916792043641768</v>
@@ -9131,7 +9139,7 @@
         <v>-11.39579639802557</v>
       </c>
       <c r="CP26" t="n">
-        <v>23.5923723497008</v>
+        <v>23.59237181591551</v>
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
@@ -9403,10 +9411,10 @@
         <v>14.96000003814697</v>
       </c>
       <c r="CA27" t="n">
-        <v>9.299118859309983</v>
+        <v>9.299118781731359</v>
       </c>
       <c r="CB27" t="n">
-        <v>17.24986548402002</v>
+        <v>17.24986534011167</v>
       </c>
       <c r="CC27" t="n">
         <v>30.82737177378653</v>
@@ -9415,23 +9423,23 @@
         <v>29.3357145487105</v>
       </c>
       <c r="CE27" t="n">
-        <v>34.7261727411532</v>
+        <v>34.72617272570776</v>
       </c>
       <c r="CF27" t="n">
-        <v>25.49555037615469</v>
+        <v>25.49555039198669</v>
       </c>
       <c r="CG27" t="n">
-        <v>15.31657760881048</v>
+        <v>15.31657770527484</v>
       </c>
       <c r="CH27" t="inlineStr"/>
       <c r="CI27" t="n">
-        <v>20.7179766233178</v>
+        <v>20.71797657190406</v>
       </c>
       <c r="CJ27" t="n">
-        <v>21.37270793008735</v>
+        <v>21.37270786604918</v>
       </c>
       <c r="CK27" t="n">
-        <v>19.23543713707862</v>
+        <v>19.23543707944426</v>
       </c>
       <c r="CL27" t="n">
         <v>4</v>
@@ -9443,10 +9451,10 @@
         <v>3.3</v>
       </c>
       <c r="CO27" t="n">
-        <v>28.57912491998378</v>
+        <v>28.57912453472742</v>
       </c>
       <c r="CP27" t="n">
-        <v>38.48914819845177</v>
+        <v>38.48914785477704</v>
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
@@ -9734,37 +9742,37 @@
         <v>26.64999961853027</v>
       </c>
       <c r="CA28" t="n">
-        <v>17.04081911348038</v>
+        <v>17.04081915921964</v>
       </c>
       <c r="CB28" t="n">
-        <v>28.24466298572847</v>
+        <v>28.24466299126953</v>
       </c>
       <c r="CC28" t="n">
-        <v>47.30306352366961</v>
+        <v>47.30306340598339</v>
       </c>
       <c r="CD28" t="n">
         <v>53.09041087001181</v>
       </c>
       <c r="CE28" t="n">
-        <v>56.22823554597153</v>
+        <v>56.22823556058753</v>
       </c>
       <c r="CF28" t="n">
-        <v>42.93945177272226</v>
+        <v>42.93945176440158</v>
       </c>
       <c r="CG28" t="n">
-        <v>23.53452114541224</v>
+        <v>23.53452109425378</v>
       </c>
       <c r="CH28" t="n">
         <v>30.99183173163939</v>
       </c>
       <c r="CI28" t="n">
-        <v>37.42162458607946</v>
+        <v>37.42162457217083</v>
       </c>
       <c r="CJ28" t="n">
-        <v>36.96564175218083</v>
+        <v>36.96564174802049</v>
       </c>
       <c r="CK28" t="n">
-        <v>33.26907757696275</v>
+        <v>33.26907757321844</v>
       </c>
       <c r="CL28" t="n">
         <v>8</v>
@@ -9776,10 +9784,10 @@
         <v>3.3</v>
       </c>
       <c r="CO28" t="n">
-        <v>24.83706586558485</v>
+        <v>24.83706585153491</v>
       </c>
       <c r="CP28" t="n">
-        <v>40.4188559915005</v>
+        <v>40.41885593931054</v>
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
@@ -10067,37 +10075,37 @@
         <v>15.11999988555908</v>
       </c>
       <c r="CA29" t="n">
-        <v>5.865830794046077</v>
+        <v>5.865830790850479</v>
       </c>
       <c r="CB29" t="n">
-        <v>8.474845209943982</v>
+        <v>8.474845212604007</v>
       </c>
       <c r="CC29" t="n">
-        <v>10.77599630748211</v>
+        <v>10.77599631673497</v>
       </c>
       <c r="CD29" t="n">
         <v>11.55627711976371</v>
       </c>
       <c r="CE29" t="n">
-        <v>9.774262762032622</v>
+        <v>9.774262767174816</v>
       </c>
       <c r="CF29" t="n">
-        <v>14.91642323776266</v>
+        <v>14.91642323889413</v>
       </c>
       <c r="CG29" t="n">
-        <v>5.368455505538072</v>
+        <v>5.368455510712384</v>
       </c>
       <c r="CH29" t="n">
         <v>10.8369287109083</v>
       </c>
       <c r="CI29" t="n">
-        <v>9.696127455934691</v>
+        <v>9.696127458455351</v>
       </c>
       <c r="CJ29" t="n">
-        <v>10.27512953475737</v>
+        <v>10.27512954195489</v>
       </c>
       <c r="CK29" t="n">
-        <v>9.24761658128163</v>
+        <v>9.247616587759405</v>
       </c>
       <c r="CL29" t="n">
         <v>8</v>
@@ -10109,10 +10117,10 @@
         <v>2.8</v>
       </c>
       <c r="CO29" t="n">
-        <v>-38.83851421114156</v>
+        <v>-38.83851416829914</v>
       </c>
       <c r="CP29" t="n">
-        <v>-35.87217242511134</v>
+        <v>-35.87217240844031</v>
       </c>
       <c r="CQ29" t="inlineStr">
         <is>
@@ -10400,37 +10408,37 @@
         <v>38.70000076293945</v>
       </c>
       <c r="CA30" t="n">
-        <v>30.84756146352459</v>
+        <v>30.84756141455194</v>
       </c>
       <c r="CB30" t="n">
-        <v>35.74245442164587</v>
+        <v>35.74245446027761</v>
       </c>
       <c r="CC30" t="n">
-        <v>39.06003421083991</v>
+        <v>39.06003431506794</v>
       </c>
       <c r="CD30" t="n">
         <v>49.9060657389037</v>
       </c>
       <c r="CE30" t="n">
-        <v>60.73976153341496</v>
+        <v>60.7397615878864</v>
       </c>
       <c r="CF30" t="n">
-        <v>16.61273117624454</v>
+        <v>16.61273118102335</v>
       </c>
       <c r="CG30" t="n">
-        <v>17.68241854075722</v>
+        <v>17.68241862755243</v>
       </c>
       <c r="CH30" t="n">
         <v>28.82212409504474</v>
       </c>
       <c r="CI30" t="n">
-        <v>34.92664389754694</v>
+        <v>34.92664392753851</v>
       </c>
       <c r="CJ30" t="n">
-        <v>33.29500794258523</v>
+        <v>33.29500793741478</v>
       </c>
       <c r="CK30" t="n">
-        <v>29.96550714832671</v>
+        <v>29.9655071436733</v>
       </c>
       <c r="CL30" t="n">
         <v>8</v>
@@ -10442,10 +10450,10 @@
         <v>3.7</v>
       </c>
       <c r="CO30" t="n">
-        <v>-22.56975049720727</v>
+        <v>-22.56975050923158</v>
       </c>
       <c r="CP30" t="n">
-        <v>-9.750275945746289</v>
+        <v>-9.750275868248682</v>
       </c>
       <c r="CQ30" t="inlineStr">
         <is>
@@ -10484,7 +10492,7 @@
         <v>-0.61632735550462</v>
       </c>
       <c r="DC30" t="n">
-        <v>-11.66799026158288</v>
+        <v>-11.66799814233929</v>
       </c>
       <c r="DD30" t="b">
         <v>1</v>
@@ -10715,35 +10723,35 @@
         <v>16.93000030517578</v>
       </c>
       <c r="CA31" t="n">
-        <v>10.07593953517678</v>
+        <v>10.07593941498686</v>
       </c>
       <c r="CB31" t="n">
-        <v>17.56133914863183</v>
+        <v>17.56133916892925</v>
       </c>
       <c r="CC31" t="n">
-        <v>28.83258830480192</v>
+        <v>28.83258868205356</v>
       </c>
       <c r="CD31" t="n">
         <v>29.26650917734455</v>
       </c>
       <c r="CE31" t="n">
-        <v>32.09021933964034</v>
+        <v>32.09021934721415</v>
       </c>
       <c r="CF31" t="n">
-        <v>27.8842854882014</v>
+        <v>27.88428551532881</v>
       </c>
       <c r="CG31" t="n">
-        <v>14.2283163021319</v>
+        <v>14.22831645158085</v>
       </c>
       <c r="CH31" t="inlineStr"/>
       <c r="CI31" t="n">
-        <v>21.08853811920299</v>
+        <v>21.08853819532462</v>
       </c>
       <c r="CJ31" t="n">
-        <v>22.72281231841662</v>
+        <v>22.72281234212903</v>
       </c>
       <c r="CK31" t="n">
-        <v>20.45053108657496</v>
+        <v>20.45053110791613</v>
       </c>
       <c r="CL31" t="n">
         <v>4</v>
@@ -10755,10 +10763,10 @@
         <v>2.9</v>
       </c>
       <c r="CO31" t="n">
-        <v>20.79462916679862</v>
+        <v>20.79462929285394</v>
       </c>
       <c r="CP31" t="n">
-        <v>24.56312899625803</v>
+        <v>24.56312944588372</v>
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
@@ -10801,7 +10809,7 @@
         <v>-4.350284884596789</v>
       </c>
       <c r="DC31" t="n">
-        <v>-20.28805503364547</v>
+        <v>-20.28806233739286</v>
       </c>
       <c r="DD31" t="b">
         <v>1</v>
@@ -11050,37 +11058,37 @@
         <v>44.06000137329102</v>
       </c>
       <c r="CA32" t="n">
-        <v>31.96233917907316</v>
+        <v>31.96233907069051</v>
       </c>
       <c r="CB32" t="n">
-        <v>43.40419596995319</v>
+        <v>43.4041961745397</v>
       </c>
       <c r="CC32" t="n">
-        <v>49.69482656228118</v>
+        <v>49.69482696503131</v>
       </c>
       <c r="CD32" t="n">
         <v>47.301358204649</v>
       </c>
       <c r="CE32" t="n">
-        <v>69.17232289553603</v>
+        <v>69.17232312013662</v>
       </c>
       <c r="CF32" t="n">
-        <v>59.81319571034596</v>
+        <v>59.81319575565071</v>
       </c>
       <c r="CG32" t="n">
-        <v>24.4605088142312</v>
+        <v>24.46050906631191</v>
       </c>
       <c r="CH32" t="n">
         <v>76.33330481362214</v>
       </c>
       <c r="CI32" t="n">
-        <v>50.26775651871148</v>
+        <v>50.26775664632899</v>
       </c>
       <c r="CJ32" t="n">
-        <v>48.49809238346509</v>
+        <v>48.49809258484015</v>
       </c>
       <c r="CK32" t="n">
-        <v>43.64828314511858</v>
+        <v>43.64828332635614</v>
       </c>
       <c r="CL32" t="n">
         <v>8</v>
@@ -11092,10 +11100,10 @@
         <v>3.1</v>
       </c>
       <c r="CO32" t="n">
-        <v>-0.9344489680883528</v>
+        <v>-0.9344485567457594</v>
       </c>
       <c r="CP32" t="n">
-        <v>14.08932127084221</v>
+        <v>14.08932156048703</v>
       </c>
       <c r="CQ32" t="inlineStr">
         <is>
@@ -11373,10 +11381,10 @@
         <v>53.7400016784668</v>
       </c>
       <c r="CA33" t="n">
-        <v>10.50731956132986</v>
+        <v>10.50731955555406</v>
       </c>
       <c r="CB33" t="n">
-        <v>19.4910777862669</v>
+        <v>19.49107777555277</v>
       </c>
       <c r="CC33" t="n">
         <v>62.18821154931746</v>
@@ -11385,7 +11393,7 @@
         <v>46.54098234247379</v>
       </c>
       <c r="CE33" t="n">
-        <v>83.24912655332926</v>
+        <v>83.24912654626714</v>
       </c>
       <c r="CF33" t="n">
         <v>11.76833333333333</v>
@@ -11395,7 +11403,7 @@
       </c>
       <c r="CH33" t="inlineStr"/>
       <c r="CI33" t="n">
-        <v>13.92224356031003</v>
+        <v>13.92224355481339</v>
       </c>
       <c r="CJ33" t="n">
         <v>11.76833333333333</v>
@@ -11416,7 +11424,7 @@
         <v>-80.29121758616556</v>
       </c>
       <c r="CP33" t="n">
-        <v>-74.09333247957719</v>
+        <v>-74.09333248980541</v>
       </c>
       <c r="CQ33" t="inlineStr">
         <is>
@@ -11694,10 +11702,10 @@
         <v>29.46999931335449</v>
       </c>
       <c r="CA34" t="n">
-        <v>15.40499612269137</v>
+        <v>15.40499616374882</v>
       </c>
       <c r="CB34" t="n">
-        <v>28.57626780759248</v>
+        <v>28.57626788375406</v>
       </c>
       <c r="CC34" t="n">
         <v>53.78477836114972</v>
@@ -11706,23 +11714,23 @@
         <v>48.59041952862963</v>
       </c>
       <c r="CE34" t="n">
-        <v>59.55728564695277</v>
+        <v>59.55728563594013</v>
       </c>
       <c r="CF34" t="n">
-        <v>36.60763963409793</v>
+        <v>36.60763962652169</v>
       </c>
       <c r="CG34" t="n">
-        <v>29.60722468926014</v>
+        <v>29.60722463257128</v>
       </c>
       <c r="CH34" t="inlineStr"/>
       <c r="CI34" t="n">
-        <v>33.59342048138287</v>
+        <v>33.59342050879357</v>
       </c>
       <c r="CJ34" t="n">
-        <v>32.5919537208452</v>
+        <v>32.59195375513788</v>
       </c>
       <c r="CK34" t="n">
-        <v>29.33275834876068</v>
+        <v>29.33275837962409</v>
       </c>
       <c r="CL34" t="n">
         <v>4</v>
@@ -11734,10 +11742,10 @@
         <v>3.5</v>
       </c>
       <c r="CO34" t="n">
-        <v>-0.465697210015259</v>
+        <v>-0.4656971052870329</v>
       </c>
       <c r="CP34" t="n">
-        <v>13.99192827995699</v>
+        <v>13.99192837296921</v>
       </c>
       <c r="CQ34" t="inlineStr">
         <is>
@@ -12027,10 +12035,10 @@
         <v>10.39999961853027</v>
       </c>
       <c r="CA35" t="n">
-        <v>12.95070196961655</v>
+        <v>12.95070197609551</v>
       </c>
       <c r="CB35" t="n">
-        <v>18.8562220677617</v>
+        <v>18.85622207719506</v>
       </c>
       <c r="CC35" t="n">
         <v>16.51297649354425</v>
@@ -12049,7 +12057,7 @@
         <v>14.71449508364002</v>
       </c>
       <c r="CI35" t="n">
-        <v>16.02578527942405</v>
+        <v>16.0257852820761</v>
       </c>
       <c r="CJ35" t="n">
         <v>15.61373578859213</v>
@@ -12070,7 +12078,7 @@
         <v>35.11887235740878</v>
       </c>
       <c r="CP35" t="n">
-        <v>54.09409487736892</v>
+        <v>54.09409490286949</v>
       </c>
       <c r="CQ35" t="inlineStr">
         <is>
@@ -12358,37 +12366,37 @@
         <v>18.73999977111816</v>
       </c>
       <c r="CA36" t="n">
-        <v>8.790659630785338</v>
+        <v>8.790659624614054</v>
       </c>
       <c r="CB36" t="n">
-        <v>9.149702328878035</v>
+        <v>9.149702329202841</v>
       </c>
       <c r="CC36" t="n">
-        <v>9.503707814315618</v>
+        <v>9.503707821324854</v>
       </c>
       <c r="CD36" t="n">
         <v>16.79875791329259</v>
       </c>
       <c r="CE36" t="n">
-        <v>9.01390751122927</v>
+        <v>9.013907516567556</v>
       </c>
       <c r="CF36" t="n">
-        <v>17.51877470625346</v>
+        <v>17.51877470778531</v>
       </c>
       <c r="CG36" t="n">
-        <v>3.803999732682379</v>
+        <v>3.803999739742328</v>
       </c>
       <c r="CH36" t="n">
         <v>16.19033501601518</v>
       </c>
       <c r="CI36" t="n">
-        <v>11.34623058168148</v>
+        <v>11.34623058356809</v>
       </c>
       <c r="CJ36" t="n">
-        <v>9.326705071596827</v>
+        <v>9.326705075263847</v>
       </c>
       <c r="CK36" t="n">
-        <v>8.394034564437144</v>
+        <v>8.394034567737462</v>
       </c>
       <c r="CL36" t="n">
         <v>8</v>
@@ -12400,10 +12408,10 @@
         <v>4.6</v>
       </c>
       <c r="CO36" t="n">
-        <v>-55.20792600342548</v>
+        <v>-55.20792598581438</v>
       </c>
       <c r="CP36" t="n">
-        <v>-39.45447854717617</v>
+        <v>-39.4544785371089</v>
       </c>
       <c r="CQ36" t="inlineStr">
         <is>
@@ -13270,10 +13278,10 @@
         <v>10.35999965667725</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.851607491869938</v>
+        <v>5.851607495201637</v>
       </c>
       <c r="CB2" t="n">
-        <v>10.85473189741873</v>
+        <v>10.85473190359903</v>
       </c>
       <c r="CC2" t="n">
         <v>41.59696831847682</v>
@@ -13282,7 +13290,7 @@
         <v>27.90166392450355</v>
       </c>
       <c r="CE2" t="n">
-        <v>71.91590901101146</v>
+        <v>71.91590902514595</v>
       </c>
       <c r="CF2" t="n">
         <v>19.57807411896471</v>
@@ -13593,10 +13601,10 @@
         <v>13.46000003814697</v>
       </c>
       <c r="CA3" t="n">
-        <v>14.84732050446674</v>
+        <v>14.84732048606202</v>
       </c>
       <c r="CB3" t="n">
-        <v>27.54177953578581</v>
+        <v>27.54177950164504</v>
       </c>
       <c r="CC3" t="n">
         <v>38.93995644223742</v>
@@ -13605,13 +13613,13 @@
         <v>23.51205793312256</v>
       </c>
       <c r="CE3" t="n">
-        <v>75.54482871709098</v>
+        <v>75.54482875116977</v>
       </c>
       <c r="CF3" t="n">
-        <v>48.5251594276379</v>
+        <v>48.52515944116575</v>
       </c>
       <c r="CG3" t="n">
-        <v>26.80868515112335</v>
+        <v>26.80868520790709</v>
       </c>
       <c r="CH3" t="n">
         <v>8.920136085713818</v>
@@ -13820,7 +13828,7 @@
         <v>1</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="AV4" t="b">
         <v>1</v>
@@ -13916,10 +13924,10 @@
         <v>24.61000061035156</v>
       </c>
       <c r="CA4" t="n">
-        <v>16.31411910363583</v>
+        <v>16.31411911768027</v>
       </c>
       <c r="CB4" t="n">
-        <v>30.26269093724446</v>
+        <v>30.2626909632969</v>
       </c>
       <c r="CC4" t="n">
         <v>72.30210822331667</v>
@@ -13928,19 +13936,19 @@
         <v>52.41049602817493</v>
       </c>
       <c r="CE4" t="n">
-        <v>127.9950261325152</v>
+        <v>127.9950261281756</v>
       </c>
       <c r="CF4" t="n">
-        <v>25.7314236559713</v>
+        <v>25.73142365399151</v>
       </c>
       <c r="CG4" t="n">
-        <v>63.19894118477155</v>
+        <v>63.19894115464003</v>
       </c>
       <c r="CH4" t="n">
         <v>42.85100954601229</v>
       </c>
       <c r="CI4" t="n">
-        <v>47.79277826258186</v>
+        <v>47.79277826157206</v>
       </c>
       <c r="CJ4" t="n">
         <v>47.63075278709361</v>
@@ -13961,7 +13969,7 @@
         <v>74.18803919229917</v>
       </c>
       <c r="CP4" t="n">
-        <v>94.20063826605134</v>
+        <v>94.20063826194811</v>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
@@ -14247,10 +14255,10 @@
         <v>4.119999885559082</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.742641509775883</v>
+        <v>3.742641507761736</v>
       </c>
       <c r="CB5" t="n">
-        <v>6.942600000634262</v>
+        <v>6.942599996898021</v>
       </c>
       <c r="CC5" t="n">
         <v>12.63657372306894</v>
@@ -14259,19 +14267,19 @@
         <v>8.512687176725057</v>
       </c>
       <c r="CE5" t="n">
-        <v>24.29899389942381</v>
+        <v>24.29899390088217</v>
       </c>
       <c r="CF5" t="n">
-        <v>11.19276559034328</v>
+        <v>11.19276559117442</v>
       </c>
       <c r="CG5" t="n">
-        <v>10.1975051884262</v>
+        <v>10.19750519344577</v>
       </c>
       <c r="CH5" t="n">
         <v>5.258139118319559</v>
       </c>
       <c r="CI5" t="n">
-        <v>8.35470175818474</v>
+        <v>8.354701758199074</v>
       </c>
       <c r="CJ5" t="n">
         <v>8.512687176725057</v>
@@ -14292,7 +14300,7 @@
         <v>85.95676388017426</v>
       </c>
       <c r="CP5" t="n">
-        <v>102.7840288896273</v>
+        <v>102.7840288899752</v>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
@@ -14580,10 +14588,10 @@
         <v>4.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.282970791652486</v>
+        <v>3.282970777757609</v>
       </c>
       <c r="CB6" t="n">
-        <v>6.089910818515362</v>
+        <v>6.089910792740364</v>
       </c>
       <c r="CC6" t="n">
         <v>12.96195652173913</v>
@@ -14592,7 +14600,7 @@
         <v>8.728772626887835</v>
       </c>
       <c r="CE6" t="n">
-        <v>24.66556327894235</v>
+        <v>24.66556323665359</v>
       </c>
       <c r="CF6" t="n">
         <v>11.57513776217851</v>
@@ -14604,7 +14612,7 @@
         <v>5.383571029035719</v>
       </c>
       <c r="CI6" t="n">
-        <v>11.60598122271972</v>
+        <v>11.60598121299633</v>
       </c>
       <c r="CJ6" t="n">
         <v>11.57513776217851</v>
@@ -14625,7 +14633,7 @@
         <v>131.5027552435702</v>
       </c>
       <c r="CP6" t="n">
-        <v>157.910693838216</v>
+        <v>157.9106936221406</v>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
@@ -14672,7 +14680,7 @@
         <v>1.836517861131659</v>
       </c>
       <c r="DC6" t="n">
-        <v>-41.72318362747433</v>
+        <v>-41.72317990102352</v>
       </c>
       <c r="DD6" t="b">
         <v>1</v>
@@ -14903,10 +14911,10 @@
         <v>48.34000015258789</v>
       </c>
       <c r="CA7" t="n">
-        <v>18.4219176096249</v>
+        <v>18.42191767002555</v>
       </c>
       <c r="CB7" t="n">
-        <v>34.17265716585418</v>
+        <v>34.17265727789739</v>
       </c>
       <c r="CC7" t="n">
         <v>74.65093263657221</v>
@@ -14915,23 +14923,23 @@
         <v>55.91472932652801</v>
       </c>
       <c r="CE7" t="n">
-        <v>99.83445504165644</v>
+        <v>99.83445494707516</v>
       </c>
       <c r="CF7" t="n">
-        <v>48.37202137697793</v>
+        <v>48.37202136222312</v>
       </c>
       <c r="CG7" t="n">
-        <v>58.9097273531987</v>
+        <v>58.90972723179822</v>
       </c>
       <c r="CH7" t="inlineStr"/>
       <c r="CI7" t="n">
-        <v>43.90438219725731</v>
+        <v>43.90438223667957</v>
       </c>
       <c r="CJ7" t="n">
-        <v>41.27233927141606</v>
+        <v>41.27233932006025</v>
       </c>
       <c r="CK7" t="n">
-        <v>37.14510534427446</v>
+        <v>37.14510538805423</v>
       </c>
       <c r="CL7" t="n">
         <v>4</v>
@@ -14943,10 +14951,10 @@
         <v>4.1</v>
       </c>
       <c r="CO7" t="n">
-        <v>-23.15865695692207</v>
+        <v>-23.15865686635571</v>
       </c>
       <c r="CP7" t="n">
-        <v>-9.175874930346117</v>
+        <v>-9.175874848794063</v>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
@@ -15449,10 +15457,10 @@
         <v>15.69999980926514</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.403272785622092</v>
+        <v>6.403272790282692</v>
       </c>
       <c r="CB9" t="n">
-        <v>11.87807101732898</v>
+        <v>11.87807102597439</v>
       </c>
       <c r="CC9" t="n">
         <v>25.39987759130195</v>
@@ -15461,19 +15469,19 @@
         <v>18.63509665364473</v>
       </c>
       <c r="CE9" t="n">
-        <v>35.24419673051138</v>
+        <v>35.24419672294257</v>
       </c>
       <c r="CF9" t="n">
-        <v>12.29886962086131</v>
+        <v>12.2988696199767</v>
       </c>
       <c r="CG9" t="n">
-        <v>20.3943531522701</v>
+        <v>20.39435314250484</v>
       </c>
       <c r="CH9" t="n">
         <v>18.40902666520164</v>
       </c>
       <c r="CI9" t="n">
-        <v>20.32278449016001</v>
+        <v>20.3227844887924</v>
       </c>
       <c r="CJ9" t="n">
         <v>18.63509665364473</v>
@@ -15494,7 +15502,7 @@
         <v>6.825396127602112</v>
       </c>
       <c r="CP9" t="n">
-        <v>29.44448877105594</v>
+        <v>29.44448876234502</v>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
@@ -15611,8 +15619,16 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Bandeira de alta</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Bandeira de alta (pré-confirmação) — pescoço R$43.15, preço 1.1% abaixo do pescoço; falta fechar acima e segurar</t>
+        </is>
+      </c>
       <c r="U10" t="b">
         <v>0</v>
       </c>
@@ -15784,10 +15800,10 @@
         <v>42.70000076293945</v>
       </c>
       <c r="CA10" t="n">
-        <v>125.1015273821003</v>
+        <v>125.1015279674615</v>
       </c>
       <c r="CB10" t="n">
-        <v>232.0633332937961</v>
+        <v>232.0633343796411</v>
       </c>
       <c r="CC10" t="n">
         <v>134.3883634463059</v>
@@ -15808,13 +15824,13 @@
         <v>54.40212095818906</v>
       </c>
       <c r="CI10" t="n">
-        <v>140.0386116732977</v>
+        <v>140.0386118821985</v>
       </c>
       <c r="CJ10" t="n">
-        <v>123.9129975665332</v>
+        <v>123.9129978592138</v>
       </c>
       <c r="CK10" t="n">
-        <v>111.5216978098799</v>
+        <v>111.5216980732924</v>
       </c>
       <c r="CL10" t="n">
         <v>8</v>
@@ -15826,10 +15842,10 @@
         <v>5.6</v>
       </c>
       <c r="CO10" t="n">
-        <v>161.1749316563777</v>
+        <v>161.174932273269</v>
       </c>
       <c r="CP10" t="n">
-        <v>227.9592720636231</v>
+        <v>227.959272552852</v>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
@@ -16117,10 +16133,10 @@
         <v>32.47999954223633</v>
       </c>
       <c r="CA11" t="n">
-        <v>45.35763236666469</v>
+        <v>45.3576324603114</v>
       </c>
       <c r="CB11" t="n">
-        <v>84.13840804016299</v>
+        <v>84.13840821387765</v>
       </c>
       <c r="CC11" t="n">
         <v>68.20285165366582</v>
@@ -16141,7 +16157,7 @@
         <v>25.67266223983068</v>
       </c>
       <c r="CI11" t="n">
-        <v>77.37745293613018</v>
+        <v>77.37745297432465</v>
       </c>
       <c r="CJ11" t="n">
         <v>68.20285165366582</v>
@@ -16162,7 +16178,7 @@
         <v>88.98573692551506</v>
       </c>
       <c r="CP11" t="n">
-        <v>138.2310776683051</v>
+        <v>138.2310777858989</v>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
@@ -16450,10 +16466,10 @@
         <v>6.920000076293945</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.500811666242972</v>
+        <v>6.500811642898193</v>
       </c>
       <c r="CB12" t="n">
-        <v>12.05900564088071</v>
+        <v>12.05900559757615</v>
       </c>
       <c r="CC12" t="n">
         <v>40.39207092990959</v>
@@ -16462,7 +16478,7 @@
         <v>27.23293457569906</v>
       </c>
       <c r="CE12" t="n">
-        <v>85.81998434881532</v>
+        <v>85.81998420483872</v>
       </c>
       <c r="CF12" t="n">
         <v>51.88018214566937</v>
@@ -16777,37 +16793,37 @@
         <v>32.84999847412109</v>
       </c>
       <c r="CA13" t="n">
-        <v>24.40198158437201</v>
+        <v>24.40198174522347</v>
       </c>
       <c r="CB13" t="n">
-        <v>32.23832936630178</v>
+        <v>32.23832821674423</v>
       </c>
       <c r="CC13" t="n">
-        <v>33.80534833525467</v>
+        <v>33.80534690698423</v>
       </c>
       <c r="CD13" t="n">
         <v>20.85130777065122</v>
       </c>
       <c r="CE13" t="n">
-        <v>48.27773820722045</v>
+        <v>48.27773695797047</v>
       </c>
       <c r="CF13" t="n">
-        <v>50.8460167963005</v>
+        <v>50.84601659046539</v>
       </c>
       <c r="CG13" t="n">
-        <v>16.49856811113381</v>
+        <v>16.4985671715297</v>
       </c>
       <c r="CH13" t="n">
         <v>24.29339039885633</v>
       </c>
       <c r="CI13" t="n">
-        <v>31.40158507126135</v>
+        <v>31.40158446980313</v>
       </c>
       <c r="CJ13" t="n">
-        <v>28.3201554753369</v>
+        <v>28.32015498098385</v>
       </c>
       <c r="CK13" t="n">
-        <v>25.48813992780321</v>
+        <v>25.48813948288546</v>
       </c>
       <c r="CL13" t="n">
         <v>8</v>
@@ -16819,10 +16835,10 @@
         <v>3.1</v>
       </c>
       <c r="CO13" t="n">
-        <v>-22.41052934026006</v>
+        <v>-22.41053069465203</v>
       </c>
       <c r="CP13" t="n">
-        <v>-4.409173425078827</v>
+        <v>-4.409175256001951</v>
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
@@ -17120,10 +17136,10 @@
         <v>47.31000137329102</v>
       </c>
       <c r="CA14" t="n">
-        <v>131.3186532722856</v>
+        <v>131.3186531307394</v>
       </c>
       <c r="CB14" t="n">
-        <v>243.5961018200898</v>
+        <v>243.5961015575216</v>
       </c>
       <c r="CC14" t="n">
         <v>134.5187807287781</v>
@@ -17144,13 +17160,13 @@
         <v>53.17581509382557</v>
       </c>
       <c r="CI14" t="n">
-        <v>142.2124817367327</v>
+        <v>142.2124816862184</v>
       </c>
       <c r="CJ14" t="n">
-        <v>127.0811095349434</v>
+        <v>127.0811094641703</v>
       </c>
       <c r="CK14" t="n">
-        <v>114.372998581449</v>
+        <v>114.3729985177533</v>
       </c>
       <c r="CL14" t="n">
         <v>8</v>
@@ -17162,10 +17178,10 @@
         <v>5.7</v>
       </c>
       <c r="CO14" t="n">
-        <v>141.7522622310018</v>
+        <v>141.7522620963669</v>
       </c>
       <c r="CP14" t="n">
-        <v>200.5970780145003</v>
+        <v>200.5970779077273</v>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
@@ -17204,7 +17220,7 @@
         <v>-1.560432066163409</v>
       </c>
       <c r="DC14" t="n">
-        <v>-10.93847029890879</v>
+        <v>-10.93846372884365</v>
       </c>
       <c r="DD14" t="b">
         <v>1</v>
@@ -17451,10 +17467,10 @@
         <v>13.64999961853027</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.2010593269665734</v>
+        <v>0.2010593269434413</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.2927423800633308</v>
+        <v>0.2927423800296505</v>
       </c>
       <c r="CC15" t="n">
         <v>75.91443638113093</v>
@@ -17762,10 +17778,10 @@
         <v>13.80000019073486</v>
       </c>
       <c r="CA16" t="n">
-        <v>10.01824952713163</v>
+        <v>10.01824950811843</v>
       </c>
       <c r="CB16" t="n">
-        <v>18.58385287282918</v>
+        <v>18.58385283755969</v>
       </c>
       <c r="CC16" t="n">
         <v>49.41891960195592</v>
@@ -17774,23 +17790,23 @@
         <v>48.6151297750832</v>
       </c>
       <c r="CE16" t="n">
-        <v>68.76522858026181</v>
+        <v>68.76522854361606</v>
       </c>
       <c r="CF16" t="n">
-        <v>33.93504903476912</v>
+        <v>33.93504903773515</v>
       </c>
       <c r="CG16" t="n">
-        <v>29.36037660162531</v>
+        <v>29.36037662381144</v>
       </c>
       <c r="CH16" t="inlineStr"/>
       <c r="CI16" t="n">
-        <v>33.97927383651808</v>
+        <v>33.97927382575025</v>
       </c>
       <c r="CJ16" t="n">
-        <v>33.93504903476912</v>
+        <v>33.93504903773515</v>
       </c>
       <c r="CK16" t="n">
-        <v>30.54154413129221</v>
+        <v>30.54154413396164</v>
       </c>
       <c r="CL16" t="n">
         <v>3</v>
@@ -17802,10 +17818,10 @@
         <v>4.9</v>
       </c>
       <c r="CO16" t="n">
-        <v>121.3155341243937</v>
+        <v>121.3155341437374</v>
       </c>
       <c r="CP16" t="n">
-        <v>146.2266186005657</v>
+        <v>146.226618522538</v>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
@@ -17993,7 +18009,7 @@
         <v>1</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="AV17" t="b">
         <v>1</v>
@@ -18089,10 +18105,10 @@
         <v>7.239999771118164</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.268913181465356</v>
+        <v>3.26891316777838</v>
       </c>
       <c r="CB17" t="n">
-        <v>6.063833951618235</v>
+        <v>6.063833926228895</v>
       </c>
       <c r="CC17" t="n">
         <v>20.4541571358882</v>
@@ -18101,7 +18117,7 @@
         <v>14.0164620450613</v>
       </c>
       <c r="CE17" t="n">
-        <v>32.91359938321693</v>
+        <v>32.91359934236029</v>
       </c>
       <c r="CF17" t="n">
         <v>10.95072400487419</v>
@@ -18394,10 +18410,10 @@
         <v>19.30999946594238</v>
       </c>
       <c r="CA18" t="n">
-        <v>13.27286328520698</v>
+        <v>13.27286328405224</v>
       </c>
       <c r="CB18" t="n">
-        <v>24.62116139405894</v>
+        <v>24.62116139191691</v>
       </c>
       <c r="CC18" t="n">
         <v>19.98886663466692</v>
@@ -18406,7 +18422,7 @@
         <v>12.49234273346821</v>
       </c>
       <c r="CE18" t="n">
-        <v>33.82719368413751</v>
+        <v>33.82719368287452</v>
       </c>
       <c r="CF18" t="n">
         <v>22.8984489302328</v>
@@ -18416,7 +18432,7 @@
       </c>
       <c r="CH18" t="inlineStr"/>
       <c r="CI18" t="n">
-        <v>20.1953350610414</v>
+        <v>20.19533506021722</v>
       </c>
       <c r="CJ18" t="n">
         <v>21.44365778244985</v>
@@ -18437,7 +18453,7 @@
         <v>-0.05545034714474761</v>
       </c>
       <c r="CP18" t="n">
-        <v>4.584855616700123</v>
+        <v>4.584855612431937</v>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
@@ -18733,10 +18749,10 @@
         <v>17.21999931335449</v>
       </c>
       <c r="CA19" t="n">
-        <v>10.55474910382358</v>
+        <v>10.55474909443632</v>
       </c>
       <c r="CB19" t="n">
-        <v>19.57905958759274</v>
+        <v>19.57905957017936</v>
       </c>
       <c r="CC19" t="n">
         <v>37.03977125031607</v>
@@ -18745,25 +18761,25 @@
         <v>36.56718452753732</v>
       </c>
       <c r="CE19" t="n">
-        <v>41.35653253861537</v>
+        <v>41.35653253460206</v>
       </c>
       <c r="CF19" t="n">
-        <v>34.51133419933809</v>
+        <v>34.51133420135141</v>
       </c>
       <c r="CG19" t="n">
-        <v>18.38517857817317</v>
+        <v>18.3851785890609</v>
       </c>
       <c r="CH19" t="n">
         <v>31.59171947190627</v>
       </c>
       <c r="CI19" t="n">
-        <v>31.290111450497</v>
+        <v>31.29011144927906</v>
       </c>
       <c r="CJ19" t="n">
-        <v>34.51133419933809</v>
+        <v>34.51133420135141</v>
       </c>
       <c r="CK19" t="n">
-        <v>31.06020077940428</v>
+        <v>31.06020078121627</v>
       </c>
       <c r="CL19" t="n">
         <v>7</v>
@@ -18775,10 +18791,10 @@
         <v>3.9</v>
       </c>
       <c r="CO19" t="n">
-        <v>80.37283401815472</v>
+        <v>80.3728340286773</v>
       </c>
       <c r="CP19" t="n">
-        <v>81.70797153418481</v>
+        <v>81.70797152711195</v>
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
@@ -19066,37 +19082,37 @@
         <v>10.10999965667725</v>
       </c>
       <c r="CA20" t="n">
-        <v>10.13143126652837</v>
+        <v>10.13143129308893</v>
       </c>
       <c r="CB20" t="n">
-        <v>18.70783436878482</v>
+        <v>18.70783429348263</v>
       </c>
       <c r="CC20" t="n">
-        <v>24.60234658832414</v>
+        <v>24.60234642479805</v>
       </c>
       <c r="CD20" t="n">
         <v>17.7286584153084</v>
       </c>
       <c r="CE20" t="n">
-        <v>37.29788764965343</v>
+        <v>37.29788762566994</v>
       </c>
       <c r="CF20" t="n">
-        <v>24.22484087319202</v>
+        <v>24.22484086184432</v>
       </c>
       <c r="CG20" t="n">
-        <v>11.97788224118745</v>
+        <v>11.97788218298796</v>
       </c>
       <c r="CH20" t="n">
         <v>10.10999965667725</v>
       </c>
       <c r="CI20" t="n">
-        <v>19.34761013245699</v>
+        <v>19.34761009423218</v>
       </c>
       <c r="CJ20" t="n">
-        <v>18.21824639204661</v>
+        <v>18.21824635439551</v>
       </c>
       <c r="CK20" t="n">
-        <v>16.39642175284195</v>
+        <v>16.39642171895596</v>
       </c>
       <c r="CL20" t="n">
         <v>8</v>
@@ -19108,10 +19124,10 @@
         <v>3.7</v>
       </c>
       <c r="CO20" t="n">
-        <v>62.18024045146999</v>
+        <v>62.18024011629704</v>
       </c>
       <c r="CP20" t="n">
-        <v>91.371026602149</v>
+        <v>91.37102622405995</v>
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
@@ -19401,10 +19417,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="CA21" t="n">
-        <v>5.044849568253714</v>
+        <v>5.04484961288621</v>
       </c>
       <c r="CB21" t="n">
-        <v>9.358195949110639</v>
+        <v>9.358196031903919</v>
       </c>
       <c r="CC21" t="n">
         <v>8.579313567043014</v>
@@ -19724,37 +19740,37 @@
         <v>35.20000076293945</v>
       </c>
       <c r="CA22" t="n">
-        <v>25.30945525840963</v>
+        <v>25.30945522188918</v>
       </c>
       <c r="CB22" t="n">
-        <v>31.056709418514</v>
+        <v>31.05670947302069</v>
       </c>
       <c r="CC22" t="n">
-        <v>34.16642412302713</v>
+        <v>34.16642423229225</v>
       </c>
       <c r="CD22" t="n">
         <v>36.55813791194976</v>
       </c>
       <c r="CE22" t="n">
-        <v>48.30444544109378</v>
+        <v>48.30444551510658</v>
       </c>
       <c r="CF22" t="n">
-        <v>48.45169427459941</v>
+        <v>48.45169429046752</v>
       </c>
       <c r="CG22" t="n">
-        <v>16.11152976767082</v>
+        <v>16.1115298497834</v>
       </c>
       <c r="CH22" t="n">
         <v>30.9183777534985</v>
       </c>
       <c r="CI22" t="n">
-        <v>33.85959674359538</v>
+        <v>33.85959678100099</v>
       </c>
       <c r="CJ22" t="n">
-        <v>32.61156677077057</v>
+        <v>32.61156685265647</v>
       </c>
       <c r="CK22" t="n">
-        <v>29.35041009369351</v>
+        <v>29.35041016739083</v>
       </c>
       <c r="CL22" t="n">
         <v>8</v>
@@ -19766,10 +19782,10 @@
         <v>3</v>
       </c>
       <c r="CO22" t="n">
-        <v>-16.618154950169</v>
+        <v>-16.61815474080161</v>
       </c>
       <c r="CP22" t="n">
-        <v>-3.807965881510234</v>
+        <v>-3.807965775244293</v>
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
@@ -20053,10 +20069,10 @@
         <v>10.97000026702881</v>
       </c>
       <c r="CA23" t="n">
-        <v>9.497073350591037</v>
+        <v>9.497073383813341</v>
       </c>
       <c r="CB23" t="n">
-        <v>17.61707106534638</v>
+        <v>17.61707112697374</v>
       </c>
       <c r="CC23" t="n">
         <v>21.98978873496697</v>
@@ -20065,25 +20081,25 @@
         <v>12.98356721691296</v>
       </c>
       <c r="CE23" t="n">
-        <v>32.25283431003437</v>
+        <v>32.25283420933102</v>
       </c>
       <c r="CF23" t="n">
-        <v>25.36723518641875</v>
+        <v>25.36723516205288</v>
       </c>
       <c r="CG23" t="n">
-        <v>12.06312339896413</v>
+        <v>12.06312329143549</v>
       </c>
       <c r="CH23" t="n">
         <v>9.632374997322403</v>
       </c>
       <c r="CI23" t="n">
-        <v>17.67538353256962</v>
+        <v>17.6753835153511</v>
       </c>
       <c r="CJ23" t="n">
-        <v>15.30031914112967</v>
+        <v>15.30031917194335</v>
       </c>
       <c r="CK23" t="n">
-        <v>13.7702872270167</v>
+        <v>13.77028725474902</v>
       </c>
       <c r="CL23" t="n">
         <v>8</v>
@@ -20095,10 +20111,10 @@
         <v>3.4</v>
       </c>
       <c r="CO23" t="n">
-        <v>25.52677203121294</v>
+        <v>25.52677228401434</v>
       </c>
       <c r="CP23" t="n">
-        <v>61.12473201750384</v>
+        <v>61.12473186054375</v>
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
@@ -20386,10 +20402,10 @@
         <v>10.63000011444092</v>
       </c>
       <c r="CA24" t="n">
-        <v>3.315435255587584</v>
+        <v>3.315435210883541</v>
       </c>
       <c r="CB24" t="n">
-        <v>6.150132399114969</v>
+        <v>6.150132316188968</v>
       </c>
       <c r="CC24" t="n">
         <v>19.53502101474926</v>
@@ -20398,13 +20414,13 @@
         <v>18.41366451165369</v>
       </c>
       <c r="CE24" t="n">
-        <v>20.99443609253708</v>
+        <v>20.99443609591905</v>
       </c>
       <c r="CF24" t="n">
-        <v>15.93437225439872</v>
+        <v>15.93437226326995</v>
       </c>
       <c r="CG24" t="n">
-        <v>13.08852151764407</v>
+        <v>13.08852157433238</v>
       </c>
       <c r="CH24" t="n">
         <v>29.73646810990179</v>
@@ -20460,7 +20476,7 @@
         <v>-21.14242970755025</v>
       </c>
       <c r="DC24" t="n">
-        <v>-35.6218103618902</v>
+        <v>-35.62181802569307</v>
       </c>
       <c r="DD24" t="b">
         <v>1</v>
@@ -20717,10 +20733,10 @@
         <v>14.72999954223633</v>
       </c>
       <c r="CA25" t="n">
-        <v>4.523502097171789</v>
+        <v>4.523502084068278</v>
       </c>
       <c r="CB25" t="n">
-        <v>8.391096390253667</v>
+        <v>8.391096365946655</v>
       </c>
       <c r="CC25" t="n">
         <v>24.2149496196813</v>
@@ -20729,25 +20745,25 @@
         <v>20.36807772582785</v>
       </c>
       <c r="CE25" t="n">
-        <v>29.43735271822437</v>
+        <v>29.43735272861319</v>
       </c>
       <c r="CF25" t="n">
-        <v>16.70161175993701</v>
+        <v>16.70161176264651</v>
       </c>
       <c r="CG25" t="n">
-        <v>18.44681919626278</v>
+        <v>18.44681921709946</v>
       </c>
       <c r="CH25" t="n">
         <v>14.61024983224005</v>
       </c>
       <c r="CI25" t="n">
-        <v>18.88145103463243</v>
+        <v>18.88145103600786</v>
       </c>
       <c r="CJ25" t="n">
-        <v>18.44681919626278</v>
+        <v>18.44681921709946</v>
       </c>
       <c r="CK25" t="n">
-        <v>16.6021372766365</v>
+        <v>16.60213729538952</v>
       </c>
       <c r="CL25" t="n">
         <v>7</v>
@@ -20759,10 +20775,10 @@
         <v>6.5</v>
       </c>
       <c r="CO25" t="n">
-        <v>12.70969309287533</v>
+        <v>12.70969322018702</v>
       </c>
       <c r="CP25" t="n">
-        <v>28.18364983985479</v>
+        <v>28.18364984919242</v>
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
@@ -21369,10 +21385,10 @@
         <v>14.31999969482422</v>
       </c>
       <c r="CA27" t="n">
-        <v>8.981535404762363</v>
+        <v>8.981535420135518</v>
       </c>
       <c r="CB27" t="n">
-        <v>16.66074817583418</v>
+        <v>16.66074820435139</v>
       </c>
       <c r="CC27" t="n">
         <v>13.52387711735003</v>
@@ -21393,7 +21409,7 @@
         <v>6.210695553020633</v>
       </c>
       <c r="CI27" t="n">
-        <v>11.29322924916103</v>
+        <v>11.29322925543109</v>
       </c>
       <c r="CJ27" t="n">
         <v>10.99565184259889</v>
@@ -21414,7 +21430,7 @@
         <v>-30.89324811985986</v>
       </c>
       <c r="CP27" t="n">
-        <v>-21.13666557379309</v>
+        <v>-21.1366655300078</v>
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
@@ -21698,10 +21714,10 @@
         <v>27.42000007629395</v>
       </c>
       <c r="CA28" t="n">
-        <v>7.265285107589708</v>
+        <v>7.265285056609213</v>
       </c>
       <c r="CB28" t="n">
-        <v>13.47710387457891</v>
+        <v>13.47710378001009</v>
       </c>
       <c r="CC28" t="n">
         <v>35.82988175649849</v>
@@ -21710,19 +21726,19 @@
         <v>28.32096620307184</v>
       </c>
       <c r="CE28" t="n">
-        <v>44.64824881193085</v>
+        <v>44.64824888800035</v>
       </c>
       <c r="CF28" t="n">
-        <v>26.46426765547184</v>
+        <v>26.4642676681783</v>
       </c>
       <c r="CG28" t="n">
-        <v>28.98335739352322</v>
+        <v>28.98335748558175</v>
       </c>
       <c r="CH28" t="n">
         <v>24.27856406616775</v>
       </c>
       <c r="CI28" t="n">
-        <v>28.85748425160613</v>
+        <v>28.8574842639298</v>
       </c>
       <c r="CJ28" t="n">
         <v>28.32096620307184</v>
@@ -21743,7 +21759,7 @@
         <v>-7.042780773727464</v>
       </c>
       <c r="CP28" t="n">
-        <v>5.242465978528443</v>
+        <v>5.242466023472536</v>
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
@@ -22031,10 +22047,10 @@
         <v>23.79999923706055</v>
       </c>
       <c r="CA29" t="n">
-        <v>12.34802659991777</v>
+        <v>12.34802658811414</v>
       </c>
       <c r="CB29" t="n">
-        <v>22.90558934284746</v>
+        <v>22.90558932095173</v>
       </c>
       <c r="CC29" t="n">
         <v>61.59179490059613</v>
@@ -22043,13 +22059,13 @@
         <v>51.73586889978424</v>
       </c>
       <c r="CE29" t="n">
-        <v>87.07810606316832</v>
+        <v>87.07810606106759</v>
       </c>
       <c r="CF29" t="n">
-        <v>33.74455760751021</v>
+        <v>33.74455760947531</v>
       </c>
       <c r="CG29" t="n">
-        <v>45.92960715873755</v>
+        <v>45.92960717770457</v>
       </c>
       <c r="CH29" t="n">
         <v>5.609791711095563</v>
@@ -22370,10 +22386,10 @@
         <v>22.60000038146973</v>
       </c>
       <c r="CA30" t="n">
-        <v>3.184692830772003</v>
+        <v>3.184692833531383</v>
       </c>
       <c r="CB30" t="n">
-        <v>5.907605201082066</v>
+        <v>5.907605206200714</v>
       </c>
       <c r="CC30" t="n">
         <v>33.79796896777358</v>
@@ -22382,7 +22398,7 @@
         <v>28.20908778885038</v>
       </c>
       <c r="CE30" t="n">
-        <v>43.29409766962235</v>
+        <v>43.29409767398253</v>
       </c>
       <c r="CF30" t="n">
         <v>10.85340539909456</v>
@@ -22673,10 +22689,10 @@
         <v>39.45000076293945</v>
       </c>
       <c r="CA31" t="n">
-        <v>36.11966575775509</v>
+        <v>36.1196657151245</v>
       </c>
       <c r="CB31" t="n">
-        <v>52.59023334329141</v>
+        <v>52.59023328122127</v>
       </c>
       <c r="CC31" t="n">
         <v>48.55384709284856</v>
@@ -22693,13 +22709,13 @@
       </c>
       <c r="CH31" t="inlineStr"/>
       <c r="CI31" t="n">
-        <v>49.19197779442819</v>
+        <v>49.19197776825301</v>
       </c>
       <c r="CJ31" t="n">
-        <v>50.57204021806999</v>
+        <v>50.57204018703491</v>
       </c>
       <c r="CK31" t="n">
-        <v>45.51483619626299</v>
+        <v>45.51483616833143</v>
       </c>
       <c r="CL31" t="n">
         <v>4</v>
@@ -22711,10 +22727,10 @@
         <v>1.6</v>
       </c>
       <c r="CO31" t="n">
-        <v>15.37347355141507</v>
+        <v>15.37347348061262</v>
       </c>
       <c r="CP31" t="n">
-        <v>24.69449136396633</v>
+        <v>24.69449129761607</v>
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
@@ -23303,35 +23319,35 @@
         <v>23.04999923706055</v>
       </c>
       <c r="CA33" t="n">
-        <v>16.54461545509324</v>
+        <v>16.5446154810169</v>
       </c>
       <c r="CB33" t="n">
-        <v>29.5743114276749</v>
+        <v>29.57431142374383</v>
       </c>
       <c r="CC33" t="n">
-        <v>49.88257136050604</v>
+        <v>49.88257127571487</v>
       </c>
       <c r="CD33" t="n">
         <v>49.40798271639872</v>
       </c>
       <c r="CE33" t="n">
-        <v>61.60540337474787</v>
+        <v>61.6054033852698</v>
       </c>
       <c r="CF33" t="n">
-        <v>45.75579822590096</v>
+        <v>45.75579822025198</v>
       </c>
       <c r="CG33" t="n">
-        <v>24.4833642931657</v>
+        <v>24.48336426111368</v>
       </c>
       <c r="CH33" t="inlineStr"/>
       <c r="CI33" t="n">
-        <v>35.43932411729379</v>
+        <v>35.4393241001819</v>
       </c>
       <c r="CJ33" t="n">
-        <v>37.66505482678793</v>
+        <v>37.66505482199791</v>
       </c>
       <c r="CK33" t="n">
-        <v>33.89854934410914</v>
+        <v>33.89854933979812</v>
       </c>
       <c r="CL33" t="n">
         <v>4</v>
@@ -23343,10 +23359,10 @@
         <v>3</v>
       </c>
       <c r="CO33" t="n">
-        <v>47.06529486389714</v>
+        <v>47.06529484519424</v>
       </c>
       <c r="CP33" t="n">
-        <v>53.74978433974642</v>
+        <v>53.7497842655083</v>
       </c>
       <c r="CQ33" t="inlineStr">
         <is>
@@ -23630,10 +23646,10 @@
         <v>33.38999938964844</v>
       </c>
       <c r="CA34" t="n">
-        <v>7.91977388125787</v>
+        <v>7.919773899614443</v>
       </c>
       <c r="CB34" t="n">
-        <v>14.69118054973335</v>
+        <v>14.69118058378479</v>
       </c>
       <c r="CC34" t="n">
         <v>63.74891814306077</v>
@@ -23642,7 +23658,7 @@
         <v>37.2141137927402</v>
       </c>
       <c r="CE34" t="n">
-        <v>88.14507567468829</v>
+        <v>88.14507571171885</v>
       </c>
       <c r="CF34" t="n">
         <v>22.51480113099953</v>
@@ -23953,10 +23969,10 @@
         <v>33.36000061035156</v>
       </c>
       <c r="CA35" t="n">
-        <v>15.11688470009254</v>
+        <v>15.11688474493058</v>
       </c>
       <c r="CB35" t="n">
-        <v>28.04182111867167</v>
+        <v>28.04182120184623</v>
       </c>
       <c r="CC35" t="n">
         <v>20.05535426892732</v>
@@ -23965,7 +23981,7 @@
         <v>36.99750756788258</v>
       </c>
       <c r="CE35" t="n">
-        <v>27.00891074502444</v>
+        <v>27.00891077350595</v>
       </c>
       <c r="CF35" t="n">
         <v>15.03391666666667</v>
@@ -23977,7 +23993,7 @@
         <v>79.30503918682102</v>
       </c>
       <c r="CI35" t="n">
-        <v>22.46273576176436</v>
+        <v>22.46273578412066</v>
       </c>
       <c r="CJ35" t="n">
         <v>20.05535426892732</v>
@@ -23998,7 +24014,7 @@
         <v>-45.89382940108894</v>
       </c>
       <c r="CP35" t="n">
-        <v>-32.66566141850069</v>
+        <v>-32.6656613514854</v>
       </c>
       <c r="CQ35" t="inlineStr">
         <is>
@@ -24111,12 +24127,12 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Bandeira de alta</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>Fundo duplo (pré-confirmação) — pescoço R$30.00, preço 15.6% acima do pescoço; falta fechar acima e segurar</t>
+          <t>Bandeira de alta (pré-confirmação) — pescoço R$32.23, preço 7.6% acima do pescoço; falta fechar acima e segurar</t>
         </is>
       </c>
       <c r="U36" t="b">
@@ -24290,10 +24306,10 @@
         <v>34.68999862670898</v>
       </c>
       <c r="CA36" t="n">
-        <v>3.441930999778089</v>
+        <v>3.44193098919063</v>
       </c>
       <c r="CB36" t="n">
-        <v>6.384782004588356</v>
+        <v>6.384781984948619</v>
       </c>
       <c r="CC36" t="n">
         <v>32.87857523633004</v>
@@ -24302,7 +24318,7 @@
         <v>23.03538757661248</v>
       </c>
       <c r="CE36" t="n">
-        <v>40.66788364789184</v>
+        <v>40.66788363728924</v>
       </c>
       <c r="CF36" t="n">
         <v>10.59424454785779</v>
@@ -24593,35 +24609,35 @@
         <v>12.84000015258789</v>
       </c>
       <c r="CA37" t="n">
-        <v>8.620481286504914</v>
+        <v>8.620481355714078</v>
       </c>
       <c r="CB37" t="n">
-        <v>13.75169161101834</v>
+        <v>13.75169153134293</v>
       </c>
       <c r="CC37" t="n">
-        <v>18.28822757306843</v>
+        <v>18.2882273202827</v>
       </c>
       <c r="CD37" t="n">
         <v>17.29599079072038</v>
       </c>
       <c r="CE37" t="n">
-        <v>22.79369014170337</v>
+        <v>22.7936900752349</v>
       </c>
       <c r="CF37" t="n">
-        <v>17.32774436624598</v>
+        <v>17.32774434692217</v>
       </c>
       <c r="CG37" t="n">
-        <v>9.132575867725885</v>
+        <v>9.132575749815619</v>
       </c>
       <c r="CH37" t="inlineStr"/>
       <c r="CI37" t="n">
-        <v>14.49703620920942</v>
+        <v>14.49703613856547</v>
       </c>
       <c r="CJ37" t="n">
-        <v>15.53971798863216</v>
+        <v>15.53971793913255</v>
       </c>
       <c r="CK37" t="n">
-        <v>13.98574618976895</v>
+        <v>13.9857461452193</v>
       </c>
       <c r="CL37" t="n">
         <v>4</v>
@@ -24633,10 +24649,10 @@
         <v>2.1</v>
       </c>
       <c r="CO37" t="n">
-        <v>8.923255635243388</v>
+        <v>8.923255288283482</v>
       </c>
       <c r="CP37" t="n">
-        <v>12.90526508512191</v>
+        <v>12.90526453493546</v>
       </c>
       <c r="CQ37" t="inlineStr">
         <is>
@@ -24910,10 +24926,10 @@
         <v>39.09999847412109</v>
       </c>
       <c r="CA38" t="n">
-        <v>19.98838182642474</v>
+        <v>19.98838170689563</v>
       </c>
       <c r="CB38" t="n">
-        <v>37.0784482880179</v>
+        <v>37.0784480662914</v>
       </c>
       <c r="CC38" t="n">
         <v>55.88726858490879</v>
@@ -24922,23 +24938,23 @@
         <v>42.23733079208057</v>
       </c>
       <c r="CE38" t="n">
-        <v>62.05594540325415</v>
+        <v>62.05594559841553</v>
       </c>
       <c r="CF38" t="n">
-        <v>45.20943449802702</v>
+        <v>45.20943453546542</v>
       </c>
       <c r="CG38" t="n">
-        <v>31.29948454409355</v>
+        <v>31.29948478023526</v>
       </c>
       <c r="CH38" t="inlineStr"/>
       <c r="CI38" t="n">
-        <v>39.54088329934461</v>
+        <v>39.54088322339031</v>
       </c>
       <c r="CJ38" t="n">
-        <v>41.14394139302246</v>
+        <v>41.14394130087841</v>
       </c>
       <c r="CK38" t="n">
-        <v>37.02954725372022</v>
+        <v>37.02954717079057</v>
       </c>
       <c r="CL38" t="n">
         <v>4</v>
@@ -24950,10 +24966,10 @@
         <v>2.8</v>
       </c>
       <c r="CO38" t="n">
-        <v>-5.295271870077523</v>
+        <v>-5.295272082173819</v>
       </c>
       <c r="CP38" t="n">
-        <v>1.127582717209874</v>
+        <v>1.127582522953352</v>
       </c>
       <c r="CQ38" t="inlineStr">
         <is>
@@ -25070,12 +25086,12 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Bandeira de alta</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Fundo duplo (pré-confirmação) — pescoço R$4.78, preço 25.7% acima do pescoço; falta fechar acima e segurar</t>
+          <t>Bandeira de alta (pré-confirmação) — pescoço R$6.04, preço 0.6% abaixo do pescoço; falta fechar acima e segurar</t>
         </is>
       </c>
       <c r="U39" t="b">
@@ -25249,10 +25265,10 @@
         <v>6.010000228881836</v>
       </c>
       <c r="CA39" t="n">
-        <v>7.12914305894854</v>
+        <v>7.129142969055732</v>
       </c>
       <c r="CB39" t="n">
-        <v>13.22456037434954</v>
+        <v>13.22456020759838</v>
       </c>
       <c r="CC39" t="n">
         <v>5.700250753950201</v>
@@ -25273,7 +25289,7 @@
         <v>5.504458217875779</v>
       </c>
       <c r="CI39" t="n">
-        <v>7.427901861097509</v>
+        <v>7.427901829017013</v>
       </c>
       <c r="CJ39" t="n">
         <v>5.916792043641768</v>
@@ -25294,7 +25310,7 @@
         <v>-11.39579639802557</v>
       </c>
       <c r="CP39" t="n">
-        <v>23.5923723497008</v>
+        <v>23.59237181591551</v>
       </c>
       <c r="CQ39" t="inlineStr">
         <is>
@@ -25566,10 +25582,10 @@
         <v>14.96000003814697</v>
       </c>
       <c r="CA40" t="n">
-        <v>9.299118859309983</v>
+        <v>9.299118781731359</v>
       </c>
       <c r="CB40" t="n">
-        <v>17.24986548402002</v>
+        <v>17.24986534011167</v>
       </c>
       <c r="CC40" t="n">
         <v>30.82737177378653</v>
@@ -25578,23 +25594,23 @@
         <v>29.3357145487105</v>
       </c>
       <c r="CE40" t="n">
-        <v>34.7261727411532</v>
+        <v>34.72617272570776</v>
       </c>
       <c r="CF40" t="n">
-        <v>25.49555037615469</v>
+        <v>25.49555039198669</v>
       </c>
       <c r="CG40" t="n">
-        <v>15.31657760881048</v>
+        <v>15.31657770527484</v>
       </c>
       <c r="CH40" t="inlineStr"/>
       <c r="CI40" t="n">
-        <v>20.7179766233178</v>
+        <v>20.71797657190406</v>
       </c>
       <c r="CJ40" t="n">
-        <v>21.37270793008735</v>
+        <v>21.37270786604918</v>
       </c>
       <c r="CK40" t="n">
-        <v>19.23543713707862</v>
+        <v>19.23543707944426</v>
       </c>
       <c r="CL40" t="n">
         <v>4</v>
@@ -25606,10 +25622,10 @@
         <v>3.3</v>
       </c>
       <c r="CO40" t="n">
-        <v>28.57912491998378</v>
+        <v>28.57912453472742</v>
       </c>
       <c r="CP40" t="n">
-        <v>38.48914819845177</v>
+        <v>38.48914785477704</v>
       </c>
       <c r="CQ40" t="inlineStr">
         <is>
@@ -25897,10 +25913,10 @@
         <v>12.75</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.570253751563669</v>
+        <v>1.57025375627463</v>
       </c>
       <c r="CB41" t="n">
-        <v>2.912820709150606</v>
+        <v>2.912820717889438</v>
       </c>
       <c r="CC41" t="n">
         <v>12.56040892193308</v>
@@ -25909,7 +25925,7 @@
         <v>9.175696506445684</v>
       </c>
       <c r="CE41" t="n">
-        <v>15.85379572653467</v>
+        <v>15.85379573143828</v>
       </c>
       <c r="CF41" t="n">
         <v>6.104046666666666</v>
@@ -26216,37 +26232,37 @@
         <v>26.64999961853027</v>
       </c>
       <c r="CA42" t="n">
-        <v>17.04081911348038</v>
+        <v>17.04081915921964</v>
       </c>
       <c r="CB42" t="n">
-        <v>28.24466298572847</v>
+        <v>28.24466299126953</v>
       </c>
       <c r="CC42" t="n">
-        <v>47.30306352366961</v>
+        <v>47.30306340598339</v>
       </c>
       <c r="CD42" t="n">
         <v>53.09041087001181</v>
       </c>
       <c r="CE42" t="n">
-        <v>56.22823554597153</v>
+        <v>56.22823556058753</v>
       </c>
       <c r="CF42" t="n">
-        <v>42.93945177272226</v>
+        <v>42.93945176440158</v>
       </c>
       <c r="CG42" t="n">
-        <v>23.53452114541224</v>
+        <v>23.53452109425378</v>
       </c>
       <c r="CH42" t="n">
         <v>30.99183173163939</v>
       </c>
       <c r="CI42" t="n">
-        <v>37.42162458607946</v>
+        <v>37.42162457217083</v>
       </c>
       <c r="CJ42" t="n">
-        <v>36.96564175218083</v>
+        <v>36.96564174802049</v>
       </c>
       <c r="CK42" t="n">
-        <v>33.26907757696275</v>
+        <v>33.26907757321844</v>
       </c>
       <c r="CL42" t="n">
         <v>8</v>
@@ -26258,10 +26274,10 @@
         <v>3.3</v>
       </c>
       <c r="CO42" t="n">
-        <v>24.83706586558485</v>
+        <v>24.83706585153491</v>
       </c>
       <c r="CP42" t="n">
-        <v>40.4188559915005</v>
+        <v>40.41885593931054</v>
       </c>
       <c r="CQ42" t="inlineStr">
         <is>
@@ -26549,37 +26565,37 @@
         <v>15.11999988555908</v>
       </c>
       <c r="CA43" t="n">
-        <v>5.865830794046077</v>
+        <v>5.865830790850479</v>
       </c>
       <c r="CB43" t="n">
-        <v>8.474845209943982</v>
+        <v>8.474845212604007</v>
       </c>
       <c r="CC43" t="n">
-        <v>10.77599630748211</v>
+        <v>10.77599631673497</v>
       </c>
       <c r="CD43" t="n">
         <v>11.55627711976371</v>
       </c>
       <c r="CE43" t="n">
-        <v>9.774262762032622</v>
+        <v>9.774262767174816</v>
       </c>
       <c r="CF43" t="n">
-        <v>14.91642323776266</v>
+        <v>14.91642323889413</v>
       </c>
       <c r="CG43" t="n">
-        <v>5.368455505538072</v>
+        <v>5.368455510712384</v>
       </c>
       <c r="CH43" t="n">
         <v>10.8369287109083</v>
       </c>
       <c r="CI43" t="n">
-        <v>9.696127455934691</v>
+        <v>9.696127458455351</v>
       </c>
       <c r="CJ43" t="n">
-        <v>10.27512953475737</v>
+        <v>10.27512954195489</v>
       </c>
       <c r="CK43" t="n">
-        <v>9.24761658128163</v>
+        <v>9.247616587759405</v>
       </c>
       <c r="CL43" t="n">
         <v>8</v>
@@ -26591,10 +26607,10 @@
         <v>2.8</v>
       </c>
       <c r="CO43" t="n">
-        <v>-38.83851421114156</v>
+        <v>-38.83851416829914</v>
       </c>
       <c r="CP43" t="n">
-        <v>-35.87217242511134</v>
+        <v>-35.87217240844031</v>
       </c>
       <c r="CQ43" t="inlineStr">
         <is>
@@ -26882,10 +26898,10 @@
         <v>11.77000045776367</v>
       </c>
       <c r="CA44" t="n">
-        <v>4.784269052954928</v>
+        <v>4.784269063922396</v>
       </c>
       <c r="CB44" t="n">
-        <v>8.874819093231391</v>
+        <v>8.874819113576045</v>
       </c>
       <c r="CC44" t="n">
         <v>25.44086558978281</v>
@@ -26894,25 +26910,25 @@
         <v>28.63793221437547</v>
       </c>
       <c r="CE44" t="n">
-        <v>23.61676923654554</v>
+        <v>23.61676924600882</v>
       </c>
       <c r="CF44" t="n">
-        <v>14.24977379955972</v>
+        <v>14.24977379847481</v>
       </c>
       <c r="CG44" t="n">
-        <v>13.10602504652211</v>
+        <v>13.10602503672596</v>
       </c>
       <c r="CH44" t="n">
         <v>4.870861694358507</v>
       </c>
       <c r="CI44" t="n">
-        <v>18.98769749666951</v>
+        <v>18.98769749982398</v>
       </c>
       <c r="CJ44" t="n">
-        <v>18.93327151805263</v>
+        <v>18.93327152224181</v>
       </c>
       <c r="CK44" t="n">
-        <v>17.03994436624737</v>
+        <v>17.03994437001763</v>
       </c>
       <c r="CL44" t="n">
         <v>6</v>
@@ -26924,10 +26940,10 @@
         <v>6</v>
       </c>
       <c r="CO44" t="n">
-        <v>44.77437301208909</v>
+        <v>44.77437304412189</v>
       </c>
       <c r="CP44" t="n">
-        <v>61.3228271724062</v>
+        <v>61.32282719920718</v>
       </c>
       <c r="CQ44" t="inlineStr">
         <is>
@@ -27211,10 +27227,10 @@
         <v>9.069999694824219</v>
       </c>
       <c r="CA45" t="n">
-        <v>2.472824426255773</v>
+        <v>2.472824454320842</v>
       </c>
       <c r="CB45" t="n">
-        <v>4.587089310704459</v>
+        <v>4.587089362765161</v>
       </c>
       <c r="CC45" t="n">
         <v>13.23540704365869</v>
@@ -27223,19 +27239,19 @@
         <v>14.96700525293176</v>
       </c>
       <c r="CE45" t="n">
-        <v>10.35281120208623</v>
+        <v>10.35281120598868</v>
       </c>
       <c r="CF45" t="n">
-        <v>7.309831176763966</v>
+        <v>7.309831174059974</v>
       </c>
       <c r="CG45" t="n">
-        <v>6.779397778187641</v>
+        <v>6.779397753440986</v>
       </c>
       <c r="CH45" t="n">
         <v>10.12863973392969</v>
       </c>
       <c r="CI45" t="n">
-        <v>9.622883071180349</v>
+        <v>9.622883075253565</v>
       </c>
       <c r="CJ45" t="n">
         <v>10.12863973392969</v>
@@ -27256,7 +27272,7 @@
         <v>0.5046975441313828</v>
       </c>
       <c r="CP45" t="n">
-        <v>6.095737540891344</v>
+        <v>6.095737585800021</v>
       </c>
       <c r="CQ45" t="inlineStr">
         <is>
@@ -27291,7 +27307,7 @@
         <v>-2.473123561220814</v>
       </c>
       <c r="DC45" t="n">
-        <v>-36.49822149343045</v>
+        <v>-36.49822591325916</v>
       </c>
       <c r="DD45" t="b">
         <v>0</v>
@@ -27540,37 +27556,37 @@
         <v>38.70000076293945</v>
       </c>
       <c r="CA46" t="n">
-        <v>30.84756146352459</v>
+        <v>30.84756141455194</v>
       </c>
       <c r="CB46" t="n">
-        <v>35.74245442164587</v>
+        <v>35.74245446027761</v>
       </c>
       <c r="CC46" t="n">
-        <v>39.06003421083991</v>
+        <v>39.06003431506794</v>
       </c>
       <c r="CD46" t="n">
         <v>49.9060657389037</v>
       </c>
       <c r="CE46" t="n">
-        <v>60.73976153341496</v>
+        <v>60.7397615878864</v>
       </c>
       <c r="CF46" t="n">
-        <v>16.61273117624454</v>
+        <v>16.61273118102335</v>
       </c>
       <c r="CG46" t="n">
-        <v>17.68241854075722</v>
+        <v>17.68241862755243</v>
       </c>
       <c r="CH46" t="n">
         <v>28.82212409504474</v>
       </c>
       <c r="CI46" t="n">
-        <v>34.92664389754694</v>
+        <v>34.92664392753851</v>
       </c>
       <c r="CJ46" t="n">
-        <v>33.29500794258523</v>
+        <v>33.29500793741478</v>
       </c>
       <c r="CK46" t="n">
-        <v>29.96550714832671</v>
+        <v>29.9655071436733</v>
       </c>
       <c r="CL46" t="n">
         <v>8</v>
@@ -27582,10 +27598,10 @@
         <v>3.7</v>
       </c>
       <c r="CO46" t="n">
-        <v>-22.56975049720727</v>
+        <v>-22.56975050923158</v>
       </c>
       <c r="CP46" t="n">
-        <v>-9.750275945746289</v>
+        <v>-9.750275868248682</v>
       </c>
       <c r="CQ46" t="inlineStr">
         <is>
@@ -27624,7 +27640,7 @@
         <v>-0.61632735550462</v>
       </c>
       <c r="DC46" t="n">
-        <v>-11.66799026158288</v>
+        <v>-11.66799814233929</v>
       </c>
       <c r="DD46" t="b">
         <v>1</v>
@@ -27881,10 +27897,10 @@
         <v>33.34999847412109</v>
       </c>
       <c r="CA47" t="n">
-        <v>14.44223110656149</v>
+        <v>14.44223105440009</v>
       </c>
       <c r="CB47" t="n">
-        <v>26.79033870267156</v>
+        <v>26.79033860591217</v>
       </c>
       <c r="CC47" t="n">
         <v>55.86440958054417</v>
@@ -27893,25 +27909,25 @@
         <v>43.13942726989067</v>
       </c>
       <c r="CE47" t="n">
-        <v>72.71632254472365</v>
+        <v>72.71632260933538</v>
       </c>
       <c r="CF47" t="n">
-        <v>38.50528575933758</v>
+        <v>38.50528577222813</v>
       </c>
       <c r="CG47" t="n">
-        <v>40.903421079076</v>
+        <v>40.90342117771947</v>
       </c>
       <c r="CH47" t="n">
         <v>21.66331906695809</v>
       </c>
       <c r="CI47" t="n">
-        <v>42.79750342902881</v>
+        <v>42.79750344036972</v>
       </c>
       <c r="CJ47" t="n">
-        <v>40.903421079076</v>
+        <v>40.90342117771947</v>
       </c>
       <c r="CK47" t="n">
-        <v>36.8130789711684</v>
+        <v>36.81307905994753</v>
       </c>
       <c r="CL47" t="n">
         <v>7</v>
@@ -27923,10 +27939,10 @@
         <v>5</v>
       </c>
       <c r="CO47" t="n">
-        <v>10.38404994151525</v>
+        <v>10.38405020771953</v>
       </c>
       <c r="CP47" t="n">
-        <v>28.32835198549946</v>
+        <v>28.32835201950519</v>
       </c>
       <c r="CQ47" t="inlineStr">
         <is>
@@ -28208,10 +28224,10 @@
         <v>6.570000171661377</v>
       </c>
       <c r="CA48" t="n">
-        <v>7.812280716514052</v>
+        <v>7.812280615512812</v>
       </c>
       <c r="CB48" t="n">
-        <v>11.37468072324446</v>
+        <v>11.37468057618666</v>
       </c>
       <c r="CC48" t="n">
         <v>8.114964582574622</v>
@@ -28230,7 +28246,7 @@
         <v>5.379803695646386</v>
       </c>
       <c r="CI48" t="n">
-        <v>8.397726720399756</v>
+        <v>8.397726679056582</v>
       </c>
       <c r="CJ48" t="n">
         <v>8.471557624874304</v>
@@ -28251,7 +28267,7 @@
         <v>16.04873155519062</v>
       </c>
       <c r="CP48" t="n">
-        <v>27.81927703171119</v>
+        <v>27.81927640243915</v>
       </c>
       <c r="CQ48" t="inlineStr">
         <is>
@@ -28517,35 +28533,35 @@
         <v>16.93000030517578</v>
       </c>
       <c r="CA49" t="n">
-        <v>10.07593953517678</v>
+        <v>10.07593941498686</v>
       </c>
       <c r="CB49" t="n">
-        <v>17.56133914863183</v>
+        <v>17.56133916892925</v>
       </c>
       <c r="CC49" t="n">
-        <v>28.83258830480192</v>
+        <v>28.83258868205356</v>
       </c>
       <c r="CD49" t="n">
         <v>29.26650917734455</v>
       </c>
       <c r="CE49" t="n">
-        <v>32.09021933964034</v>
+        <v>32.09021934721415</v>
       </c>
       <c r="CF49" t="n">
-        <v>27.8842854882014</v>
+        <v>27.88428551532881</v>
       </c>
       <c r="CG49" t="n">
-        <v>14.2283163021319</v>
+        <v>14.22831645158085</v>
       </c>
       <c r="CH49" t="inlineStr"/>
       <c r="CI49" t="n">
-        <v>21.08853811920299</v>
+        <v>21.08853819532462</v>
       </c>
       <c r="CJ49" t="n">
-        <v>22.72281231841662</v>
+        <v>22.72281234212903</v>
       </c>
       <c r="CK49" t="n">
-        <v>20.45053108657496</v>
+        <v>20.45053110791613</v>
       </c>
       <c r="CL49" t="n">
         <v>4</v>
@@ -28557,10 +28573,10 @@
         <v>2.9</v>
       </c>
       <c r="CO49" t="n">
-        <v>20.79462916679862</v>
+        <v>20.79462929285394</v>
       </c>
       <c r="CP49" t="n">
-        <v>24.56312899625803</v>
+        <v>24.56312944588372</v>
       </c>
       <c r="CQ49" t="inlineStr">
         <is>
@@ -28603,7 +28619,7 @@
         <v>-4.350284884596789</v>
       </c>
       <c r="DC49" t="n">
-        <v>-20.28805503364547</v>
+        <v>-20.28806233739286</v>
       </c>
       <c r="DD49" t="b">
         <v>1</v>
@@ -28852,10 +28868,10 @@
         <v>32.52999877929688</v>
       </c>
       <c r="CA50" t="n">
-        <v>11.05396023052786</v>
+        <v>11.05396019502937</v>
       </c>
       <c r="CB50" t="n">
-        <v>20.50509622762917</v>
+        <v>20.50509616177948</v>
       </c>
       <c r="CC50" t="n">
         <v>55.47264914101462</v>
@@ -28864,19 +28880,19 @@
         <v>52.30651498008846</v>
       </c>
       <c r="CE50" t="n">
-        <v>57.8667368486734</v>
+        <v>57.86673685617772</v>
       </c>
       <c r="CF50" t="n">
-        <v>28.13054908897375</v>
+        <v>28.1305490030386</v>
       </c>
       <c r="CG50" t="n">
-        <v>35.03833473717194</v>
+        <v>35.03833478209315</v>
       </c>
       <c r="CH50" t="n">
         <v>54.48085949640561</v>
       </c>
       <c r="CI50" t="n">
-        <v>43.40010578856528</v>
+        <v>43.40010577437108</v>
       </c>
       <c r="CJ50" t="n">
         <v>52.30651498008846</v>
@@ -28897,7 +28913,7 @@
         <v>44.71523285774048</v>
       </c>
       <c r="CP50" t="n">
-        <v>33.41563915516186</v>
+        <v>33.4156391115277</v>
       </c>
       <c r="CQ50" t="inlineStr">
         <is>
@@ -29181,37 +29197,37 @@
         <v>44.06000137329102</v>
       </c>
       <c r="CA51" t="n">
-        <v>31.96233917907316</v>
+        <v>31.96233907069051</v>
       </c>
       <c r="CB51" t="n">
-        <v>43.40419596995319</v>
+        <v>43.4041961745397</v>
       </c>
       <c r="CC51" t="n">
-        <v>49.69482656228118</v>
+        <v>49.69482696503131</v>
       </c>
       <c r="CD51" t="n">
         <v>47.301358204649</v>
       </c>
       <c r="CE51" t="n">
-        <v>69.17232289553603</v>
+        <v>69.17232312013662</v>
       </c>
       <c r="CF51" t="n">
-        <v>59.81319571034596</v>
+        <v>59.81319575565071</v>
       </c>
       <c r="CG51" t="n">
-        <v>24.4605088142312</v>
+        <v>24.46050906631191</v>
       </c>
       <c r="CH51" t="n">
         <v>76.33330481362214</v>
       </c>
       <c r="CI51" t="n">
-        <v>50.26775651871148</v>
+        <v>50.26775664632899</v>
       </c>
       <c r="CJ51" t="n">
-        <v>48.49809238346509</v>
+        <v>48.49809258484015</v>
       </c>
       <c r="CK51" t="n">
-        <v>43.64828314511858</v>
+        <v>43.64828332635614</v>
       </c>
       <c r="CL51" t="n">
         <v>8</v>
@@ -29223,10 +29239,10 @@
         <v>3.1</v>
       </c>
       <c r="CO51" t="n">
-        <v>-0.9344489680883528</v>
+        <v>-0.9344485567457594</v>
       </c>
       <c r="CP51" t="n">
-        <v>14.08932127084221</v>
+        <v>14.08932156048703</v>
       </c>
       <c r="CQ51" t="inlineStr">
         <is>
@@ -29514,37 +29530,37 @@
         <v>10.65999984741211</v>
       </c>
       <c r="CA52" t="n">
-        <v>8.155913709013452</v>
+        <v>8.15591373521908</v>
       </c>
       <c r="CB52" t="n">
-        <v>11.52280744853984</v>
+        <v>11.52280745571912</v>
       </c>
       <c r="CC52" t="n">
-        <v>17.2121383365854</v>
+        <v>17.21213829200539</v>
       </c>
       <c r="CD52" t="n">
         <v>24.17460734763337</v>
       </c>
       <c r="CE52" t="n">
-        <v>24.61732006239898</v>
+        <v>24.61732007978904</v>
       </c>
       <c r="CF52" t="n">
-        <v>21.03193964603175</v>
+        <v>21.03193964112049</v>
       </c>
       <c r="CG52" t="n">
-        <v>8.546606043139425</v>
+        <v>8.546606017172792</v>
       </c>
       <c r="CH52" t="n">
         <v>9.746272614957581</v>
       </c>
       <c r="CI52" t="n">
-        <v>15.62595065103747</v>
+        <v>15.62595064795211</v>
       </c>
       <c r="CJ52" t="n">
-        <v>14.36747289256262</v>
+        <v>14.36747287386225</v>
       </c>
       <c r="CK52" t="n">
-        <v>12.93072560330636</v>
+        <v>12.93072558647603</v>
       </c>
       <c r="CL52" t="n">
         <v>8</v>
@@ -29556,10 +29572,10 @@
         <v>3</v>
       </c>
       <c r="CO52" t="n">
-        <v>21.3013676209902</v>
+        <v>21.30136746310718</v>
       </c>
       <c r="CP52" t="n">
-        <v>46.58490501602521</v>
+        <v>46.58490498708181</v>
       </c>
       <c r="CQ52" t="inlineStr">
         <is>
@@ -29833,10 +29849,10 @@
         <v>53.7400016784668</v>
       </c>
       <c r="CA53" t="n">
-        <v>10.50731956132986</v>
+        <v>10.50731955555406</v>
       </c>
       <c r="CB53" t="n">
-        <v>19.4910777862669</v>
+        <v>19.49107777555277</v>
       </c>
       <c r="CC53" t="n">
         <v>62.18821154931746</v>
@@ -29845,7 +29861,7 @@
         <v>46.54098234247379</v>
       </c>
       <c r="CE53" t="n">
-        <v>83.24912655332926</v>
+        <v>83.24912654626714</v>
       </c>
       <c r="CF53" t="n">
         <v>11.76833333333333</v>
@@ -29855,7 +29871,7 @@
       </c>
       <c r="CH53" t="inlineStr"/>
       <c r="CI53" t="n">
-        <v>13.92224356031003</v>
+        <v>13.92224355481339</v>
       </c>
       <c r="CJ53" t="n">
         <v>11.76833333333333</v>
@@ -29876,7 +29892,7 @@
         <v>-80.29121758616556</v>
       </c>
       <c r="CP53" t="n">
-        <v>-74.09333247957719</v>
+        <v>-74.09333248980541</v>
       </c>
       <c r="CQ53" t="inlineStr">
         <is>
@@ -30154,10 +30170,10 @@
         <v>29.46999931335449</v>
       </c>
       <c r="CA54" t="n">
-        <v>15.40499612269137</v>
+        <v>15.40499616374882</v>
       </c>
       <c r="CB54" t="n">
-        <v>28.57626780759248</v>
+        <v>28.57626788375406</v>
       </c>
       <c r="CC54" t="n">
         <v>53.78477836114972</v>
@@ -30166,23 +30182,23 @@
         <v>48.59041952862963</v>
       </c>
       <c r="CE54" t="n">
-        <v>59.55728564695277</v>
+        <v>59.55728563594013</v>
       </c>
       <c r="CF54" t="n">
-        <v>36.60763963409793</v>
+        <v>36.60763962652169</v>
       </c>
       <c r="CG54" t="n">
-        <v>29.60722468926014</v>
+        <v>29.60722463257128</v>
       </c>
       <c r="CH54" t="inlineStr"/>
       <c r="CI54" t="n">
-        <v>33.59342048138287</v>
+        <v>33.59342050879357</v>
       </c>
       <c r="CJ54" t="n">
-        <v>32.5919537208452</v>
+        <v>32.59195375513788</v>
       </c>
       <c r="CK54" t="n">
-        <v>29.33275834876068</v>
+        <v>29.33275837962409</v>
       </c>
       <c r="CL54" t="n">
         <v>4</v>
@@ -30194,10 +30210,10 @@
         <v>3.5</v>
       </c>
       <c r="CO54" t="n">
-        <v>-0.465697210015259</v>
+        <v>-0.4656971052870329</v>
       </c>
       <c r="CP54" t="n">
-        <v>13.99192827995699</v>
+        <v>13.99192837296921</v>
       </c>
       <c r="CQ54" t="inlineStr">
         <is>
@@ -30487,10 +30503,10 @@
         <v>10.39999961853027</v>
       </c>
       <c r="CA55" t="n">
-        <v>12.95070196961655</v>
+        <v>12.95070197609551</v>
       </c>
       <c r="CB55" t="n">
-        <v>18.8562220677617</v>
+        <v>18.85622207719506</v>
       </c>
       <c r="CC55" t="n">
         <v>16.51297649354425</v>
@@ -30509,7 +30525,7 @@
         <v>14.71449508364002</v>
       </c>
       <c r="CI55" t="n">
-        <v>16.02578527942405</v>
+        <v>16.0257852820761</v>
       </c>
       <c r="CJ55" t="n">
         <v>15.61373578859213</v>
@@ -30530,7 +30546,7 @@
         <v>35.11887235740878</v>
       </c>
       <c r="CP55" t="n">
-        <v>54.09409487736892</v>
+        <v>54.09409490286949</v>
       </c>
       <c r="CQ55" t="inlineStr">
         <is>
@@ -30818,10 +30834,10 @@
         <v>33.16999816894531</v>
       </c>
       <c r="CA56" t="n">
-        <v>11.72042512663754</v>
+        <v>11.7204251079301</v>
       </c>
       <c r="CB56" t="n">
-        <v>21.74138860991263</v>
+        <v>21.74138857521033</v>
       </c>
       <c r="CC56" t="n">
         <v>40.50714062106224</v>
@@ -30830,25 +30846,25 @@
         <v>33.04065851780371</v>
       </c>
       <c r="CE56" t="n">
-        <v>42.38658023072776</v>
+        <v>42.38658025700568</v>
       </c>
       <c r="CF56" t="n">
-        <v>23.85616542896008</v>
+        <v>23.85616543257217</v>
       </c>
       <c r="CG56" t="n">
-        <v>25.30396468957667</v>
+        <v>25.30396472126708</v>
       </c>
       <c r="CH56" t="n">
         <v>26.88952120736854</v>
       </c>
       <c r="CI56" t="n">
-        <v>28.18073055400615</v>
+        <v>28.18073055502748</v>
       </c>
       <c r="CJ56" t="n">
-        <v>26.0967429484726</v>
+        <v>26.09674296431781</v>
       </c>
       <c r="CK56" t="n">
-        <v>23.48706865362534</v>
+        <v>23.48706866788602</v>
       </c>
       <c r="CL56" t="n">
         <v>8</v>
@@ -30860,10 +30876,10 @@
         <v>3.6</v>
       </c>
       <c r="CO56" t="n">
-        <v>-29.19183011708877</v>
+        <v>-29.19183007409605</v>
       </c>
       <c r="CP56" t="n">
-        <v>-15.04150705564482</v>
+        <v>-15.04150705256573</v>
       </c>
       <c r="CQ56" t="inlineStr">
         <is>
@@ -31143,10 +31159,10 @@
         <v>24.18000030517578</v>
       </c>
       <c r="CA57" t="n">
-        <v>4.24014614487791</v>
+        <v>4.240146148338128</v>
       </c>
       <c r="CB57" t="n">
-        <v>7.865471098748522</v>
+        <v>7.865471105167228</v>
       </c>
       <c r="CC57" t="n">
         <v>28.58028582012302</v>
@@ -31155,13 +31171,13 @@
         <v>28.44859048200662</v>
       </c>
       <c r="CE57" t="n">
-        <v>25.50998700021137</v>
+        <v>25.50998699826909</v>
       </c>
       <c r="CF57" t="n">
-        <v>2.971261370124125</v>
+        <v>2.971261370045236</v>
       </c>
       <c r="CG57" t="n">
-        <v>18.46855616134489</v>
+        <v>18.46855615740771</v>
       </c>
       <c r="CH57" t="n">
         <v>17.91045698312367</v>
@@ -31470,10 +31486,10 @@
         <v>50.25</v>
       </c>
       <c r="CA58" t="n">
-        <v>8.363254055170597</v>
+        <v>8.363254033944109</v>
       </c>
       <c r="CB58" t="n">
-        <v>15.51383627234146</v>
+        <v>15.51383623296632</v>
       </c>
       <c r="CC58" t="n">
         <v>19.85129695885509</v>
@@ -31482,25 +31498,25 @@
         <v>12.34222338033302</v>
       </c>
       <c r="CE58" t="n">
-        <v>14.34603214029834</v>
+        <v>14.34603222997999</v>
       </c>
       <c r="CF58" t="n">
-        <v>20.65461072003468</v>
+        <v>20.65461073270204</v>
       </c>
       <c r="CG58" t="n">
-        <v>10.82557538690757</v>
+        <v>10.82557544884815</v>
       </c>
       <c r="CH58" t="n">
         <v>13.23570535215743</v>
       </c>
       <c r="CI58" t="n">
-        <v>14.39156678326227</v>
+        <v>14.39156679622327</v>
       </c>
       <c r="CJ58" t="n">
-        <v>13.79086874622788</v>
+        <v>13.79086879106871</v>
       </c>
       <c r="CK58" t="n">
-        <v>12.4117818716051</v>
+        <v>12.41178191196184</v>
       </c>
       <c r="CL58" t="n">
         <v>8</v>
@@ -31512,10 +31528,10 @@
         <v>2.5</v>
       </c>
       <c r="CO58" t="n">
-        <v>-75.29993657392021</v>
+        <v>-75.29993649360827</v>
       </c>
       <c r="CP58" t="n">
-        <v>-71.36006610296064</v>
+        <v>-71.36006607716763</v>
       </c>
       <c r="CQ58" t="inlineStr">
         <is>
@@ -31817,10 +31833,10 @@
         <v>4.760000228881836</v>
       </c>
       <c r="CA59" t="n">
-        <v>1.101256969808371</v>
+        <v>1.101256970356079</v>
       </c>
       <c r="CB59" t="n">
-        <v>2.042831678994529</v>
+        <v>2.042831680010527</v>
       </c>
       <c r="CC59" t="n">
         <v>9.302360329304472</v>
@@ -31829,13 +31845,13 @@
         <v>8.759319099989012</v>
       </c>
       <c r="CE59" t="n">
-        <v>10.22932956638733</v>
+        <v>10.22932956640491</v>
       </c>
       <c r="CF59" t="n">
-        <v>4.217909910016151</v>
+        <v>4.217909909956068</v>
       </c>
       <c r="CG59" t="n">
-        <v>6.876020534436607</v>
+        <v>6.876020533736769</v>
       </c>
       <c r="CH59" t="n">
         <v>6.539351670742607</v>
@@ -32136,37 +32152,37 @@
         <v>24.3700008392334</v>
       </c>
       <c r="CA60" t="n">
-        <v>10.76553939602004</v>
+        <v>10.76553943704861</v>
       </c>
       <c r="CB60" t="n">
-        <v>14.15877735088281</v>
+        <v>14.15877732897098</v>
       </c>
       <c r="CC60" t="n">
-        <v>17.23929063006058</v>
+        <v>17.23929053768072</v>
       </c>
       <c r="CD60" t="n">
         <v>21.14737695048065</v>
       </c>
       <c r="CE60" t="n">
-        <v>16.91392922779036</v>
+        <v>16.91392917356769</v>
       </c>
       <c r="CF60" t="n">
-        <v>23.1561610303848</v>
+        <v>23.1561610184468</v>
       </c>
       <c r="CG60" t="n">
-        <v>8.400134482971987</v>
+        <v>8.400134421701569</v>
       </c>
       <c r="CH60" t="n">
         <v>18.63306280322801</v>
       </c>
       <c r="CI60" t="n">
-        <v>16.3017839839774</v>
+        <v>16.30178395889063</v>
       </c>
       <c r="CJ60" t="n">
-        <v>17.07660992892547</v>
+        <v>17.07660985562421</v>
       </c>
       <c r="CK60" t="n">
-        <v>15.36894893603292</v>
+        <v>15.36894887006179</v>
       </c>
       <c r="CL60" t="n">
         <v>8</v>
@@ -32178,10 +32194,10 @@
         <v>2.8</v>
       </c>
       <c r="CO60" t="n">
-        <v>-36.93496755531347</v>
+        <v>-36.93496782601981</v>
       </c>
       <c r="CP60" t="n">
-        <v>-33.10716691591954</v>
+        <v>-33.10716701886076</v>
       </c>
       <c r="CQ60" t="inlineStr">
         <is>
@@ -32465,10 +32481,10 @@
         <v>4.409999847412109</v>
       </c>
       <c r="CA61" t="n">
-        <v>2.86414812572561</v>
+        <v>2.864148116970006</v>
       </c>
       <c r="CB61" t="n">
-        <v>5.312994773221006</v>
+        <v>5.31299475697936</v>
       </c>
       <c r="CC61" t="n">
         <v>13.62062889934975</v>
@@ -32477,13 +32493,13 @@
         <v>15.2256151851382</v>
       </c>
       <c r="CE61" t="n">
-        <v>15.7923404397296</v>
+        <v>15.7923404237576</v>
       </c>
       <c r="CF61" t="n">
-        <v>9.476368785079263</v>
+        <v>9.476368786172355</v>
       </c>
       <c r="CG61" t="n">
-        <v>6.797592099308851</v>
+        <v>6.797592107229521</v>
       </c>
       <c r="CH61" t="n">
         <v>1.534123064462555</v>
@@ -32784,37 +32800,37 @@
         <v>29.38999938964844</v>
       </c>
       <c r="CA62" t="n">
-        <v>13.71847501346808</v>
+        <v>13.71847505105665</v>
       </c>
       <c r="CB62" t="n">
-        <v>14.34620342721268</v>
+        <v>14.34620343503041</v>
       </c>
       <c r="CC62" t="n">
-        <v>15.16121923191696</v>
+        <v>15.16121919863713</v>
       </c>
       <c r="CD62" t="n">
         <v>30.32006495022776</v>
       </c>
       <c r="CE62" t="n">
-        <v>14.36027030069958</v>
+        <v>14.360270284155</v>
       </c>
       <c r="CF62" t="n">
-        <v>30.4690583856103</v>
+        <v>30.46905837771374</v>
       </c>
       <c r="CG62" t="n">
-        <v>6.111448985348889</v>
+        <v>6.11144895210556</v>
       </c>
       <c r="CH62" t="n">
         <v>37.5668789909021</v>
       </c>
       <c r="CI62" t="n">
-        <v>17.78382004206918</v>
+        <v>17.78382003556089</v>
       </c>
       <c r="CJ62" t="n">
-        <v>14.36027030069958</v>
+        <v>14.360270284155</v>
       </c>
       <c r="CK62" t="n">
-        <v>12.92424327062962</v>
+        <v>12.9242432557395</v>
       </c>
       <c r="CL62" t="n">
         <v>7</v>
@@ -32826,10 +32842,10 @@
         <v>6.1</v>
       </c>
       <c r="CO62" t="n">
-        <v>-56.02503048985528</v>
+        <v>-56.02503054051918</v>
       </c>
       <c r="CP62" t="n">
-        <v>-39.49023337396569</v>
+        <v>-39.49023339611026</v>
       </c>
       <c r="CQ62" t="inlineStr">
         <is>
@@ -32864,7 +32880,7 @@
         <v>-4.508006105756812</v>
       </c>
       <c r="DC62" t="n">
-        <v>-28.45091748718991</v>
+        <v>-28.45092417641193</v>
       </c>
       <c r="DD62" t="b">
         <v>0</v>
@@ -33121,35 +33137,35 @@
         <v>3.430000066757202</v>
       </c>
       <c r="CA63" t="n">
-        <v>2.632869213176799</v>
+        <v>2.63286921211784</v>
       </c>
       <c r="CB63" t="n">
-        <v>3.088140475013425</v>
+        <v>3.088140474659584</v>
       </c>
       <c r="CC63" t="n">
-        <v>3.82134293186334</v>
+        <v>3.82134293296246</v>
       </c>
       <c r="CD63" t="n">
         <v>6.992141669127824</v>
       </c>
       <c r="CE63" t="n">
-        <v>5.742640636391389</v>
+        <v>5.742640635844647</v>
       </c>
       <c r="CF63" t="n">
-        <v>8.486989515988732</v>
+        <v>8.486989516249031</v>
       </c>
       <c r="CG63" t="n">
-        <v>1.747126730501275</v>
+        <v>1.747126731396816</v>
       </c>
       <c r="CH63" t="inlineStr"/>
       <c r="CI63" t="n">
-        <v>4.644464453151826</v>
+        <v>4.64446445319403</v>
       </c>
       <c r="CJ63" t="n">
-        <v>3.82134293186334</v>
+        <v>3.82134293296246</v>
       </c>
       <c r="CK63" t="n">
-        <v>3.439208638677006</v>
+        <v>3.439208639666214</v>
       </c>
       <c r="CL63" t="n">
         <v>7</v>
@@ -33161,10 +33177,10 @@
         <v>4.9</v>
       </c>
       <c r="CO63" t="n">
-        <v>0.2684714793172116</v>
+        <v>0.2684715081570754</v>
       </c>
       <c r="CP63" t="n">
-        <v>35.4071242786536</v>
+        <v>35.40712427988404</v>
       </c>
       <c r="CQ63" t="inlineStr">
         <is>
@@ -33456,37 +33472,37 @@
         <v>18.73999977111816</v>
       </c>
       <c r="CA64" t="n">
-        <v>8.790659630785338</v>
+        <v>8.790659624614054</v>
       </c>
       <c r="CB64" t="n">
-        <v>9.149702328878035</v>
+        <v>9.149702329202841</v>
       </c>
       <c r="CC64" t="n">
-        <v>9.503707814315618</v>
+        <v>9.503707821324854</v>
       </c>
       <c r="CD64" t="n">
         <v>16.79875791329259</v>
       </c>
       <c r="CE64" t="n">
-        <v>9.01390751122927</v>
+        <v>9.013907516567556</v>
       </c>
       <c r="CF64" t="n">
-        <v>17.51877470625346</v>
+        <v>17.51877470778531</v>
       </c>
       <c r="CG64" t="n">
-        <v>3.803999732682379</v>
+        <v>3.803999739742328</v>
       </c>
       <c r="CH64" t="n">
         <v>16.19033501601518</v>
       </c>
       <c r="CI64" t="n">
-        <v>11.34623058168148</v>
+        <v>11.34623058356809</v>
       </c>
       <c r="CJ64" t="n">
-        <v>9.326705071596827</v>
+        <v>9.326705075263847</v>
       </c>
       <c r="CK64" t="n">
-        <v>8.394034564437144</v>
+        <v>8.394034567737462</v>
       </c>
       <c r="CL64" t="n">
         <v>8</v>
@@ -33498,10 +33514,10 @@
         <v>4.6</v>
       </c>
       <c r="CO64" t="n">
-        <v>-55.20792600342548</v>
+        <v>-55.20792598581438</v>
       </c>
       <c r="CP64" t="n">
-        <v>-39.45447854717617</v>
+        <v>-39.4544785371089</v>
       </c>
       <c r="CQ64" t="inlineStr">
         <is>
@@ -33797,10 +33813,10 @@
         <v>8.199999809265137</v>
       </c>
       <c r="CA65" t="n">
-        <v>0.4878659183183344</v>
+        <v>0.487865917150065</v>
       </c>
       <c r="CB65" t="n">
-        <v>0.9049912784805101</v>
+        <v>0.9049912763133706</v>
       </c>
       <c r="CC65" t="n">
         <v>9.48908274871293</v>
@@ -33809,13 +33825,13 @@
         <v>8.714204226367567</v>
       </c>
       <c r="CE65" t="n">
-        <v>10.45040643190669</v>
+        <v>10.45040643296595</v>
       </c>
       <c r="CF65" t="n">
-        <v>0.7360977972294792</v>
+        <v>0.7360977972519562</v>
       </c>
       <c r="CG65" t="n">
-        <v>8.107035956385623</v>
+        <v>8.107035957949327</v>
       </c>
       <c r="CH65" t="inlineStr"/>
       <c r="CI65" t="inlineStr"/>
@@ -34122,10 +34138,10 @@
         <v>35.31000137329102</v>
       </c>
       <c r="CA66" t="n">
-        <v>10.11005122874284</v>
+        <v>10.11005121931007</v>
       </c>
       <c r="CB66" t="n">
-        <v>18.75414502931797</v>
+        <v>18.75414501182017</v>
       </c>
       <c r="CC66" t="n">
         <v>28.42390754532843</v>
@@ -34134,25 +34150,25 @@
         <v>21.09476497433801</v>
       </c>
       <c r="CE66" t="n">
-        <v>25.57406594331166</v>
+        <v>25.57406596600552</v>
       </c>
       <c r="CF66" t="n">
-        <v>22.87188582534859</v>
+        <v>22.87188582838345</v>
       </c>
       <c r="CG66" t="n">
-        <v>16.40074658799155</v>
+        <v>16.40074660729931</v>
       </c>
       <c r="CH66" t="n">
         <v>26.23735511627599</v>
       </c>
       <c r="CI66" t="n">
-        <v>21.18336528133188</v>
+        <v>21.18336528359512</v>
       </c>
       <c r="CJ66" t="n">
-        <v>21.9833253998433</v>
+        <v>21.98332540136073</v>
       </c>
       <c r="CK66" t="n">
-        <v>19.78499285985897</v>
+        <v>19.78499286122466</v>
       </c>
       <c r="CL66" t="n">
         <v>8</v>
@@ -34164,10 +34180,10 @@
         <v>2.8</v>
       </c>
       <c r="CO66" t="n">
-        <v>-43.96773692899198</v>
+        <v>-43.96773692512427</v>
       </c>
       <c r="CP66" t="n">
-        <v>-40.00746401172537</v>
+        <v>-40.00746400531574</v>
       </c>
       <c r="CQ66" t="inlineStr">
         <is>
@@ -34202,7 +34218,7 @@
         <v>-2.107009503640933</v>
       </c>
       <c r="DC66" t="n">
-        <v>-21.44953582303043</v>
+        <v>-21.44954253181865</v>
       </c>
       <c r="DD66" t="b">
         <v>0</v>
@@ -34754,10 +34770,10 @@
         <v>12.86999988555908</v>
       </c>
       <c r="CA68" t="n">
-        <v>10.88409500833714</v>
+        <v>10.88409499145743</v>
       </c>
       <c r="CB68" t="n">
-        <v>15.84724233213888</v>
+        <v>15.84724230756201</v>
       </c>
       <c r="CC68" t="n">
         <v>15.47375708783982</v>
@@ -34774,13 +34790,13 @@
       </c>
       <c r="CH68" t="inlineStr"/>
       <c r="CI68" t="n">
-        <v>12.3846069404123</v>
+        <v>12.38460693004815</v>
       </c>
       <c r="CJ68" t="n">
-        <v>13.17892604808848</v>
+        <v>13.17892603964862</v>
       </c>
       <c r="CK68" t="n">
-        <v>11.86103344327963</v>
+        <v>11.86103343568376</v>
       </c>
       <c r="CL68" t="n">
         <v>4</v>
@@ -34792,10 +34808,10 @@
         <v>2.2</v>
       </c>
       <c r="CO68" t="n">
-        <v>-7.83967716589935</v>
+        <v>-7.839677224919351</v>
       </c>
       <c r="CP68" t="n">
-        <v>-3.771506988833984</v>
+        <v>-3.771507069363489</v>
       </c>
       <c r="CQ68" t="inlineStr">
         <is>
@@ -35079,10 +35095,10 @@
         <v>8.329999923706055</v>
       </c>
       <c r="CA69" t="n">
-        <v>1.605082990780117</v>
+        <v>1.605082990736824</v>
       </c>
       <c r="CB69" t="n">
-        <v>2.977428947897116</v>
+        <v>2.977428947816807</v>
       </c>
       <c r="CC69" t="n">
         <v>24.04629607605778</v>
@@ -35091,13 +35107,13 @@
         <v>23.80972001921325</v>
       </c>
       <c r="CE69" t="n">
-        <v>25.67832652337463</v>
+        <v>25.6783265233218</v>
       </c>
       <c r="CF69" t="n">
-        <v>6.709160235361832</v>
+        <v>6.709160235364461</v>
       </c>
       <c r="CG69" t="n">
-        <v>17.91152719599509</v>
+        <v>17.91152719604488</v>
       </c>
       <c r="CH69" t="n">
         <v>14.80472650453005</v>
@@ -35406,10 +35422,10 @@
         <v>21.25</v>
       </c>
       <c r="CA70" t="n">
-        <v>5.876635896280653</v>
+        <v>5.876635879395255</v>
       </c>
       <c r="CB70" t="n">
-        <v>10.90115958760061</v>
+        <v>10.9011595562782</v>
       </c>
       <c r="CC70" t="n">
         <v>32.70180023228804</v>
@@ -35418,25 +35434,25 @@
         <v>33.68464293302805</v>
       </c>
       <c r="CE70" t="n">
-        <v>29.46401509227307</v>
+        <v>29.464015093421</v>
       </c>
       <c r="CF70" t="n">
-        <v>25.30918137056408</v>
+        <v>25.30918137327836</v>
       </c>
       <c r="CG70" t="n">
-        <v>19.10716735597785</v>
+        <v>19.10716737395742</v>
       </c>
       <c r="CH70" t="n">
         <v>13.22580990542387</v>
       </c>
       <c r="CI70" t="n">
-        <v>23.48482521102223</v>
+        <v>23.48482520966784</v>
       </c>
       <c r="CJ70" t="n">
-        <v>25.30918137056408</v>
+        <v>25.30918137327836</v>
       </c>
       <c r="CK70" t="n">
-        <v>22.77826323350767</v>
+        <v>22.77826323595053</v>
       </c>
       <c r="CL70" t="n">
         <v>7</v>
@@ -35448,10 +35464,10 @@
         <v>5.7</v>
       </c>
       <c r="CO70" t="n">
-        <v>7.191826981212568</v>
+        <v>7.191826992708372</v>
       </c>
       <c r="CP70" t="n">
-        <v>10.51682452245755</v>
+        <v>10.51682451608396</v>
       </c>
       <c r="CQ70" t="inlineStr">
         <is>
@@ -35735,25 +35751,25 @@
         <v>17.14999961853027</v>
       </c>
       <c r="CA71" t="n">
-        <v>3.991825577807206</v>
+        <v>3.991825600901917</v>
       </c>
       <c r="CB71" t="n">
-        <v>6.867699843803461</v>
+        <v>6.867699872374448</v>
       </c>
       <c r="CC71" t="n">
-        <v>23.57427305191861</v>
+        <v>23.57427301360325</v>
       </c>
       <c r="CD71" t="n">
         <v>32.99378636564864</v>
       </c>
       <c r="CE71" t="n">
-        <v>16.6512710445418</v>
+        <v>16.65127105597358</v>
       </c>
       <c r="CF71" t="n">
-        <v>20.3023163772502</v>
+        <v>20.30231637476711</v>
       </c>
       <c r="CG71" t="n">
-        <v>11.66191970408579</v>
+        <v>11.66191968853843</v>
       </c>
       <c r="CH71" t="n">
         <v>22.29340682675621</v>
@@ -36054,10 +36070,10 @@
         <v>3.970000028610229</v>
       </c>
       <c r="CA72" t="n">
-        <v>0.9630390070159548</v>
+        <v>0.9630390056418175</v>
       </c>
       <c r="CB72" t="n">
-        <v>1.786437358014596</v>
+        <v>1.786437355465571</v>
       </c>
       <c r="CC72" t="n">
         <v>6.217789642917912</v>
@@ -36066,7 +36082,7 @@
         <v>4.127898727162465</v>
       </c>
       <c r="CE72" t="n">
-        <v>8.632688714819954</v>
+        <v>8.632688712545967</v>
       </c>
       <c r="CF72" t="n">
         <v>3.760485277130923</v>
@@ -36124,7 +36140,7 @@
         <v>-3.17072875722394</v>
       </c>
       <c r="DC72" t="n">
-        <v>-45.72659463574499</v>
+        <v>-45.72659102148787</v>
       </c>
       <c r="DD72" t="b">
         <v>0</v>
@@ -36373,35 +36389,35 @@
         <v>24.02000045776367</v>
       </c>
       <c r="CA73" t="n">
-        <v>23.07830346616155</v>
+        <v>23.07830345135993</v>
       </c>
       <c r="CB73" t="n">
-        <v>28.90113962702012</v>
+        <v>28.90113962303369</v>
       </c>
       <c r="CC73" t="n">
-        <v>37.96117380415502</v>
+        <v>37.96117382326587</v>
       </c>
       <c r="CD73" t="n">
         <v>61.82732111992195</v>
       </c>
       <c r="CE73" t="n">
-        <v>67.85077927499576</v>
+        <v>67.85077926041174</v>
       </c>
       <c r="CF73" t="n">
-        <v>41.68738826047305</v>
+        <v>41.68738826258333</v>
       </c>
       <c r="CG73" t="n">
-        <v>18.10465224909449</v>
+        <v>18.1046522629405</v>
       </c>
       <c r="CH73" t="inlineStr"/>
       <c r="CI73" t="n">
-        <v>39.91582254311742</v>
+        <v>39.91582254335958</v>
       </c>
       <c r="CJ73" t="n">
-        <v>37.96117380415502</v>
+        <v>37.96117382326587</v>
       </c>
       <c r="CK73" t="n">
-        <v>34.16505642373952</v>
+        <v>34.16505644093928</v>
       </c>
       <c r="CL73" t="n">
         <v>7</v>
@@ -36413,10 +36429,10 @@
         <v>3.7</v>
       </c>
       <c r="CO73" t="n">
-        <v>42.23586916167936</v>
+        <v>42.23586923328535</v>
       </c>
       <c r="CP73" t="n">
-        <v>66.17744289099691</v>
+        <v>66.17744289200506</v>
       </c>
       <c r="CQ73" t="inlineStr">
         <is>
@@ -36704,10 +36720,10 @@
         <v>25.07999992370605</v>
       </c>
       <c r="CA74" t="n">
-        <v>4.600671617619905</v>
+        <v>4.600671625068194</v>
       </c>
       <c r="CB74" t="n">
-        <v>8.534245850684922</v>
+        <v>8.534245864501498</v>
       </c>
       <c r="CC74" t="n">
         <v>30.04611202433139</v>
@@ -36716,19 +36732,19 @@
         <v>25.48637760632342</v>
       </c>
       <c r="CE74" t="n">
-        <v>34.72259479983572</v>
+        <v>34.7225947907028</v>
       </c>
       <c r="CF74" t="n">
-        <v>11.77818656856278</v>
+        <v>11.77818656770768</v>
       </c>
       <c r="CG74" t="n">
-        <v>24.22287497115891</v>
+        <v>24.2228749594919</v>
       </c>
       <c r="CH74" t="n">
         <v>25.07999992370605</v>
       </c>
       <c r="CI74" t="n">
-        <v>25.22269098231972</v>
+        <v>25.22269097871054</v>
       </c>
       <c r="CJ74" t="n">
         <v>25.28318876501474</v>
@@ -36749,7 +36765,7 @@
         <v>-9.270853438061765</v>
       </c>
       <c r="CP74" t="n">
-        <v>0.5689436166177453</v>
+        <v>0.5689436022271011</v>
       </c>
       <c r="CQ74" t="inlineStr">
         <is>
@@ -37041,10 +37057,10 @@
         <v>12.42000007629395</v>
       </c>
       <c r="CA75" t="n">
-        <v>2.054914844356821</v>
+        <v>2.054914840369594</v>
       </c>
       <c r="CB75" t="n">
-        <v>3.811867036281902</v>
+        <v>3.811867028885596</v>
       </c>
       <c r="CC75" t="n">
         <v>15.91537727378093</v>
@@ -37053,7 +37069,7 @@
         <v>12.64279048217724</v>
       </c>
       <c r="CE75" t="n">
-        <v>20.79969138930413</v>
+        <v>20.79969138390556</v>
       </c>
       <c r="CF75" t="n">
         <v>9.294207014285712</v>
@@ -37358,10 +37374,10 @@
         <v>55.20000076293945</v>
       </c>
       <c r="CA76" t="n">
-        <v>40.14457042915611</v>
+        <v>40.14457043391327</v>
       </c>
       <c r="CB76" t="n">
-        <v>58.4504945448513</v>
+        <v>58.45049455177772</v>
       </c>
       <c r="CC76" t="n">
         <v>35.6793044086122</v>
@@ -37380,13 +37396,13 @@
         <v>48.81663041531538</v>
       </c>
       <c r="CI76" t="n">
-        <v>43.24561936197106</v>
+        <v>43.24561936391832</v>
       </c>
       <c r="CJ76" t="n">
-        <v>41.36290939679628</v>
+        <v>41.36290939917485</v>
       </c>
       <c r="CK76" t="n">
-        <v>37.22661845711666</v>
+        <v>37.22661845925737</v>
       </c>
       <c r="CL76" t="n">
         <v>6</v>
@@ -37398,10 +37414,10 @@
         <v>6.4</v>
       </c>
       <c r="CO76" t="n">
-        <v>-32.56047474167769</v>
+        <v>-32.56047473779959</v>
       </c>
       <c r="CP76" t="n">
-        <v>-21.65648774591034</v>
+        <v>-21.6564877423827</v>
       </c>
       <c r="CQ76" t="inlineStr">
         <is>
@@ -37685,10 +37701,10 @@
         <v>28.85000038146973</v>
       </c>
       <c r="CA77" t="n">
-        <v>13.47826689531939</v>
+        <v>13.47826690192063</v>
       </c>
       <c r="CB77" t="n">
-        <v>25.00218509081748</v>
+        <v>25.00218510306276</v>
       </c>
       <c r="CC77" t="n">
         <v>37.07686760955129</v>
@@ -37697,19 +37713,19 @@
         <v>25.84183193227743</v>
       </c>
       <c r="CE77" t="n">
-        <v>42.33310174373844</v>
+        <v>42.33310172833185</v>
       </c>
       <c r="CF77" t="n">
-        <v>42.16403727257172</v>
+        <v>42.16403726919</v>
       </c>
       <c r="CG77" t="n">
-        <v>22.58047102514563</v>
+        <v>22.58047100982707</v>
       </c>
       <c r="CH77" t="n">
         <v>25.39446734308974</v>
       </c>
       <c r="CI77" t="n">
-        <v>29.23390361406389</v>
+        <v>29.23390361215635</v>
       </c>
       <c r="CJ77" t="n">
         <v>25.61814963768359</v>
@@ -37730,7 +37746,7 @@
         <v>-20.08202991662958</v>
       </c>
       <c r="CP77" t="n">
-        <v>1.330687097116101</v>
+        <v>1.330687090504168</v>
       </c>
       <c r="CQ77" t="inlineStr">
         <is>
@@ -38022,10 +38038,10 @@
         <v>15.07999992370605</v>
       </c>
       <c r="CA78" t="n">
-        <v>2.433443111108075</v>
+        <v>2.433443121610054</v>
       </c>
       <c r="CB78" t="n">
-        <v>4.514036971105479</v>
+        <v>4.514036990586651</v>
       </c>
       <c r="CC78" t="n">
         <v>25.45350305593697</v>
@@ -38034,7 +38050,7 @@
         <v>19.52359161971606</v>
       </c>
       <c r="CE78" t="n">
-        <v>33.15518502052279</v>
+        <v>33.15518503925243</v>
       </c>
       <c r="CF78" t="n">
         <v>10.38593205872702</v>
@@ -38341,10 +38357,10 @@
         <v>14.56999969482422</v>
       </c>
       <c r="CA79" t="n">
-        <v>9.522149334652612</v>
+        <v>9.522149288026398</v>
       </c>
       <c r="CB79" t="n">
-        <v>17.66358701578059</v>
+        <v>17.66358692928896</v>
       </c>
       <c r="CC79" t="n">
         <v>13.81907630325131</v>
@@ -38365,7 +38381,7 @@
         <v>12.2203515982404</v>
       </c>
       <c r="CI79" t="n">
-        <v>14.92972000136729</v>
+        <v>14.92971998472756</v>
       </c>
       <c r="CJ79" t="n">
         <v>13.18184499442705</v>
@@ -38386,7 +38402,7 @@
         <v>-18.57473751904922</v>
       </c>
       <c r="CP79" t="n">
-        <v>2.468910872186614</v>
+        <v>2.468910757981191</v>
       </c>
       <c r="CQ79" t="inlineStr">
         <is>
@@ -38670,25 +38686,25 @@
         <v>26.20999908447266</v>
       </c>
       <c r="CA80" t="n">
-        <v>11.9385459919552</v>
+        <v>11.93854600326578</v>
       </c>
       <c r="CB80" t="n">
-        <v>12.61580797102097</v>
+        <v>12.61580797626808</v>
       </c>
       <c r="CC80" t="n">
-        <v>13.88314113748146</v>
+        <v>13.88314113010279</v>
       </c>
       <c r="CD80" t="n">
         <v>32.29491627828039</v>
       </c>
       <c r="CE80" t="n">
-        <v>12.94974348458021</v>
+        <v>12.94974348418045</v>
       </c>
       <c r="CF80" t="n">
-        <v>24.67209426857107</v>
+        <v>24.67209426703706</v>
       </c>
       <c r="CG80" t="n">
-        <v>5.680816704344635</v>
+        <v>5.680816697108577</v>
       </c>
       <c r="CH80" t="n">
         <v>61.56724104958222</v>
@@ -38989,10 +39005,10 @@
         <v>6.960000038146973</v>
       </c>
       <c r="CA81" t="n">
-        <v>1.254324383550125</v>
+        <v>1.254324383766995</v>
       </c>
       <c r="CB81" t="n">
-        <v>2.326771731485482</v>
+        <v>2.326771731887776</v>
       </c>
       <c r="CC81" t="n">
         <v>10.46765045464783</v>
@@ -39001,13 +39017,13 @@
         <v>10.28299479481327</v>
       </c>
       <c r="CE81" t="n">
-        <v>10.15256190818006</v>
+        <v>10.15256190812148</v>
       </c>
       <c r="CF81" t="n">
-        <v>1.873720564864715</v>
+        <v>1.873720564856047</v>
       </c>
       <c r="CG81" t="n">
-        <v>7.239168615134628</v>
+        <v>7.239168614881185</v>
       </c>
       <c r="CH81" t="n">
         <v>11.45586349250206</v>
@@ -39308,10 +39324,10 @@
         <v>10.44999980926514</v>
       </c>
       <c r="CA82" t="n">
-        <v>6.405398367019009</v>
+        <v>6.405398458580922</v>
       </c>
       <c r="CB82" t="n">
-        <v>11.88201397082026</v>
+        <v>11.88201414066761</v>
       </c>
       <c r="CC82" t="n">
         <v>7.980547404770202</v>
@@ -39332,7 +39348,7 @@
         <v>39.67377387971943</v>
       </c>
       <c r="CI82" t="n">
-        <v>10.25156151065322</v>
+        <v>10.2515615479974</v>
       </c>
       <c r="CJ82" t="n">
         <v>7.980547404770202</v>
@@ -39353,7 +39369,7 @@
         <v>-31.26801152737755</v>
       </c>
       <c r="CP82" t="n">
-        <v>-1.898931121854952</v>
+        <v>-1.898930764494355</v>
       </c>
       <c r="CQ82" t="inlineStr">
         <is>
@@ -39637,35 +39653,35 @@
         <v>2.779999971389771</v>
       </c>
       <c r="CA83" t="n">
-        <v>1.278437324952654</v>
+        <v>1.278437328213088</v>
       </c>
       <c r="CB83" t="n">
-        <v>1.746572821362998</v>
+        <v>1.746572824447232</v>
       </c>
       <c r="CC83" t="n">
-        <v>3.757394663757759</v>
+        <v>3.75739466081027</v>
       </c>
       <c r="CD83" t="n">
         <v>7.235833015165504</v>
       </c>
       <c r="CE83" t="n">
-        <v>3.789507988601228</v>
+        <v>3.789507992020309</v>
       </c>
       <c r="CF83" t="n">
-        <v>1.340404108818218</v>
+        <v>1.340404108720483</v>
       </c>
       <c r="CG83" t="n">
-        <v>1.852381282742166</v>
+        <v>1.852381280917366</v>
       </c>
       <c r="CH83" t="inlineStr"/>
       <c r="CI83" t="n">
-        <v>2.29411636503917</v>
+        <v>2.294116365854791</v>
       </c>
       <c r="CJ83" t="n">
-        <v>1.799477052052582</v>
+        <v>1.799477052682299</v>
       </c>
       <c r="CK83" t="n">
-        <v>1.619529346847324</v>
+        <v>1.619529347414069</v>
       </c>
       <c r="CL83" t="n">
         <v>6</v>
@@ -39677,10 +39693,10 @@
         <v>5.7</v>
       </c>
       <c r="CO83" t="n">
-        <v>-41.74354807501337</v>
+        <v>-41.74354805462686</v>
       </c>
       <c r="CP83" t="n">
-        <v>-17.47782774644053</v>
+        <v>-17.47782771710166</v>
       </c>
       <c r="CQ83" t="inlineStr">
         <is>
@@ -39962,10 +39978,10 @@
         <v>5.269999980926514</v>
       </c>
       <c r="CA84" t="n">
-        <v>3.116563119576812</v>
+        <v>3.116563121222506</v>
       </c>
       <c r="CB84" t="n">
-        <v>4.537715902103838</v>
+        <v>4.53771590449997</v>
       </c>
       <c r="CC84" t="n">
         <v>4.409332244701186</v>
@@ -40287,10 +40303,10 @@
         <v>18.8700008392334</v>
       </c>
       <c r="CA85" t="n">
-        <v>4.583569634785647</v>
+        <v>4.583569625721722</v>
       </c>
       <c r="CB85" t="n">
-        <v>8.502521672527374</v>
+        <v>8.502521655713794</v>
       </c>
       <c r="CC85" t="n">
         <v>32.85512629695696</v>
@@ -40299,13 +40315,13 @@
         <v>35.40227792012859</v>
       </c>
       <c r="CE85" t="n">
-        <v>28.64957925632845</v>
+        <v>28.64957925361213</v>
       </c>
       <c r="CF85" t="n">
-        <v>11.13129413262653</v>
+        <v>11.1312941332059</v>
       </c>
       <c r="CG85" t="n">
-        <v>19.33215014097561</v>
+        <v>19.33215014974948</v>
       </c>
       <c r="CH85" t="n">
         <v>44.34329506457097</v>
@@ -40433,8 +40449,16 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Bandeira de alta</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Bandeira de alta (pré-confirmação) — pescoço R$62.96, preço 3.0% abaixo do pescoço; falta fechar acima e segurar</t>
+        </is>
+      </c>
       <c r="U86" t="b">
         <v>0</v>
       </c>
@@ -40931,25 +40955,25 @@
         <v>1.559999942779541</v>
       </c>
       <c r="CA87" t="n">
-        <v>0.139120419420455</v>
+        <v>0.1391204195244934</v>
       </c>
       <c r="CB87" t="n">
-        <v>0.1588600557035727</v>
+        <v>0.1588600558179771</v>
       </c>
       <c r="CC87" t="n">
-        <v>0.7587301048694177</v>
+        <v>0.7587301048484227</v>
       </c>
       <c r="CD87" t="n">
         <v>3.145519198624604</v>
       </c>
       <c r="CE87" t="n">
-        <v>0.2602920092505782</v>
+        <v>0.2602920093088837</v>
       </c>
       <c r="CF87" t="n">
-        <v>0.5416071244229079</v>
+        <v>0.5416071244212713</v>
       </c>
       <c r="CG87" t="n">
-        <v>0.339114131291073</v>
+        <v>0.3391141312731284</v>
       </c>
       <c r="CH87" t="inlineStr"/>
       <c r="CI87" t="inlineStr"/>
@@ -41248,10 +41272,10 @@
         <v>23.96999931335449</v>
       </c>
       <c r="CA88" t="n">
-        <v>12.07935616962814</v>
+        <v>12.07935631205035</v>
       </c>
       <c r="CB88" t="n">
-        <v>22.4072056946602</v>
+        <v>22.40720595885339</v>
       </c>
       <c r="CC88" t="n">
         <v>15.09517542309634</v>
@@ -41272,13 +41296,13 @@
         <v>23.16277622804454</v>
       </c>
       <c r="CI88" t="n">
-        <v>19.87730235966485</v>
+        <v>19.87730241049178</v>
       </c>
       <c r="CJ88" t="n">
-        <v>18.75119055887827</v>
+        <v>18.75119069097487</v>
       </c>
       <c r="CK88" t="n">
-        <v>16.87607150299045</v>
+        <v>16.87607162187738</v>
       </c>
       <c r="CL88" t="n">
         <v>8</v>
@@ -41290,10 +41314,10 @@
         <v>2.9</v>
       </c>
       <c r="CO88" t="n">
-        <v>-29.59502717387139</v>
+        <v>-29.59502667788917</v>
       </c>
       <c r="CP88" t="n">
-        <v>-17.07424727129408</v>
+        <v>-17.07424705925016</v>
       </c>
       <c r="CQ88" t="inlineStr">
         <is>
@@ -41575,10 +41599,10 @@
         <v>14.03999996185303</v>
       </c>
       <c r="CA89" t="n">
-        <v>6.060896418544134</v>
+        <v>6.060896413507834</v>
       </c>
       <c r="CB89" t="n">
-        <v>8.82466518540026</v>
+        <v>8.824665178067406</v>
       </c>
       <c r="CC89" t="n">
         <v>3.751695776034725</v>
@@ -41892,10 +41916,10 @@
         <v>7.210000038146973</v>
       </c>
       <c r="CA90" t="n">
-        <v>3.000514726708099</v>
+        <v>3.000514730608235</v>
       </c>
       <c r="CB90" t="n">
-        <v>5.565954818043524</v>
+        <v>5.565954825278276</v>
       </c>
       <c r="CC90" t="n">
         <v>14.71995385291947</v>
@@ -41904,17 +41928,17 @@
         <v>15.82114567812849</v>
       </c>
       <c r="CE90" t="n">
-        <v>14.12742075417105</v>
+        <v>14.1274207565344</v>
       </c>
       <c r="CF90" t="n">
-        <v>15.00312295174442</v>
+        <v>15.00312295098005</v>
       </c>
       <c r="CG90" t="n">
-        <v>7.779395126661632</v>
+        <v>7.779395122858846</v>
       </c>
       <c r="CH90" t="inlineStr"/>
       <c r="CI90" t="n">
-        <v>13.49020767272501</v>
+        <v>13.49020767228425</v>
       </c>
       <c r="CJ90" t="n">
         <v>14.71995385291947</v>
@@ -41935,7 +41959,7 @@
         <v>83.74422187981506</v>
       </c>
       <c r="CP90" t="n">
-        <v>87.10412761928504</v>
+        <v>87.10412761317185</v>
       </c>
       <c r="CQ90" t="inlineStr">
         <is>
@@ -42203,10 +42227,10 @@
         <v>55.22999954223633</v>
       </c>
       <c r="CA91" t="n">
-        <v>11.59547547337404</v>
+        <v>11.59547551352601</v>
       </c>
       <c r="CB91" t="n">
-        <v>16.88301228923261</v>
+        <v>16.88301234769387</v>
       </c>
       <c r="CC91" t="inlineStr"/>
       <c r="CD91" t="inlineStr"/>
@@ -42217,13 +42241,13 @@
       <c r="CG91" t="inlineStr"/>
       <c r="CH91" t="inlineStr"/>
       <c r="CI91" t="n">
-        <v>18.26872925420222</v>
+        <v>18.2687292870733</v>
       </c>
       <c r="CJ91" t="n">
-        <v>16.88301228923261</v>
+        <v>16.88301234769387</v>
       </c>
       <c r="CK91" t="n">
-        <v>15.19471106030935</v>
+        <v>15.19471111292448</v>
       </c>
       <c r="CL91" t="n">
         <v>3</v>
@@ -42235,10 +42259,10 @@
         <v>2.3</v>
       </c>
       <c r="CO91" t="n">
-        <v>-72.4883013104329</v>
+        <v>-72.48830121516741</v>
       </c>
       <c r="CP91" t="n">
-        <v>-66.92245264236971</v>
+        <v>-66.92245258285298</v>
       </c>
       <c r="CQ91" t="inlineStr">
         <is>
@@ -42285,7 +42309,7 @@
         <v>3.426962479524587</v>
       </c>
       <c r="DC91" t="n">
-        <v>-14.66839399830475</v>
+        <v>-14.66838871705677</v>
       </c>
       <c r="DD91" t="b">
         <v>0</v>
@@ -42536,10 +42560,10 @@
         <v>3.660000085830688</v>
       </c>
       <c r="CA92" t="n">
-        <v>33.40407224899656</v>
+        <v>33.40407224850232</v>
       </c>
       <c r="CB92" t="n">
-        <v>61.9645540218886</v>
+        <v>61.9645540209718</v>
       </c>
       <c r="CC92" t="n">
         <v>4.712828098858758</v>
@@ -42853,10 +42877,10 @@
         <v>7.739999771118164</v>
       </c>
       <c r="CA93" t="n">
-        <v>4.982339140019103</v>
+        <v>4.982339186553481</v>
       </c>
       <c r="CB93" t="n">
-        <v>7.254285787867816</v>
+        <v>7.254285855621869</v>
       </c>
       <c r="CC93" t="n">
         <v>5.854254372336648</v>
@@ -42875,13 +42899,13 @@
         <v>7.739999771118164</v>
       </c>
       <c r="CI93" t="n">
-        <v>6.606025187387023</v>
+        <v>6.606025206435095</v>
       </c>
       <c r="CJ93" t="n">
-        <v>6.554270080102231</v>
+        <v>6.554270113979259</v>
       </c>
       <c r="CK93" t="n">
-        <v>5.898843072092008</v>
+        <v>5.898843102581333</v>
       </c>
       <c r="CL93" t="n">
         <v>6</v>
@@ -42893,10 +42917,10 @@
         <v>5.9</v>
       </c>
       <c r="CO93" t="n">
-        <v>-23.78755495441277</v>
+        <v>-23.78755456049383</v>
       </c>
       <c r="CP93" t="n">
-        <v>-14.6508348483752</v>
+        <v>-14.65083460227607</v>
       </c>
       <c r="CQ93" t="inlineStr">
         <is>
@@ -43180,10 +43204,10 @@
         <v>35.06000137329102</v>
       </c>
       <c r="CA94" t="n">
-        <v>8.680155238892739</v>
+        <v>8.680155227013746</v>
       </c>
       <c r="CB94" t="n">
-        <v>16.10168796814603</v>
+        <v>16.1016879461105</v>
       </c>
       <c r="CC94" t="n">
         <v>40.64260876606351</v>
@@ -43192,19 +43216,19 @@
         <v>40.99197343130513</v>
       </c>
       <c r="CE94" t="n">
-        <v>34.02445210406701</v>
+        <v>34.02445211052151</v>
       </c>
       <c r="CF94" t="n">
-        <v>50.06592930352212</v>
+        <v>50.06592930670755</v>
       </c>
       <c r="CG94" t="n">
-        <v>22.89816533161465</v>
+        <v>22.89816534481743</v>
       </c>
       <c r="CH94" t="n">
         <v>54.19026455668205</v>
       </c>
       <c r="CI94" t="n">
-        <v>36.98786878020007</v>
+        <v>36.98786878031539</v>
       </c>
       <c r="CJ94" t="n">
         <v>40.64260876606351</v>
@@ -43225,7 +43249,7 @@
         <v>4.330708661417315</v>
       </c>
       <c r="CP94" t="n">
-        <v>5.498765919552207</v>
+        <v>5.498765919881099</v>
       </c>
       <c r="CQ94" t="inlineStr">
         <is>
@@ -43507,10 +43531,10 @@
         <v>79.11000061035156</v>
       </c>
       <c r="CA95" t="n">
-        <v>59.14580343791874</v>
+        <v>59.14580340378554</v>
       </c>
       <c r="CB95" t="n">
-        <v>86.1162898056097</v>
+        <v>86.11628975591175</v>
       </c>
       <c r="CC95" t="n">
         <v>24.45731291164257</v>
@@ -43814,35 +43838,35 @@
         <v>19.96999931335449</v>
       </c>
       <c r="CA96" t="n">
-        <v>11.90594416734853</v>
+        <v>11.90594412154626</v>
       </c>
       <c r="CB96" t="n">
-        <v>15.10171756326644</v>
+        <v>15.1017175354657</v>
       </c>
       <c r="CC96" t="n">
-        <v>22.67303325472404</v>
+        <v>22.67303330020862</v>
       </c>
       <c r="CD96" t="n">
         <v>41.91581127865282</v>
       </c>
       <c r="CE96" t="n">
-        <v>27.56465657578011</v>
+        <v>27.56465654665966</v>
       </c>
       <c r="CF96" t="n">
-        <v>15.76132613263354</v>
+        <v>15.76132613577654</v>
       </c>
       <c r="CG96" t="n">
-        <v>10.88226008127193</v>
+        <v>10.88226011347643</v>
       </c>
       <c r="CH96" t="inlineStr"/>
       <c r="CI96" t="n">
-        <v>16.36050527949314</v>
+        <v>16.36050527324928</v>
       </c>
       <c r="CJ96" t="n">
-        <v>15.43152184794999</v>
+        <v>15.43152183562112</v>
       </c>
       <c r="CK96" t="n">
-        <v>13.88836966315499</v>
+        <v>13.888369652059</v>
       </c>
       <c r="CL96" t="n">
         <v>4</v>
@@ -43854,10 +43878,10 @@
         <v>1.9</v>
       </c>
       <c r="CO96" t="n">
-        <v>-30.45383004160919</v>
+        <v>-30.45383009717247</v>
       </c>
       <c r="CP96" t="n">
-        <v>-18.07458266384408</v>
+        <v>-18.07458269511028</v>
       </c>
       <c r="CQ96" t="inlineStr">
         <is>
@@ -44153,10 +44177,10 @@
         <v>19.39999961853027</v>
       </c>
       <c r="CA97" t="n">
-        <v>2.002220649267907</v>
+        <v>2.002220649826353</v>
       </c>
       <c r="CB97" t="n">
-        <v>3.714119304391967</v>
+        <v>3.714119305427885</v>
       </c>
       <c r="CC97" t="n">
         <v>10.17214067849332</v>
@@ -44165,19 +44189,19 @@
         <v>8.489143658487551</v>
       </c>
       <c r="CE97" t="n">
-        <v>10.08225774380416</v>
+        <v>10.08225774267421</v>
       </c>
       <c r="CF97" t="n">
-        <v>7.542853166483961</v>
+        <v>7.542853166357342</v>
       </c>
       <c r="CG97" t="n">
-        <v>7.691046836393862</v>
+        <v>7.691046835489135</v>
       </c>
       <c r="CH97" t="n">
         <v>13.63549921457183</v>
       </c>
       <c r="CI97" t="n">
-        <v>8.761008657518092</v>
+        <v>8.761008657357323</v>
       </c>
       <c r="CJ97" t="n">
         <v>8.489143658487551</v>
@@ -44198,7 +44222,7 @@
         <v>-60.61737400581654</v>
       </c>
       <c r="CP97" t="n">
-        <v>-54.84016067118965</v>
+        <v>-54.84016067201836</v>
       </c>
       <c r="CQ97" t="inlineStr">
         <is>
@@ -44490,10 +44514,10 @@
         <v>16.01000022888184</v>
       </c>
       <c r="CA98" t="n">
-        <v>8.061612835698385</v>
+        <v>8.061612844622262</v>
       </c>
       <c r="CB98" t="n">
-        <v>14.95429181022051</v>
+        <v>14.9542918267743</v>
       </c>
       <c r="CC98" t="n">
         <v>10.47567916210787</v>
@@ -44514,7 +44538,7 @@
         <v>10.00660187036776</v>
       </c>
       <c r="CI98" t="n">
-        <v>12.47880699658911</v>
+        <v>12.47880699977381</v>
       </c>
       <c r="CJ98" t="n">
         <v>10.24114051623781</v>
@@ -44535,7 +44559,7 @@
         <v>-42.4295669403762</v>
       </c>
       <c r="CP98" t="n">
-        <v>-22.05617227863933</v>
+        <v>-22.05617225874734</v>
       </c>
       <c r="CQ98" t="inlineStr">
         <is>
@@ -44819,10 +44843,10 @@
         <v>7.170000076293945</v>
       </c>
       <c r="CA99" t="n">
-        <v>3.214416914576922</v>
+        <v>3.214416921708266</v>
       </c>
       <c r="CB99" t="n">
-        <v>5.96274337654019</v>
+        <v>5.962743389768833</v>
       </c>
       <c r="CC99" t="inlineStr"/>
       <c r="CD99" t="inlineStr"/>
@@ -44833,13 +44857,13 @@
         <v>9.809989751681186</v>
       </c>
       <c r="CI99" t="n">
-        <v>6.329050014266099</v>
+        <v>6.329050021052762</v>
       </c>
       <c r="CJ99" t="n">
-        <v>5.96274337654019</v>
+        <v>5.962743389768833</v>
       </c>
       <c r="CK99" t="n">
-        <v>5.366469038886171</v>
+        <v>5.36646905079195</v>
       </c>
       <c r="CL99" t="n">
         <v>3</v>
@@ -44851,10 +44875,10 @@
         <v>3.1</v>
       </c>
       <c r="CO99" t="n">
-        <v>-25.1538496264562</v>
+        <v>-25.1538494604063</v>
       </c>
       <c r="CP99" t="n">
-        <v>-11.72873156317342</v>
+        <v>-11.72873146851983</v>
       </c>
       <c r="CQ99" t="inlineStr">
         <is>
@@ -45146,37 +45170,37 @@
         <v>23.05999946594238</v>
       </c>
       <c r="CA100" t="n">
-        <v>5.050688926532513</v>
+        <v>5.050688915059773</v>
       </c>
       <c r="CB100" t="n">
-        <v>7.175729498410869</v>
+        <v>7.175729495849572</v>
       </c>
       <c r="CC100" t="n">
-        <v>10.62745758743696</v>
+        <v>10.62745760778408</v>
       </c>
       <c r="CD100" t="n">
         <v>14.56873729010693</v>
       </c>
       <c r="CE100" t="n">
-        <v>7.163504684185467</v>
+        <v>7.163504695555116</v>
       </c>
       <c r="CF100" t="n">
-        <v>8.436256191126738</v>
+        <v>8.436256192575577</v>
       </c>
       <c r="CG100" t="n">
-        <v>5.281933268328021</v>
+        <v>5.281933280059588</v>
       </c>
       <c r="CH100" t="n">
         <v>10.72687534044447</v>
       </c>
       <c r="CI100" t="n">
-        <v>8.628897848321497</v>
+        <v>8.628897852179389</v>
       </c>
       <c r="CJ100" t="n">
-        <v>7.805992844768804</v>
+        <v>7.805992844212574</v>
       </c>
       <c r="CK100" t="n">
-        <v>7.025393560291924</v>
+        <v>7.025393559791317</v>
       </c>
       <c r="CL100" t="n">
         <v>8</v>
@@ -45188,10 +45212,10 @@
         <v>2.9</v>
       </c>
       <c r="CO100" t="n">
-        <v>-69.53428567651174</v>
+        <v>-69.53428567868262</v>
       </c>
       <c r="CP100" t="n">
-        <v>-62.58066761421382</v>
+        <v>-62.58066759748402</v>
       </c>
       <c r="CQ100" t="inlineStr">
         <is>
@@ -45475,10 +45499,10 @@
         <v>46.40000152587891</v>
       </c>
       <c r="CA101" t="n">
-        <v>10.15177886092706</v>
+        <v>10.15177887192081</v>
       </c>
       <c r="CB101" t="n">
-        <v>18.8315497870197</v>
+        <v>18.83154980741311</v>
       </c>
       <c r="CC101" t="n">
         <v>86.34831744633361</v>
@@ -45487,13 +45511,13 @@
         <v>76.25640482050953</v>
       </c>
       <c r="CE101" t="n">
-        <v>103.7331108774021</v>
+        <v>103.7331108737158</v>
       </c>
       <c r="CF101" t="n">
-        <v>16.00171149719812</v>
+        <v>16.00171149664758</v>
       </c>
       <c r="CG101" t="n">
-        <v>70.06583764582827</v>
+        <v>70.06583762992339</v>
       </c>
       <c r="CH101" t="n">
         <v>22.72912505392368</v>
@@ -45806,25 +45830,25 @@
         <v>47.5</v>
       </c>
       <c r="CA102" t="n">
-        <v>18.2566818854614</v>
+        <v>18.2566817680585</v>
       </c>
       <c r="CB102" t="n">
-        <v>20.19873862123098</v>
+        <v>20.19873856658959</v>
       </c>
       <c r="CC102" t="n">
-        <v>23.86378086661586</v>
+        <v>23.86378095552023</v>
       </c>
       <c r="CD102" t="n">
         <v>51.4328502242105</v>
       </c>
       <c r="CE102" t="n">
-        <v>19.85694201384302</v>
+        <v>19.85694203722744</v>
       </c>
       <c r="CF102" t="n">
-        <v>23.27481925980414</v>
+        <v>23.27481926954393</v>
       </c>
       <c r="CG102" t="n">
-        <v>10.33491114810354</v>
+        <v>10.33491122848226</v>
       </c>
       <c r="CH102" t="n">
         <v>120.2965411332743</v>
@@ -46133,37 +46157,37 @@
         <v>52.59999847412109</v>
       </c>
       <c r="CA103" t="n">
-        <v>16.06764462180982</v>
+        <v>16.06764463542064</v>
       </c>
       <c r="CB103" t="n">
-        <v>24.44956362337622</v>
+        <v>24.44956363121922</v>
       </c>
       <c r="CC103" t="n">
-        <v>44.11350736964302</v>
+        <v>44.11350734642555</v>
       </c>
       <c r="CD103" t="n">
         <v>61.25894385652082</v>
       </c>
       <c r="CE103" t="n">
-        <v>35.1954555909188</v>
+        <v>35.19545558683347</v>
       </c>
       <c r="CF103" t="n">
-        <v>26.7629734702888</v>
+        <v>26.76297346910204</v>
       </c>
       <c r="CG103" t="n">
-        <v>22.05510055532554</v>
+        <v>22.05510054351571</v>
       </c>
       <c r="CH103" t="n">
         <v>21.52547978006953</v>
       </c>
       <c r="CI103" t="n">
-        <v>31.42858360849407</v>
+        <v>31.42858360613837</v>
       </c>
       <c r="CJ103" t="n">
-        <v>25.60626854683251</v>
+        <v>25.60626855016063</v>
       </c>
       <c r="CK103" t="n">
-        <v>23.04564169214926</v>
+        <v>23.04564169514457</v>
       </c>
       <c r="CL103" t="n">
         <v>8</v>
@@ -46175,10 +46199,10 @@
         <v>3.8</v>
       </c>
       <c r="CO103" t="n">
-        <v>-56.18699170972869</v>
+        <v>-56.18699170403418</v>
       </c>
       <c r="CP103" t="n">
-        <v>-40.24983931519169</v>
+        <v>-40.24983931967022</v>
       </c>
       <c r="CQ103" t="inlineStr">
         <is>
@@ -46482,10 +46506,10 @@
         <v>11.97000026702881</v>
       </c>
       <c r="CA104" t="n">
-        <v>2.129633596371886</v>
+        <v>2.129633598520432</v>
       </c>
       <c r="CB104" t="n">
-        <v>3.950470321269849</v>
+        <v>3.950470325255401</v>
       </c>
       <c r="CC104" t="n">
         <v>12.16276867623709</v>
@@ -46494,25 +46518,25 @@
         <v>13.48270925178679</v>
       </c>
       <c r="CE104" t="n">
-        <v>8.763285706457124</v>
+        <v>8.76328570562052</v>
       </c>
       <c r="CF104" t="n">
-        <v>5.73762168890867</v>
+        <v>5.737621688725145</v>
       </c>
       <c r="CG104" t="n">
-        <v>6.523398949940999</v>
+        <v>6.523398947965197</v>
       </c>
       <c r="CH104" t="n">
         <v>11.97000026702881</v>
       </c>
       <c r="CI104" t="n">
-        <v>8.941464980232762</v>
+        <v>8.941464980374137</v>
       </c>
       <c r="CJ104" t="n">
-        <v>8.763285706457124</v>
+        <v>8.76328570562052</v>
       </c>
       <c r="CK104" t="n">
-        <v>7.886957135811412</v>
+        <v>7.886957135058468</v>
       </c>
       <c r="CL104" t="n">
         <v>7</v>
@@ -46524,10 +46548,10 @@
         <v>6.3</v>
       </c>
       <c r="CO104" t="n">
-        <v>-34.11063525590789</v>
+        <v>-34.11063526219814</v>
       </c>
       <c r="CP104" t="n">
-        <v>-25.30104610889694</v>
+        <v>-25.30104610771586</v>
       </c>
       <c r="CQ104" t="inlineStr">
         <is>
@@ -46811,10 +46835,10 @@
         <v>3.029999971389771</v>
       </c>
       <c r="CA105" t="n">
-        <v>0.6343933978702244</v>
+        <v>0.6343934000049017</v>
       </c>
       <c r="CB105" t="n">
-        <v>1.176799753049266</v>
+        <v>1.176799757009093</v>
       </c>
       <c r="CC105" t="n">
         <v>3.469965395066072</v>
@@ -46823,13 +46847,13 @@
         <v>4.010566432856011</v>
       </c>
       <c r="CE105" t="n">
-        <v>2.423903796093823</v>
+        <v>2.423903795816797</v>
       </c>
       <c r="CF105" t="n">
-        <v>2.635949510583644</v>
+        <v>2.635949510312895</v>
       </c>
       <c r="CG105" t="n">
-        <v>1.740689722283334</v>
+        <v>1.740689720485594</v>
       </c>
       <c r="CH105" t="n">
         <v>9.095071583324174</v>
@@ -47128,10 +47152,10 @@
         <v>55.18999862670898</v>
       </c>
       <c r="CA106" t="n">
-        <v>62.46314087046265</v>
+        <v>62.46314021902227</v>
       </c>
       <c r="CB106" t="n">
-        <v>90.94633310739363</v>
+        <v>90.94633215889644</v>
       </c>
       <c r="CC106" t="n">
         <v>24.38300703983744</v>
@@ -48053,10 +48077,10 @@
         <v>97.61000061035156</v>
       </c>
       <c r="CA109" t="n">
-        <v>4.982479577288823</v>
+        <v>4.982479587013226</v>
       </c>
       <c r="CB109" t="n">
-        <v>9.242499615870765</v>
+        <v>9.242499633909533</v>
       </c>
       <c r="CC109" t="n">
         <v>42.72654470059987</v>
@@ -48065,13 +48089,13 @@
         <v>42.39662181432417</v>
       </c>
       <c r="CE109" t="n">
-        <v>35.18195900624188</v>
+        <v>35.18195899302742</v>
       </c>
       <c r="CF109" t="n">
-        <v>17.64650212015547</v>
+        <v>17.64650211927588</v>
       </c>
       <c r="CG109" t="n">
-        <v>29.28029178147117</v>
+        <v>29.28029177033789</v>
       </c>
       <c r="CH109" t="n">
         <v>44.08436660991484</v>
@@ -48691,10 +48715,10 @@
         <v>17.03000068664551</v>
       </c>
       <c r="CA111" t="n">
-        <v>3.197534149963832</v>
+        <v>3.197534144689631</v>
       </c>
       <c r="CB111" t="n">
-        <v>5.931425848182909</v>
+        <v>5.931425838399264</v>
       </c>
       <c r="CC111" t="n">
         <v>14.94354364887768</v>
@@ -48703,23 +48727,23 @@
         <v>15.89715452361429</v>
       </c>
       <c r="CE111" t="n">
-        <v>10.65040732300807</v>
+        <v>10.65040732646187</v>
       </c>
       <c r="CF111" t="n">
-        <v>13.03125309571383</v>
+        <v>13.03125309661639</v>
       </c>
       <c r="CG111" t="n">
-        <v>7.843954321127297</v>
+        <v>7.843954326371962</v>
       </c>
       <c r="CH111" t="inlineStr"/>
       <c r="CI111" t="n">
-        <v>11.38295646008734</v>
+        <v>11.38295646005691</v>
       </c>
       <c r="CJ111" t="n">
-        <v>11.84083020936095</v>
+        <v>11.84083021153913</v>
       </c>
       <c r="CK111" t="n">
-        <v>10.65674718842485</v>
+        <v>10.65674719038522</v>
       </c>
       <c r="CL111" t="n">
         <v>6</v>
@@ -48731,10 +48755,10 @@
         <v>5</v>
       </c>
       <c r="CO111" t="n">
-        <v>-37.42368315474231</v>
+        <v>-37.42368314323107</v>
       </c>
       <c r="CP111" t="n">
-        <v>-33.1593893063459</v>
+        <v>-33.15938930652461</v>
       </c>
       <c r="CQ111" t="inlineStr">
         <is>
@@ -49018,25 +49042,25 @@
         <v>14.78999996185303</v>
       </c>
       <c r="CA112" t="n">
-        <v>3.734050399994813</v>
+        <v>3.73405039744296</v>
       </c>
       <c r="CB112" t="n">
-        <v>4.75096549153728</v>
+        <v>4.750965488714784</v>
       </c>
       <c r="CC112" t="n">
-        <v>14.39113215659596</v>
+        <v>14.39113215788126</v>
       </c>
       <c r="CD112" t="n">
         <v>37.23867291481046</v>
       </c>
       <c r="CE112" t="n">
-        <v>9.871878897748525</v>
+        <v>9.871878895363233</v>
       </c>
       <c r="CF112" t="n">
-        <v>48.41104883996949</v>
+        <v>48.41104884039808</v>
       </c>
       <c r="CG112" t="n">
-        <v>6.917256497841</v>
+        <v>6.917256498745988</v>
       </c>
       <c r="CH112" t="n">
         <v>27.46854012923095</v>
@@ -49337,25 +49361,25 @@
         <v>14.8100004196167</v>
       </c>
       <c r="CA113" t="n">
-        <v>1.386019545449728</v>
+        <v>1.386019550169894</v>
       </c>
       <c r="CB113" t="n">
-        <v>2.562681321724585</v>
+        <v>2.56268132752196</v>
       </c>
       <c r="CC113" t="n">
-        <v>8.677574926671523</v>
+        <v>8.677574916750233</v>
       </c>
       <c r="CD113" t="n">
         <v>10.7066274318662</v>
       </c>
       <c r="CE113" t="n">
-        <v>4.78721844722353</v>
+        <v>4.787218444551529</v>
       </c>
       <c r="CF113" t="n">
-        <v>7.688860391559766</v>
+        <v>7.688860390940986</v>
       </c>
       <c r="CG113" t="n">
-        <v>4.223256309855304</v>
+        <v>4.223256306332927</v>
       </c>
       <c r="CH113" t="n">
         <v>11.50778129173654</v>
@@ -49656,10 +49680,10 @@
         <v>11.21000003814697</v>
       </c>
       <c r="CA114" t="n">
-        <v>2.436021028890328</v>
+        <v>2.43602102312452</v>
       </c>
       <c r="CB114" t="n">
-        <v>4.518819008591558</v>
+        <v>4.518818997895985</v>
       </c>
       <c r="CC114" t="n">
         <v>12.15486910846541</v>
@@ -49668,13 +49692,13 @@
         <v>12.67593560098585</v>
       </c>
       <c r="CE114" t="n">
-        <v>9.597028727312301</v>
+        <v>9.597028730239817</v>
       </c>
       <c r="CF114" t="n">
-        <v>0.7922538303855846</v>
+        <v>0.7922538304622297</v>
       </c>
       <c r="CG114" t="n">
-        <v>6.728795253025859</v>
+        <v>6.728795259018149</v>
       </c>
       <c r="CH114" t="n">
         <v>7.42587936633825</v>
@@ -49975,10 +49999,10 @@
         <v>18.32999992370605</v>
       </c>
       <c r="CA115" t="n">
-        <v>11.72168816791328</v>
+        <v>11.72168813783896</v>
       </c>
       <c r="CB115" t="n">
-        <v>14.62662827909178</v>
+        <v>14.62662824156427</v>
       </c>
       <c r="CC115" t="inlineStr"/>
       <c r="CD115" t="inlineStr"/>
@@ -50286,25 +50310,25 @@
         <v>8.859999656677246</v>
       </c>
       <c r="CA116" t="n">
-        <v>2.278494627479795</v>
+        <v>2.278494624924066</v>
       </c>
       <c r="CB116" t="n">
-        <v>2.457217338745752</v>
+        <v>2.457217336700073</v>
       </c>
       <c r="CC116" t="n">
-        <v>3.198208819397106</v>
+        <v>3.198208820321887</v>
       </c>
       <c r="CD116" t="n">
         <v>9.985934437661033</v>
       </c>
       <c r="CE116" t="n">
-        <v>1.868987657607944</v>
+        <v>1.868987657323121</v>
       </c>
       <c r="CF116" t="n">
-        <v>5.906665058266654</v>
+        <v>5.9066650584629</v>
       </c>
       <c r="CG116" t="n">
-        <v>1.344337860663172</v>
+        <v>1.344337861538049</v>
       </c>
       <c r="CH116" t="n">
         <v>14.36284499478099</v>
@@ -50617,10 +50641,10 @@
         <v>4.820000171661377</v>
       </c>
       <c r="CA117" t="n">
-        <v>1.482729246311887</v>
+        <v>1.482729243802358</v>
       </c>
       <c r="CB117" t="n">
-        <v>1.545333370045055</v>
+        <v>1.545333367429569</v>
       </c>
       <c r="CC117" t="inlineStr"/>
       <c r="CD117" t="inlineStr"/>
@@ -50926,10 +50950,10 @@
         <v>3.339999914169312</v>
       </c>
       <c r="CA118" t="n">
-        <v>1.645463643602964</v>
+        <v>1.645463646645273</v>
       </c>
       <c r="CB118" t="n">
-        <v>3.052335058883498</v>
+        <v>3.052335064526982</v>
       </c>
       <c r="CC118" t="n">
         <v>1.157901592431799</v>
@@ -50938,7 +50962,7 @@
         <v>4.60268789222791</v>
       </c>
       <c r="CE118" t="n">
-        <v>1.607705128817075</v>
+        <v>1.607705129931474</v>
       </c>
       <c r="CF118" t="n">
         <v>0.7445919647652398</v>
@@ -51245,10 +51269,10 @@
         <v>6.53000020980835</v>
       </c>
       <c r="CA119" t="n">
-        <v>1.050039167604812</v>
+        <v>1.050039160366295</v>
       </c>
       <c r="CB119" t="n">
-        <v>1.947822655906926</v>
+        <v>1.947822642479476</v>
       </c>
       <c r="CC119" t="inlineStr"/>
       <c r="CD119" t="inlineStr"/>
@@ -51554,25 +51578,25 @@
         <v>3.680000066757202</v>
       </c>
       <c r="CA120" t="n">
-        <v>1.260908970841923</v>
+        <v>1.260908969715155</v>
       </c>
       <c r="CB120" t="n">
-        <v>1.270673793123084</v>
+        <v>1.270673792398243</v>
       </c>
       <c r="CC120" t="n">
-        <v>1.29785783892542</v>
+        <v>1.297857839344858</v>
       </c>
       <c r="CD120" t="n">
         <v>4.028317282462615</v>
       </c>
       <c r="CE120" t="n">
-        <v>0.881937817743869</v>
+        <v>0.8819378176824171</v>
       </c>
       <c r="CF120" t="n">
-        <v>2.295529039193208</v>
+        <v>2.295529039283699</v>
       </c>
       <c r="CG120" t="n">
-        <v>0.4923745532943772</v>
+        <v>0.4923745537415686</v>
       </c>
       <c r="CH120" t="n">
         <v>5.189162701709523</v>
@@ -51877,10 +51901,10 @@
         <v>5.369999885559082</v>
       </c>
       <c r="CA121" t="n">
-        <v>5.323748905251827</v>
+        <v>5.323748899584477</v>
       </c>
       <c r="CB121" t="n">
-        <v>7.751378406046661</v>
+        <v>7.751378397794999</v>
       </c>
       <c r="CC121" t="inlineStr"/>
       <c r="CD121" t="inlineStr"/>
@@ -51889,13 +51913,13 @@
       <c r="CG121" t="inlineStr"/>
       <c r="CH121" t="inlineStr"/>
       <c r="CI121" t="n">
-        <v>6.537563655649244</v>
+        <v>6.537563648689739</v>
       </c>
       <c r="CJ121" t="n">
-        <v>6.537563655649244</v>
+        <v>6.537563648689739</v>
       </c>
       <c r="CK121" t="n">
-        <v>5.883807290084319</v>
+        <v>5.883807283820765</v>
       </c>
       <c r="CL121" t="n">
         <v>2</v>
@@ -51907,10 +51931,10 @@
         <v>1.5</v>
       </c>
       <c r="CO121" t="n">
-        <v>9.568108295625111</v>
+        <v>9.568108178985369</v>
       </c>
       <c r="CP121" t="n">
-        <v>21.74234255069456</v>
+        <v>21.74234242109485</v>
       </c>
       <c r="CQ121" t="inlineStr">
         <is>
@@ -52194,10 +52218,10 @@
         <v>5.369999885559082</v>
       </c>
       <c r="CA122" t="n">
-        <v>5.911211507335186</v>
+        <v>5.911211521619795</v>
       </c>
       <c r="CB122" t="n">
-        <v>10.53904914283688</v>
+        <v>10.53904916830478</v>
       </c>
       <c r="CC122" t="inlineStr"/>
       <c r="CD122" t="inlineStr"/>
@@ -52206,13 +52230,13 @@
       <c r="CG122" t="inlineStr"/>
       <c r="CH122" t="inlineStr"/>
       <c r="CI122" t="n">
-        <v>8.225130325086031</v>
+        <v>8.22513034496229</v>
       </c>
       <c r="CJ122" t="n">
-        <v>8.225130325086031</v>
+        <v>8.22513034496229</v>
       </c>
       <c r="CK122" t="n">
-        <v>7.402617292577428</v>
+        <v>7.402617310466061</v>
       </c>
       <c r="CL122" t="n">
         <v>2</v>
@@ -52224,10 +52248,10 @@
         <v>1.8</v>
       </c>
       <c r="CO122" t="n">
-        <v>37.85134916826402</v>
+        <v>37.85134950138567</v>
       </c>
       <c r="CP122" t="n">
-        <v>53.16816574251557</v>
+        <v>53.16816611265074</v>
       </c>
       <c r="CQ122" t="inlineStr">
         <is>
@@ -52497,10 +52521,10 @@
         <v>22.35000038146973</v>
       </c>
       <c r="CA123" t="n">
-        <v>38.7827104273716</v>
+        <v>38.7827105266895</v>
       </c>
       <c r="CB123" t="n">
-        <v>71.94192784277432</v>
+        <v>71.94192802700901</v>
       </c>
       <c r="CC123" t="n">
         <v>19.80852876618554</v>
@@ -52519,7 +52543,7 @@
       </c>
       <c r="CH123" t="inlineStr"/>
       <c r="CI123" t="n">
-        <v>25.97687183728271</v>
+        <v>25.97687185383569</v>
       </c>
       <c r="CJ123" t="n">
         <v>23.0354806164258</v>
@@ -52540,7 +52564,7 @@
         <v>-7.239676953330354</v>
       </c>
       <c r="CP123" t="n">
-        <v>16.2276125007139</v>
+        <v>16.22761257477645</v>
       </c>
       <c r="CQ123" t="inlineStr">
         <is>
@@ -52828,25 +52852,25 @@
         <v>9.090000152587891</v>
       </c>
       <c r="CA124" t="n">
-        <v>3.513201113729493</v>
+        <v>3.513201133787768</v>
       </c>
       <c r="CB124" t="n">
-        <v>3.627571358518037</v>
+        <v>3.627571376047641</v>
       </c>
       <c r="CC124" t="n">
-        <v>4.393334528921876</v>
+        <v>4.393334525068588</v>
       </c>
       <c r="CD124" t="n">
         <v>18.92946868244077</v>
       </c>
       <c r="CE124" t="n">
-        <v>3.454654099350264</v>
+        <v>3.454654111490158</v>
       </c>
       <c r="CF124" t="n">
-        <v>7.742523562331491</v>
+        <v>7.742523561520691</v>
       </c>
       <c r="CG124" t="n">
-        <v>1.736838692140338</v>
+        <v>1.736838688204102</v>
       </c>
       <c r="CH124" t="n">
         <v>21.77146113239846</v>
@@ -53454,10 +53478,10 @@
         <v>11.25</v>
       </c>
       <c r="CA126" t="n">
-        <v>0.7656099592395338</v>
+        <v>0.7656099593230949</v>
       </c>
       <c r="CB126" t="n">
-        <v>1.420206474389335</v>
+        <v>1.420206474544341</v>
       </c>
       <c r="CC126" t="n">
         <v>15.28846153846153</v>
@@ -53466,13 +53490,13 @@
         <v>15.93648555693364</v>
       </c>
       <c r="CE126" t="n">
-        <v>13.40806790970839</v>
+        <v>13.4080679096908</v>
       </c>
       <c r="CF126" t="n">
-        <v>1.648078624705886</v>
+        <v>1.648078624704111</v>
       </c>
       <c r="CG126" t="n">
-        <v>10.81933391703054</v>
+        <v>10.81933391694407</v>
       </c>
       <c r="CH126" t="inlineStr"/>
       <c r="CI126" t="inlineStr"/>
@@ -53771,25 +53795,25 @@
         <v>18.46054267883301</v>
       </c>
       <c r="CA127" t="n">
-        <v>0.5760472931370921</v>
+        <v>0.5760472922299662</v>
       </c>
       <c r="CB127" t="n">
-        <v>0.7744861405802382</v>
+        <v>0.7744861394434408</v>
       </c>
       <c r="CC127" t="n">
-        <v>4.579823771478012</v>
+        <v>4.579823771967749</v>
       </c>
       <c r="CD127" t="n">
         <v>11.45343257282958</v>
       </c>
       <c r="CE127" t="n">
-        <v>1.757660189601812</v>
+        <v>1.757660189770299</v>
       </c>
       <c r="CF127" t="n">
-        <v>0.6742367133576108</v>
+        <v>0.6742367133644104</v>
       </c>
       <c r="CG127" t="n">
-        <v>2.247847912944871</v>
+        <v>2.247847913256994</v>
       </c>
       <c r="CH127" t="n">
         <v>18.46054267883301</v>
@@ -54090,10 +54114,10 @@
         <v>5.239999771118164</v>
       </c>
       <c r="CA128" t="n">
-        <v>1.29429977328673</v>
+        <v>1.294299770702029</v>
       </c>
       <c r="CB128" t="n">
-        <v>2.166187166018972</v>
+        <v>2.166187161693123</v>
       </c>
       <c r="CC128" t="inlineStr"/>
       <c r="CD128" t="inlineStr"/>
@@ -54104,13 +54128,13 @@
         <v>6.020931258896678</v>
       </c>
       <c r="CI128" t="n">
-        <v>1.730243469652851</v>
+        <v>1.730243466197576</v>
       </c>
       <c r="CJ128" t="n">
-        <v>1.730243469652851</v>
+        <v>1.730243466197576</v>
       </c>
       <c r="CK128" t="n">
-        <v>1.557219122687566</v>
+        <v>1.557219119577818</v>
       </c>
       <c r="CL128" t="n">
         <v>2</v>
@@ -54122,10 +54146,10 @@
         <v>4.7</v>
       </c>
       <c r="CO128" t="n">
-        <v>-70.28207651323484</v>
+        <v>-70.28207657258116</v>
       </c>
       <c r="CP128" t="n">
-        <v>-66.98008501470537</v>
+        <v>-66.98008508064575</v>
       </c>
       <c r="CQ128" t="inlineStr">
         <is>
@@ -54724,37 +54748,37 @@
         <v>17.54999923706055</v>
       </c>
       <c r="CA130" t="n">
-        <v>2.114176579589143</v>
+        <v>2.114176581058406</v>
       </c>
       <c r="CB130" t="n">
-        <v>3.730125103748781</v>
+        <v>3.730125105155595</v>
       </c>
       <c r="CC130" t="n">
-        <v>9.632950370306933</v>
+        <v>9.632950367245501</v>
       </c>
       <c r="CD130" t="n">
         <v>11.96027571768681</v>
       </c>
       <c r="CE130" t="n">
-        <v>5.584250643625776</v>
+        <v>5.584250642635428</v>
       </c>
       <c r="CF130" t="n">
-        <v>5.535381010689189</v>
+        <v>5.53538101055986</v>
       </c>
       <c r="CG130" t="n">
-        <v>4.741756131483272</v>
+        <v>4.741756130297635</v>
       </c>
       <c r="CH130" t="n">
         <v>15.78993633088096</v>
       </c>
       <c r="CI130" t="n">
-        <v>6.86412316292346</v>
+        <v>6.864123162263471</v>
       </c>
       <c r="CJ130" t="n">
-        <v>5.559815827157482</v>
+        <v>5.559815826597644</v>
       </c>
       <c r="CK130" t="n">
-        <v>5.003834244441735</v>
+        <v>5.00383424393788</v>
       </c>
       <c r="CL130" t="n">
         <v>6</v>
@@ -54766,10 +54790,10 @@
         <v>7.5</v>
       </c>
       <c r="CO130" t="n">
-        <v>-71.48812272381713</v>
+        <v>-71.48812272668809</v>
       </c>
       <c r="CP130" t="n">
-        <v>-60.88818540556738</v>
+        <v>-60.888185409328</v>
       </c>
       <c r="CQ130" t="inlineStr">
         <is>
@@ -55045,10 +55069,10 @@
         <v>4.329999923706055</v>
       </c>
       <c r="CA131" t="n">
-        <v>0.9106060404411094</v>
+        <v>0.9106060416591855</v>
       </c>
       <c r="CB131" t="n">
-        <v>1.689174205018258</v>
+        <v>1.689174207277789</v>
       </c>
       <c r="CC131" t="inlineStr"/>
       <c r="CD131" t="inlineStr"/>
@@ -55057,13 +55081,13 @@
       <c r="CG131" t="inlineStr"/>
       <c r="CH131" t="inlineStr"/>
       <c r="CI131" t="n">
-        <v>1.299890122729684</v>
+        <v>1.299890124468487</v>
       </c>
       <c r="CJ131" t="n">
-        <v>1.299890122729684</v>
+        <v>1.299890124468487</v>
       </c>
       <c r="CK131" t="n">
-        <v>1.169901110456715</v>
+        <v>1.169901112021638</v>
       </c>
       <c r="CL131" t="n">
         <v>2</v>
@@ -55075,10 +55099,10 @@
         <v>1.9</v>
       </c>
       <c r="CO131" t="n">
-        <v>-72.98149812770909</v>
+        <v>-72.98149809156767</v>
       </c>
       <c r="CP131" t="n">
-        <v>-69.97944236412121</v>
+        <v>-69.97944232396409</v>
       </c>
       <c r="CQ131" t="inlineStr">
         <is>
@@ -55364,10 +55388,10 @@
         <v>1.179999947547913</v>
       </c>
       <c r="CA132" t="n">
-        <v>0.3468781106801614</v>
+        <v>0.3468781107904809</v>
       </c>
       <c r="CB132" t="n">
-        <v>0.6434588953116993</v>
+        <v>0.6434588955163419</v>
       </c>
       <c r="CC132" t="inlineStr"/>
       <c r="CD132" t="inlineStr"/>
@@ -55376,13 +55400,13 @@
       <c r="CG132" t="inlineStr"/>
       <c r="CH132" t="inlineStr"/>
       <c r="CI132" t="n">
-        <v>0.4951685029959303</v>
+        <v>0.4951685031534114</v>
       </c>
       <c r="CJ132" t="n">
-        <v>0.4951685029959303</v>
+        <v>0.4951685031534114</v>
       </c>
       <c r="CK132" t="n">
-        <v>0.4456516526963373</v>
+        <v>0.4456516528380703</v>
       </c>
       <c r="CL132" t="n">
         <v>2</v>
@@ -55394,10 +55418,10 @@
         <v>1.9</v>
       </c>
       <c r="CO132" t="n">
-        <v>-62.23290910966399</v>
+        <v>-62.23290909765274</v>
       </c>
       <c r="CP132" t="n">
-        <v>-58.03656567740444</v>
+        <v>-58.03656566405859</v>
       </c>
       <c r="CQ132" t="inlineStr">
         <is>
@@ -55679,10 +55703,10 @@
         <v>5.46999979019165</v>
       </c>
       <c r="CA133" t="n">
-        <v>1.043475835173986</v>
+        <v>1.043475837353275</v>
       </c>
       <c r="CB133" t="n">
-        <v>1.935647674247744</v>
+        <v>1.935647678290324</v>
       </c>
       <c r="CC133" t="inlineStr"/>
       <c r="CD133" t="inlineStr"/>
@@ -55693,13 +55717,13 @@
         <v>3.086391414577443</v>
       </c>
       <c r="CI133" t="n">
-        <v>2.021838307999724</v>
+        <v>2.021838310073681</v>
       </c>
       <c r="CJ133" t="n">
-        <v>1.935647674247744</v>
+        <v>1.935647678290324</v>
       </c>
       <c r="CK133" t="n">
-        <v>1.74208290682297</v>
+        <v>1.742082910461292</v>
       </c>
       <c r="CL133" t="n">
         <v>3</v>
@@ -55711,10 +55735,10 @@
         <v>3</v>
       </c>
       <c r="CO133" t="n">
-        <v>-68.15204801384584</v>
+        <v>-68.15204794733172</v>
       </c>
       <c r="CP133" t="n">
-        <v>-63.03768947806695</v>
+        <v>-63.03768944015184</v>
       </c>
       <c r="CQ133" t="inlineStr">
         <is>
@@ -56311,10 +56335,10 @@
         <v>36.70999908447266</v>
       </c>
       <c r="CA135" t="n">
-        <v>8.268344963622502</v>
+        <v>8.268344959502961</v>
       </c>
       <c r="CB135" t="n">
-        <v>12.03871026703436</v>
+        <v>12.03871026103631</v>
       </c>
       <c r="CC135" t="n">
         <v>7.906067311627989</v>
@@ -56628,25 +56652,25 @@
         <v>4.920000076293945</v>
       </c>
       <c r="CA136" t="n">
-        <v>1.527637925308267</v>
+        <v>1.527637920188642</v>
       </c>
       <c r="CB136" t="n">
-        <v>1.686462929346638</v>
+        <v>1.686462924945599</v>
       </c>
       <c r="CC136" t="n">
-        <v>2.469546774717689</v>
+        <v>2.46954677654937</v>
       </c>
       <c r="CD136" t="n">
         <v>7.731331217553538</v>
       </c>
       <c r="CE136" t="n">
-        <v>1.72780068418552</v>
+        <v>1.727800682267953</v>
       </c>
       <c r="CF136" t="n">
-        <v>1.781870301562807</v>
+        <v>1.781870301711547</v>
       </c>
       <c r="CG136" t="n">
-        <v>1.06696371484357</v>
+        <v>1.066963716506015</v>
       </c>
       <c r="CH136" t="n">
         <v>0.3081571864153818</v>
@@ -56945,10 +56969,10 @@
         <v>2.220000028610229</v>
       </c>
       <c r="CA137" t="n">
-        <v>0.6232610168887069</v>
+        <v>0.623261018586029</v>
       </c>
       <c r="CB137" t="n">
-        <v>0.9074680405899573</v>
+        <v>0.9074680430612583</v>
       </c>
       <c r="CC137" t="n">
         <v>0.3656057054243292</v>
@@ -57011,7 +57035,7 @@
         <v>8.292686841375918</v>
       </c>
       <c r="DC137" t="n">
-        <v>-47.81913051232355</v>
+        <v>-47.8191363881519</v>
       </c>
       <c r="DD137" t="b">
         <v>0</v>
@@ -57549,10 +57573,10 @@
         <v>6.869999885559082</v>
       </c>
       <c r="CA139" t="n">
-        <v>1.8852993490839</v>
+        <v>1.885299339030719</v>
       </c>
       <c r="CB139" t="n">
-        <v>2.744995852266159</v>
+        <v>2.744995837628726</v>
       </c>
       <c r="CC139" t="n">
         <v>1.690276763894357</v>
@@ -57768,7 +57792,7 @@
         <v>0</v>
       </c>
       <c r="AU140" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="AV140" t="b">
         <v>1</v>
@@ -58456,25 +58480,25 @@
         <v>4.840000152587891</v>
       </c>
       <c r="CA142" t="n">
-        <v>0.8111693281433602</v>
+        <v>0.8111693300150393</v>
       </c>
       <c r="CB142" t="n">
-        <v>0.8137713589376933</v>
+        <v>0.8137713607003161</v>
       </c>
       <c r="CC142" t="n">
-        <v>0.8563537349717655</v>
+        <v>0.8563537348506844</v>
       </c>
       <c r="CD142" t="n">
         <v>6.37726014905843</v>
       </c>
       <c r="CE142" t="n">
-        <v>0.2850987640246648</v>
+        <v>0.2850987644646573</v>
       </c>
       <c r="CF142" t="n">
-        <v>0.4174305995468469</v>
+        <v>0.417430599539619</v>
       </c>
       <c r="CG142" t="n">
-        <v>0.322203075798793</v>
+        <v>0.3222030756686739</v>
       </c>
       <c r="CH142" t="inlineStr"/>
       <c r="CI142" t="inlineStr"/>
@@ -58775,10 +58799,10 @@
         <v>18.76000022888184</v>
       </c>
       <c r="CA143" t="n">
-        <v>28.48986178681072</v>
+        <v>28.4898617011241</v>
       </c>
       <c r="CB143" t="n">
-        <v>38.11310399035567</v>
+        <v>38.11310387572601</v>
       </c>
       <c r="CC143" t="n">
         <v>2.597626784658967</v>
@@ -58787,7 +58811,7 @@
         <v>7.205629833517744</v>
       </c>
       <c r="CE143" t="n">
-        <v>6.649616950409679</v>
+        <v>6.649616933026506</v>
       </c>
       <c r="CF143" t="n">
         <v>3.046690502845772</v>
@@ -59094,10 +59118,10 @@
         <v>3.710000038146973</v>
       </c>
       <c r="CA144" t="n">
-        <v>0.6711165064974021</v>
+        <v>0.6711165067038204</v>
       </c>
       <c r="CB144" t="n">
-        <v>1.244921119552681</v>
+        <v>1.244921119935587</v>
       </c>
       <c r="CC144" t="inlineStr"/>
       <c r="CD144" t="inlineStr"/>
@@ -59108,13 +59132,13 @@
         <v>3.383752809074293</v>
       </c>
       <c r="CI144" t="n">
-        <v>0.9580188130250414</v>
+        <v>0.9580188133197036</v>
       </c>
       <c r="CJ144" t="n">
-        <v>0.9580188130250414</v>
+        <v>0.9580188133197036</v>
       </c>
       <c r="CK144" t="n">
-        <v>0.8622169317225373</v>
+        <v>0.8622169319877333</v>
       </c>
       <c r="CL144" t="n">
         <v>2</v>
@@ -59126,10 +59150,10 @@
         <v>5</v>
       </c>
       <c r="CO144" t="n">
-        <v>-76.75965167501218</v>
+        <v>-76.75965166786405</v>
       </c>
       <c r="CP144" t="n">
-        <v>-74.17739075001354</v>
+        <v>-74.17739074207115</v>
       </c>
       <c r="CQ144" t="inlineStr">
         <is>
@@ -59411,10 +59435,10 @@
         <v>18.79000091552734</v>
       </c>
       <c r="CA145" t="n">
-        <v>9.525161207651804</v>
+        <v>9.525161236034677</v>
       </c>
       <c r="CB145" t="n">
-        <v>13.86863471834103</v>
+        <v>13.86863475966649</v>
       </c>
       <c r="CC145" t="n">
         <v>4.657197557709351</v>
@@ -60362,10 +60386,10 @@
         <v>10.85999965667725</v>
       </c>
       <c r="CA148" t="n">
-        <v>5.802515956281911</v>
+        <v>5.802515930936931</v>
       </c>
       <c r="CB148" t="n">
-        <v>10.6207532799797</v>
+        <v>10.620753233589</v>
       </c>
       <c r="CC148" t="inlineStr"/>
       <c r="CD148" t="inlineStr"/>
@@ -60376,13 +60400,13 @@
         <v>3.332701500657688</v>
       </c>
       <c r="CI148" t="n">
-        <v>6.5853235789731</v>
+        <v>6.585323555061207</v>
       </c>
       <c r="CJ148" t="n">
-        <v>5.802515956281911</v>
+        <v>5.802515930936931</v>
       </c>
       <c r="CK148" t="n">
-        <v>5.22226436065372</v>
+        <v>5.222264337843238</v>
       </c>
       <c r="CL148" t="n">
         <v>3</v>
@@ -60394,10 +60418,10 @@
         <v>3.2</v>
       </c>
       <c r="CO148" t="n">
-        <v>-51.91284967083012</v>
+        <v>-51.91284988087139</v>
       </c>
       <c r="CP148" t="n">
-        <v>-39.36165941843166</v>
+        <v>-39.36165963861485</v>
       </c>
       <c r="CQ148" t="inlineStr">
         <is>
@@ -61000,10 +61024,10 @@
         <v>15.42000007629395</v>
       </c>
       <c r="CA150" t="n">
-        <v>3.945356590456175</v>
+        <v>3.945356588015093</v>
       </c>
       <c r="CB150" t="n">
-        <v>5.744439195704191</v>
+        <v>5.744439192149976</v>
       </c>
       <c r="CC150" t="inlineStr"/>
       <c r="CD150" t="inlineStr"/>
@@ -61014,7 +61038,7 @@
         <v>5.488479853420727</v>
       </c>
       <c r="CI150" t="n">
-        <v>5.059425213193698</v>
+        <v>5.059425211195265</v>
       </c>
       <c r="CJ150" t="n">
         <v>5.488479853420727</v>
@@ -61035,7 +61059,7 @@
         <v>-67.96607105292668</v>
       </c>
       <c r="CP150" t="n">
-        <v>-67.1892011143901</v>
+        <v>-67.18920112735012</v>
       </c>
       <c r="CQ150" t="inlineStr">
         <is>
